--- a/outputs/role_quiz/岗位学习考核题库.xlsx
+++ b/outputs/role_quiz/岗位学习考核题库.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="题库" sheetId="1" r:id="R7999918adb5a4da5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="题库" sheetId="1" r:id="Rac2d08eaf6464ca7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -227,8 +227,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RoleQuizTable" displayName="RoleQuizTable" ref="A1:AY315" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:AY315"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RoleQuizTable" displayName="RoleQuizTable" ref="A1:AY316" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:AY316"/>
   <x:tableColumns count="51">
     <x:tableColumn id="1" name="id"/>
     <x:tableColumn id="2" name="bank"/>
@@ -26982,10 +26982,10 @@
         <x:v>["系统货品资料已建立","有相应仓库查看或编辑权限"]</x:v>
       </x:c>
       <x:c r="Z230" s="21" t="str">
-        <x:v>["按货品或仓库筛选库存","打开详情查看库存、库位和出入库记录","批量维护时下载模板并填写仓库、库区、默认库位和系统商家编码后导入","单笔维护时开启编辑并修改默认库位"]</x:v>
+        <x:v>["按货品或仓库筛选库存","进入库存明细查看商品的生产开始日期和批次信息","打开详情查看库存、库位和出入库记录","批量维护时下载模板并填写仓库、库区、默认库位和系统商家编码后导入","单笔维护时开启编辑并修改默认库位"]</x:v>
       </x:c>
       <x:c r="AA230" s="21" t="str">
-        <x:v>["库存详情与目标仓库一致","默认库位已正确显示","停售货品仅在库存为零时删除"]</x:v>
+        <x:v>["库存详情与目标仓库一致","生产开始日期和批次信息可正常核对","默认库位已正确显示","停售货品仅在库存为零时删除"]</x:v>
       </x:c>
       <x:c r="AB230" s="21" t="str">
         <x:v>["停售货品库存不为零时不能删除"]</x:v>
@@ -27001,7 +27001,7 @@
       </x:c>
       <x:c r="AF230" s="21" t="str"/>
       <x:c r="AG230" s="21" t="str">
-        <x:v>库存查询—详情、默认库位与删除</x:v>
+        <x:v>库存查询—库存明细、详情、默认库位与删除</x:v>
       </x:c>
       <x:c r="AH230" s="21" t="str">
         <x:v>库存查询详情可查看库存、库位及出入库记录。</x:v>
@@ -27051,7 +27051,7 @@
         <x:v>查询库存明细并维护默认库位</x:v>
       </x:c>
       <x:c r="AY230" s="21" t="str">
-        <x:v>2026-08-11</x:v>
+        <x:v>2026-08-12</x:v>
       </x:c>
     </x:row>
     <x:row r="231" ht="46" customHeight="1">
@@ -27131,10 +27131,10 @@
         <x:v>["系统货品资料已建立","有相应仓库查看或编辑权限"]</x:v>
       </x:c>
       <x:c r="Z231" s="21" t="str">
-        <x:v>["按货品或仓库筛选库存","打开详情查看库存、库位和出入库记录","批量维护时下载模板并填写仓库、库区、默认库位和系统商家编码后导入","单笔维护时开启编辑并修改默认库位"]</x:v>
+        <x:v>["按货品或仓库筛选库存","进入库存明细查看商品的生产开始日期和批次信息","打开详情查看库存、库位和出入库记录","批量维护时下载模板并填写仓库、库区、默认库位和系统商家编码后导入","单笔维护时开启编辑并修改默认库位"]</x:v>
       </x:c>
       <x:c r="AA231" s="21" t="str">
-        <x:v>["库存详情与目标仓库一致","默认库位已正确显示","停售货品仅在库存为零时删除"]</x:v>
+        <x:v>["库存详情与目标仓库一致","生产开始日期和批次信息可正常核对","默认库位已正确显示","停售货品仅在库存为零时删除"]</x:v>
       </x:c>
       <x:c r="AB231" s="21" t="str">
         <x:v>["停售货品库存不为零时不能删除"]</x:v>
@@ -27150,7 +27150,7 @@
       </x:c>
       <x:c r="AF231" s="21" t="str"/>
       <x:c r="AG231" s="21" t="str">
-        <x:v>库存查询—详情、默认库位与删除</x:v>
+        <x:v>库存查询—库存明细、详情、默认库位与删除</x:v>
       </x:c>
       <x:c r="AH231" s="21" t="str">
         <x:v>停售货品库存为 0 时才可删除。</x:v>
@@ -27200,21 +27200,21 @@
         <x:v>查询库存明细并维护默认库位</x:v>
       </x:c>
       <x:c r="AY231" s="21" t="str">
-        <x:v>2026-08-11</x:v>
+        <x:v>2026-08-12</x:v>
       </x:c>
     </x:row>
     <x:row r="232" ht="46" customHeight="1">
       <x:c r="A232" s="21" t="str">
-        <x:v>WDT-019-A</x:v>
+        <x:v>WDT-018-C</x:v>
       </x:c>
       <x:c r="B232" s="21" t="str">
-        <x:v>旺店通-采购</x:v>
+        <x:v>旺店通-客服</x:v>
       </x:c>
       <x:c r="C232" s="21" t="str">
-        <x:v>采购</x:v>
+        <x:v>客服</x:v>
       </x:c>
       <x:c r="D232" s="21" t="str">
-        <x:v>采购入库</x:v>
+        <x:v>库存管理</x:v>
       </x:c>
       <x:c r="E232" s="21" t="str">
         <x:v>通用</x:v>
@@ -27235,74 +27235,76 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K232" s="21" t="str">
-        <x:v>WDT-K019</x:v>
+        <x:v>WDT-K018</x:v>
       </x:c>
       <x:c r="L232" s="21" t="str">
-        <x:v>入库单总入口</x:v>
+        <x:v>库存查询与库位</x:v>
       </x:c>
       <x:c r="M232" s="21" t="str">
-        <x:v>所有入库类型统一查</x:v>
+        <x:v>从库存总量追到库位和出入库记录</x:v>
       </x:c>
       <x:c r="N232" s="21" t="str">
-        <x:v>仓库要统一查询采购入库、退货入库和调拨入库，应使用哪个入口？</x:v>
+        <x:v>在哪里查看商品的生产开始日期和批次信息？</x:v>
       </x:c>
       <x:c r="O232" s="21" t="str">
-        <x:v>进入仓储—库存查询，按库存流水替代入库单筛选</x:v>
+        <x:v>进入【采购】&gt;【采购单】&gt;【采购明细】</x:v>
       </x:c>
       <x:c r="P232" s="21" t="str">
-        <x:v>进入仓储—入库管理，按入库类型筛选单据</x:v>
+        <x:v>进入【仓储】&gt;【库存查询】&gt;【有效期管理】</x:v>
       </x:c>
       <x:c r="Q232" s="21" t="str">
-        <x:v>进入采购—采购单，只查询采购来源的收货记录</x:v>
+        <x:v>进入【仓储】&gt;【库存查询】&gt;【库存明细】</x:v>
       </x:c>
       <x:c r="R232" s="21" t="str">
-        <x:v>进入售后—智能退货入库，切换查看全部入库类型</x:v>
+        <x:v>进入【仓储】&gt;【入库管理】&gt;【入库单明细】</x:v>
       </x:c>
       <x:c r="S232" s="21" t="str">
-        <x:v>B</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="T232" s="21" t="str">
-        <x:v>进入仓储—入库管理，按入库类型筛选单据</x:v>
+        <x:v>进入【仓储】&gt;【库存查询】&gt;【库存明细】</x:v>
       </x:c>
       <x:c r="U232" s="21" t="str">
-        <x:v>入库管理是多种入库单的统一查询入口；其他入口只能覆盖部分对象或结果。</x:v>
+        <x:v>旺店通的库存明细列表可查看商品的生产开始日期和批次信息。</x:v>
       </x:c>
       <x:c r="V232" s="21" t="str">
-        <x:v>{"A":"错对象：库存查询展示库存与流水，不是多类型入库单总入口。","C":"错范围：采购单只能覆盖采购来源，不能统一查询退货和调拨入库。","D":"错范围：智能退货入库只覆盖售后退货收货，不能替代入库管理。"}</x:v>
+        <x:v>{"A":"错模块：采购明细不是库存批次查询入口。","B":"错页面：有效期管理展示保质期、有效期和距离到期天数。","D":"错模块：入库单明细用于核对入库业务。"}</x:v>
       </x:c>
       <x:c r="W232" s="21" t="str">
-        <x:v>快速定位采购、退货、调拨等不同来源的入库单及明细。</x:v>
+        <x:v>快速查到仓库、库存、库区库位及出入库记录，并安全维护默认库位。</x:v>
       </x:c>
       <x:c r="X232" s="21" t="str">
-        <x:v>["仓储","入库管理"]</x:v>
+        <x:v>["仓储","库存查询","库存明细"]</x:v>
       </x:c>
       <x:c r="Y232" s="21" t="str">
-        <x:v>["账号具备入库管理查看权限"]</x:v>
+        <x:v>["系统货品资料已建立","有相应仓库查看或编辑权限"]</x:v>
       </x:c>
       <x:c r="Z232" s="21" t="str">
-        <x:v>["进入入库管理","按入库类型、状态或单号筛选","打开单据详情核对来源和货品"]</x:v>
+        <x:v>["进入仓储","打开库存查询","进入库存明细","按商品筛选并查看生产开始日期和批次信息"]</x:v>
       </x:c>
       <x:c r="AA232" s="21" t="str">
-        <x:v>["能区分采购、调拨、退货、盘盈、生产、其他、委外、纠错和预入库单","筛选结果与目标单据来源一致"]</x:v>
+        <x:v>["列表显示目标商品的生产开始日期","列表显示对应批次信息"]</x:v>
       </x:c>
       <x:c r="AB232" s="21" t="str">
-        <x:v>["入库管理是总入口，具体来源单据仍需结合对应业务模块核对"]</x:v>
+        <x:v>["停售货品库存不为零时不能删除"]</x:v>
       </x:c>
       <x:c r="AC232" s="21" t="str">
-        <x:v>["把采购单当全部入库总表","用库存结果替代单据查询"]</x:v>
+        <x:v>["把有效期管理误当成批次明细入口","到入库单或采购单中反查库存批次"]</x:v>
       </x:c>
       <x:c r="AD232" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
       </x:c>
       <x:c r="AE232" s="21" t="str">
-        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/neeximegebrnshqi</x:v>
-      </x:c>
-      <x:c r="AF232" s="21" t="str"/>
+        <x:v>internal://jinzun/wdt/inventory-detail/2026-08-12</x:v>
+      </x:c>
+      <x:c r="AF232" s="21" t="str">
+        <x:v>[{"section":"库存明细中查看","title":"用户提供的旺店通库存明细截图","url":"internal://jinzun/wdt/inventory-detail/2026-08-12"}]</x:v>
+      </x:c>
       <x:c r="AG232" s="21" t="str">
-        <x:v>入库管理—单据范围</x:v>
+        <x:v>库存明细中查看（用户2026-08-12截图补充）</x:v>
       </x:c>
       <x:c r="AH232" s="21" t="str">
-        <x:v>入库管理统一展示多种来源入库单。</x:v>
+        <x:v>仓储→库存查询→库存明细；列表显示商品生产开始日期和批次信息。</x:v>
       </x:c>
       <x:c r="AI232" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -27335,26 +27337,26 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AS232" s="21" t="str">
-        <x:v>2026-08-11</x:v>
+        <x:v>2026-08-12</x:v>
       </x:c>
       <x:c r="AT232" s="21" t="str">
-        <x:v>已按旺店通语雀操作手册和金尊内部操作口径核对题干、步骤、答案与干扰项。</x:v>
+        <x:v>已按用户2026-08-12提供的旺店通截图核对入口、题干、答案与干扰项。</x:v>
       </x:c>
       <x:c r="AU232" s="21" t="str">
-        <x:v>20260811-wangdiantong-quiz1</x:v>
+        <x:v>20260812-wdt-cs-inventory1</x:v>
       </x:c>
       <x:c r="AV232" s="21" t="str"/>
       <x:c r="AW232" s="21" t="str"/>
       <x:c r="AX232" s="21" t="str">
-        <x:v>在入库管理集中查询入库单</x:v>
+        <x:v>查询库存明细并维护默认库位</x:v>
       </x:c>
       <x:c r="AY232" s="21" t="str">
-        <x:v>2026-08-11</x:v>
+        <x:v>2026-08-12</x:v>
       </x:c>
     </x:row>
     <x:row r="233" ht="46" customHeight="1">
       <x:c r="A233" s="21" t="str">
-        <x:v>WDT-019-B</x:v>
+        <x:v>WDT-019-A</x:v>
       </x:c>
       <x:c r="B233" s="21" t="str">
         <x:v>旺店通-采购</x:v>
@@ -27372,10 +27374,10 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G233" s="21" t="str">
-        <x:v>进阶</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="H233" s="21" t="str">
-        <x:v>中</x:v>
+        <x:v>低</x:v>
       </x:c>
       <x:c r="I233" s="21" t="str">
         <x:v>practice</x:v>
@@ -27393,31 +27395,31 @@
         <x:v>所有入库类型统一查</x:v>
       </x:c>
       <x:c r="N233" s="21" t="str">
-        <x:v>在入库管理找到一笔单据后，下一步最稳妥的核对方式是什么？</x:v>
+        <x:v>仓库要统一查询采购入库、退货入库和调拨入库，应使用哪个入口？</x:v>
       </x:c>
       <x:c r="O233" s="21" t="str">
-        <x:v>打开详情只核对来源单号，不核对货品和数量</x:v>
+        <x:v>进入仓储—库存查询，按库存流水替代入库单筛选</x:v>
       </x:c>
       <x:c r="P233" s="21" t="str">
-        <x:v>打开详情核对货品，但沿用列表默认入库类型、不核对来源</x:v>
+        <x:v>进入仓储—入库管理，按入库类型筛选单据</x:v>
       </x:c>
       <x:c r="Q233" s="21" t="str">
-        <x:v>打开详情核对入库类型、来源单据和货品明细</x:v>
+        <x:v>进入采购—采购单，只查询采购来源的收货记录</x:v>
       </x:c>
       <x:c r="R233" s="21" t="str">
-        <x:v>先在列表核对入库类型和金额，金额一致就不再打开详情</x:v>
+        <x:v>进入售后—智能退货入库，切换查看全部入库类型</x:v>
       </x:c>
       <x:c r="S233" s="21" t="str">
-        <x:v>C</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="T233" s="21" t="str">
-        <x:v>打开详情核对入库类型、来源单据和货品明细</x:v>
+        <x:v>进入仓储—入库管理，按入库类型筛选单据</x:v>
       </x:c>
       <x:c r="U233" s="21" t="str">
-        <x:v>统一入口包含多种来源，必须下钻详情确认对象后再操作。</x:v>
+        <x:v>入库管理是多种入库单的统一查询入口；其他入口只能覆盖部分对象或结果。</x:v>
       </x:c>
       <x:c r="V233" s="21" t="str">
-        <x:v>{"A":"漏范围：只核来源单号仍无法确认货品和数量。","B":"漏范围：核对货品后仍要确认入库类型和单据来源。","D":"漏步骤：列表金额一致也必须打开详情核对来源和货品。"}</x:v>
+        <x:v>{"A":"错对象：库存查询展示库存与流水，不是多类型入库单总入口。","C":"错范围：采购单只能覆盖采购来源，不能统一查询退货和调拨入库。","D":"错范围：智能退货入库只覆盖售后退货收货，不能替代入库管理。"}</x:v>
       </x:c>
       <x:c r="W233" s="21" t="str">
         <x:v>快速定位采购、退货、调拨等不同来源的入库单及明细。</x:v>
@@ -27438,7 +27440,7 @@
         <x:v>["入库管理是总入口，具体来源单据仍需结合对应业务模块核对"]</x:v>
       </x:c>
       <x:c r="AC233" s="21" t="str">
-        <x:v>["只看列表不看详情","按单号相似误判来源"]</x:v>
+        <x:v>["把采购单当全部入库总表","用库存结果替代单据查询"]</x:v>
       </x:c>
       <x:c r="AD233" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -27451,7 +27453,7 @@
         <x:v>入库管理—单据范围</x:v>
       </x:c>
       <x:c r="AH233" s="21" t="str">
-        <x:v>入库管理可筛选全部单据并查看详情。</x:v>
+        <x:v>入库管理统一展示多种来源入库单。</x:v>
       </x:c>
       <x:c r="AI233" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -27503,7 +27505,7 @@
     </x:row>
     <x:row r="234" ht="46" customHeight="1">
       <x:c r="A234" s="21" t="str">
-        <x:v>WDT-020-A</x:v>
+        <x:v>WDT-019-B</x:v>
       </x:c>
       <x:c r="B234" s="21" t="str">
         <x:v>旺店通-采购</x:v>
@@ -27521,10 +27523,10 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G234" s="21" t="str">
-        <x:v>基础</x:v>
+        <x:v>进阶</x:v>
       </x:c>
       <x:c r="H234" s="21" t="str">
-        <x:v>低</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I234" s="21" t="str">
         <x:v>practice</x:v>
@@ -27533,61 +27535,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K234" s="21" t="str">
-        <x:v>WDT-K020</x:v>
+        <x:v>WDT-K019</x:v>
       </x:c>
       <x:c r="L234" s="21" t="str">
-        <x:v>入库单建单方式</x:v>
+        <x:v>入库单总入口</x:v>
       </x:c>
       <x:c r="M234" s="21" t="str">
-        <x:v>扫码、手选与批量导入</x:v>
+        <x:v>所有入库类型统一查</x:v>
       </x:c>
       <x:c r="N234" s="21" t="str">
-        <x:v>少量到货且外箱条码已在系统货品中维护，建入库单优先可用哪种方式？</x:v>
+        <x:v>在入库管理找到一笔单据后，下一步最稳妥的核对方式是什么？</x:v>
       </x:c>
       <x:c r="O234" s="21" t="str">
-        <x:v>在入库单中扫描物流条码，按包裹号选择货品</x:v>
+        <x:v>打开详情只核对来源单号，不核对货品和数量</x:v>
       </x:c>
       <x:c r="P234" s="21" t="str">
-        <x:v>先确认空白入库单，再扫描条码追加入库货品</x:v>
+        <x:v>打开详情核对货品，但沿用列表默认入库类型、不核对来源</x:v>
       </x:c>
       <x:c r="Q234" s="21" t="str">
-        <x:v>在入库单中扫描供应商编码，带出全部到货货品</x:v>
+        <x:v>打开详情核对入库类型、来源单据和货品明细</x:v>
       </x:c>
       <x:c r="R234" s="21" t="str">
-        <x:v>在入库单中扫描条码选入对应系统货品</x:v>
+        <x:v>先在列表核对入库类型和金额，金额一致就不再打开详情</x:v>
       </x:c>
       <x:c r="S234" s="21" t="str">
-        <x:v>D</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="T234" s="21" t="str">
-        <x:v>在入库单中扫描条码选入对应系统货品</x:v>
+        <x:v>打开详情核对入库类型、来源单据和货品明细</x:v>
       </x:c>
       <x:c r="U234" s="21" t="str">
-        <x:v>条码资料已完成时，可在入库单用扫码快速选货；库存查询不是建单入口。</x:v>
+        <x:v>统一入口包含多种来源，必须下钻详情确认对象后再操作。</x:v>
       </x:c>
       <x:c r="V234" s="21" t="str">
-        <x:v>{"A":"错条码：应扫描已维护的货品条码。","B":"错顺序：不能确认空单后再追加货品。","C":"错对象：供应商编码不能替代货品条码。"}</x:v>
+        <x:v>{"A":"漏范围：只核来源单号仍无法确认货品和数量。","B":"漏范围：核对货品后仍要确认入库类型和单据来源。","D":"漏步骤：列表金额一致也必须打开详情核对来源和货品。"}</x:v>
       </x:c>
       <x:c r="W234" s="21" t="str">
-        <x:v>按货品规模选择高效且可复核的入库建单方式。</x:v>
+        <x:v>快速定位采购、退货、调拨等不同来源的入库单及明细。</x:v>
       </x:c>
       <x:c r="X234" s="21" t="str">
-        <x:v>["仓储","入库管理","新建入库单"]</x:v>
+        <x:v>["仓储","入库管理"]</x:v>
       </x:c>
       <x:c r="Y234" s="21" t="str">
-        <x:v>["系统货品资料已完成","条码扫描前货品条码已维护"]</x:v>
+        <x:v>["账号具备入库管理查看权限"]</x:v>
       </x:c>
       <x:c r="Z234" s="21" t="str">
-        <x:v>["选择正确入库类型和仓库","按场景使用条码扫描、手工选择或批量导入货品","核对选入的系统货品与实际到货"]</x:v>
+        <x:v>["进入入库管理","按入库类型、状态或单号筛选","打开单据详情核对来源和货品"]</x:v>
       </x:c>
       <x:c r="AA234" s="21" t="str">
-        <x:v>["扫描条码能匹配正确系统货品","批量导入后行数和货品数量与来源一致"]</x:v>
+        <x:v>["能区分采购、调拨、退货、盘盈、生产、其他、委外、纠错和预入库单","筛选结果与目标单据来源一致"]</x:v>
       </x:c>
       <x:c r="AB234" s="21" t="str">
-        <x:v>["货品资料未完成时不能依赖条码扫描准确建单"]</x:v>
+        <x:v>["入库管理是总入口，具体来源单据仍需结合对应业务模块核对"]</x:v>
       </x:c>
       <x:c r="AC234" s="21" t="str">
-        <x:v>["在库存查询直接改数量","扫码后不核对货品"]</x:v>
+        <x:v>["只看列表不看详情","按单号相似误判来源"]</x:v>
       </x:c>
       <x:c r="AD234" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -27597,10 +27599,10 @@
       </x:c>
       <x:c r="AF234" s="21" t="str"/>
       <x:c r="AG234" s="21" t="str">
-        <x:v>入库管理—选择货品</x:v>
+        <x:v>入库管理—单据范围</x:v>
       </x:c>
       <x:c r="AH234" s="21" t="str">
-        <x:v>货品资料完成后，入库单支持条码扫描选货。</x:v>
+        <x:v>入库管理可筛选全部单据并查看详情。</x:v>
       </x:c>
       <x:c r="AI234" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -27644,7 +27646,7 @@
       <x:c r="AV234" s="21" t="str"/>
       <x:c r="AW234" s="21" t="str"/>
       <x:c r="AX234" s="21" t="str">
-        <x:v>创建入库单并选择货品</x:v>
+        <x:v>在入库管理集中查询入库单</x:v>
       </x:c>
       <x:c r="AY234" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -27652,7 +27654,7 @@
     </x:row>
     <x:row r="235" ht="46" customHeight="1">
       <x:c r="A235" s="21" t="str">
-        <x:v>WDT-020-B</x:v>
+        <x:v>WDT-020-A</x:v>
       </x:c>
       <x:c r="B235" s="21" t="str">
         <x:v>旺店通-采购</x:v>
@@ -27670,10 +27672,10 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G235" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="H235" s="21" t="str">
-        <x:v>中</x:v>
+        <x:v>低</x:v>
       </x:c>
       <x:c r="I235" s="21" t="str">
         <x:v>practice</x:v>
@@ -27691,31 +27693,31 @@
         <x:v>扫码、手选与批量导入</x:v>
       </x:c>
       <x:c r="N235" s="21" t="str">
-        <x:v>一次到货有数百个货品行，资料支持的高效建单方式是什么？</x:v>
+        <x:v>少量到货且外箱条码已在系统货品中维护，建入库单优先可用哪种方式？</x:v>
       </x:c>
       <x:c r="O235" s="21" t="str">
-        <x:v>不下载模板，直接导入任意列顺序表格自动匹配</x:v>
+        <x:v>在入库单中扫描物流条码，按包裹号选择货品</x:v>
       </x:c>
       <x:c r="P235" s="21" t="str">
-        <x:v>按入库模板批量导入，再核对导入结果和异常行</x:v>
+        <x:v>先确认空白入库单，再扫描条码追加入库货品</x:v>
       </x:c>
       <x:c r="Q235" s="21" t="str">
-        <x:v>把全部条码数量粘到一个货品行，让系统自动拆行</x:v>
+        <x:v>在入库单中扫描供应商编码，带出全部到货货品</x:v>
       </x:c>
       <x:c r="R235" s="21" t="str">
-        <x:v>先确认空白入库单，再用入库纠错逐行新增货品</x:v>
+        <x:v>在入库单中扫描条码选入对应系统货品</x:v>
       </x:c>
       <x:c r="S235" s="21" t="str">
-        <x:v>B</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="T235" s="21" t="str">
-        <x:v>按入库模板批量导入，再核对导入结果和异常行</x:v>
+        <x:v>在入库单中扫描条码选入对应系统货品</x:v>
       </x:c>
       <x:c r="U235" s="21" t="str">
-        <x:v>批量导入是资料列明的大批量选货方式，但导入后仍要复核。</x:v>
+        <x:v>条码资料已完成时，可在入库单用扫码快速选货；库存查询不是建单入口。</x:v>
       </x:c>
       <x:c r="V235" s="21" t="str">
-        <x:v>{"A":"错格式：应按系统模板组织导入字段。","C":"无资料依据：未说明单行可自动拆分多行。","D":"错顺序：纠错不用于补建整张入库单。"}</x:v>
+        <x:v>{"A":"错条码：应扫描已维护的货品条码。","B":"错顺序：不能确认空单后再追加货品。","C":"错对象：供应商编码不能替代货品条码。"}</x:v>
       </x:c>
       <x:c r="W235" s="21" t="str">
         <x:v>按货品规模选择高效且可复核的入库建单方式。</x:v>
@@ -27736,7 +27738,7 @@
         <x:v>["货品资料未完成时不能依赖条码扫描准确建单"]</x:v>
       </x:c>
       <x:c r="AC235" s="21" t="str">
-        <x:v>["先确认空单再纠错","假定系统支持截图识别"]</x:v>
+        <x:v>["在库存查询直接改数量","扫码后不核对货品"]</x:v>
       </x:c>
       <x:c r="AD235" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -27749,7 +27751,7 @@
         <x:v>入库管理—选择货品</x:v>
       </x:c>
       <x:c r="AH235" s="21" t="str">
-        <x:v>入库单支持批量导入货品。</x:v>
+        <x:v>货品资料完成后，入库单支持条码扫描选货。</x:v>
       </x:c>
       <x:c r="AI235" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -27801,7 +27803,7 @@
     </x:row>
     <x:row r="236" ht="46" customHeight="1">
       <x:c r="A236" s="21" t="str">
-        <x:v>WDT-021-A</x:v>
+        <x:v>WDT-020-B</x:v>
       </x:c>
       <x:c r="B236" s="21" t="str">
         <x:v>旺店通-采购</x:v>
@@ -27822,70 +27824,70 @@
         <x:v>场景</x:v>
       </x:c>
       <x:c r="H236" s="21" t="str">
-        <x:v>高</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I236" s="21" t="str">
-        <x:v>redline</x:v>
+        <x:v>practice</x:v>
       </x:c>
       <x:c r="J236" s="22" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K236" s="21" t="str">
-        <x:v>WDT-K021</x:v>
+        <x:v>WDT-K020</x:v>
       </x:c>
       <x:c r="L236" s="21" t="str">
-        <x:v>入库明细编辑</x:v>
+        <x:v>入库单建单方式</x:v>
       </x:c>
       <x:c r="M236" s="21" t="str">
-        <x:v>库位、良残、数量、价格一起核</x:v>
+        <x:v>扫码、手选与批量导入</x:v>
       </x:c>
       <x:c r="N236" s="21" t="str">
-        <x:v>同一货品到货 20 件，其中 2 件破损，入库时应怎样记录？</x:v>
+        <x:v>一次到货有数百个货品行，资料支持的高效建单方式是什么？</x:v>
       </x:c>
       <x:c r="O236" s="21" t="str">
-        <x:v>18 件录正品、2 件只写破损备注不选残次属性</x:v>
+        <x:v>不下载模板，直接导入任意列顺序表格自动匹配</x:v>
       </x:c>
       <x:c r="P236" s="21" t="str">
-        <x:v>18 件录正品、2 件仍录正品但放入残次库位</x:v>
+        <x:v>按入库模板批量导入，再核对导入结果和异常行</x:v>
       </x:c>
       <x:c r="Q236" s="21" t="str">
-        <x:v>正品和残次分别建行，但正品行仍填写到货总数 20 件</x:v>
+        <x:v>把全部条码数量粘到一个货品行，让系统自动拆行</x:v>
       </x:c>
       <x:c r="R236" s="21" t="str">
-        <x:v>按实际情况分别记录正品与残次数量，并核对库位</x:v>
+        <x:v>先确认空白入库单，再用入库纠错逐行新增货品</x:v>
       </x:c>
       <x:c r="S236" s="21" t="str">
-        <x:v>D</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="T236" s="21" t="str">
-        <x:v>按实际情况分别记录正品与残次数量，并核对库位</x:v>
+        <x:v>按入库模板批量导入，再核对导入结果和异常行</x:v>
       </x:c>
       <x:c r="U236" s="21" t="str">
-        <x:v>入库单支持正品和残次属性，应按实收质量拆分记录，避免可售库存虚高。</x:v>
+        <x:v>批量导入是资料列明的大批量选货方式，但导入后仍要复核。</x:v>
       </x:c>
       <x:c r="V236" s="21" t="str">
-        <x:v>{"A":"漏字段：破损备注不能替代残次属性。","B":"错属性：库位不能替代残次库存属性。","C":"错数量：正品行填写总数会把破损数量重复计入。"}</x:v>
+        <x:v>{"A":"错格式：应按系统模板组织导入字段。","C":"无资料依据：未说明单行可自动拆分多行。","D":"错顺序：纠错不用于补建整张入库单。"}</x:v>
       </x:c>
       <x:c r="W236" s="21" t="str">
-        <x:v>保证实际到货、库存属性和金额记录一致。</x:v>
+        <x:v>按货品规模选择高效且可复核的入库建单方式。</x:v>
       </x:c>
       <x:c r="X236" s="21" t="str">
-        <x:v>["仓储","入库管理","入库单","货品明细"]</x:v>
+        <x:v>["仓储","入库管理","新建入库单"]</x:v>
       </x:c>
       <x:c r="Y236" s="21" t="str">
-        <x:v>["入库单已选入正确货品","实际收货数量和质量已清点"]</x:v>
+        <x:v>["系统货品资料已完成","条码扫描前货品条码已维护"]</x:v>
       </x:c>
       <x:c r="Z236" s="21" t="str">
-        <x:v>["核对并编辑入库库位","选择正品或残次库存属性","填写数量、序列号数量、价格和金额","有箱规时核对箱规与箱数"]</x:v>
+        <x:v>["选择正确入库类型和仓库","按场景使用条码扫描、手工选择或批量导入货品","核对选入的系统货品与实际到货"]</x:v>
       </x:c>
       <x:c r="AA236" s="21" t="str">
-        <x:v>["良品与残次品数量分开记录","数量、价格、金额及箱数与实收一致"]</x:v>
+        <x:v>["扫描条码能匹配正确系统货品","批量导入后行数和货品数量与来源一致"]</x:v>
       </x:c>
       <x:c r="AB236" s="21" t="str">
-        <x:v>["序列号货品应同时核对序列号数量，不能只填总数量"]</x:v>
+        <x:v>["货品资料未完成时不能依赖条码扫描准确建单"]</x:v>
       </x:c>
       <x:c r="AC236" s="21" t="str">
-        <x:v>["残次混入良品","实物未全量记账"]</x:v>
+        <x:v>["先确认空单再纠错","假定系统支持截图识别"]</x:v>
       </x:c>
       <x:c r="AD236" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -27895,10 +27897,10 @@
       </x:c>
       <x:c r="AF236" s="21" t="str"/>
       <x:c r="AG236" s="21" t="str">
-        <x:v>入库管理—货品明细</x:v>
+        <x:v>入库管理—选择货品</x:v>
       </x:c>
       <x:c r="AH236" s="21" t="str">
-        <x:v>入库明细可选择正品或残次库存属性并填写数量。</x:v>
+        <x:v>入库单支持批量导入货品。</x:v>
       </x:c>
       <x:c r="AI236" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -27942,7 +27944,7 @@
       <x:c r="AV236" s="21" t="str"/>
       <x:c r="AW236" s="21" t="str"/>
       <x:c r="AX236" s="21" t="str">
-        <x:v>核对入库货品属性与金额</x:v>
+        <x:v>创建入库单并选择货品</x:v>
       </x:c>
       <x:c r="AY236" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -27950,7 +27952,7 @@
     </x:row>
     <x:row r="237" ht="46" customHeight="1">
       <x:c r="A237" s="21" t="str">
-        <x:v>WDT-021-B</x:v>
+        <x:v>WDT-021-A</x:v>
       </x:c>
       <x:c r="B237" s="21" t="str">
         <x:v>旺店通-采购</x:v>
@@ -27968,16 +27970,16 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G237" s="21" t="str">
-        <x:v>进阶</x:v>
+        <x:v>场景</x:v>
       </x:c>
       <x:c r="H237" s="21" t="str">
         <x:v>高</x:v>
       </x:c>
       <x:c r="I237" s="21" t="str">
-        <x:v>practice</x:v>
+        <x:v>redline</x:v>
       </x:c>
       <x:c r="J237" s="22" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K237" s="21" t="str">
         <x:v>WDT-K021</x:v>
@@ -27989,31 +27991,31 @@
         <x:v>库位、良残、数量、价格一起核</x:v>
       </x:c>
       <x:c r="N237" s="21" t="str">
-        <x:v>序列号管理货品入库时，除总数量外还应重点核对什么？</x:v>
+        <x:v>同一货品到货 20 件，其中 2 件破损，入库时应怎样记录？</x:v>
       </x:c>
       <x:c r="O237" s="21" t="str">
-        <x:v>只核对序列号是否重复，不核对数量与实收数量</x:v>
+        <x:v>18 件录正品、2 件只写破损备注不选残次属性</x:v>
       </x:c>
       <x:c r="P237" s="21" t="str">
-        <x:v>只核对入库总数，序列号数量可在入库后任意补录</x:v>
+        <x:v>18 件录正品、2 件仍录正品但放入残次库位</x:v>
       </x:c>
       <x:c r="Q237" s="21" t="str">
-        <x:v>让序列号数量对应采购计划数量，不按本次实收核对</x:v>
+        <x:v>正品和残次分别建行，但正品行仍填写到货总数 20 件</x:v>
       </x:c>
       <x:c r="R237" s="21" t="str">
-        <x:v>序列号数量与实收数量是否对应</x:v>
+        <x:v>按实际情况分别记录正品与残次数量，并核对库位</x:v>
       </x:c>
       <x:c r="S237" s="21" t="str">
         <x:v>D</x:v>
       </x:c>
       <x:c r="T237" s="21" t="str">
-        <x:v>序列号数量与实收数量是否对应</x:v>
+        <x:v>按实际情况分别记录正品与残次数量，并核对库位</x:v>
       </x:c>
       <x:c r="U237" s="21" t="str">
-        <x:v>资料把序列号数量列为入库明细字段，序列号货品必须核对数量一致。</x:v>
+        <x:v>入库单支持正品和残次属性，应按实收质量拆分记录，避免可售库存虚高。</x:v>
       </x:c>
       <x:c r="V237" s="21" t="str">
-        <x:v>{"A":"漏核对：去重不能替代数量一致性。","B":"错时点：入库时就应核对序列号数量。","C":"错基准：应按实际收货数量核对。"}</x:v>
+        <x:v>{"A":"漏字段：破损备注不能替代残次属性。","B":"错属性：库位不能替代残次库存属性。","C":"错数量：正品行填写总数会把破损数量重复计入。"}</x:v>
       </x:c>
       <x:c r="W237" s="21" t="str">
         <x:v>保证实际到货、库存属性和金额记录一致。</x:v>
@@ -28034,7 +28036,7 @@
         <x:v>["序列号货品应同时核对序列号数量，不能只填总数量"]</x:v>
       </x:c>
       <x:c r="AC237" s="21" t="str">
-        <x:v>["只填总数量","序列号数量与实收不一致"]</x:v>
+        <x:v>["残次混入良品","实物未全量记账"]</x:v>
       </x:c>
       <x:c r="AD237" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -28047,7 +28049,7 @@
         <x:v>入库管理—货品明细</x:v>
       </x:c>
       <x:c r="AH237" s="21" t="str">
-        <x:v>入库明细可填写序列号数量。</x:v>
+        <x:v>入库明细可选择正品或残次库存属性并填写数量。</x:v>
       </x:c>
       <x:c r="AI237" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -28099,7 +28101,7 @@
     </x:row>
     <x:row r="238" ht="46" customHeight="1">
       <x:c r="A238" s="21" t="str">
-        <x:v>WDT-022-A</x:v>
+        <x:v>WDT-021-B</x:v>
       </x:c>
       <x:c r="B238" s="21" t="str">
         <x:v>旺店通-采购</x:v>
@@ -28117,10 +28119,10 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G238" s="21" t="str">
-        <x:v>基础</x:v>
+        <x:v>进阶</x:v>
       </x:c>
       <x:c r="H238" s="21" t="str">
-        <x:v>中</x:v>
+        <x:v>高</x:v>
       </x:c>
       <x:c r="I238" s="21" t="str">
         <x:v>practice</x:v>
@@ -28129,61 +28131,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K238" s="21" t="str">
-        <x:v>WDT-K022</x:v>
+        <x:v>WDT-K021</x:v>
       </x:c>
       <x:c r="L238" s="21" t="str">
-        <x:v>入库金额与纠错</x:v>
+        <x:v>入库明细编辑</x:v>
       </x:c>
       <x:c r="M238" s="21" t="str">
-        <x:v>先选分摊规则，入库后用纠错修正</x:v>
+        <x:v>库位、良残、数量、价格一起核</x:v>
       </x:c>
       <x:c r="N238" s="21" t="str">
-        <x:v>入库单的运费分摊，资料明确支持哪三种方式？</x:v>
+        <x:v>序列号管理货品入库时，除总数量外还应重点核对什么？</x:v>
       </x:c>
       <x:c r="O238" s="21" t="str">
-        <x:v>按重量分摊、按体积分摊、按距离分摊</x:v>
+        <x:v>只核对序列号是否重复，不核对数量与实收数量</x:v>
       </x:c>
       <x:c r="P238" s="21" t="str">
-        <x:v>不分摊、按数量分摊、按金额分摊</x:v>
+        <x:v>只核对入库总数，序列号数量可在入库后任意补录</x:v>
       </x:c>
       <x:c r="Q238" s="21" t="str">
-        <x:v>按仓库分摊、按店铺分摊、按平台分摊</x:v>
+        <x:v>让序列号数量对应采购计划数量，不按本次实收核对</x:v>
       </x:c>
       <x:c r="R238" s="21" t="str">
-        <x:v>按订单分摊、按客户分摊、按员工分摊</x:v>
+        <x:v>序列号数量与实收数量是否对应</x:v>
       </x:c>
       <x:c r="S238" s="21" t="str">
-        <x:v>B</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="T238" s="21" t="str">
-        <x:v>不分摊、按数量分摊、按金额分摊</x:v>
+        <x:v>序列号数量与实收数量是否对应</x:v>
       </x:c>
       <x:c r="U238" s="21" t="str">
-        <x:v>只有这三种是本次资料明确列出的入库运费分摊方式。</x:v>
+        <x:v>资料把序列号数量列为入库明细字段，序列号货品必须核对数量一致。</x:v>
       </x:c>
       <x:c r="V238" s="21" t="str">
-        <x:v>{"A":"无资料依据：未列重量体积距离。","C":"错维度：未列仓库店铺平台。","D":"错维度：未列订单客户员工。"}</x:v>
+        <x:v>{"A":"漏核对：去重不能替代数量一致性。","B":"错时点：入库时就应核对序列号数量。","C":"错基准：应按实际收货数量核对。"}</x:v>
       </x:c>
       <x:c r="W238" s="21" t="str">
-        <x:v>把运费按明确规则计入货品，并在入库后可追踪地修正数量或金额。</x:v>
+        <x:v>保证实际到货、库存属性和金额记录一致。</x:v>
       </x:c>
       <x:c r="X238" s="21" t="str">
-        <x:v>["仓储","入库管理","入库单"]</x:v>
+        <x:v>["仓储","入库管理","入库单","货品明细"]</x:v>
       </x:c>
       <x:c r="Y238" s="21" t="str">
-        <x:v>["入库货品和费用已核对","纠错仅用于已入库记录的数量、属性或金额修正"]</x:v>
+        <x:v>["入库单已选入正确货品","实际收货数量和质量已清点"]</x:v>
       </x:c>
       <x:c r="Z238" s="21" t="str">
-        <x:v>["按业务口径选择不分摊、按数量或按金额分摊运费","确认入库","发现差错时打开入库记录","使用入库纠错修修改正品/残次数量、价格或金额"]</x:v>
+        <x:v>["核对并编辑入库库位","选择正品或残次库存属性","填写数量、序列号数量、价格和金额","有箱规时核对箱规与箱数"]</x:v>
       </x:c>
       <x:c r="AA238" s="21" t="str">
-        <x:v>["分摊方式与财务口径一致","纠错后库存属性、数量和金额与凭证一致"]</x:v>
+        <x:v>["良品与残次品数量分开记录","数量、价格、金额及箱数与实收一致"]</x:v>
       </x:c>
       <x:c r="AB238" s="21" t="str">
-        <x:v>["入库纠错是修正已入库记录，不应替代正常建单和复核"]</x:v>
+        <x:v>["序列号货品应同时核对序列号数量，不能只填总数量"]</x:v>
       </x:c>
       <x:c r="AC238" s="21" t="str">
-        <x:v>["自行假定按重量分摊","未与财务口径确认"]</x:v>
+        <x:v>["只填总数量","序列号数量与实收不一致"]</x:v>
       </x:c>
       <x:c r="AD238" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -28193,10 +28195,10 @@
       </x:c>
       <x:c r="AF238" s="21" t="str"/>
       <x:c r="AG238" s="21" t="str">
-        <x:v>入库管理—运费分摊与入库纠错</x:v>
+        <x:v>入库管理—货品明细</x:v>
       </x:c>
       <x:c r="AH238" s="21" t="str">
-        <x:v>运费分摊方式为不分摊、按数量、按金额。</x:v>
+        <x:v>入库明细可填写序列号数量。</x:v>
       </x:c>
       <x:c r="AI238" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -28240,7 +28242,7 @@
       <x:c r="AV238" s="21" t="str"/>
       <x:c r="AW238" s="21" t="str"/>
       <x:c r="AX238" s="21" t="str">
-        <x:v>设置运费分摊并使用入库纠错</x:v>
+        <x:v>核对入库货品属性与金额</x:v>
       </x:c>
       <x:c r="AY238" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -28248,7 +28250,7 @@
     </x:row>
     <x:row r="239" ht="46" customHeight="1">
       <x:c r="A239" s="21" t="str">
-        <x:v>WDT-022-B</x:v>
+        <x:v>WDT-022-A</x:v>
       </x:c>
       <x:c r="B239" s="21" t="str">
         <x:v>旺店通-采购</x:v>
@@ -28266,10 +28268,10 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G239" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="H239" s="21" t="str">
-        <x:v>高</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I239" s="21" t="str">
         <x:v>practice</x:v>
@@ -28287,31 +28289,31 @@
         <x:v>先选分摊规则，入库后用纠错修正</x:v>
       </x:c>
       <x:c r="N239" s="21" t="str">
-        <x:v>入库完成后发现残次数量和单价录错，应使用什么功能修正？</x:v>
+        <x:v>入库单的运费分摊，资料明确支持哪三种方式？</x:v>
       </x:c>
       <x:c r="O239" s="21" t="str">
-        <x:v>返回原采购单改残次数量和单价，等待已入库记录自动回写</x:v>
+        <x:v>按重量分摊、按体积分摊、按距离分摊</x:v>
       </x:c>
       <x:c r="P239" s="21" t="str">
-        <x:v>在库存查询调整正残数量，再单独修改采购金额</x:v>
+        <x:v>不分摊、按数量分摊、按金额分摊</x:v>
       </x:c>
       <x:c r="Q239" s="21" t="str">
-        <x:v>打开入库记录，使用入库纠错修改数量、价格和金额</x:v>
+        <x:v>按仓库分摊、按店铺分摊、按平台分摊</x:v>
       </x:c>
       <x:c r="R239" s="21" t="str">
-        <x:v>在入库管理新建差额入库单修正原记录</x:v>
+        <x:v>按订单分摊、按客户分摊、按员工分摊</x:v>
       </x:c>
       <x:c r="S239" s="21" t="str">
-        <x:v>C</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="T239" s="21" t="str">
-        <x:v>打开入库记录，使用入库纠错修改数量、价格和金额</x:v>
+        <x:v>不分摊、按数量分摊、按金额分摊</x:v>
       </x:c>
       <x:c r="U239" s="21" t="str">
-        <x:v>入库纠错就是已入库记录的指定修正入口，能修改正品/残次数量、价格和金额。</x:v>
+        <x:v>只有这三种是本次资料明确列出的入库运费分摊方式。</x:v>
       </x:c>
       <x:c r="V239" s="21" t="str">
-        <x:v>{"A":"错机制：修改采购单不会自动回写已确认入库记录。","B":"错链路：分开改库存和采购金额会破坏原入库记录的一致性。","D":"错对象：新建差额单不能替代对原入库记录的纠错。"}</x:v>
+        <x:v>{"A":"无资料依据：未列重量体积距离。","C":"错维度：未列仓库店铺平台。","D":"错维度：未列订单客户员工。"}</x:v>
       </x:c>
       <x:c r="W239" s="21" t="str">
         <x:v>把运费按明确规则计入货品，并在入库后可追踪地修正数量或金额。</x:v>
@@ -28332,7 +28334,7 @@
         <x:v>["入库纠错是修正已入库记录，不应替代正常建单和复核"]</x:v>
       </x:c>
       <x:c r="AC239" s="21" t="str">
-        <x:v>["用新单冲销但无制度依据","直接改库存不留入库链路"]</x:v>
+        <x:v>["自行假定按重量分摊","未与财务口径确认"]</x:v>
       </x:c>
       <x:c r="AD239" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -28345,7 +28347,7 @@
         <x:v>入库管理—运费分摊与入库纠错</x:v>
       </x:c>
       <x:c r="AH239" s="21" t="str">
-        <x:v>已入库后可用入库纠错修修改正品/残次数量、价格和金额。</x:v>
+        <x:v>运费分摊方式为不分摊、按数量、按金额。</x:v>
       </x:c>
       <x:c r="AI239" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -28397,7 +28399,7 @@
     </x:row>
     <x:row r="240" ht="46" customHeight="1">
       <x:c r="A240" s="21" t="str">
-        <x:v>WDT-023-A</x:v>
+        <x:v>WDT-022-B</x:v>
       </x:c>
       <x:c r="B240" s="21" t="str">
         <x:v>旺店通-采购</x:v>
@@ -28415,10 +28417,10 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G240" s="21" t="str">
-        <x:v>基础</x:v>
+        <x:v>场景</x:v>
       </x:c>
       <x:c r="H240" s="21" t="str">
-        <x:v>中</x:v>
+        <x:v>高</x:v>
       </x:c>
       <x:c r="I240" s="21" t="str">
         <x:v>practice</x:v>
@@ -28427,74 +28429,74 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K240" s="21" t="str">
-        <x:v>WDT-K023</x:v>
+        <x:v>WDT-K022</x:v>
       </x:c>
       <x:c r="L240" s="21" t="str">
-        <x:v>采购建单</x:v>
+        <x:v>入库金额与纠错</x:v>
       </x:c>
       <x:c r="M240" s="21" t="str">
-        <x:v>先供应商，后采购单</x:v>
+        <x:v>先选分摊规则，入库后用纠错修正</x:v>
       </x:c>
       <x:c r="N240" s="21" t="str">
-        <x:v>首次向新供应商采购，正确的建单顺序是什么？</x:v>
+        <x:v>入库完成后发现残次数量和单价录错，应使用什么功能修正？</x:v>
       </x:c>
       <x:c r="O240" s="21" t="str">
-        <x:v>先新建采购单填临时供应商，再到入库时补建供应商</x:v>
+        <x:v>返回原采购单改残次数量和单价，等待已入库记录自动回写</x:v>
       </x:c>
       <x:c r="P240" s="21" t="str">
-        <x:v>先新建供应商并填编码名称，再新建采购单关联该供应商</x:v>
+        <x:v>在库存查询调整正残数量，再单独修改采购金额</x:v>
       </x:c>
       <x:c r="Q240" s="21" t="str">
-        <x:v>先审核空白采购单，再新建供应商补填采购货品</x:v>
+        <x:v>打开入库记录，使用入库纠错修改数量、价格和金额</x:v>
       </x:c>
       <x:c r="R240" s="21" t="str">
-        <x:v>先新建入库单确认库存，再倒推生成供应商和采购单</x:v>
+        <x:v>在入库管理新建差额入库单修正原记录</x:v>
       </x:c>
       <x:c r="S240" s="21" t="str">
-        <x:v>B</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="T240" s="21" t="str">
-        <x:v>先新建供应商并填编码名称，再新建采购单关联该供应商</x:v>
+        <x:v>打开入库记录，使用入库纠错修改数量、价格和金额</x:v>
       </x:c>
       <x:c r="U240" s="21" t="str">
-        <x:v>资料流程先建立供应商主数据，再在采购单选择供应商并填写货品价格数量。</x:v>
+        <x:v>入库纠错就是已入库记录的指定修正入口，能修改正品/残次数量、价格和金额。</x:v>
       </x:c>
       <x:c r="V240" s="21" t="str">
-        <x:v>{"A":"错顺序：供应商应先建立。","C":"错前置：空白采购单不能先审核。","D":"错顺序：采购入库应有前置采购来源。"}</x:v>
+        <x:v>{"A":"错机制：修改采购单不会自动回写已确认入库记录。","B":"错链路：分开改库存和采购金额会破坏原入库记录的一致性。","D":"错对象：新建差额单不能替代对原入库记录的纠错。"}</x:v>
       </x:c>
       <x:c r="W240" s="21" t="str">
-        <x:v>建立完整的供应商与采购订单来源链路。</x:v>
+        <x:v>把运费按明确规则计入货品，并在入库后可追踪地修正数量或金额。</x:v>
       </x:c>
       <x:c r="X240" s="21" t="str">
-        <x:v>["采购","供应商","新建供应商","采购","采购单","新建采购单"]</x:v>
+        <x:v>["仓储","入库管理","入库单"]</x:v>
       </x:c>
       <x:c r="Y240" s="21" t="str">
-        <x:v>["供应商编码和名称已确定","采购品项、价格和数量已确认"]</x:v>
+        <x:v>["入库货品和费用已核对","纠错仅用于已入库记录的数量、属性或金额修正"]</x:v>
       </x:c>
       <x:c r="Z240" s="21" t="str">
-        <x:v>["在供应商中新建并填写必填编码和名称","进入采购单新建采购单","手工添加或导入货品","填写供应商、价格和数量","保存并提交审核"]</x:v>
+        <x:v>["按业务口径选择不分摊、按数量或按金额分摊运费","确认入库","发现差错时打开入库记录","使用入库纠错修修改正品/残次数量、价格或金额"]</x:v>
       </x:c>
       <x:c r="AA240" s="21" t="str">
-        <x:v>["采购单关联正确供应商","货品、价格、数量与采购依据一致"]</x:v>
+        <x:v>["分摊方式与财务口径一致","纠错后库存属性、数量和金额与凭证一致"]</x:v>
       </x:c>
       <x:c r="AB240" s="21" t="str">
-        <x:v>["供应商编码和名称为资料明确的必填项"]</x:v>
+        <x:v>["入库纠错是修正已入库记录，不应替代正常建单和复核"]</x:v>
       </x:c>
       <x:c r="AC240" s="21" t="str">
-        <x:v>["入库后倒建采购链路","使用临时供应商造成对账混乱"]</x:v>
+        <x:v>["用新单冲销但无制度依据","直接改库存不留入库链路"]</x:v>
       </x:c>
       <x:c r="AD240" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
       </x:c>
       <x:c r="AE240" s="21" t="str">
-        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/ncmtzsrt12cpbnq5</x:v>
+        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/neeximegebrnshqi</x:v>
       </x:c>
       <x:c r="AF240" s="21" t="str"/>
       <x:c r="AG240" s="21" t="str">
-        <x:v>采购入库—供应商与采购单</x:v>
+        <x:v>入库管理—运费分摊与入库纠错</x:v>
       </x:c>
       <x:c r="AH240" s="21" t="str">
-        <x:v>先新建供应商，再新建采购单。</x:v>
+        <x:v>已入库后可用入库纠错修修改正品/残次数量、价格和金额。</x:v>
       </x:c>
       <x:c r="AI240" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -28538,7 +28540,7 @@
       <x:c r="AV240" s="21" t="str"/>
       <x:c r="AW240" s="21" t="str"/>
       <x:c r="AX240" s="21" t="str">
-        <x:v>新建供应商与采购单</x:v>
+        <x:v>设置运费分摊并使用入库纠错</x:v>
       </x:c>
       <x:c r="AY240" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -28546,7 +28548,7 @@
     </x:row>
     <x:row r="241" ht="46" customHeight="1">
       <x:c r="A241" s="21" t="str">
-        <x:v>WDT-023-B</x:v>
+        <x:v>WDT-023-A</x:v>
       </x:c>
       <x:c r="B241" s="21" t="str">
         <x:v>旺店通-采购</x:v>
@@ -28567,7 +28569,7 @@
         <x:v>基础</x:v>
       </x:c>
       <x:c r="H241" s="21" t="str">
-        <x:v>低</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I241" s="21" t="str">
         <x:v>practice</x:v>
@@ -28585,31 +28587,31 @@
         <x:v>先供应商，后采购单</x:v>
       </x:c>
       <x:c r="N241" s="21" t="str">
-        <x:v>新建供应商时，本次资料明确要求的两个必填信息是什么？</x:v>
+        <x:v>首次向新供应商采购，正确的建单顺序是什么？</x:v>
       </x:c>
       <x:c r="O241" s="21" t="str">
-        <x:v>供应商仓库和供应商库位</x:v>
+        <x:v>先新建采购单填临时供应商，再到入库时补建供应商</x:v>
       </x:c>
       <x:c r="P241" s="21" t="str">
-        <x:v>供应商等级和供应商账期</x:v>
+        <x:v>先新建供应商并填编码名称，再新建采购单关联该供应商</x:v>
       </x:c>
       <x:c r="Q241" s="21" t="str">
-        <x:v>供应商平台和供应商店铺</x:v>
+        <x:v>先审核空白采购单，再新建供应商补填采购货品</x:v>
       </x:c>
       <x:c r="R241" s="21" t="str">
-        <x:v>供应商编码和供应商名称</x:v>
+        <x:v>先新建入库单确认库存，再倒推生成供应商和采购单</x:v>
       </x:c>
       <x:c r="S241" s="21" t="str">
-        <x:v>D</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="T241" s="21" t="str">
-        <x:v>供应商编码和供应商名称</x:v>
+        <x:v>先新建供应商并填编码名称，再新建采购单关联该供应商</x:v>
       </x:c>
       <x:c r="U241" s="21" t="str">
-        <x:v>编码和名称是资料明确列出的新建供应商必填项，其他字段本次资料未列为必填。</x:v>
+        <x:v>资料流程先建立供应商主数据，再在采购单选择供应商并填写货品价格数量。</x:v>
       </x:c>
       <x:c r="V241" s="21" t="str">
-        <x:v>{"A":"错对象：仓库库位不是供应商基本必填。","B":"无资料依据：等级账期未列为这一步必填。","C":"错对象：平台店铺不是供应商基本必填。"}</x:v>
+        <x:v>{"A":"错顺序：供应商应先建立。","C":"错前置：空白采购单不能先审核。","D":"错顺序：采购入库应有前置采购来源。"}</x:v>
       </x:c>
       <x:c r="W241" s="21" t="str">
         <x:v>建立完整的供应商与采购订单来源链路。</x:v>
@@ -28630,7 +28632,7 @@
         <x:v>["供应商编码和名称为资料明确的必填项"]</x:v>
       </x:c>
       <x:c r="AC241" s="21" t="str">
-        <x:v>["漏填供应商编码","把未说明字段当强制必填"]</x:v>
+        <x:v>["入库后倒建采购链路","使用临时供应商造成对账混乱"]</x:v>
       </x:c>
       <x:c r="AD241" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -28643,7 +28645,7 @@
         <x:v>采购入库—供应商与采购单</x:v>
       </x:c>
       <x:c r="AH241" s="21" t="str">
-        <x:v>新建供应商必填供应商编码和名称。</x:v>
+        <x:v>先新建供应商，再新建采购单。</x:v>
       </x:c>
       <x:c r="AI241" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -28695,7 +28697,7 @@
     </x:row>
     <x:row r="242" ht="46" customHeight="1">
       <x:c r="A242" s="21" t="str">
-        <x:v>WDT-024-A</x:v>
+        <x:v>WDT-023-B</x:v>
       </x:c>
       <x:c r="B242" s="21" t="str">
         <x:v>旺店通-采购</x:v>
@@ -28713,10 +28715,10 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G242" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="H242" s="21" t="str">
-        <x:v>中</x:v>
+        <x:v>低</x:v>
       </x:c>
       <x:c r="I242" s="21" t="str">
         <x:v>practice</x:v>
@@ -28725,61 +28727,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K242" s="21" t="str">
-        <x:v>WDT-K024</x:v>
+        <x:v>WDT-K023</x:v>
       </x:c>
       <x:c r="L242" s="21" t="str">
-        <x:v>采购单审核与入库入口</x:v>
+        <x:v>采购建单</x:v>
       </x:c>
       <x:c r="M242" s="21" t="str">
-        <x:v>未审核采购单不能入库</x:v>
+        <x:v>先供应商，后采购单</x:v>
       </x:c>
       <x:c r="N242" s="21" t="str">
-        <x:v>采购单保存后看不到可执行入库，最先应检查什么？</x:v>
+        <x:v>新建供应商时，本次资料明确要求的两个必填信息是什么？</x:v>
       </x:c>
       <x:c r="O242" s="21" t="str">
-        <x:v>采购单是否填写了预计到货日期</x:v>
+        <x:v>供应商仓库和供应商库位</x:v>
       </x:c>
       <x:c r="P242" s="21" t="str">
-        <x:v>全部货品是否已经维护默认库位</x:v>
+        <x:v>供应商等级和供应商账期</x:v>
       </x:c>
       <x:c r="Q242" s="21" t="str">
-        <x:v>采购单是否已经审核通过</x:v>
+        <x:v>供应商平台和供应商店铺</x:v>
       </x:c>
       <x:c r="R242" s="21" t="str">
-        <x:v>供应商资料是否设置了默认联系人</x:v>
+        <x:v>供应商编码和供应商名称</x:v>
       </x:c>
       <x:c r="S242" s="21" t="str">
-        <x:v>C</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="T242" s="21" t="str">
-        <x:v>采购单是否已经审核通过</x:v>
+        <x:v>供应商编码和供应商名称</x:v>
       </x:c>
       <x:c r="U242" s="21" t="str">
-        <x:v>未审核采购单不能进入采购入库流程，审核状态是首要前置。</x:v>
+        <x:v>编码和名称是资料明确列出的新建供应商必填项，其他字段本次资料未列为必填。</x:v>
       </x:c>
       <x:c r="V242" s="21" t="str">
-        <x:v>{"A":"错前置：预计到货日期不是可执行入库的首要状态门槛。","B":"错前置：默认库位便于收货，但不能替代采购单审核。","D":"错前置：默认联系人不决定采购单能否进入入库。"}</x:v>
+        <x:v>{"A":"错对象：仓库库位不是供应商基本必填。","B":"无资料依据：等级账期未列为这一步必填。","C":"错对象：平台店铺不是供应商基本必填。"}</x:v>
       </x:c>
       <x:c r="W242" s="21" t="str">
-        <x:v>在采购单审核后按实际收货复杂度选择去入库或一键入库。</x:v>
+        <x:v>建立完整的供应商与采购订单来源链路。</x:v>
       </x:c>
       <x:c r="X242" s="21" t="str">
-        <x:v>["采购","采购单","采购单列表"]</x:v>
+        <x:v>["采购","供应商","新建供应商","采购","采购单","新建采购单"]</x:v>
       </x:c>
       <x:c r="Y242" s="21" t="str">
-        <x:v>["采购单货品、供应商、价格和数量已复核"]</x:v>
+        <x:v>["供应商编码和名称已确定","采购品项、价格和数量已确认"]</x:v>
       </x:c>
       <x:c r="Z242" s="21" t="str">
-        <x:v>["保存并审核采购单","复杂到货选择去入库进入入库管理后编辑","确认无差异时可选择一键入库","检查生成的采购入库单"]</x:v>
+        <x:v>["在供应商中新建并填写必填编码和名称","进入采购单新建采购单","手工添加或导入货品","填写供应商、价格和数量","保存并提交审核"]</x:v>
       </x:c>
       <x:c r="AA242" s="21" t="str">
-        <x:v>["采购单状态为已审核","一键入库仅按剩余未入库货品和库存生成入库单"]</x:v>
+        <x:v>["采购单关联正确供应商","货品、价格、数量与采购依据一致"]</x:v>
       </x:c>
       <x:c r="AB242" s="21" t="str">
-        <x:v>["未审核采购单不能入库","一键入库会直接创建并确认入库，差异收货应优先去入库编辑"]</x:v>
+        <x:v>["供应商编码和名称为资料明确的必填项"]</x:v>
       </x:c>
       <x:c r="AC242" s="21" t="str">
-        <x:v>["保存等同审核","反复刷新而不查状态"]</x:v>
+        <x:v>["漏填供应商编码","把未说明字段当强制必填"]</x:v>
       </x:c>
       <x:c r="AD242" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -28789,10 +28791,10 @@
       </x:c>
       <x:c r="AF242" s="21" t="str"/>
       <x:c r="AG242" s="21" t="str">
-        <x:v>采购入库—审核、去入库与一键入库</x:v>
+        <x:v>采购入库—供应商与采购单</x:v>
       </x:c>
       <x:c r="AH242" s="21" t="str">
-        <x:v>未审核采购单不能入库。</x:v>
+        <x:v>新建供应商必填供应商编码和名称。</x:v>
       </x:c>
       <x:c r="AI242" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -28836,7 +28838,7 @@
       <x:c r="AV242" s="21" t="str"/>
       <x:c r="AW242" s="21" t="str"/>
       <x:c r="AX242" s="21" t="str">
-        <x:v>审核采购单并选择入库方式</x:v>
+        <x:v>新建供应商与采购单</x:v>
       </x:c>
       <x:c r="AY242" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -28844,7 +28846,7 @@
     </x:row>
     <x:row r="243" ht="46" customHeight="1">
       <x:c r="A243" s="21" t="str">
-        <x:v>WDT-024-B</x:v>
+        <x:v>WDT-024-A</x:v>
       </x:c>
       <x:c r="B243" s="21" t="str">
         <x:v>旺店通-采购</x:v>
@@ -28865,7 +28867,7 @@
         <x:v>场景</x:v>
       </x:c>
       <x:c r="H243" s="21" t="str">
-        <x:v>高</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I243" s="21" t="str">
         <x:v>practice</x:v>
@@ -28883,31 +28885,31 @@
         <x:v>未审核采购单不能入库</x:v>
       </x:c>
       <x:c r="N243" s="21" t="str">
-        <x:v>到货存在短到和残次，需要调整数量与库存属性，应该选择哪种入库方式？</x:v>
+        <x:v>采购单保存后看不到可执行入库，最先应检查什么？</x:v>
       </x:c>
       <x:c r="O243" s="21" t="str">
-        <x:v>先把采购单标记全部到货，再从库存查询改数量</x:v>
+        <x:v>采购单是否填写了预计到货日期</x:v>
       </x:c>
       <x:c r="P243" s="21" t="str">
-        <x:v>选择一键入库，确认后再忽略短到和残次差异</x:v>
+        <x:v>全部货品是否已经维护默认库位</x:v>
       </x:c>
       <x:c r="Q243" s="21" t="str">
-        <x:v>先取消采购单，再按预计数量新建普通入库单</x:v>
+        <x:v>采购单是否已经审核通过</x:v>
       </x:c>
       <x:c r="R243" s="21" t="str">
-        <x:v>选择去入库，进入入库管理按实收编辑后确认</x:v>
+        <x:v>供应商资料是否设置了默认联系人</x:v>
       </x:c>
       <x:c r="S243" s="21" t="str">
-        <x:v>D</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="T243" s="21" t="str">
-        <x:v>选择去入库，进入入库管理按实收编辑后确认</x:v>
+        <x:v>采购单是否已经审核通过</x:v>
       </x:c>
       <x:c r="U243" s="21" t="str">
-        <x:v>去入库会进入可编辑的入库管理，适合有数量或正残差异的收货。</x:v>
+        <x:v>未审核采购单不能进入采购入库流程，审核状态是首要前置。</x:v>
       </x:c>
       <x:c r="V243" s="21" t="str">
-        <x:v>{"A":"错入口：库存查询不能替代收货记录。","B":"错适用：一键入库不适合先有差异后再忽略。","C":"错流程：不应取消正确的采购来源。"}</x:v>
+        <x:v>{"A":"错前置：预计到货日期不是可执行入库的首要状态门槛。","B":"错前置：默认库位便于收货，但不能替代采购单审核。","D":"错前置：默认联系人不决定采购单能否进入入库。"}</x:v>
       </x:c>
       <x:c r="W243" s="21" t="str">
         <x:v>在采购单审核后按实际收货复杂度选择去入库或一键入库。</x:v>
@@ -28928,7 +28930,7 @@
         <x:v>["未审核采购单不能入库","一键入库会直接创建并确认入库，差异收货应优先去入库编辑"]</x:v>
       </x:c>
       <x:c r="AC243" s="21" t="str">
-        <x:v>["有差异仍一键入库","绕过采购来源建普通入库"]</x:v>
+        <x:v>["保存等同审核","反复刷新而不查状态"]</x:v>
       </x:c>
       <x:c r="AD243" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -28941,7 +28943,7 @@
         <x:v>采购入库—审核、去入库与一键入库</x:v>
       </x:c>
       <x:c r="AH243" s="21" t="str">
-        <x:v>去入库进入入库管理并可编辑；一键入库直接按剩余未入库货品入库。</x:v>
+        <x:v>未审核采购单不能入库。</x:v>
       </x:c>
       <x:c r="AI243" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -28993,7 +28995,7 @@
     </x:row>
     <x:row r="244" ht="46" customHeight="1">
       <x:c r="A244" s="21" t="str">
-        <x:v>WDT-025-A</x:v>
+        <x:v>WDT-024-B</x:v>
       </x:c>
       <x:c r="B244" s="21" t="str">
         <x:v>旺店通-采购</x:v>
@@ -29011,73 +29013,73 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G244" s="21" t="str">
-        <x:v>基础</x:v>
+        <x:v>场景</x:v>
       </x:c>
       <x:c r="H244" s="21" t="str">
         <x:v>高</x:v>
       </x:c>
       <x:c r="I244" s="21" t="str">
-        <x:v>redline</x:v>
+        <x:v>practice</x:v>
       </x:c>
       <x:c r="J244" s="22" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K244" s="21" t="str">
-        <x:v>WDT-K025</x:v>
+        <x:v>WDT-K024</x:v>
       </x:c>
       <x:c r="L244" s="21" t="str">
-        <x:v>采购入库确认</x:v>
+        <x:v>采购单审核与入库入口</x:v>
       </x:c>
       <x:c r="M244" s="21" t="str">
-        <x:v>仓库、货品、数量、价格四项一致</x:v>
+        <x:v>未审核采购单不能入库</x:v>
       </x:c>
       <x:c r="N244" s="21" t="str">
-        <x:v>点击采购入库确认前，必须同时核对哪四项？</x:v>
+        <x:v>到货存在短到和残次，需要调整数量与库存属性，应该选择哪种入库方式？</x:v>
       </x:c>
       <x:c r="O244" s="21" t="str">
-        <x:v>仓库、货品、数量、库位</x:v>
+        <x:v>先把采购单标记全部到货，再从库存查询改数量</x:v>
       </x:c>
       <x:c r="P244" s="21" t="str">
-        <x:v>库位、货品、箱数、金额</x:v>
+        <x:v>选择一键入库，确认后再忽略短到和残次差异</x:v>
       </x:c>
       <x:c r="Q244" s="21" t="str">
-        <x:v>仓库、货品、数量、价格</x:v>
+        <x:v>先取消采购单，再按预计数量新建普通入库单</x:v>
       </x:c>
       <x:c r="R244" s="21" t="str">
-        <x:v>仓库、供应商、数量、价格</x:v>
+        <x:v>选择去入库，进入入库管理按实收编辑后确认</x:v>
       </x:c>
       <x:c r="S244" s="21" t="str">
-        <x:v>C</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="T244" s="21" t="str">
-        <x:v>仓库、货品、数量、价格</x:v>
+        <x:v>选择去入库，进入入库管理按实收编辑后确认</x:v>
       </x:c>
       <x:c r="U244" s="21" t="str">
-        <x:v>这四项是资料明确列出的采购入库最终确认对象。</x:v>
+        <x:v>去入库会进入可编辑的入库管理，适合有数量或正残差异的收货。</x:v>
       </x:c>
       <x:c r="V244" s="21" t="str">
-        <x:v>{"A":"错一项：库位替换了价格。","B":"错范围：不是资料列明的四项组合。","D":"错一项：供应商替换了货品。"}</x:v>
+        <x:v>{"A":"错入口：库存查询不能替代收货记录。","B":"错适用：一键入库不适合先有差异后再忽略。","C":"错流程：不应取消正确的采购来源。"}</x:v>
       </x:c>
       <x:c r="W244" s="21" t="str">
-        <x:v>在库存与成本正式生效前拦截错仓、错品、错数和错价。</x:v>
+        <x:v>在采购单审核后按实际收货复杂度选择去入库或一键入库。</x:v>
       </x:c>
       <x:c r="X244" s="21" t="str">
-        <x:v>["采购","采购单","去入库","入库管理","确认入库"]</x:v>
+        <x:v>["采购","采购单","采购单列表"]</x:v>
       </x:c>
       <x:c r="Y244" s="21" t="str">
-        <x:v>["采购单已审核","实际到货已清点"]</x:v>
+        <x:v>["采购单货品、供应商、价格和数量已复核"]</x:v>
       </x:c>
       <x:c r="Z244" s="21" t="str">
-        <x:v>["核对收货仓库","核对系统货品和规格","核对实收数量","核对采购价格","确认入库并查看入库记录"]</x:v>
+        <x:v>["保存并审核采购单","复杂到货选择去入库进入入库管理后编辑","确认无差异时可选择一键入库","检查生成的采购入库单"]</x:v>
       </x:c>
       <x:c r="AA244" s="21" t="str">
-        <x:v>["仓库、货品、数量、价格与实际和采购凭证一致","确认后可在入库记录查到来源"]</x:v>
+        <x:v>["采购单状态为已审核","一键入库仅按剩余未入库货品和库存生成入库单"]</x:v>
       </x:c>
       <x:c r="AB244" s="21" t="str">
-        <x:v>["发现任一不一致应先返回修正，不能先确认再依赖纠错"]</x:v>
+        <x:v>["未审核采购单不能入库","一键入库会直接创建并确认入库，差异收货应优先去入库编辑"]</x:v>
       </x:c>
       <x:c r="AC244" s="21" t="str">
-        <x:v>["漏核仓库","漏核价格"]</x:v>
+        <x:v>["有差异仍一键入库","绕过采购来源建普通入库"]</x:v>
       </x:c>
       <x:c r="AD244" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -29087,10 +29089,10 @@
       </x:c>
       <x:c r="AF244" s="21" t="str"/>
       <x:c r="AG244" s="21" t="str">
-        <x:v>采购入库—最终确认</x:v>
+        <x:v>采购入库—审核、去入库与一键入库</x:v>
       </x:c>
       <x:c r="AH244" s="21" t="str">
-        <x:v>入库前核对仓库、货品、数量、价格。</x:v>
+        <x:v>去入库进入入库管理并可编辑；一键入库直接按剩余未入库货品入库。</x:v>
       </x:c>
       <x:c r="AI244" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -29134,7 +29136,7 @@
       <x:c r="AV244" s="21" t="str"/>
       <x:c r="AW244" s="21" t="str"/>
       <x:c r="AX244" s="21" t="str">
-        <x:v>采购入库前做最终四项复核</x:v>
+        <x:v>审核采购单并选择入库方式</x:v>
       </x:c>
       <x:c r="AY244" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -29142,7 +29144,7 @@
     </x:row>
     <x:row r="245" ht="46" customHeight="1">
       <x:c r="A245" s="21" t="str">
-        <x:v>WDT-025-B</x:v>
+        <x:v>WDT-025-A</x:v>
       </x:c>
       <x:c r="B245" s="21" t="str">
         <x:v>旺店通-采购</x:v>
@@ -29160,16 +29162,16 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G245" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="H245" s="21" t="str">
         <x:v>高</x:v>
       </x:c>
       <x:c r="I245" s="21" t="str">
-        <x:v>practice</x:v>
+        <x:v>redline</x:v>
       </x:c>
       <x:c r="J245" s="22" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K245" s="21" t="str">
         <x:v>WDT-K025</x:v>
@@ -29181,31 +29183,31 @@
         <x:v>仓库、货品、数量、价格四项一致</x:v>
       </x:c>
       <x:c r="N245" s="21" t="str">
-        <x:v>最终复核发现收货仓库选错，但其他三项正确，最稳妥的处理是什么？</x:v>
+        <x:v>点击采购入库确认前，必须同时核对哪四项？</x:v>
       </x:c>
       <x:c r="O245" s="21" t="str">
-        <x:v>先确认入库，再通过仓间调拨转到实际收货仓库</x:v>
+        <x:v>仓库、货品、数量、库位</x:v>
       </x:c>
       <x:c r="P245" s="21" t="str">
-        <x:v>修改系统默认仓库，保留本张入库单选择后确认</x:v>
+        <x:v>库位、货品、箱数、金额</x:v>
       </x:c>
       <x:c r="Q245" s="21" t="str">
-        <x:v>先改为实际收货仓库并重新复核，再确认入库</x:v>
+        <x:v>仓库、货品、数量、价格</x:v>
       </x:c>
       <x:c r="R245" s="21" t="str">
-        <x:v>先按错误仓库确认，再用入库纠错修改收货仓库</x:v>
+        <x:v>仓库、供应商、数量、价格</x:v>
       </x:c>
       <x:c r="S245" s="21" t="str">
         <x:v>C</x:v>
       </x:c>
       <x:c r="T245" s="21" t="str">
-        <x:v>先改为实际收货仓库并重新复核，再确认入库</x:v>
+        <x:v>仓库、货品、数量、价格</x:v>
       </x:c>
       <x:c r="U245" s="21" t="str">
-        <x:v>确认前发现错误应当立即修正，不能故意制造错仓后再依赖后续调整。</x:v>
+        <x:v>这四项是资料明确列出的采购入库最终确认对象。</x:v>
       </x:c>
       <x:c r="V245" s="21" t="str">
-        <x:v>{"A":"错顺序：不应故意先造成错仓再调拨。","B":"错对象：默认仓库不改变本单已选仓库。","D":"错范围：纠错字段不含收货仓库。"}</x:v>
+        <x:v>{"A":"错一项：库位替换了价格。","B":"错范围：不是资料列明的四项组合。","D":"错一项：供应商替换了货品。"}</x:v>
       </x:c>
       <x:c r="W245" s="21" t="str">
         <x:v>在库存与成本正式生效前拦截错仓、错品、错数和错价。</x:v>
@@ -29226,7 +29228,7 @@
         <x:v>["发现任一不一致应先返回修正，不能先确认再依赖纠错"]</x:v>
       </x:c>
       <x:c r="AC245" s="21" t="str">
-        <x:v>["明知错仓仍确认","用库位名称替代仓库"]</x:v>
+        <x:v>["漏核仓库","漏核价格"]</x:v>
       </x:c>
       <x:c r="AD245" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -29239,7 +29241,7 @@
         <x:v>采购入库—最终确认</x:v>
       </x:c>
       <x:c r="AH245" s="21" t="str">
-        <x:v>确认入库前需核对并确保仓库正确。</x:v>
+        <x:v>入库前核对仓库、货品、数量、价格。</x:v>
       </x:c>
       <x:c r="AI245" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -29291,16 +29293,16 @@
     </x:row>
     <x:row r="246" ht="46" customHeight="1">
       <x:c r="A246" s="21" t="str">
-        <x:v>WDT-026-A</x:v>
+        <x:v>WDT-025-B</x:v>
       </x:c>
       <x:c r="B246" s="21" t="str">
-        <x:v>旺店通-客服</x:v>
+        <x:v>旺店通-采购</x:v>
       </x:c>
       <x:c r="C246" s="21" t="str">
-        <x:v>客服</x:v>
+        <x:v>采购</x:v>
       </x:c>
       <x:c r="D246" s="21" t="str">
-        <x:v>售后管理</x:v>
+        <x:v>采购入库</x:v>
       </x:c>
       <x:c r="E246" s="21" t="str">
         <x:v>通用</x:v>
@@ -29309,10 +29311,10 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G246" s="21" t="str">
-        <x:v>基础</x:v>
+        <x:v>场景</x:v>
       </x:c>
       <x:c r="H246" s="21" t="str">
-        <x:v>中</x:v>
+        <x:v>高</x:v>
       </x:c>
       <x:c r="I246" s="21" t="str">
         <x:v>practice</x:v>
@@ -29321,74 +29323,74 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K246" s="21" t="str">
-        <x:v>WDT-K026</x:v>
+        <x:v>WDT-K025</x:v>
       </x:c>
       <x:c r="L246" s="21" t="str">
-        <x:v>售后单查询与状态</x:v>
+        <x:v>采购入库确认</x:v>
       </x:c>
       <x:c r="M246" s="21" t="str">
-        <x:v>先查售后单，再按状态处理</x:v>
+        <x:v>仓库、货品、数量、价格四项一致</x:v>
       </x:c>
       <x:c r="N246" s="21" t="str">
-        <x:v>客服要核对一笔平台售后的当前进度、申请数量和退款金额，正确入口和动作是什么？</x:v>
+        <x:v>最终复核发现收货仓库选错，但其他三项正确，最稳妥的处理是什么？</x:v>
       </x:c>
       <x:c r="O246" s="21" t="str">
-        <x:v>进入售后→售后单，只核对退货物流并以签收状态代替售后状态</x:v>
+        <x:v>先确认入库，再通过仓间调拨转到实际收货仓库</x:v>
       </x:c>
       <x:c r="P246" s="21" t="str">
-        <x:v>进入售后→售后设置，核对店铺策略并以启用状态代替单笔状态</x:v>
+        <x:v>修改系统默认仓库，保留本张入库单选择后确认</x:v>
       </x:c>
       <x:c r="Q246" s="21" t="str">
-        <x:v>进入售后→售后单，筛选目标记录并核对申请状态、数量和金额</x:v>
+        <x:v>先改为实际收货仓库并重新复核，再确认入库</x:v>
       </x:c>
       <x:c r="R246" s="21" t="str">
-        <x:v>进入售后→智能退货入库，扫描订单并以收货状态代替售后状态</x:v>
+        <x:v>先按错误仓库确认，再用入库纠错修改收货仓库</x:v>
       </x:c>
       <x:c r="S246" s="21" t="str">
         <x:v>C</x:v>
       </x:c>
       <x:c r="T246" s="21" t="str">
-        <x:v>进入售后→售后单，筛选目标记录并核对申请状态、数量和金额</x:v>
+        <x:v>先改为实际收货仓库并重新复核，再确认入库</x:v>
       </x:c>
       <x:c r="U246" s="21" t="str">
-        <x:v>售后单列表是统一查询平台售后的入口，可直接查看状态、申请数量和金额。</x:v>
+        <x:v>确认前发现错误应当立即修正，不能故意制造错仓后再依赖后续调整。</x:v>
       </x:c>
       <x:c r="V246" s="21" t="str">
-        <x:v>{"A":"错口径：物流签收不能替代售后状态、申请数量和金额核对。","B":"错对象：策略启用状态不能代表某一笔售后的处理进度。","D":"错入口：智能退货入库只反映退货收货，不是售后全量查询。"}</x:v>
+        <x:v>{"A":"错顺序：不应故意先造成错仓再调拨。","B":"错对象：默认仓库不改变本单已选仓库。","D":"错范围：纠错字段不含收货仓库。"}</x:v>
       </x:c>
       <x:c r="W246" s="21" t="str">
-        <x:v>从统一售后入口核对平台售后进度、申请数量和金额，避免漏处理或重复处理。</x:v>
+        <x:v>在库存与成本正式生效前拦截错仓、错品、错数和错价。</x:v>
       </x:c>
       <x:c r="X246" s="21" t="str">
-        <x:v>["售后","售后单"]</x:v>
+        <x:v>["采购","采购单","去入库","入库管理","确认入库"]</x:v>
       </x:c>
       <x:c r="Y246" s="21" t="str">
-        <x:v>["平台售后数据已同步到 ERP","已明确要查询的店铺、平台订单或售后状态"]</x:v>
+        <x:v>["采购单已审核","实际到货已清点"]</x:v>
       </x:c>
       <x:c r="Z246" s="21" t="str">
-        <x:v>["进入售后单列表","按条件筛选目标售后","核对售后类型、状态、申请数量和金额","需要追溯时查看日志并补充售后备注","按当前状态执行后续动作"]</x:v>
+        <x:v>["核对收货仓库","核对系统货品和规格","核对实收数量","核对采购价格","确认入库并查看入库记录"]</x:v>
       </x:c>
       <x:c r="AA246" s="21" t="str">
-        <x:v>["已定位到唯一目标售后单","处理动作与当前售后状态一致","日志或备注能说明本次处理结果"]</x:v>
+        <x:v>["仓库、货品、数量、价格与实际和采购凭证一致","确认后可在入库记录查到来源"]</x:v>
       </x:c>
       <x:c r="AB246" s="21" t="str">
-        <x:v>["单笔售后可执行退款上传、查看日志、填写售后备注或创建售后等动作，具体可用动作以当前状态为准"]</x:v>
+        <x:v>["发现任一不一致应先返回修正，不能先确认再依赖纠错"]</x:v>
       </x:c>
       <x:c r="AC246" s="21" t="str">
-        <x:v>["从智能退货入库反查所有售后","只看原订单状态判断售后进度"]</x:v>
+        <x:v>["明知错仓仍确认","用库位名称替代仓库"]</x:v>
       </x:c>
       <x:c r="AD246" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
       </x:c>
       <x:c r="AE246" s="21" t="str">
-        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/lfgmgszg7muigf79</x:v>
+        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/ncmtzsrt12cpbnq5</x:v>
       </x:c>
       <x:c r="AF246" s="21" t="str"/>
       <x:c r="AG246" s="21" t="str">
-        <x:v>售后单—查询与单笔操作</x:v>
+        <x:v>采购入库—最终确认</x:v>
       </x:c>
       <x:c r="AH246" s="21" t="str">
-        <x:v>售后→售后单可实时查看各平台售后状态、申请数量和金额。</x:v>
+        <x:v>确认入库前需核对并确保仓库正确。</x:v>
       </x:c>
       <x:c r="AI246" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -29432,7 +29434,7 @@
       <x:c r="AV246" s="21" t="str"/>
       <x:c r="AW246" s="21" t="str"/>
       <x:c r="AX246" s="21" t="str">
-        <x:v>集中查询售后单并识别处理状态</x:v>
+        <x:v>采购入库前做最终四项复核</x:v>
       </x:c>
       <x:c r="AY246" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -29440,7 +29442,7 @@
     </x:row>
     <x:row r="247" ht="46" customHeight="1">
       <x:c r="A247" s="21" t="str">
-        <x:v>WDT-026-B</x:v>
+        <x:v>WDT-026-A</x:v>
       </x:c>
       <x:c r="B247" s="21" t="str">
         <x:v>旺店通-客服</x:v>
@@ -29458,7 +29460,7 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G247" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="H247" s="21" t="str">
         <x:v>中</x:v>
@@ -29479,31 +29481,31 @@
         <x:v>先查售后单，再按状态处理</x:v>
       </x:c>
       <x:c r="N247" s="21" t="str">
-        <x:v>客服已找到目标售后单，想追溯此前处理并留下本次结论，哪组操作最合适？</x:v>
+        <x:v>客服要核对一笔平台售后的当前进度、申请数量和退款金额，正确入口和动作是什么？</x:v>
       </x:c>
       <x:c r="O247" s="21" t="str">
-        <x:v>先新建一张系统售后，再把原售后备注复制到新记录</x:v>
+        <x:v>进入售后→售后单，只核对退货物流并以签收状态代替售后状态</x:v>
       </x:c>
       <x:c r="P247" s="21" t="str">
-        <x:v>先查看售后日志，再填写售后备注记录本次处理结论</x:v>
+        <x:v>进入售后→售后设置，核对店铺策略并以启用状态代替单笔状态</x:v>
       </x:c>
       <x:c r="Q247" s="21" t="str">
-        <x:v>先查看原订单日志，再只在订单客服备注记录本次结论</x:v>
+        <x:v>进入售后→售后单，筛选目标记录并核对申请状态、数量和金额</x:v>
       </x:c>
       <x:c r="R247" s="21" t="str">
-        <x:v>先执行退款上传，再查看售后日志判断此前是否处理过</x:v>
+        <x:v>进入售后→智能退货入库，扫描订单并以收货状态代替售后状态</x:v>
       </x:c>
       <x:c r="S247" s="21" t="str">
-        <x:v>B</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="T247" s="21" t="str">
-        <x:v>先查看售后日志，再填写售后备注记录本次处理结论</x:v>
+        <x:v>进入售后→售后单，筛选目标记录并核对申请状态、数量和金额</x:v>
       </x:c>
       <x:c r="U247" s="21" t="str">
-        <x:v>售后单支持查看日志和填写售后备注，两者分别用于追溯过程和记录当前处理。</x:v>
+        <x:v>售后单列表是统一查询平台售后的入口，可直接查看状态、申请数量和金额。</x:v>
       </x:c>
       <x:c r="V247" s="21" t="str">
-        <x:v>{"A":"错动作：已有售后不应为记录结论重复新建系统售后。","C":"错记录位置：订单日志和客服备注不能完整替代售后日志与售后备注。","D":"错顺序：应先追溯日志，避免重复执行退款上传。"}</x:v>
+        <x:v>{"A":"错口径：物流签收不能替代售后状态、申请数量和金额核对。","B":"错对象：策略启用状态不能代表某一笔售后的处理进度。","D":"错入口：智能退货入库只反映退货收货，不是售后全量查询。"}</x:v>
       </x:c>
       <x:c r="W247" s="21" t="str">
         <x:v>从统一售后入口核对平台售后进度、申请数量和金额，避免漏处理或重复处理。</x:v>
@@ -29524,7 +29526,7 @@
         <x:v>["单笔售后可执行退款上传、查看日志、填写售后备注或创建售后等动作，具体可用动作以当前状态为准"]</x:v>
       </x:c>
       <x:c r="AC247" s="21" t="str">
-        <x:v>["用原订单备注替代售后记录","未追溯日志就重复执行退款动作"]</x:v>
+        <x:v>["从智能退货入库反查所有售后","只看原订单状态判断售后进度"]</x:v>
       </x:c>
       <x:c r="AD247" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -29537,7 +29539,7 @@
         <x:v>售后单—查询与单笔操作</x:v>
       </x:c>
       <x:c r="AH247" s="21" t="str">
-        <x:v>售后单的单笔操作包含查看日志和填写售后备注。</x:v>
+        <x:v>售后→售后单可实时查看各平台售后状态、申请数量和金额。</x:v>
       </x:c>
       <x:c r="AI247" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -29589,7 +29591,7 @@
     </x:row>
     <x:row r="248" ht="46" customHeight="1">
       <x:c r="A248" s="21" t="str">
-        <x:v>WDT-027-A</x:v>
+        <x:v>WDT-026-B</x:v>
       </x:c>
       <x:c r="B248" s="21" t="str">
         <x:v>旺店通-客服</x:v>
@@ -29607,73 +29609,73 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G248" s="21" t="str">
-        <x:v>基础</x:v>
+        <x:v>场景</x:v>
       </x:c>
       <x:c r="H248" s="21" t="str">
-        <x:v>高</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I248" s="21" t="str">
-        <x:v>redline</x:v>
+        <x:v>practice</x:v>
       </x:c>
       <x:c r="J248" s="22" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K248" s="21" t="str">
-        <x:v>WDT-K027</x:v>
+        <x:v>WDT-K026</x:v>
       </x:c>
       <x:c r="L248" s="21" t="str">
-        <x:v>自动退款总设置</x:v>
+        <x:v>售后单查询与状态</x:v>
       </x:c>
       <x:c r="M248" s="21" t="str">
-        <x:v>平台策略与 ERP 设置必须同时匹配</x:v>
+        <x:v>先查售后单，再按状态处理</x:v>
       </x:c>
       <x:c r="N248" s="21" t="str">
-        <x:v>管理员已在平台端建好自动退款策略，客服在旺店通还应在哪里完成 ERP 侧设置？</x:v>
+        <x:v>客服已找到目标售后单，想追溯此前处理并留下本次结论，哪组操作最合适？</x:v>
       </x:c>
       <x:c r="O248" s="21" t="str">
-        <x:v>售后→智能退货入库→入库设置，开启自动退款并选择收货仓库</x:v>
+        <x:v>先新建一张系统售后，再把原售后备注复制到新记录</x:v>
       </x:c>
       <x:c r="P248" s="21" t="str">
-        <x:v>售后→售后管理→售后设置，只开启下载换货单并配置店铺</x:v>
+        <x:v>先查看售后日志，再填写售后备注记录本次处理结论</x:v>
       </x:c>
       <x:c r="Q248" s="21" t="str">
-        <x:v>售后→售后管理→售后设置，开启自动退款并配置策略和店铺</x:v>
+        <x:v>先查看原订单日志，再只在订单客服备注记录本次结论</x:v>
       </x:c>
       <x:c r="R248" s="21" t="str">
-        <x:v>售后→售后单→批量操作，开启自动退款并选择当前售后</x:v>
+        <x:v>先执行退款上传，再查看售后日志判断此前是否处理过</x:v>
       </x:c>
       <x:c r="S248" s="21" t="str">
-        <x:v>C</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="T248" s="21" t="str">
-        <x:v>售后→售后管理→售后设置，开启自动退款并配置策略和店铺</x:v>
+        <x:v>先查看售后日志，再填写售后备注记录本次处理结论</x:v>
       </x:c>
       <x:c r="U248" s="21" t="str">
-        <x:v>自动退款的 ERP 总设置位于售后管理的售后设置中，需同时限定策略和店铺。</x:v>
+        <x:v>售后单支持查看日志和填写售后备注，两者分别用于追溯过程和记录当前处理。</x:v>
       </x:c>
       <x:c r="V248" s="21" t="str">
-        <x:v>{"A":"错入口：智能退货入库负责收货，不配置自动退款总策略。","B":"错开关：下载换货单不等于开启自动退款。","D":"错层级：单笔售后操作不能替代 ERP 自动退款总设置。"}</x:v>
+        <x:v>{"A":"错动作：已有售后不应为记录结论重复新建系统售后。","C":"错记录位置：订单日志和客服备注不能完整替代售后日志与售后备注。","D":"错顺序：应先追溯日志，避免重复执行退款上传。"}</x:v>
       </x:c>
       <x:c r="W248" s="21" t="str">
-        <x:v>在店铺和策略范围准确的前提下启用自动退款，减少人工退款并避免误退。</x:v>
+        <x:v>从统一售后入口核对平台售后进度、申请数量和金额，避免漏处理或重复处理。</x:v>
       </x:c>
       <x:c r="X248" s="21" t="str">
-        <x:v>["售后","售后管理","售后设置"]</x:v>
+        <x:v>["售后","售后单"]</x:v>
       </x:c>
       <x:c r="Y248" s="21" t="str">
-        <x:v>["目标平台已建立对应自动退款策略","已确认允许自动退款的店铺和业务场景"]</x:v>
+        <x:v>["平台售后数据已同步到 ERP","已明确要查询的店铺、平台订单或售后状态"]</x:v>
       </x:c>
       <x:c r="Z248" s="21" t="str">
-        <x:v>["进入售后设置","开启自动退款","选择对应退款策略","限定适用店铺","结合平台端策略验证测试单"]</x:v>
+        <x:v>["进入售后单列表","按条件筛选目标售后","核对售后类型、状态、申请数量和金额","需要追溯时查看日志并补充售后备注","按当前状态执行后续动作"]</x:v>
       </x:c>
       <x:c r="AA248" s="21" t="str">
-        <x:v>["ERP 自动退款开关已开启","策略与店铺范围和平台端配置一致","测试售后满足条件时可正常触发"]</x:v>
+        <x:v>["已定位到唯一目标售后单","处理动作与当前售后状态一致","日志或备注能说明本次处理结果"]</x:v>
       </x:c>
       <x:c r="AB248" s="21" t="str">
-        <x:v>["资料虽提到视频号支持自动退款，但未给出视频号平台端的细分配置步骤，实际配置应先向管理员或旺店通支持确认，不得套用其他平台路径"]</x:v>
+        <x:v>["单笔售后可执行退款上传、查看日志、填写售后备注或创建售后等动作，具体可用动作以当前状态为准"]</x:v>
       </x:c>
       <x:c r="AC248" s="21" t="str">
-        <x:v>["误在订单审核中配置退款","只启用开关而漏选店铺"]</x:v>
+        <x:v>["用原订单备注替代售后记录","未追溯日志就重复执行退款动作"]</x:v>
       </x:c>
       <x:c r="AD248" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -29683,10 +29685,10 @@
       </x:c>
       <x:c r="AF248" s="21" t="str"/>
       <x:c r="AG248" s="21" t="str">
-        <x:v>售后设置—自动退款总配置</x:v>
+        <x:v>售后单—查询与单笔操作</x:v>
       </x:c>
       <x:c r="AH248" s="21" t="str">
-        <x:v>售后→售后管理→售后设置：开启自动退款，设置策略和店铺。</x:v>
+        <x:v>售后单的单笔操作包含查看日志和填写售后备注。</x:v>
       </x:c>
       <x:c r="AI248" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -29730,7 +29732,7 @@
       <x:c r="AV248" s="21" t="str"/>
       <x:c r="AW248" s="21" t="str"/>
       <x:c r="AX248" s="21" t="str">
-        <x:v>配置自动退款的 ERP 总开关与范围</x:v>
+        <x:v>集中查询售后单并识别处理状态</x:v>
       </x:c>
       <x:c r="AY248" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -29738,7 +29740,7 @@
     </x:row>
     <x:row r="249" ht="46" customHeight="1">
       <x:c r="A249" s="21" t="str">
-        <x:v>WDT-027-B</x:v>
+        <x:v>WDT-027-A</x:v>
       </x:c>
       <x:c r="B249" s="21" t="str">
         <x:v>旺店通-客服</x:v>
@@ -29756,16 +29758,16 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G249" s="21" t="str">
-        <x:v>进阶</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="H249" s="21" t="str">
         <x:v>高</x:v>
       </x:c>
       <x:c r="I249" s="21" t="str">
-        <x:v>practice</x:v>
+        <x:v>redline</x:v>
       </x:c>
       <x:c r="J249" s="22" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K249" s="21" t="str">
         <x:v>WDT-K027</x:v>
@@ -29777,31 +29779,31 @@
         <x:v>平台策略与 ERP 设置必须同时匹配</x:v>
       </x:c>
       <x:c r="N249" s="21" t="str">
-        <x:v>ERP 已开启自动退款，但一笔符合售后类型的申请仍未触发，第一轮核对应覆盖哪组条件？</x:v>
+        <x:v>管理员已在平台端建好自动退款策略，客服在旺店通还应在哪里完成 ERP 侧设置？</x:v>
       </x:c>
       <x:c r="O249" s="21" t="str">
-        <x:v>只核对平台退款策略已启用，不再检查 ERP 开关和策略选择</x:v>
+        <x:v>售后→智能退货入库→入库设置，开启自动退款并选择收货仓库</x:v>
       </x:c>
       <x:c r="P249" s="21" t="str">
-        <x:v>同时核对平台策略、ERP 自动退款开关、策略选择和适用店铺</x:v>
+        <x:v>售后→售后管理→售后设置，只开启下载换货单并配置店铺</x:v>
       </x:c>
       <x:c r="Q249" s="21" t="str">
-        <x:v>只核对 ERP 自动退款开关已开启，不再检查平台策略和店铺范围</x:v>
+        <x:v>售后→售后管理→售后设置，开启自动退款并配置策略和店铺</x:v>
       </x:c>
       <x:c r="R249" s="21" t="str">
-        <x:v>只核对 ERP 中选择了同名策略，不再检查适用店铺和平台条件</x:v>
+        <x:v>售后→售后单→批量操作，开启自动退款并选择当前售后</x:v>
       </x:c>
       <x:c r="S249" s="21" t="str">
-        <x:v>B</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="T249" s="21" t="str">
-        <x:v>同时核对平台策略、ERP 自动退款开关、策略选择和适用店铺</x:v>
+        <x:v>售后→售后管理→售后设置，开启自动退款并配置策略和店铺</x:v>
       </x:c>
       <x:c r="U249" s="21" t="str">
-        <x:v>自动退款依赖平台端和 ERP 端共同配置，任一环节缺失或范围不匹配都会导致不触发。</x:v>
+        <x:v>自动退款的 ERP 总设置位于售后管理的售后设置中，需同时限定策略和店铺。</x:v>
       </x:c>
       <x:c r="V249" s="21" t="str">
-        <x:v>{"A":"核对不完整：平台策略启用后仍需检查 ERP 配置。","C":"核对不完整：ERP 开关不能替代平台策略和店铺范围。","D":"核对不完整：策略名称相同也要核对店铺与平台条件。"}</x:v>
+        <x:v>{"A":"错入口：智能退货入库负责收货，不配置自动退款总策略。","B":"错开关：下载换货单不等于开启自动退款。","D":"错层级：单笔售后操作不能替代 ERP 自动退款总设置。"}</x:v>
       </x:c>
       <x:c r="W249" s="21" t="str">
         <x:v>在店铺和策略范围准确的前提下启用自动退款，减少人工退款并避免误退。</x:v>
@@ -29822,7 +29824,7 @@
         <x:v>["资料虽提到视频号支持自动退款，但未给出视频号平台端的细分配置步骤，实际配置应先向管理员或旺店通支持确认，不得套用其他平台路径"]</x:v>
       </x:c>
       <x:c r="AC249" s="21" t="str">
-        <x:v>["只检查 ERP 不检查平台策略","只检查平台策略不检查适用店铺"]</x:v>
+        <x:v>["误在订单审核中配置退款","只启用开关而漏选店铺"]</x:v>
       </x:c>
       <x:c r="AD249" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -29835,7 +29837,7 @@
         <x:v>售后设置—自动退款总配置</x:v>
       </x:c>
       <x:c r="AH249" s="21" t="str">
-        <x:v>自动退款需要平台端策略与 ERP 端开关、策略、店铺范围相互匹配。</x:v>
+        <x:v>售后→售后管理→售后设置：开启自动退款，设置策略和店铺。</x:v>
       </x:c>
       <x:c r="AI249" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -29887,7 +29889,7 @@
     </x:row>
     <x:row r="250" ht="46" customHeight="1">
       <x:c r="A250" s="21" t="str">
-        <x:v>WDT-028-A</x:v>
+        <x:v>WDT-027-B</x:v>
       </x:c>
       <x:c r="B250" s="21" t="str">
         <x:v>旺店通-客服</x:v>
@@ -29896,16 +29898,16 @@
         <x:v>客服</x:v>
       </x:c>
       <x:c r="D250" s="21" t="str">
-        <x:v>售后自动退款</x:v>
+        <x:v>售后管理</x:v>
       </x:c>
       <x:c r="E250" s="21" t="str">
-        <x:v>拼多多</x:v>
+        <x:v>通用</x:v>
       </x:c>
       <x:c r="F250" s="21" t="str">
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G250" s="21" t="str">
-        <x:v>基础</x:v>
+        <x:v>进阶</x:v>
       </x:c>
       <x:c r="H250" s="21" t="str">
         <x:v>高</x:v>
@@ -29917,61 +29919,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K250" s="21" t="str">
-        <x:v>WDT-K028</x:v>
+        <x:v>WDT-K027</x:v>
       </x:c>
       <x:c r="L250" s="21" t="str">
-        <x:v>拼多多退货入库自动退</x:v>
+        <x:v>自动退款总设置</x:v>
       </x:c>
       <x:c r="M250" s="21" t="str">
-        <x:v>退货入库成功后再自动退款</x:v>
+        <x:v>平台策略与 ERP 设置必须同时匹配</x:v>
       </x:c>
       <x:c r="N250" s="21" t="str">
-        <x:v>配置拼多多退货入库自动退款时，平台策略应采用哪组关键设置？</x:v>
+        <x:v>ERP 已开启自动退款，但一笔符合售后类型的申请仍未触发，第一轮核对应覆盖哪组条件？</x:v>
       </x:c>
       <x:c r="O250" s="21" t="str">
-        <x:v>创建退货成功自动退，触发选退货入库成功，应用选旺店通 ERP</x:v>
+        <x:v>只核对平台退款策略已启用，不再检查 ERP 开关和策略选择</x:v>
       </x:c>
       <x:c r="P250" s="21" t="str">
-        <x:v>创建换货完成自动退，触发选换货单已发货，应用选旺店通 ERP</x:v>
+        <x:v>同时核对平台策略、ERP 自动退款开关、策略选择和适用店铺</x:v>
       </x:c>
       <x:c r="Q250" s="21" t="str">
-        <x:v>创建取消发货自动退，触发选订单审核成功，应用选旺店通 ERP</x:v>
+        <x:v>只核对 ERP 自动退款开关已开启，不再检查平台策略和店铺范围</x:v>
       </x:c>
       <x:c r="R250" s="21" t="str">
-        <x:v>创建退货成功自动退，触发选买家寄件成功，应用选平台默认仓库</x:v>
+        <x:v>只核对 ERP 中选择了同名策略，不再检查适用店铺和平台条件</x:v>
       </x:c>
       <x:c r="S250" s="21" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="T250" s="21" t="str">
-        <x:v>创建退货成功自动退，触发选退货入库成功，应用选旺店通 ERP</x:v>
+        <x:v>同时核对平台策略、ERP 自动退款开关、策略选择和适用店铺</x:v>
       </x:c>
       <x:c r="U250" s="21" t="str">
-        <x:v>资料指定平台策略为退货成功自动退，触发节点是退货入库成功，并选择旺店通 ERP。</x:v>
+        <x:v>自动退款依赖平台端和 ERP 端共同配置，任一环节缺失或范围不匹配都会导致不触发。</x:v>
       </x:c>
       <x:c r="V250" s="21" t="str">
-        <x:v>{"B":"错售后类型：换货完成不是退货退款触发。","C":"错策略和节点：取消发货不是退货入库。","D":"错节点和应用：资料要求入库成功且应用为旺店通 ERP。"}</x:v>
+        <x:v>{"A":"核对不完整：平台策略启用后仍需检查 ERP 配置。","C":"核对不完整：ERP 开关不能替代平台策略和店铺范围。","D":"核对不完整：策略名称相同也要核对店铺与平台条件。"}</x:v>
       </x:c>
       <x:c r="W250" s="21" t="str">
-        <x:v>让满足策略的拼多多退货在旺店通收货入库后自动确认退款，降低人工处理时长。</x:v>
+        <x:v>在店铺和策略范围准确的前提下启用自动退款，减少人工退款并避免误退。</x:v>
       </x:c>
       <x:c r="X250" s="21" t="str">
-        <x:v>["拼多多平台后台","自动退款策略","退货成功自动退"]</x:v>
+        <x:v>["售后","售后管理","售后设置"]</x:v>
       </x:c>
       <x:c r="Y250" s="21" t="str">
-        <x:v>["拼多多平台已创建并启用退货成功自动退策略","策略触发节点选择退货入库成功","应用选择旺店通 ERP","ERP 已开启相应自动退款"]</x:v>
+        <x:v>["目标平台已建立对应自动退款策略","已确认允许自动退款的店铺和业务场景"]</x:v>
       </x:c>
       <x:c r="Z250" s="21" t="str">
-        <x:v>["在平台新建退货成功自动退策略","选择退货入库成功并指定旺店通 ERP","启用平台策略","在 ERP 选择全部收货或部分及全部收货的触发口径","用智能退货入库完成收货并观察自动退款结果"]</x:v>
+        <x:v>["进入售后设置","开启自动退款","选择对应退款策略","限定适用店铺","结合平台端策略验证测试单"]</x:v>
       </x:c>
       <x:c r="AA250" s="21" t="str">
-        <x:v>["策略处于启用状态","退货收货达到 ERP 配置口径后平台自动确认退款","售后日志能看到处理结果"]</x:v>
+        <x:v>["ERP 自动退款开关已开启","策略与店铺范围和平台端配置一致","测试售后满足条件时可正常触发"]</x:v>
       </x:c>
       <x:c r="AB250" s="21" t="str">
-        <x:v>["未创建或未启用平台策略时，ERP 完成退货入库也可能无法自动退款"]</x:v>
+        <x:v>["资料虽提到视频号支持自动退款，但未给出视频号平台端的细分配置步骤，实际配置应先向管理员或旺店通支持确认，不得套用其他平台路径"]</x:v>
       </x:c>
       <x:c r="AC250" s="21" t="str">
-        <x:v>["把买家寄件当成入库成功","把取消发货策略用于退货入库"]</x:v>
+        <x:v>["只检查 ERP 不检查平台策略","只检查平台策略不检查适用店铺"]</x:v>
       </x:c>
       <x:c r="AD250" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -29981,10 +29983,10 @@
       </x:c>
       <x:c r="AF250" s="21" t="str"/>
       <x:c r="AG250" s="21" t="str">
-        <x:v>拼多多—退货入库成功自动退款</x:v>
+        <x:v>售后设置—自动退款总配置</x:v>
       </x:c>
       <x:c r="AH250" s="21" t="str">
-        <x:v>拼多多平台创建退货成功自动退，选择退货入库成功与旺店通 ERP。</x:v>
+        <x:v>自动退款需要平台端策略与 ERP 端开关、策略、店铺范围相互匹配。</x:v>
       </x:c>
       <x:c r="AI250" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -30028,7 +30030,7 @@
       <x:c r="AV250" s="21" t="str"/>
       <x:c r="AW250" s="21" t="str"/>
       <x:c r="AX250" s="21" t="str">
-        <x:v>配置拼多多退货入库自动退款</x:v>
+        <x:v>配置自动退款的 ERP 总开关与范围</x:v>
       </x:c>
       <x:c r="AY250" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -30036,7 +30038,7 @@
     </x:row>
     <x:row r="251" ht="46" customHeight="1">
       <x:c r="A251" s="21" t="str">
-        <x:v>WDT-028-B</x:v>
+        <x:v>WDT-028-A</x:v>
       </x:c>
       <x:c r="B251" s="21" t="str">
         <x:v>旺店通-客服</x:v>
@@ -30054,7 +30056,7 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G251" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="H251" s="21" t="str">
         <x:v>高</x:v>
@@ -30075,31 +30077,31 @@
         <x:v>退货入库成功后再自动退款</x:v>
       </x:c>
       <x:c r="N251" s="21" t="str">
-        <x:v>平台策略和 ERP 自动退款均已启用后，哪一步会按所选收货口径推动拼多多自动退款？</x:v>
+        <x:v>配置拼多多退货入库自动退款时，平台策略应采用哪组关键设置？</x:v>
       </x:c>
       <x:c r="O251" s="21" t="str">
-        <x:v>在智能退货入库完成收货，使退货达到全部或已配置的部分收货口径</x:v>
+        <x:v>创建退货成功自动退，触发选退货入库成功，应用选旺店通 ERP</x:v>
       </x:c>
       <x:c r="P251" s="21" t="str">
-        <x:v>在售后单执行退款上传，不核对智能退货是否达到所设收货口径</x:v>
+        <x:v>创建换货完成自动退，触发选换货单已发货，应用选旺店通 ERP</x:v>
       </x:c>
       <x:c r="Q251" s="21" t="str">
-        <x:v>在售后设置只选择部分收货口径，不实际完成本次退货收货</x:v>
+        <x:v>创建取消发货自动退，触发选订单审核成功，应用选旺店通 ERP</x:v>
       </x:c>
       <x:c r="R251" s="21" t="str">
-        <x:v>在拼多多把售后改为买家已寄回，不等待 ERP 生成退货入库结果</x:v>
+        <x:v>创建退货成功自动退，触发选买家寄件成功，应用选平台默认仓库</x:v>
       </x:c>
       <x:c r="S251" s="21" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="T251" s="21" t="str">
-        <x:v>在智能退货入库完成收货，使退货达到全部或已配置的部分收货口径</x:v>
+        <x:v>创建退货成功自动退，触发选退货入库成功，应用选旺店通 ERP</x:v>
       </x:c>
       <x:c r="U251" s="21" t="str">
-        <x:v>拼多多退货自动退款以退货入库成功为触发，ERP 可配置全部收货或部分及全部收货口径。</x:v>
+        <x:v>资料指定平台策略为退货成功自动退，触发节点是退货入库成功，并选择旺店通 ERP。</x:v>
       </x:c>
       <x:c r="V251" s="21" t="str">
-        <x:v>{"B":"错动作：退款上传属于人工动作，不能证明自动触发链路生效。","C":"缺触发结果：只选口径但未完成实际收货不会形成入库成功。","D":"错节点：买家寄回不等于 ERP 退货入库成功。"}</x:v>
+        <x:v>{"B":"错售后类型：换货完成不是退货退款触发。","C":"错策略和节点：取消发货不是退货入库。","D":"错节点和应用：资料要求入库成功且应用为旺店通 ERP。"}</x:v>
       </x:c>
       <x:c r="W251" s="21" t="str">
         <x:v>让满足策略的拼多多退货在旺店通收货入库后自动确认退款，降低人工处理时长。</x:v>
@@ -30120,7 +30122,7 @@
         <x:v>["未创建或未启用平台策略时，ERP 完成退货入库也可能无法自动退款"]</x:v>
       </x:c>
       <x:c r="AC251" s="21" t="str">
-        <x:v>["用采购入库代替售后退货入库","未达到设定收货口径就判断策略失效"]</x:v>
+        <x:v>["把买家寄件当成入库成功","把取消发货策略用于退货入库"]</x:v>
       </x:c>
       <x:c r="AD251" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -30133,7 +30135,7 @@
         <x:v>拼多多—退货入库成功自动退款</x:v>
       </x:c>
       <x:c r="AH251" s="21" t="str">
-        <x:v>智能退货入库达到 ERP 设置的收货口径后，可推动平台自动确认退款。</x:v>
+        <x:v>拼多多平台创建退货成功自动退，选择退货入库成功与旺店通 ERP。</x:v>
       </x:c>
       <x:c r="AI251" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -30185,7 +30187,7 @@
     </x:row>
     <x:row r="252" ht="46" customHeight="1">
       <x:c r="A252" s="21" t="str">
-        <x:v>WDT-029-A</x:v>
+        <x:v>WDT-028-B</x:v>
       </x:c>
       <x:c r="B252" s="21" t="str">
         <x:v>旺店通-客服</x:v>
@@ -30215,61 +30217,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K252" s="21" t="str">
-        <x:v>WDT-K029</x:v>
+        <x:v>WDT-K028</x:v>
       </x:c>
       <x:c r="L252" s="21" t="str">
-        <x:v>拼多多取消发货自动退</x:v>
+        <x:v>拼多多退货入库自动退</x:v>
       </x:c>
       <x:c r="M252" s="21" t="str">
-        <x:v>取消发货原因必须命中平台策略</x:v>
+        <x:v>退货入库成功后再自动退款</x:v>
       </x:c>
       <x:c r="N252" s="21" t="str">
-        <x:v>要让拼多多未发货订单在 ERP 取消后自动退款，正确的成套配置是什么？</x:v>
+        <x:v>平台策略和 ERP 自动退款均已启用后，哪一步会按所选收货口径推动拼多多自动退款？</x:v>
       </x:c>
       <x:c r="O252" s="21" t="str">
-        <x:v>平台创建取消发货策略但保持停用，ERP 开启未发货自动退款</x:v>
+        <x:v>在智能退货入库完成收货，使退货达到全部或已配置的部分收货口径</x:v>
       </x:c>
       <x:c r="P252" s="21" t="str">
-        <x:v>平台创建退货入库自动退但不选原因，ERP 开启已发货自动退款</x:v>
+        <x:v>在售后单执行退款上传，不核对智能退货是否达到所设收货口径</x:v>
       </x:c>
       <x:c r="Q252" s="21" t="str">
-        <x:v>平台只选择退款原因但不创建策略，ERP 开启未发货自动退款</x:v>
+        <x:v>在售后设置只选择部分收货口径，不实际完成本次退货收货</x:v>
       </x:c>
       <x:c r="R252" s="21" t="str">
-        <x:v>平台启用erp取消发货自动退并选原因，ERP开未发货自动退款</x:v>
+        <x:v>在拼多多把售后改为买家已寄回，不等待 ERP 生成退货入库结果</x:v>
       </x:c>
       <x:c r="S252" s="21" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="T252" s="21" t="str">
-        <x:v>平台启用erp取消发货自动退并选原因，ERP开未发货自动退款</x:v>
+        <x:v>在智能退货入库完成收货，使退货达到全部或已配置的部分收货口径</x:v>
       </x:c>
       <x:c r="U252" s="21" t="str">
-        <x:v>平台策略、适用原因和 ERP 未发货自动退款缺一不可。</x:v>
+        <x:v>拼多多退货自动退款以退货入库成功为触发，ERP 可配置全部收货或部分及全部收货口径。</x:v>
       </x:c>
       <x:c r="V252" s="21" t="str">
-        <x:v>{"A":"错状态：策略停用时不会按其自动处理。","B":"错策略和场景：退货入库不等于取消未发货。","C":"缺少策略：只选原因不能形成触发规则。"}</x:v>
+        <x:v>{"B":"错动作：退款上传属于人工动作，不能证明自动触发链路生效。","C":"缺触发结果：只选口径但未完成实际收货不会形成入库成功。","D":"错节点：买家寄回不等于 ERP 退货入库成功。"}</x:v>
       </x:c>
       <x:c r="W252" s="21" t="str">
-        <x:v>让 ERP 中未发货订单取消后，按平台允许的退款原因自动处理，减少仓内拦截后的人工退款。</x:v>
+        <x:v>让满足策略的拼多多退货在旺店通收货入库后自动确认退款，降低人工处理时长。</x:v>
       </x:c>
       <x:c r="X252" s="21" t="str">
-        <x:v>["拼多多平台后台","自动退款策略","erp取消发货自动退"]</x:v>
+        <x:v>["拼多多平台后台","自动退款策略","退货成功自动退"]</x:v>
       </x:c>
       <x:c r="Y252" s="21" t="str">
-        <x:v>["平台已创建并启用 erp取消发货自动退策略","策略已选择适用退款原因","ERP 已开启未发货自动退款"]</x:v>
+        <x:v>["拼多多平台已创建并启用退货成功自动退策略","策略触发节点选择退货入库成功","应用选择旺店通 ERP","ERP 已开启相应自动退款"]</x:v>
       </x:c>
       <x:c r="Z252" s="21" t="str">
-        <x:v>["创建平台 erp取消发货自动退策略","勾选允许触发的退款原因","启用策略","在 ERP 开启未发货自动退款","用测试单验证取消发货原因是否命中"]</x:v>
+        <x:v>["在平台新建退货成功自动退策略","选择退货入库成功并指定旺店通 ERP","启用平台策略","在 ERP 选择全部收货或部分及全部收货的触发口径","用智能退货入库完成收货并观察自动退款结果"]</x:v>
       </x:c>
       <x:c r="AA252" s="21" t="str">
-        <x:v>["ERP 取消未发货订单后，符合原因的申请自动退款","不符合策略的申请未被错误自动处理"]</x:v>
+        <x:v>["策略处于启用状态","退货收货达到 ERP 配置口径后平台自动确认退款","售后日志能看到处理结果"]</x:v>
       </x:c>
       <x:c r="AB252" s="21" t="str">
-        <x:v>["策略缺失、未启用或取消原因不在策略范围内都会导致自动退款失败"]</x:v>
+        <x:v>["未创建或未启用平台策略时，ERP 完成退货入库也可能无法自动退款"]</x:v>
       </x:c>
       <x:c r="AC252" s="21" t="str">
-        <x:v>["平台策略保持停用","未选择匹配的取消退款原因"]</x:v>
+        <x:v>["用采购入库代替售后退货入库","未达到设定收货口径就判断策略失效"]</x:v>
       </x:c>
       <x:c r="AD252" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -30279,10 +30281,10 @@
       </x:c>
       <x:c r="AF252" s="21" t="str"/>
       <x:c r="AG252" s="21" t="str">
-        <x:v>拼多多—ERP取消发货自动退款</x:v>
+        <x:v>拼多多—退货入库成功自动退款</x:v>
       </x:c>
       <x:c r="AH252" s="21" t="str">
-        <x:v>拼多多 erp取消发货自动退需平台策略启用、原因配置和 ERP 未发货自动退款同时生效。</x:v>
+        <x:v>智能退货入库达到 ERP 设置的收货口径后，可推动平台自动确认退款。</x:v>
       </x:c>
       <x:c r="AI252" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -30326,7 +30328,7 @@
       <x:c r="AV252" s="21" t="str"/>
       <x:c r="AW252" s="21" t="str"/>
       <x:c r="AX252" s="21" t="str">
-        <x:v>配置拼多多 ERP 取消发货自动退款</x:v>
+        <x:v>配置拼多多退货入库自动退款</x:v>
       </x:c>
       <x:c r="AY252" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -30334,7 +30336,7 @@
     </x:row>
     <x:row r="253" ht="46" customHeight="1">
       <x:c r="A253" s="21" t="str">
-        <x:v>WDT-029-B</x:v>
+        <x:v>WDT-029-A</x:v>
       </x:c>
       <x:c r="B253" s="21" t="str">
         <x:v>旺店通-客服</x:v>
@@ -30352,7 +30354,7 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G253" s="21" t="str">
-        <x:v>进阶</x:v>
+        <x:v>场景</x:v>
       </x:c>
       <x:c r="H253" s="21" t="str">
         <x:v>高</x:v>
@@ -30373,31 +30375,31 @@
         <x:v>取消发货原因必须命中平台策略</x:v>
       </x:c>
       <x:c r="N253" s="21" t="str">
-        <x:v>拼多多订单已在 ERP 取消发货却未自动退款，哪项最应优先核对？</x:v>
+        <x:v>要让拼多多未发货订单在 ERP 取消后自动退款，正确的成套配置是什么？</x:v>
       </x:c>
       <x:c r="O253" s="21" t="str">
-        <x:v>只核对 ERP 未发货自动退款已开启，不检查平台策略是否启用</x:v>
+        <x:v>平台创建取消发货策略但保持停用，ERP 开启未发货自动退款</x:v>
       </x:c>
       <x:c r="P253" s="21" t="str">
-        <x:v>只核对退货成功自动退策略是否启用，不检查取消发货策略和原因</x:v>
+        <x:v>平台创建退货入库自动退但不选原因，ERP 开启已发货自动退款</x:v>
       </x:c>
       <x:c r="Q253" s="21" t="str">
-        <x:v>只核对平台取消发货策略名称正确，不检查原因范围和 ERP 开关状态</x:v>
+        <x:v>平台只选择退款原因但不创建策略，ERP 开启未发货自动退款</x:v>
       </x:c>
       <x:c r="R253" s="21" t="str">
-        <x:v>核对取消发货策略状态、退款原因范围和 ERP 未发货自动退款开关</x:v>
+        <x:v>平台启用erp取消发货自动退并选原因，ERP开未发货自动退款</x:v>
       </x:c>
       <x:c r="S253" s="21" t="str">
         <x:v>D</x:v>
       </x:c>
       <x:c r="T253" s="21" t="str">
-        <x:v>核对取消发货策略状态、退款原因范围和 ERP 未发货自动退款开关</x:v>
+        <x:v>平台启用erp取消发货自动退并选原因，ERP开未发货自动退款</x:v>
       </x:c>
       <x:c r="U253" s="21" t="str">
-        <x:v>资料列出的核心失败点就是平台策略、退款原因和 ERP 侧开关。</x:v>
+        <x:v>平台策略、适用原因和 ERP 未发货自动退款缺一不可。</x:v>
       </x:c>
       <x:c r="V253" s="21" t="str">
-        <x:v>{"A":"核对不完整：ERP 开启后仍需平台策略生效。","B":"错策略：退货成功自动退不处理取消发货。","C":"核对不完整：策略名称正确也要核对原因和 ERP 开关。"}</x:v>
+        <x:v>{"A":"错状态：策略停用时不会按其自动处理。","B":"错策略和场景：退货入库不等于取消未发货。","C":"缺少策略：只选原因不能形成触发规则。"}</x:v>
       </x:c>
       <x:c r="W253" s="21" t="str">
         <x:v>让 ERP 中未发货订单取消后，按平台允许的退款原因自动处理，减少仓内拦截后的人工退款。</x:v>
@@ -30418,7 +30420,7 @@
         <x:v>["策略缺失、未启用或取消原因不在策略范围内都会导致自动退款失败"]</x:v>
       </x:c>
       <x:c r="AC253" s="21" t="str">
-        <x:v>["只检查 ERP 开关","忽略平台策略的退款原因范围"]</x:v>
+        <x:v>["平台策略保持停用","未选择匹配的取消退款原因"]</x:v>
       </x:c>
       <x:c r="AD253" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -30431,7 +30433,7 @@
         <x:v>拼多多—ERP取消发货自动退款</x:v>
       </x:c>
       <x:c r="AH253" s="21" t="str">
-        <x:v>拼多多取消发货自动退款失败常见于策略缺失或停用、原因不匹配、ERP未开启。</x:v>
+        <x:v>拼多多 erp取消发货自动退需平台策略启用、原因配置和 ERP 未发货自动退款同时生效。</x:v>
       </x:c>
       <x:c r="AI253" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -30483,7 +30485,7 @@
     </x:row>
     <x:row r="254" ht="46" customHeight="1">
       <x:c r="A254" s="21" t="str">
-        <x:v>WDT-030-A</x:v>
+        <x:v>WDT-029-B</x:v>
       </x:c>
       <x:c r="B254" s="21" t="str">
         <x:v>旺店通-客服</x:v>
@@ -30495,13 +30497,13 @@
         <x:v>售后自动退款</x:v>
       </x:c>
       <x:c r="E254" s="21" t="str">
-        <x:v>抖音电商</x:v>
+        <x:v>拼多多</x:v>
       </x:c>
       <x:c r="F254" s="21" t="str">
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G254" s="21" t="str">
-        <x:v>基础</x:v>
+        <x:v>进阶</x:v>
       </x:c>
       <x:c r="H254" s="21" t="str">
         <x:v>高</x:v>
@@ -30513,61 +30515,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K254" s="21" t="str">
-        <x:v>WDT-K030</x:v>
+        <x:v>WDT-K029</x:v>
       </x:c>
       <x:c r="L254" s="21" t="str">
-        <x:v>抖音退货入仓自动退</x:v>
+        <x:v>拼多多取消发货自动退</x:v>
       </x:c>
       <x:c r="M254" s="21" t="str">
-        <x:v>售后小助手策略启用后再联动 ERP 收货</x:v>
+        <x:v>取消发货原因必须命中平台策略</x:v>
       </x:c>
       <x:c r="N254" s="21" t="str">
-        <x:v>抖音退货入仓自动同意退款的正确平台配置入口是什么？</x:v>
+        <x:v>拼多多订单已在 ERP 取消发货却未自动退款，哪项最应优先核对？</x:v>
       </x:c>
       <x:c r="O254" s="21" t="str">
-        <x:v>抖店后台→售后→售后小助手→模板→退货退款→erp退货入仓自动同意退款</x:v>
+        <x:v>只核对 ERP 未发货自动退款已开启，不检查平台策略是否启用</x:v>
       </x:c>
       <x:c r="P254" s="21" t="str">
-        <x:v>抖店后台→售后→售后工作台→模板→退货退款→erp退货入仓自动同意退款</x:v>
+        <x:v>只核对退货成功自动退策略是否启用，不检查取消发货策略和原因</x:v>
       </x:c>
       <x:c r="Q254" s="21" t="str">
-        <x:v>抖店后台→售后→售后小助手→模板→仅退款→erp退货入仓自动同意退款</x:v>
+        <x:v>只核对平台取消发货策略名称正确，不检查原因范围和 ERP 开关状态</x:v>
       </x:c>
       <x:c r="R254" s="21" t="str">
-        <x:v>抖店后台→售后→售后小助手→策略记录→退货退款→erp退货入仓自动同意退款</x:v>
+        <x:v>核对取消发货策略状态、退款原因范围和 ERP 未发货自动退款开关</x:v>
       </x:c>
       <x:c r="S254" s="21" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="T254" s="21" t="str">
-        <x:v>抖店后台→售后→售后小助手→模板→退货退款→erp退货入仓自动同意退款</x:v>
+        <x:v>核对取消发货策略状态、退款原因范围和 ERP 未发货自动退款开关</x:v>
       </x:c>
       <x:c r="U254" s="21" t="str">
-        <x:v>资料明确给出了抖店售后小助手中退货退款模板的完整入口。</x:v>
+        <x:v>资料列出的核心失败点就是平台策略、退款原因和 ERP 侧开关。</x:v>
       </x:c>
       <x:c r="V254" s="21" t="str">
-        <x:v>{"B":"错入口：资料指定售后小助手，不是售后工作台。","C":"错模板类型：资料指定退货退款，不是仅退款。","D":"错层级：应从模板进入退货退款策略，不是策略记录。"}</x:v>
+        <x:v>{"A":"核对不完整：ERP 开启后仍需平台策略生效。","B":"错策略：退货成功自动退不处理取消发货。","C":"核对不完整：策略名称正确也要核对原因和 ERP 开关。"}</x:v>
       </x:c>
       <x:c r="W254" s="21" t="str">
-        <x:v>在退货完成入仓且商品满足策略时，自动同意抖音退款，缩短售后处理时间。</x:v>
+        <x:v>让 ERP 中未发货订单取消后，按平台允许的退款原因自动处理，减少仓内拦截后的人工退款。</x:v>
       </x:c>
       <x:c r="X254" s="21" t="str">
-        <x:v>["抖店后台","售后","售后小助手","模板","退货退款","erp退货入仓自动同意退款"]</x:v>
+        <x:v>["拼多多平台后台","自动退款策略","erp取消发货自动退"]</x:v>
       </x:c>
       <x:c r="Y254" s="21" t="str">
-        <x:v>["抖店售后小助手中已填写并启用对应策略","ERP 已完成自动退款设置","售后商品满足平台策略条件"]</x:v>
+        <x:v>["平台已创建并启用 erp取消发货自动退策略","策略已选择适用退款原因","ERP 已开启未发货自动退款"]</x:v>
       </x:c>
       <x:c r="Z254" s="21" t="str">
-        <x:v>["进入售后小助手的退货退款模板","配置 erp退货入仓自动同意退款策略","核对条件并启用","在 ERP 开启对应自动退款","退货入仓后检查平台处理结果"]</x:v>
+        <x:v>["创建平台 erp取消发货自动退策略","勾选允许触发的退款原因","启用策略","在 ERP 开启未发货自动退款","用测试单验证取消发货原因是否命中"]</x:v>
       </x:c>
       <x:c r="AA254" s="21" t="str">
-        <x:v>["策略显示启用","符合条件的退货入仓后自动同意退款","不满足策略的商品不会被误判为系统故障"]</x:v>
+        <x:v>["ERP 取消未发货订单后，符合原因的申请自动退款","不符合策略的申请未被错误自动处理"]</x:v>
       </x:c>
       <x:c r="AB254" s="21" t="str">
-        <x:v>["没有策略、策略未启用或商品不满足策略条件时，自动退款可能失败"]</x:v>
+        <x:v>["策略缺失、未启用或取消原因不在策略范围内都会导致自动退款失败"]</x:v>
       </x:c>
       <x:c r="AC254" s="21" t="str">
-        <x:v>["在旺店通中寻找平台模板","进入抖店发货管理配置售后策略"]</x:v>
+        <x:v>["只检查 ERP 开关","忽略平台策略的退款原因范围"]</x:v>
       </x:c>
       <x:c r="AD254" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -30577,10 +30579,10 @@
       </x:c>
       <x:c r="AF254" s="21" t="str"/>
       <x:c r="AG254" s="21" t="str">
-        <x:v>抖音—退货入仓自动同意退款</x:v>
+        <x:v>拼多多—ERP取消发货自动退款</x:v>
       </x:c>
       <x:c r="AH254" s="21" t="str">
-        <x:v>抖店后台→售后→售后小助手→模板→退货退款→erp退货入仓自动同意退款。</x:v>
+        <x:v>拼多多取消发货自动退款失败常见于策略缺失或停用、原因不匹配、ERP未开启。</x:v>
       </x:c>
       <x:c r="AI254" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -30624,7 +30626,7 @@
       <x:c r="AV254" s="21" t="str"/>
       <x:c r="AW254" s="21" t="str"/>
       <x:c r="AX254" s="21" t="str">
-        <x:v>配置抖音 ERP 退货入仓自动同意退款</x:v>
+        <x:v>配置拼多多 ERP 取消发货自动退款</x:v>
       </x:c>
       <x:c r="AY254" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -30632,7 +30634,7 @@
     </x:row>
     <x:row r="255" ht="46" customHeight="1">
       <x:c r="A255" s="21" t="str">
-        <x:v>WDT-030-B</x:v>
+        <x:v>WDT-030-A</x:v>
       </x:c>
       <x:c r="B255" s="21" t="str">
         <x:v>旺店通-客服</x:v>
@@ -30650,7 +30652,7 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G255" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="H255" s="21" t="str">
         <x:v>高</x:v>
@@ -30671,31 +30673,31 @@
         <x:v>售后小助手策略启用后再联动 ERP 收货</x:v>
       </x:c>
       <x:c r="N255" s="21" t="str">
-        <x:v>退货已在 ERP 入仓，但抖音没有自动同意退款，哪组检查最符合资料？</x:v>
+        <x:v>抖音退货入仓自动同意退款的正确平台配置入口是什么？</x:v>
       </x:c>
       <x:c r="O255" s="21" t="str">
-        <x:v>只检查售后小助手中策略名称存在，不检查策略状态和商品范围</x:v>
+        <x:v>抖店后台→售后→售后小助手→模板→退货退款→erp退货入仓自动同意退款</x:v>
       </x:c>
       <x:c r="P255" s="21" t="str">
-        <x:v>只检查退货已在 ERP 入仓，不检查商品是否命中售后小助手策略</x:v>
+        <x:v>抖店后台→售后→售后工作台→模板→退货退款→erp退货入仓自动同意退款</x:v>
       </x:c>
       <x:c r="Q255" s="21" t="str">
-        <x:v>检查售后小助手策略是否存在并启用，以及商品是否满足策略条件</x:v>
+        <x:v>抖店后台→售后→售后小助手→模板→仅退款→erp退货入仓自动同意退款</x:v>
       </x:c>
       <x:c r="R255" s="21" t="str">
-        <x:v>只检查 ERP 自动退款已开启，不检查抖店策略是否启用和商品条件</x:v>
+        <x:v>抖店后台→售后→售后小助手→策略记录→退货退款→erp退货入仓自动同意退款</x:v>
       </x:c>
       <x:c r="S255" s="21" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="T255" s="21" t="str">
-        <x:v>检查售后小助手策略是否存在并启用，以及商品是否满足策略条件</x:v>
+        <x:v>抖店后台→售后→售后小助手→模板→退货退款→erp退货入仓自动同意退款</x:v>
       </x:c>
       <x:c r="U255" s="21" t="str">
-        <x:v>抖音该流程的已知失败点包括缺少或未启用策略，以及商品不符合策略。</x:v>
+        <x:v>资料明确给出了抖店售后小助手中退货退款模板的完整入口。</x:v>
       </x:c>
       <x:c r="V255" s="21" t="str">
-        <x:v>{"A":"核对不完整：策略存在还要确认启用状态与适用商品。","B":"核对不完整：入仓成功后仍需商品命中平台策略。","D":"核对不完整：ERP 开关不能替代抖店策略和商品条件。"}</x:v>
+        <x:v>{"B":"错入口：资料指定售后小助手，不是售后工作台。","C":"错模板类型：资料指定退货退款，不是仅退款。","D":"错层级：应从模板进入退货退款策略，不是策略记录。"}</x:v>
       </x:c>
       <x:c r="W255" s="21" t="str">
         <x:v>在退货完成入仓且商品满足策略时，自动同意抖音退款，缩短售后处理时间。</x:v>
@@ -30716,7 +30718,7 @@
         <x:v>["没有策略、策略未启用或商品不满足策略条件时，自动退款可能失败"]</x:v>
       </x:c>
       <x:c r="AC255" s="21" t="str">
-        <x:v>["把策略不命中当成入库失败","只检查 ERP 不检查抖店策略"]</x:v>
+        <x:v>["在旺店通中寻找平台模板","进入抖店发货管理配置售后策略"]</x:v>
       </x:c>
       <x:c r="AD255" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -30729,7 +30731,7 @@
         <x:v>抖音—退货入仓自动同意退款</x:v>
       </x:c>
       <x:c r="AH255" s="21" t="str">
-        <x:v>抖音退货入仓自动退款失败可由没有策略或商品不满足策略导致。</x:v>
+        <x:v>抖店后台→售后→售后小助手→模板→退货退款→erp退货入仓自动同意退款。</x:v>
       </x:c>
       <x:c r="AI255" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -30781,7 +30783,7 @@
     </x:row>
     <x:row r="256" ht="46" customHeight="1">
       <x:c r="A256" s="21" t="str">
-        <x:v>WDT-031-A</x:v>
+        <x:v>WDT-030-B</x:v>
       </x:c>
       <x:c r="B256" s="21" t="str">
         <x:v>旺店通-客服</x:v>
@@ -30811,61 +30813,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K256" s="21" t="str">
-        <x:v>WDT-K031</x:v>
+        <x:v>WDT-K030</x:v>
       </x:c>
       <x:c r="L256" s="21" t="str">
-        <x:v>抖音取消发货自动退</x:v>
+        <x:v>抖音退货入仓自动退</x:v>
       </x:c>
       <x:c r="M256" s="21" t="str">
-        <x:v>策略、原因、商品条件共同决定触发</x:v>
+        <x:v>售后小助手策略启用后再联动 ERP 收货</x:v>
       </x:c>
       <x:c r="N256" s="21" t="str">
-        <x:v>抖音未发货订单要在 ERP 取消后自动退款，哪组前置条件是完整的？</x:v>
+        <x:v>退货已在 ERP 入仓，但抖音没有自动同意退款，哪组检查最符合资料？</x:v>
       </x:c>
       <x:c r="O256" s="21" t="str">
-        <x:v>只在 ERP 开启未发货自动退款，不需要平台策略或条件</x:v>
+        <x:v>只检查售后小助手中策略名称存在，不检查策略状态和商品范围</x:v>
       </x:c>
       <x:c r="P256" s="21" t="str">
-        <x:v>抖店保留取消发货策略为停用，ERP开启自动退款，商品满足条件</x:v>
+        <x:v>只检查退货已在 ERP 入仓，不检查商品是否命中售后小助手策略</x:v>
       </x:c>
       <x:c r="Q256" s="21" t="str">
-        <x:v>抖店启用取消发货策略，ERP开未发货自动退，原因和商品均符合</x:v>
+        <x:v>检查售后小助手策略是否存在并启用，以及商品是否满足策略条件</x:v>
       </x:c>
       <x:c r="R256" s="21" t="str">
-        <x:v>抖店启用退货入仓策略，ERP关闭未发货自动退款，原因满足条件</x:v>
+        <x:v>只检查 ERP 自动退款已开启，不检查抖店策略是否启用和商品条件</x:v>
       </x:c>
       <x:c r="S256" s="21" t="str">
         <x:v>C</x:v>
       </x:c>
       <x:c r="T256" s="21" t="str">
-        <x:v>抖店启用取消发货策略，ERP开未发货自动退，原因和商品均符合</x:v>
+        <x:v>检查售后小助手策略是否存在并启用，以及商品是否满足策略条件</x:v>
       </x:c>
       <x:c r="U256" s="21" t="str">
-        <x:v>该流程需要平台策略和 ERP 开关同时生效，并且订单原因和商品需满足策略条件。</x:v>
+        <x:v>抖音该流程的已知失败点包括缺少或未启用策略，以及商品不符合策略。</x:v>
       </x:c>
       <x:c r="V256" s="21" t="str">
-        <x:v>{"A":"缺平台侧条件：只有 ERP 开关不足以触发。","B":"错状态：平台策略停用不会生效。","D":"错策略和开关：退货入仓不是取消发货，且 ERP 开关关闭。"}</x:v>
+        <x:v>{"A":"核对不完整：策略存在还要确认启用状态与适用商品。","B":"核对不完整：入仓成功后仍需商品命中平台策略。","D":"核对不完整：ERP 开关不能替代抖店策略和商品条件。"}</x:v>
       </x:c>
       <x:c r="W256" s="21" t="str">
-        <x:v>让符合规则的抖音未发货订单在 ERP 取消后自动处理退款，同时阻止不合条件的误退。</x:v>
+        <x:v>在退货完成入仓且商品满足策略时，自动同意抖音退款，缩短售后处理时间。</x:v>
       </x:c>
       <x:c r="X256" s="21" t="str">
-        <x:v>["抖店后台","售后","售后小助手","取消发货相关策略"]</x:v>
+        <x:v>["抖店后台","售后","售后小助手","模板","退货退款","erp退货入仓自动同意退款"]</x:v>
       </x:c>
       <x:c r="Y256" s="21" t="str">
-        <x:v>["抖店售后小助手已配置并启用 ERP 取消发货对应策略","ERP 已开启未发货自动退款","取消原因和商品满足策略"]</x:v>
+        <x:v>["抖店售后小助手中已填写并启用对应策略","ERP 已完成自动退款设置","售后商品满足平台策略条件"]</x:v>
       </x:c>
       <x:c r="Z256" s="21" t="str">
-        <x:v>["在抖店售后小助手配置取消发货对应策略","核对适用原因和商品条件","启用平台策略","在 ERP 开启未发货自动退款","用符合条件的测试单验证"]</x:v>
+        <x:v>["进入售后小助手的退货退款模板","配置 erp退货入仓自动同意退款策略","核对条件并启用","在 ERP 开启对应自动退款","退货入仓后检查平台处理结果"]</x:v>
       </x:c>
       <x:c r="AA256" s="21" t="str">
-        <x:v>["符合原因和商品条件的 ERP 取消发货可触发自动退款","不符合策略的申请保留人工核查"]</x:v>
+        <x:v>["策略显示启用","符合条件的退货入仓后自动同意退款","不满足策略的商品不会被误判为系统故障"]</x:v>
       </x:c>
       <x:c r="AB256" s="21" t="str">
-        <x:v>["资料未提供该策略的完整固定模板名称，实际页面以抖店售后小助手当前展示为准；不得照搬其他平台策略名称"]</x:v>
+        <x:v>["没有策略、策略未启用或商品不满足策略条件时，自动退款可能失败"]</x:v>
       </x:c>
       <x:c r="AC256" s="21" t="str">
-        <x:v>["只开 ERP 开关","用退货入仓策略代替取消发货策略"]</x:v>
+        <x:v>["把策略不命中当成入库失败","只检查 ERP 不检查抖店策略"]</x:v>
       </x:c>
       <x:c r="AD256" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -30875,10 +30877,10 @@
       </x:c>
       <x:c r="AF256" s="21" t="str"/>
       <x:c r="AG256" s="21" t="str">
-        <x:v>抖音—取消发货自动退款</x:v>
+        <x:v>抖音—退货入仓自动同意退款</x:v>
       </x:c>
       <x:c r="AH256" s="21" t="str">
-        <x:v>抖音取消发货自动退款依赖平台策略、ERP开关、正确原因和符合条件的商品。</x:v>
+        <x:v>抖音退货入仓自动退款失败可由没有策略或商品不满足策略导致。</x:v>
       </x:c>
       <x:c r="AI256" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -30922,7 +30924,7 @@
       <x:c r="AV256" s="21" t="str"/>
       <x:c r="AW256" s="21" t="str"/>
       <x:c r="AX256" s="21" t="str">
-        <x:v>配置抖音取消发货自动退款</x:v>
+        <x:v>配置抖音 ERP 退货入仓自动同意退款</x:v>
       </x:c>
       <x:c r="AY256" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -30930,7 +30932,7 @@
     </x:row>
     <x:row r="257" ht="46" customHeight="1">
       <x:c r="A257" s="21" t="str">
-        <x:v>WDT-031-B</x:v>
+        <x:v>WDT-031-A</x:v>
       </x:c>
       <x:c r="B257" s="21" t="str">
         <x:v>旺店通-客服</x:v>
@@ -30948,7 +30950,7 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G257" s="21" t="str">
-        <x:v>进阶</x:v>
+        <x:v>场景</x:v>
       </x:c>
       <x:c r="H257" s="21" t="str">
         <x:v>高</x:v>
@@ -30969,31 +30971,31 @@
         <x:v>策略、原因、商品条件共同决定触发</x:v>
       </x:c>
       <x:c r="N257" s="21" t="str">
-        <x:v>抖音取消发货自动退款未触发时，以下哪项排查最贴近资料列出的失败点？</x:v>
+        <x:v>抖音未发货订单要在 ERP 取消后自动退款，哪组前置条件是完整的？</x:v>
       </x:c>
       <x:c r="O257" s="21" t="str">
-        <x:v>只核对 ERP 未发货自动退款开关，不检查抖店策略和商品条件</x:v>
+        <x:v>只在 ERP 开启未发货自动退款，不需要平台策略或条件</x:v>
       </x:c>
       <x:c r="P257" s="21" t="str">
-        <x:v>核对平台策略是否存在启用、取消原因是否正确、商品是否满足条件</x:v>
+        <x:v>抖店保留取消发货策略为停用，ERP开启自动退款，商品满足条件</x:v>
       </x:c>
       <x:c r="Q257" s="21" t="str">
-        <x:v>只核对取消原因名称相同，不检查商品是否满足策略和 ERP 开关</x:v>
+        <x:v>抖店启用取消发货策略，ERP开未发货自动退，原因和商品均符合</x:v>
       </x:c>
       <x:c r="R257" s="21" t="str">
-        <x:v>只核对抖店取消发货策略已启用，不检查取消原因是否命中</x:v>
+        <x:v>抖店启用退货入仓策略，ERP关闭未发货自动退款，原因满足条件</x:v>
       </x:c>
       <x:c r="S257" s="21" t="str">
-        <x:v>B</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="T257" s="21" t="str">
-        <x:v>核对平台策略是否存在启用、取消原因是否正确、商品是否满足条件</x:v>
+        <x:v>抖店启用取消发货策略，ERP开未发货自动退，原因和商品均符合</x:v>
       </x:c>
       <x:c r="U257" s="21" t="str">
-        <x:v>资料明确把没有策略、原因错误和商品不满足列为该流程失败原因。</x:v>
+        <x:v>该流程需要平台策略和 ERP 开关同时生效，并且订单原因和商品需满足策略条件。</x:v>
       </x:c>
       <x:c r="V257" s="21" t="str">
-        <x:v>{"A":"核对不完整：只查 ERP 开关会遗漏平台策略和商品条件。","C":"核对不完整：原因之外还需商品条件和 ERP 开关。","D":"核对不完整：策略启用不代表取消原因一定命中。"}</x:v>
+        <x:v>{"A":"缺平台侧条件：只有 ERP 开关不足以触发。","B":"错状态：平台策略停用不会生效。","D":"错策略和开关：退货入仓不是取消发货，且 ERP 开关关闭。"}</x:v>
       </x:c>
       <x:c r="W257" s="21" t="str">
         <x:v>让符合规则的抖音未发货订单在 ERP 取消后自动处理退款，同时阻止不合条件的误退。</x:v>
@@ -31014,7 +31016,7 @@
         <x:v>["资料未提供该策略的完整固定模板名称，实际页面以抖店售后小助手当前展示为准；不得照搬其他平台策略名称"]</x:v>
       </x:c>
       <x:c r="AC257" s="21" t="str">
-        <x:v>["忽略商品条件","把未触发原因归结为报表延迟"]</x:v>
+        <x:v>["只开 ERP 开关","用退货入仓策略代替取消发货策略"]</x:v>
       </x:c>
       <x:c r="AD257" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -31027,7 +31029,7 @@
         <x:v>抖音—取消发货自动退款</x:v>
       </x:c>
       <x:c r="AH257" s="21" t="str">
-        <x:v>抖音取消发货自动退款失败点：无策略、错误原因或商品不满足策略。</x:v>
+        <x:v>抖音取消发货自动退款依赖平台策略、ERP开关、正确原因和符合条件的商品。</x:v>
       </x:c>
       <x:c r="AI257" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -31079,7 +31081,7 @@
     </x:row>
     <x:row r="258" ht="46" customHeight="1">
       <x:c r="A258" s="21" t="str">
-        <x:v>WDT-032-A</x:v>
+        <x:v>WDT-031-B</x:v>
       </x:c>
       <x:c r="B258" s="21" t="str">
         <x:v>旺店通-客服</x:v>
@@ -31091,13 +31093,13 @@
         <x:v>售后自动退款</x:v>
       </x:c>
       <x:c r="E258" s="21" t="str">
-        <x:v>天猫/淘宝</x:v>
+        <x:v>抖音电商</x:v>
       </x:c>
       <x:c r="F258" s="21" t="str">
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G258" s="21" t="str">
-        <x:v>基础</x:v>
+        <x:v>进阶</x:v>
       </x:c>
       <x:c r="H258" s="21" t="str">
         <x:v>高</x:v>
@@ -31109,61 +31111,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K258" s="21" t="str">
-        <x:v>WDT-K032</x:v>
+        <x:v>WDT-K031</x:v>
       </x:c>
       <x:c r="L258" s="21" t="str">
-        <x:v>淘宝天猫入仓自动退</x:v>
+        <x:v>抖音取消发货自动退</x:v>
       </x:c>
       <x:c r="M258" s="21" t="str">
-        <x:v>策略先验证，货品全部到仓后再推送</x:v>
+        <x:v>策略、原因、商品条件共同决定触发</x:v>
       </x:c>
       <x:c r="N258" s="21" t="str">
-        <x:v>淘宝天猫入仓自动退款的正确平台配置路径和顺序是哪一项？</x:v>
+        <x:v>抖音取消发货自动退款未触发时，以下哪项排查最贴近资料列出的失败点？</x:v>
       </x:c>
       <x:c r="O258" s="21" t="str">
-        <x:v>千牛售后服务平台→策略中心→应用库→入仓自动退，配置后不验证直接启用</x:v>
+        <x:v>只核对 ERP 未发货自动退款开关，不检查抖店策略和商品条件</x:v>
       </x:c>
       <x:c r="P258" s="21" t="str">
-        <x:v>千牛售后服务平台→策略中心→应用库→入仓自动退，只设备注不配置策略因素</x:v>
+        <x:v>核对平台策略是否存在启用、取消原因是否正确、商品是否满足条件</x:v>
       </x:c>
       <x:c r="Q258" s="21" t="str">
-        <x:v>千牛售后服务平台→策略中心→应用库→入仓自动退，配置并案例验证后启用</x:v>
+        <x:v>只核对取消原因名称相同，不检查商品是否满足策略和 ERP 开关</x:v>
       </x:c>
       <x:c r="R258" s="21" t="str">
-        <x:v>千牛售后服务平台→策略中心→应用库→ERP仓内拦截自动退，验证后启用</x:v>
+        <x:v>只核对抖店取消发货策略已启用，不检查取消原因是否命中</x:v>
       </x:c>
       <x:c r="S258" s="21" t="str">
-        <x:v>C</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="T258" s="21" t="str">
-        <x:v>千牛售后服务平台→策略中心→应用库→入仓自动退，配置并案例验证后启用</x:v>
+        <x:v>核对平台策略是否存在启用、取消原因是否正确、商品是否满足条件</x:v>
       </x:c>
       <x:c r="U258" s="21" t="str">
-        <x:v>资料要求在千牛售后服务平台的应用库中配置入仓自动退，并先用案例验证。</x:v>
+        <x:v>资料明确把没有策略、原因错误和商品不满足列为该流程失败原因。</x:v>
       </x:c>
       <x:c r="V258" s="21" t="str">
-        <x:v>{"A":"漏验证：资料要求案例验证通过后再启用。","B":"配置不完整：备注不能替代策略因素设置。","D":"错应用：ERP仓内拦截用于取消发货，不是退货入仓。"}</x:v>
+        <x:v>{"A":"核对不完整：只查 ERP 开关会遗漏平台策略和商品条件。","C":"核对不完整：原因之外还需商品条件和 ERP 开关。","D":"核对不完整：策略启用不代表取消原因一定命中。"}</x:v>
       </x:c>
       <x:c r="W258" s="21" t="str">
-        <x:v>让淘宝天猫退货在满足千牛策略并完整入仓后自动退款，降低误退和少件风险。</x:v>
+        <x:v>让符合规则的抖音未发货订单在 ERP 取消后自动处理退款，同时阻止不合条件的误退。</x:v>
       </x:c>
       <x:c r="X258" s="21" t="str">
-        <x:v>["千牛售后服务平台","策略中心","应用库","入仓自动退"]</x:v>
+        <x:v>["抖店后台","售后","售后小助手","取消发货相关策略"]</x:v>
       </x:c>
       <x:c r="Y258" s="21" t="str">
-        <x:v>["已在千牛店铺管理创建并实名售后子账号","子账号先完成支付宝授权，再取得售后、退款及应用权限","已在 ERP 售后→售后管理→售后设置授权该子账号","已在千牛入仓自动退中新增策略并设置条件","策略已用案例验证后启用","ERP 已设置对应自动退款"]</x:v>
+        <x:v>["抖店售后小助手已配置并启用 ERP 取消发货对应策略","ERP 已开启未发货自动退款","取消原因和商品满足策略"]</x:v>
       </x:c>
       <x:c r="Z258" s="21" t="str">
-        <x:v>["在千牛完成子账号实名与支付宝授权","授予子账号售后、退款和应用权限","在 ERP 售后设置授权子账号","进入千牛入仓自动退应用","新增策略并配置因素和备注","用案例验证后启用","货品全部到仓后再推送 AG 入仓"]</x:v>
+        <x:v>["在抖店售后小助手配置取消发货对应策略","核对适用原因和商品条件","启用平台策略","在 ERP 开启未发货自动退款","用符合条件的测试单验证"]</x:v>
       </x:c>
       <x:c r="AA258" s="21" t="str">
-        <x:v>["子账号在千牛和 ERP 两端均完成授权","策略验证通过且处于启用状态","退货全部到仓并推送后符合条件的售后自动退款","未超过平台限制"]</x:v>
+        <x:v>["符合原因和商品条件的 ERP 取消发货可触发自动退款","不符合策略的申请保留人工核查"]</x:v>
       </x:c>
       <x:c r="AB258" s="21" t="str">
-        <x:v>["未创建或未实名子账号、未先完成支付宝授权、退款或应用权限不完整、ERP 未授权子账号，均会影响淘系退款审批","策略、商品、退款原因或平台每日额度限制也可能导致失败；资料建议全部货品到齐后再推送 AG 入仓"]</x:v>
+        <x:v>["资料未提供该策略的完整固定模板名称，实际页面以抖店售后小助手当前展示为准；不得照搬其他平台策略名称"]</x:v>
       </x:c>
       <x:c r="AC258" s="21" t="str">
-        <x:v>["在旺店通里寻找千牛应用","未验证策略就直接启用"]</x:v>
+        <x:v>["忽略商品条件","把未触发原因归结为报表延迟"]</x:v>
       </x:c>
       <x:c r="AD258" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -31171,14 +31173,12 @@
       <x:c r="AE258" s="21" t="str">
         <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/lfgmgszg7muigf79</x:v>
       </x:c>
-      <x:c r="AF258" s="21" t="str">
-        <x:v>[{"section":"淘宝天猫入仓自动退款","url":"https://zsxj.yuque.com/da3ftb/vgswhb/lfgmgszg7muigf79"},{"section":"淘系子账号退款授权","url":"https://zsxj.yuque.com/da3ftb/vgswhb/loknewprcqw3hhcg"}]</x:v>
-      </x:c>
+      <x:c r="AF258" s="21" t="str"/>
       <x:c r="AG258" s="21" t="str">
-        <x:v>淘宝天猫—入仓自动退款与退款子账号授权</x:v>
+        <x:v>抖音—取消发货自动退款</x:v>
       </x:c>
       <x:c r="AH258" s="21" t="str">
-        <x:v>千牛售后服务平台→策略中心→应用库→入仓自动退；新增配置、案例验证、启用。</x:v>
+        <x:v>抖音取消发货自动退款失败点：无策略、错误原因或商品不满足策略。</x:v>
       </x:c>
       <x:c r="AI258" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -31222,7 +31222,7 @@
       <x:c r="AV258" s="21" t="str"/>
       <x:c r="AW258" s="21" t="str"/>
       <x:c r="AX258" s="21" t="str">
-        <x:v>配置淘宝天猫入仓自动退款</x:v>
+        <x:v>配置抖音取消发货自动退款</x:v>
       </x:c>
       <x:c r="AY258" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -31230,7 +31230,7 @@
     </x:row>
     <x:row r="259" ht="46" customHeight="1">
       <x:c r="A259" s="21" t="str">
-        <x:v>WDT-032-B</x:v>
+        <x:v>WDT-032-A</x:v>
       </x:c>
       <x:c r="B259" s="21" t="str">
         <x:v>旺店通-客服</x:v>
@@ -31248,16 +31248,16 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G259" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="H259" s="21" t="str">
         <x:v>高</x:v>
       </x:c>
       <x:c r="I259" s="21" t="str">
-        <x:v>redline</x:v>
+        <x:v>practice</x:v>
       </x:c>
       <x:c r="J259" s="22" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K259" s="21" t="str">
         <x:v>WDT-K032</x:v>
@@ -31269,31 +31269,31 @@
         <x:v>策略先验证，货品全部到仓后再推送</x:v>
       </x:c>
       <x:c r="N259" s="21" t="str">
-        <x:v>一笔淘宝退货分两箱返回，当前只收到第一箱；按资料建议，怎样降低自动退款后的少件风险？</x:v>
+        <x:v>淘宝天猫入仓自动退款的正确平台配置路径和顺序是哪一项？</x:v>
       </x:c>
       <x:c r="O259" s="21" t="str">
-        <x:v>每到一箱就新建一张售后单，并分别向 AG 推送一次入仓结果</x:v>
+        <x:v>千牛售后服务平台→策略中心→应用库→入仓自动退，配置后不验证直接启用</x:v>
       </x:c>
       <x:c r="P259" s="21" t="str">
-        <x:v>等退货商品全部到齐后，再推送 AG 入仓并触发后续自动退款</x:v>
+        <x:v>千牛售后服务平台→策略中心→应用库→入仓自动退，只设备注不配置策略因素</x:v>
       </x:c>
       <x:c r="Q259" s="21" t="str">
-        <x:v>第一箱到仓后停用入仓自动退，第二箱到仓后再重新启用同一策略</x:v>
+        <x:v>千牛售后服务平台→策略中心→应用库→入仓自动退，配置并案例验证后启用</x:v>
       </x:c>
       <x:c r="R259" s="21" t="str">
-        <x:v>第一箱到仓后立即推送 AG 入仓，第二箱到仓后再补做剩余收货</x:v>
+        <x:v>千牛售后服务平台→策略中心→应用库→ERP仓内拦截自动退，验证后启用</x:v>
       </x:c>
       <x:c r="S259" s="21" t="str">
-        <x:v>B</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="T259" s="21" t="str">
-        <x:v>等退货商品全部到齐后，再推送 AG 入仓并触发后续自动退款</x:v>
+        <x:v>千牛售后服务平台→策略中心→应用库→入仓自动退，配置并案例验证后启用</x:v>
       </x:c>
       <x:c r="U259" s="21" t="str">
-        <x:v>资料建议全部货品到齐后再推送 AG 入仓，避免部分收货即退款产生少件风险。</x:v>
+        <x:v>资料要求在千牛售后服务平台的应用库中配置入仓自动退，并先用案例验证。</x:v>
       </x:c>
       <x:c r="V259" s="21" t="str">
-        <x:v>{"A":"错单据：同一售后分箱退回不应重复新建售后单。","C":"错控制方式：反复停启策略不能替代全部到仓核验。","D":"风险动作：部分到仓即推送可能提前退款。"}</x:v>
+        <x:v>{"A":"漏验证：资料要求案例验证通过后再启用。","B":"配置不完整：备注不能替代策略因素设置。","D":"错应用：ERP仓内拦截用于取消发货，不是退货入仓。"}</x:v>
       </x:c>
       <x:c r="W259" s="21" t="str">
         <x:v>让淘宝天猫退货在满足千牛策略并完整入仓后自动退款，降低误退和少件风险。</x:v>
@@ -31314,7 +31314,7 @@
         <x:v>["未创建或未实名子账号、未先完成支付宝授权、退款或应用权限不完整、ERP 未授权子账号，均会影响淘系退款审批","策略、商品、退款原因或平台每日额度限制也可能导致失败；资料建议全部货品到齐后再推送 AG 入仓"]</x:v>
       </x:c>
       <x:c r="AC259" s="21" t="str">
-        <x:v>["部分到仓就推送自动退款","用反复开关策略代替收货核验"]</x:v>
+        <x:v>["在旺店通里寻找千牛应用","未验证策略就直接启用"]</x:v>
       </x:c>
       <x:c r="AD259" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -31329,7 +31329,7 @@
         <x:v>淘宝天猫—入仓自动退款与退款子账号授权</x:v>
       </x:c>
       <x:c r="AH259" s="21" t="str">
-        <x:v>淘宝天猫入仓自动退建议待全部商品到仓后再推送 AG 入仓。</x:v>
+        <x:v>千牛售后服务平台→策略中心→应用库→入仓自动退；新增配置、案例验证、启用。</x:v>
       </x:c>
       <x:c r="AI259" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -31381,7 +31381,7 @@
     </x:row>
     <x:row r="260" ht="46" customHeight="1">
       <x:c r="A260" s="21" t="str">
-        <x:v>WDT-033-A</x:v>
+        <x:v>WDT-032-B</x:v>
       </x:c>
       <x:c r="B260" s="21" t="str">
         <x:v>旺店通-客服</x:v>
@@ -31399,73 +31399,73 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G260" s="21" t="str">
-        <x:v>基础</x:v>
+        <x:v>场景</x:v>
       </x:c>
       <x:c r="H260" s="21" t="str">
         <x:v>高</x:v>
       </x:c>
       <x:c r="I260" s="21" t="str">
-        <x:v>practice</x:v>
+        <x:v>redline</x:v>
       </x:c>
       <x:c r="J260" s="22" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K260" s="21" t="str">
-        <x:v>WDT-K033</x:v>
+        <x:v>WDT-K032</x:v>
       </x:c>
       <x:c r="L260" s="21" t="str">
-        <x:v>淘宝天猫仓内拦截自动退</x:v>
+        <x:v>淘宝天猫入仓自动退</x:v>
       </x:c>
       <x:c r="M260" s="21" t="str">
-        <x:v>取消发货要命中仓内拦截策略</x:v>
+        <x:v>策略先验证，货品全部到仓后再推送</x:v>
       </x:c>
       <x:c r="N260" s="21" t="str">
-        <x:v>淘宝天猫未发货订单在 ERP 取消后要自动退款，应配置哪个千牛应用策略？</x:v>
+        <x:v>一笔淘宝退货分两箱返回，当前只收到第一箱；按资料建议，怎样降低自动退款后的少件风险？</x:v>
       </x:c>
       <x:c r="O260" s="21" t="str">
-        <x:v>配置ERP仓内拦截自动退，以仓内取消发货触发退款</x:v>
+        <x:v>每到一箱就新建一张售后单，并分别向 AG 推送一次入仓结果</x:v>
       </x:c>
       <x:c r="P260" s="21" t="str">
-        <x:v>配置换货入仓自动退，用换货收货状态触发取消发货退款</x:v>
+        <x:v>等退货商品全部到齐后，再推送 AG 入仓并触发后续自动退款</x:v>
       </x:c>
       <x:c r="Q260" s="21" t="str">
-        <x:v>配置补寄完成自动退，用补寄发货状态触发取消发货退款</x:v>
+        <x:v>第一箱到仓后停用入仓自动退，第二箱到仓后再重新启用同一策略</x:v>
       </x:c>
       <x:c r="R260" s="21" t="str">
-        <x:v>配置入仓自动退，用退货入库状态触发取消发货退款</x:v>
+        <x:v>第一箱到仓后立即推送 AG 入仓，第二箱到仓后再补做剩余收货</x:v>
       </x:c>
       <x:c r="S260" s="21" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="T260" s="21" t="str">
-        <x:v>配置ERP仓内拦截自动退，以仓内取消发货触发退款</x:v>
+        <x:v>等退货商品全部到齐后，再推送 AG 入仓并触发后续自动退款</x:v>
       </x:c>
       <x:c r="U260" s="21" t="str">
-        <x:v>取消发货对应 ERP 仓内拦截场景，不应使用退货入仓或换货补寄策略。</x:v>
+        <x:v>资料建议全部货品到齐后再推送 AG 入仓，避免部分收货即退款产生少件风险。</x:v>
       </x:c>
       <x:c r="V260" s="21" t="str">
-        <x:v>{"B":"错售后类型：换货收货不是取消发货退款。","C":"错售后类型：补寄发货不产生该退款触发。","D":"错场景：入仓自动退用于买家退货收货。"}</x:v>
+        <x:v>{"A":"错单据：同一售后分箱退回不应重复新建售后单。","C":"错控制方式：反复停启策略不能替代全部到仓核验。","D":"风险动作：部分到仓即推送可能提前退款。"}</x:v>
       </x:c>
       <x:c r="W260" s="21" t="str">
-        <x:v>在未发货订单被 ERP 仓内拦截后，按千牛策略自动退款并保留不符合条件的人工复核。</x:v>
+        <x:v>让淘宝天猫退货在满足千牛策略并完整入仓后自动退款，降低误退和少件风险。</x:v>
       </x:c>
       <x:c r="X260" s="21" t="str">
-        <x:v>["千牛售后服务平台","策略中心","应用库","ERP仓内拦截自动退"]</x:v>
+        <x:v>["千牛售后服务平台","策略中心","应用库","入仓自动退"]</x:v>
       </x:c>
       <x:c r="Y260" s="21" t="str">
-        <x:v>["千牛已配置并启用 ERP仓内拦截自动退策略","ERP 已开启未发货自动退款","退款原因与商品满足策略"]</x:v>
+        <x:v>["已在千牛店铺管理创建并实名售后子账号","子账号先完成支付宝授权，再取得售后、退款及应用权限","已在 ERP 售后→售后管理→售后设置授权该子账号","已在千牛入仓自动退中新增策略并设置条件","策略已用案例验证后启用","ERP 已设置对应自动退款"]</x:v>
       </x:c>
       <x:c r="Z260" s="21" t="str">
-        <x:v>["进入千牛 ERP仓内拦截自动退应用","新增并设置策略条件","用案例验证后启用","在 ERP 开启未发货自动退款","取消发货后核对平台退款结果"]</x:v>
+        <x:v>["在千牛完成子账号实名与支付宝授权","授予子账号售后、退款和应用权限","在 ERP 售后设置授权子账号","进入千牛入仓自动退应用","新增策略并配置因素和备注","用案例验证后启用","货品全部到仓后再推送 AG 入仓"]</x:v>
       </x:c>
       <x:c r="AA260" s="21" t="str">
-        <x:v>["符合条件的仓内拦截订单自动退款","不满足条件的售后转为人工核查"]</x:v>
+        <x:v>["子账号在千牛和 ERP 两端均完成授权","策略验证通过且处于启用状态","退货全部到仓并推送后符合条件的售后自动退款","未超过平台限制"]</x:v>
       </x:c>
       <x:c r="AB260" s="21" t="str">
-        <x:v>["策略、商品、退款原因或平台每日额度限制可能导致自动退款失败"]</x:v>
+        <x:v>["未创建或未实名子账号、未先完成支付宝授权、退款或应用权限不完整、ERP 未授权子账号，均会影响淘系退款审批","策略、商品、退款原因或平台每日额度限制也可能导致失败；资料建议全部货品到齐后再推送 AG 入仓"]</x:v>
       </x:c>
       <x:c r="AC260" s="21" t="str">
-        <x:v>["把入仓自动退和仓内拦截混用","只开 ERP 开关不建千牛策略"]</x:v>
+        <x:v>["部分到仓就推送自动退款","用反复开关策略代替收货核验"]</x:v>
       </x:c>
       <x:c r="AD260" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -31473,12 +31473,14 @@
       <x:c r="AE260" s="21" t="str">
         <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/lfgmgszg7muigf79</x:v>
       </x:c>
-      <x:c r="AF260" s="21" t="str"/>
+      <x:c r="AF260" s="21" t="str">
+        <x:v>[{"section":"淘宝天猫入仓自动退款","url":"https://zsxj.yuque.com/da3ftb/vgswhb/lfgmgszg7muigf79"},{"section":"淘系子账号退款授权","url":"https://zsxj.yuque.com/da3ftb/vgswhb/loknewprcqw3hhcg"}]</x:v>
+      </x:c>
       <x:c r="AG260" s="21" t="str">
-        <x:v>淘宝天猫—ERP仓内拦截自动退款</x:v>
+        <x:v>淘宝天猫—入仓自动退款与退款子账号授权</x:v>
       </x:c>
       <x:c r="AH260" s="21" t="str">
-        <x:v>淘宝天猫取消发货自动退款对应千牛 ERP仓内拦截自动退。</x:v>
+        <x:v>淘宝天猫入仓自动退建议待全部商品到仓后再推送 AG 入仓。</x:v>
       </x:c>
       <x:c r="AI260" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -31522,7 +31524,7 @@
       <x:c r="AV260" s="21" t="str"/>
       <x:c r="AW260" s="21" t="str"/>
       <x:c r="AX260" s="21" t="str">
-        <x:v>配置淘宝天猫 ERP 仓内拦截自动退款</x:v>
+        <x:v>配置淘宝天猫入仓自动退款</x:v>
       </x:c>
       <x:c r="AY260" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -31530,7 +31532,7 @@
     </x:row>
     <x:row r="261" ht="46" customHeight="1">
       <x:c r="A261" s="21" t="str">
-        <x:v>WDT-033-B</x:v>
+        <x:v>WDT-033-A</x:v>
       </x:c>
       <x:c r="B261" s="21" t="str">
         <x:v>旺店通-客服</x:v>
@@ -31548,7 +31550,7 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G261" s="21" t="str">
-        <x:v>进阶</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="H261" s="21" t="str">
         <x:v>高</x:v>
@@ -31569,31 +31571,31 @@
         <x:v>取消发货要命中仓内拦截策略</x:v>
       </x:c>
       <x:c r="N261" s="21" t="str">
-        <x:v>千牛仓内拦截策略已创建，但某笔取消发货仍未自动退款，哪组原因都属于应排查范围？</x:v>
+        <x:v>淘宝天猫未发货订单在 ERP 取消后要自动退款，应配置哪个千牛应用策略？</x:v>
       </x:c>
       <x:c r="O261" s="21" t="str">
-        <x:v>只检查千牛策略名称正确，不核对策略启用状态和适用商品</x:v>
+        <x:v>配置ERP仓内拦截自动退，以仓内取消发货触发退款</x:v>
       </x:c>
       <x:c r="P261" s="21" t="str">
-        <x:v>只检查取消原因文字相同，不核对 ERP 开关和平台每日额度</x:v>
+        <x:v>配置换货入仓自动退，用换货收货状态触发取消发货退款</x:v>
       </x:c>
       <x:c r="Q261" s="21" t="str">
-        <x:v>只检查 ERP 未发货自动退款已开启，不核对千牛策略和原因范围</x:v>
+        <x:v>配置补寄完成自动退，用补寄发货状态触发取消发货退款</x:v>
       </x:c>
       <x:c r="R261" s="21" t="str">
-        <x:v>策略未启用、商品或退款原因不满足、达到平台每日额度限制</x:v>
+        <x:v>配置入仓自动退，用退货入库状态触发取消发货退款</x:v>
       </x:c>
       <x:c r="S261" s="21" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="T261" s="21" t="str">
-        <x:v>策略未启用、商品或退款原因不满足、达到平台每日额度限制</x:v>
+        <x:v>配置ERP仓内拦截自动退，以仓内取消发货触发退款</x:v>
       </x:c>
       <x:c r="U261" s="21" t="str">
-        <x:v>资料列明策略、商品、退款原因和每日额度都可能阻断淘宝天猫自动退款。</x:v>
+        <x:v>取消发货对应 ERP 仓内拦截场景，不应使用退货入仓或换货补寄策略。</x:v>
       </x:c>
       <x:c r="V261" s="21" t="str">
-        <x:v>{"A":"核对不完整：策略名称正确也需启用且商品命中。","B":"核对不完整：原因之外还需 ERP 开关和平台额度。","C":"核对不完整：ERP 开关不能替代千牛策略和原因范围。"}</x:v>
+        <x:v>{"B":"错售后类型：换货收货不是取消发货退款。","C":"错售后类型：补寄发货不产生该退款触发。","D":"错场景：入仓自动退用于买家退货收货。"}</x:v>
       </x:c>
       <x:c r="W261" s="21" t="str">
         <x:v>在未发货订单被 ERP 仓内拦截后，按千牛策略自动退款并保留不符合条件的人工复核。</x:v>
@@ -31614,7 +31616,7 @@
         <x:v>["策略、商品、退款原因或平台每日额度限制可能导致自动退款失败"]</x:v>
       </x:c>
       <x:c r="AC261" s="21" t="str">
-        <x:v>["忽略平台每日额度","只检查 ERP 取消结果不检查千牛条件"]</x:v>
+        <x:v>["把入仓自动退和仓内拦截混用","只开 ERP 开关不建千牛策略"]</x:v>
       </x:c>
       <x:c r="AD261" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -31627,7 +31629,7 @@
         <x:v>淘宝天猫—ERP仓内拦截自动退款</x:v>
       </x:c>
       <x:c r="AH261" s="21" t="str">
-        <x:v>淘宝天猫自动退款失败可由策略、商品、退款原因或每日额度限制导致。</x:v>
+        <x:v>淘宝天猫取消发货自动退款对应千牛 ERP仓内拦截自动退。</x:v>
       </x:c>
       <x:c r="AI261" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -31679,7 +31681,7 @@
     </x:row>
     <x:row r="262" ht="46" customHeight="1">
       <x:c r="A262" s="21" t="str">
-        <x:v>WDT-034-A</x:v>
+        <x:v>WDT-033-B</x:v>
       </x:c>
       <x:c r="B262" s="21" t="str">
         <x:v>旺店通-客服</x:v>
@@ -31688,19 +31690,19 @@
         <x:v>客服</x:v>
       </x:c>
       <x:c r="D262" s="21" t="str">
-        <x:v>换货流程</x:v>
+        <x:v>售后自动退款</x:v>
       </x:c>
       <x:c r="E262" s="21" t="str">
-        <x:v>通用</x:v>
+        <x:v>天猫/淘宝</x:v>
       </x:c>
       <x:c r="F262" s="21" t="str">
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G262" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>进阶</x:v>
       </x:c>
       <x:c r="H262" s="21" t="str">
-        <x:v>中</x:v>
+        <x:v>高</x:v>
       </x:c>
       <x:c r="I262" s="21" t="str">
         <x:v>practice</x:v>
@@ -31709,74 +31711,74 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K262" s="21" t="str">
-        <x:v>WDT-K034</x:v>
+        <x:v>WDT-K033</x:v>
       </x:c>
       <x:c r="L262" s="21" t="str">
-        <x:v>换货开关与状态</x:v>
+        <x:v>淘宝天猫仓内拦截自动退</x:v>
       </x:c>
       <x:c r="M262" s="21" t="str">
-        <x:v>先开启下载换货单，再按换货类型筛选</x:v>
+        <x:v>取消发货要命中仓内拦截策略</x:v>
       </x:c>
       <x:c r="N262" s="21" t="str">
-        <x:v>平台已有换货申请，但旺店通售后单中一直查不到；首先应核对哪个设置？</x:v>
+        <x:v>千牛仓内拦截策略已创建，但某笔取消发货仍未自动退款，哪组原因都属于应排查范围？</x:v>
       </x:c>
       <x:c r="O262" s="21" t="str">
-        <x:v>售后→售后管理→售后设置中的下载换货单是否已开启</x:v>
+        <x:v>只检查千牛策略名称正确，不核对策略启用状态和适用商品</x:v>
       </x:c>
       <x:c r="P262" s="21" t="str">
-        <x:v>售后→售后管理→售后设置中的自动退款是否已开启</x:v>
+        <x:v>只检查取消原因文字相同，不核对 ERP 开关和平台每日额度</x:v>
       </x:c>
       <x:c r="Q262" s="21" t="str">
-        <x:v>售后→售后管理→售后设置中的下载补寄单是否已开启</x:v>
+        <x:v>只检查 ERP 未发货自动退款已开启，不核对千牛策略和原因范围</x:v>
       </x:c>
       <x:c r="R262" s="21" t="str">
-        <x:v>售后→售后单中是否只筛选了退货退款而未检查下载开关</x:v>
+        <x:v>策略未启用、商品或退款原因不满足、达到平台每日额度限制</x:v>
       </x:c>
       <x:c r="S262" s="21" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="T262" s="21" t="str">
-        <x:v>售后→售后管理→售后设置中的下载换货单是否已开启</x:v>
+        <x:v>策略未启用、商品或退款原因不满足、达到平台每日额度限制</x:v>
       </x:c>
       <x:c r="U262" s="21" t="str">
-        <x:v>下载换货单默认关闭，换货售后查不到时应先核对这一开关。</x:v>
+        <x:v>资料列明策略、商品、退款原因和每日额度都可能阻断淘宝天猫自动退款。</x:v>
       </x:c>
       <x:c r="V262" s="21" t="str">
-        <x:v>{"B":"错开关：自动退款不控制换货单下载。","C":"错开关：下载补寄单不控制换货单。","D":"只改筛选不够：下载开关未启用时仍不会取得换货单。"}</x:v>
+        <x:v>{"A":"核对不完整：策略名称正确也需启用且商品命中。","B":"核对不完整：原因之外还需 ERP 开关和平台额度。","C":"核对不完整：ERP 开关不能替代千牛策略和原因范围。"}</x:v>
       </x:c>
       <x:c r="W262" s="21" t="str">
-        <x:v>确保平台换货单进入 ERP，并让客服按换货生命周期跟进收货和补发。</x:v>
+        <x:v>在未发货订单被 ERP 仓内拦截后，按千牛策略自动退款并保留不符合条件的人工复核。</x:v>
       </x:c>
       <x:c r="X262" s="21" t="str">
-        <x:v>["售后","售后管理","售后设置","下载换货单"]</x:v>
+        <x:v>["千牛售后服务平台","策略中心","应用库","ERP仓内拦截自动退"]</x:v>
       </x:c>
       <x:c r="Y262" s="21" t="str">
-        <x:v>["目标店铺支持并产生平台换货售后","ERP 下载换货单功能已开启"]</x:v>
+        <x:v>["千牛已配置并启用 ERP仓内拦截自动退策略","ERP 已开启未发货自动退款","退款原因与商品满足策略"]</x:v>
       </x:c>
       <x:c r="Z262" s="21" t="str">
-        <x:v>["进入售后设置开启下载换货单","回到售后单列表","筛选售后类型为换货","按卖家或买家处理状态推进","退回货品到仓后进入收货和补发流程"]</x:v>
+        <x:v>["进入千牛 ERP仓内拦截自动退应用","新增并设置策略条件","用案例验证后启用","在 ERP 开启未发货自动退款","取消发货后核对平台退款结果"]</x:v>
       </x:c>
       <x:c r="AA262" s="21" t="str">
-        <x:v>["换货售后能在列表中检索","当前状态能反映买卖双方处理进度"]</x:v>
+        <x:v>["符合条件的仓内拦截订单自动退款","不满足条件的售后转为人工核查"]</x:v>
       </x:c>
       <x:c r="AB262" s="21" t="str">
-        <x:v>["下载换货单默认关闭；未开启前不能以列表没有记录直接判断平台不存在换货申请"]</x:v>
+        <x:v>["策略、商品、退款原因或平台每日额度限制可能导致自动退款失败"]</x:v>
       </x:c>
       <x:c r="AC262" s="21" t="str">
-        <x:v>["把补寄开关当换货开关","未核对开关就重复抓单"]</x:v>
+        <x:v>["忽略平台每日额度","只检查 ERP 取消结果不检查千牛条件"]</x:v>
       </x:c>
       <x:c r="AD262" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
       </x:c>
       <x:c r="AE262" s="21" t="str">
-        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/zr84k6f4fb69aatg</x:v>
+        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/lfgmgszg7muigf79</x:v>
       </x:c>
       <x:c r="AF262" s="21" t="str"/>
       <x:c r="AG262" s="21" t="str">
-        <x:v>换货—开关、列表与状态</x:v>
+        <x:v>淘宝天猫—ERP仓内拦截自动退款</x:v>
       </x:c>
       <x:c r="AH262" s="21" t="str">
-        <x:v>下载换货单默认关闭，入口为售后→售后管理→售后设置。</x:v>
+        <x:v>淘宝天猫自动退款失败可由策略、商品、退款原因或每日额度限制导致。</x:v>
       </x:c>
       <x:c r="AI262" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -31820,7 +31822,7 @@
       <x:c r="AV262" s="21" t="str"/>
       <x:c r="AW262" s="21" t="str"/>
       <x:c r="AX262" s="21" t="str">
-        <x:v>启用并查询换货售后</x:v>
+        <x:v>配置淘宝天猫 ERP 仓内拦截自动退款</x:v>
       </x:c>
       <x:c r="AY262" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -31828,7 +31830,7 @@
     </x:row>
     <x:row r="263" ht="46" customHeight="1">
       <x:c r="A263" s="21" t="str">
-        <x:v>WDT-034-B</x:v>
+        <x:v>WDT-034-A</x:v>
       </x:c>
       <x:c r="B263" s="21" t="str">
         <x:v>旺店通-客服</x:v>
@@ -31846,7 +31848,7 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G263" s="21" t="str">
-        <x:v>基础</x:v>
+        <x:v>场景</x:v>
       </x:c>
       <x:c r="H263" s="21" t="str">
         <x:v>中</x:v>
@@ -31867,31 +31869,31 @@
         <x:v>先开启下载换货单，再按换货类型筛选</x:v>
       </x:c>
       <x:c r="N263" s="21" t="str">
-        <x:v>下载换货单已开启后，客服要集中跟进换货进度，正确的筛选方式是什么？</x:v>
+        <x:v>平台已有换货申请，但旺店通售后单中一直查不到；首先应核对哪个设置？</x:v>
       </x:c>
       <x:c r="O263" s="21" t="str">
-        <x:v>在售后单筛选售后类型为补寄，再按商家处理状态推断换货进度</x:v>
+        <x:v>售后→售后管理→售后设置中的下载换货单是否已开启</x:v>
       </x:c>
       <x:c r="P263" s="21" t="str">
-        <x:v>在售后单筛选售后类型为换货，再按买卖双方处理状态持续跟进</x:v>
+        <x:v>售后→售后管理→售后设置中的自动退款是否已开启</x:v>
       </x:c>
       <x:c r="Q263" s="21" t="str">
-        <x:v>在售后单筛选售后类型为退货退款，再按入库状态推断换货进度</x:v>
+        <x:v>售后→售后管理→售后设置中的下载补寄单是否已开启</x:v>
       </x:c>
       <x:c r="R263" s="21" t="str">
-        <x:v>在智能退货入库只筛已收货记录，再以收货状态代替全部换货状态</x:v>
+        <x:v>售后→售后单中是否只筛选了退货退款而未检查下载开关</x:v>
       </x:c>
       <x:c r="S263" s="21" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="T263" s="21" t="str">
-        <x:v>在售后单筛选售后类型为换货，再按买卖双方处理状态持续跟进</x:v>
+        <x:v>售后→售后管理→售后设置中的下载换货单是否已开启</x:v>
       </x:c>
       <x:c r="U263" s="21" t="str">
-        <x:v>换货记录位于售后单中，可按售后类型=换货筛选并跟进状态。</x:v>
+        <x:v>下载换货单默认关闭，换货售后查不到时应先核对这一开关。</x:v>
       </x:c>
       <x:c r="V263" s="21" t="str">
-        <x:v>{"A":"错类型：补寄和换货是不同售后类型。","C":"错类型：退货退款筛选会漏掉换货售后。","D":"错口径：收货状态只反映入库环节，不是完整换货生命周期。"}</x:v>
+        <x:v>{"B":"错开关：自动退款不控制换货单下载。","C":"错开关：下载补寄单不控制换货单。","D":"只改筛选不够：下载开关未启用时仍不会取得换货单。"}</x:v>
       </x:c>
       <x:c r="W263" s="21" t="str">
         <x:v>确保平台换货单进入 ERP，并让客服按换货生命周期跟进收货和补发。</x:v>
@@ -31912,7 +31914,7 @@
         <x:v>["下载换货单默认关闭；未开启前不能以列表没有记录直接判断平台不存在换货申请"]</x:v>
       </x:c>
       <x:c r="AC263" s="21" t="str">
-        <x:v>["在原订单列表追换货生命周期","用报表代替售后状态查询"]</x:v>
+        <x:v>["把补寄开关当换货开关","未核对开关就重复抓单"]</x:v>
       </x:c>
       <x:c r="AD263" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -31925,7 +31927,7 @@
         <x:v>换货—开关、列表与状态</x:v>
       </x:c>
       <x:c r="AH263" s="21" t="str">
-        <x:v>售后单按售后类型=换货筛选，状态反映买卖双方处理生命周期。</x:v>
+        <x:v>下载换货单默认关闭，入口为售后→售后管理→售后设置。</x:v>
       </x:c>
       <x:c r="AI263" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -31977,7 +31979,7 @@
     </x:row>
     <x:row r="264" ht="46" customHeight="1">
       <x:c r="A264" s="21" t="str">
-        <x:v>WDT-035-A</x:v>
+        <x:v>WDT-034-B</x:v>
       </x:c>
       <x:c r="B264" s="21" t="str">
         <x:v>旺店通-客服</x:v>
@@ -31995,10 +31997,10 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G264" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="H264" s="21" t="str">
-        <x:v>高</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I264" s="21" t="str">
         <x:v>practice</x:v>
@@ -32007,61 +32009,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K264" s="21" t="str">
-        <x:v>WDT-K035</x:v>
+        <x:v>WDT-K034</x:v>
       </x:c>
       <x:c r="L264" s="21" t="str">
-        <x:v>换货收货与换货单生成</x:v>
+        <x:v>换货开关与状态</x:v>
       </x:c>
       <x:c r="M264" s="21" t="str">
-        <x:v>退回货品先收货，符合状态再生成补发单</x:v>
+        <x:v>先开启下载换货单，再按换货类型筛选</x:v>
       </x:c>
       <x:c r="N264" s="21" t="str">
-        <x:v>换货退回件已到仓且订单审核功能开启，正确的后续处理是什么？</x:v>
+        <x:v>下载换货单已开启后，客服要集中跟进换货进度，正确的筛选方式是什么？</x:v>
       </x:c>
       <x:c r="O264" s="21" t="str">
-        <x:v>只对实际退回货品收货，生成换货补发单后直接跳到待发货处理</x:v>
+        <x:v>在售后单筛选售后类型为补寄，再按商家处理状态推断换货进度</x:v>
       </x:c>
       <x:c r="P264" s="21" t="str">
-        <x:v>只对实际退回货品收货，未核对状态就直接再次生成换货补发单</x:v>
+        <x:v>在售后单筛选售后类型为换货，再按买卖双方处理状态持续跟进</x:v>
       </x:c>
       <x:c r="Q264" s="21" t="str">
-        <x:v>把退回货品和换出货品一起收货，再将换货补发单合并到原订单</x:v>
+        <x:v>在售后单筛选售后类型为退货退款，再按入库状态推断换货进度</x:v>
       </x:c>
       <x:c r="R264" s="21" t="str">
-        <x:v>只对实际退回货品收货，生成换货补发单后到待审核中继续处理</x:v>
+        <x:v>在智能退货入库只筛已收货记录，再以收货状态代替全部换货状态</x:v>
       </x:c>
       <x:c r="S264" s="21" t="str">
-        <x:v>D</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="T264" s="21" t="str">
-        <x:v>只对实际退回货品收货，生成换货补发单后到待审核中继续处理</x:v>
+        <x:v>在售后单筛选售后类型为换货，再按买卖双方处理状态持续跟进</x:v>
       </x:c>
       <x:c r="U264" s="21" t="str">
-        <x:v>智能退货入库只接收退回货品；订单审核开启时，生成的换货补发单进入待审核。</x:v>
+        <x:v>换货记录位于售后单中，可按售后类型=换货筛选并跟进状态。</x:v>
       </x:c>
       <x:c r="V264" s="21" t="str">
-        <x:v>{"A":"错状态：审核开启时生成后应进入待审核，不是直接待发货。","B":"缺状态核对：可能造成已生成补发单的售后重复生成。","C":"错货品与限制：只收退回品，且换货补发单不能合并。"}</x:v>
+        <x:v>{"A":"错类型：补寄和换货是不同售后类型。","C":"错类型：退货退款筛选会漏掉换货售后。","D":"错口径：收货状态只反映入库环节，不是完整换货生命周期。"}</x:v>
       </x:c>
       <x:c r="W264" s="21" t="str">
-        <x:v>在确认退回货品后正确生成换货补发单，并阻止重复补发或异常状态下生成。</x:v>
+        <x:v>确保平台换货单进入 ERP，并让客服按换货生命周期跟进收货和补发。</x:v>
       </x:c>
       <x:c r="X264" s="21" t="str">
-        <x:v>["售后","智能退货入库","扫描退货信息","收货","生成换货单"]</x:v>
+        <x:v>["售后","售后管理","售后设置","下载换货单"]</x:v>
       </x:c>
       <x:c r="Y264" s="21" t="str">
-        <x:v>["已定位到换货售后","已核对退回货品、换出货品及申请数量","售后状态允许生成且未生成过补发单"]</x:v>
+        <x:v>["目标店铺支持并产生平台换货售后","ERP 下载换货单功能已开启"]</x:v>
       </x:c>
       <x:c r="Z264" s="21" t="str">
-        <x:v>["扫描退货物流、手机号或平台订单定位售后","只对实际退回货品确认收货数量","完成智能退货入库","手工生成或按设置自动生成换货补发单","在订单审核开启时到待审核继续处理，否则到待发货"]</x:v>
+        <x:v>["进入售后设置开启下载换货单","回到售后单列表","筛选售后类型为换货","按卖家或买家处理状态推进","退回货品到仓后进入收货和补发流程"]</x:v>
       </x:c>
       <x:c r="AA264" s="21" t="str">
-        <x:v>["退回货品和换出货品信息核对一致","换货补发单只生成一次","生成后进入正确订单状态"]</x:v>
+        <x:v>["换货售后能在列表中检索","当前状态能反映买卖双方处理进度"]</x:v>
       </x:c>
       <x:c r="AB264" s="21" t="str">
-        <x:v>["待确认、待推单、推单失败、已取消、拒绝后等待买家修改或已发送换货单等状态会阻止生成","换货补发单不能预发货、拆分或合并","打印或发货后取消会被异常订单拦截"]</x:v>
+        <x:v>["下载换货单默认关闭；未开启前不能以列表没有记录直接判断平台不存在换货申请"]</x:v>
       </x:c>
       <x:c r="AC264" s="21" t="str">
-        <x:v>["把换出货品计入退货入库","在换货单上执行预发货或合并"]</x:v>
+        <x:v>["在原订单列表追换货生命周期","用报表代替售后状态查询"]</x:v>
       </x:c>
       <x:c r="AD264" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -32071,10 +32073,10 @@
       </x:c>
       <x:c r="AF264" s="21" t="str"/>
       <x:c r="AG264" s="21" t="str">
-        <x:v>换货—智能收货、生成换货单与限制</x:v>
+        <x:v>换货—开关、列表与状态</x:v>
       </x:c>
       <x:c r="AH264" s="21" t="str">
-        <x:v>换货智能入库只收退回货品；生成的换货补发单在开启审核时进入待审核。</x:v>
+        <x:v>售后单按售后类型=换货筛选，状态反映买卖双方处理生命周期。</x:v>
       </x:c>
       <x:c r="AI264" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -32118,7 +32120,7 @@
       <x:c r="AV264" s="21" t="str"/>
       <x:c r="AW264" s="21" t="str"/>
       <x:c r="AX264" s="21" t="str">
-        <x:v>收货后生成换货补发单并识别限制</x:v>
+        <x:v>启用并查询换货售后</x:v>
       </x:c>
       <x:c r="AY264" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -32126,7 +32128,7 @@
     </x:row>
     <x:row r="265" ht="46" customHeight="1">
       <x:c r="A265" s="21" t="str">
-        <x:v>WDT-035-B</x:v>
+        <x:v>WDT-035-A</x:v>
       </x:c>
       <x:c r="B265" s="21" t="str">
         <x:v>旺店通-客服</x:v>
@@ -32144,7 +32146,7 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G265" s="21" t="str">
-        <x:v>进阶</x:v>
+        <x:v>场景</x:v>
       </x:c>
       <x:c r="H265" s="21" t="str">
         <x:v>高</x:v>
@@ -32165,31 +32167,31 @@
         <x:v>退回货品先收货，符合状态再生成补发单</x:v>
       </x:c>
       <x:c r="N265" s="21" t="str">
-        <x:v>以下哪种售后状态会阻止再次生成换货补发单？</x:v>
+        <x:v>换货退回件已到仓且订单审核功能开启，正确的后续处理是什么？</x:v>
       </x:c>
       <x:c r="O265" s="21" t="str">
-        <x:v>退回货品已全部收货，且当前状态允许生成补发单</x:v>
+        <x:v>只对实际退回货品收货，生成换货补发单后直接跳到待发货处理</x:v>
       </x:c>
       <x:c r="P265" s="21" t="str">
-        <x:v>已发送换货单，或处于待确认、推单失败等受限状态</x:v>
+        <x:v>只对实际退回货品收货，未核对状态就直接再次生成换货补发单</x:v>
       </x:c>
       <x:c r="Q265" s="21" t="str">
-        <x:v>售后已完成智能退货入库，且订单审核功能当前已开启</x:v>
+        <x:v>把退回货品和换出货品一起收货，再将换货补发单合并到原订单</x:v>
       </x:c>
       <x:c r="R265" s="21" t="str">
-        <x:v>买家已填写退货物流，但换货补发单尚未生成</x:v>
+        <x:v>只对实际退回货品收货，生成换货补发单后到待审核中继续处理</x:v>
       </x:c>
       <x:c r="S265" s="21" t="str">
-        <x:v>B</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="T265" s="21" t="str">
-        <x:v>已发送换货单，或处于待确认、推单失败等受限状态</x:v>
+        <x:v>只对实际退回货品收货，生成换货补发单后到待审核中继续处理</x:v>
       </x:c>
       <x:c r="U265" s="21" t="str">
-        <x:v>资料明确列出已发送换货单以及待确认、待推单、推单失败、已取消等状态不可生成。</x:v>
+        <x:v>智能退货入库只接收退回货品；订单审核开启时，生成的换货补发单进入待审核。</x:v>
       </x:c>
       <x:c r="V265" s="21" t="str">
-        <x:v>{"A":"允许场景：已收货且状态允许时可生成。","C":"错条件：审核开启只决定生成后进入待审核。","D":"非必然阻止：填写物流且未生成并不是资料列出的禁止状态。"}</x:v>
+        <x:v>{"A":"错状态：审核开启时生成后应进入待审核，不是直接待发货。","B":"缺状态核对：可能造成已生成补发单的售后重复生成。","C":"错货品与限制：只收退回品，且换货补发单不能合并。"}</x:v>
       </x:c>
       <x:c r="W265" s="21" t="str">
         <x:v>在确认退回货品后正确生成换货补发单，并阻止重复补发或异常状态下生成。</x:v>
@@ -32210,7 +32212,7 @@
         <x:v>["待确认、待推单、推单失败、已取消、拒绝后等待买家修改或已发送换货单等状态会阻止生成","换货补发单不能预发货、拆分或合并","打印或发货后取消会被异常订单拦截"]</x:v>
       </x:c>
       <x:c r="AC265" s="21" t="str">
-        <x:v>["忽略已生成标记导致重复补发","把审核开关误当生成限制"]</x:v>
+        <x:v>["把换出货品计入退货入库","在换货单上执行预发货或合并"]</x:v>
       </x:c>
       <x:c r="AD265" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -32223,7 +32225,7 @@
         <x:v>换货—智能收货、生成换货单与限制</x:v>
       </x:c>
       <x:c r="AH265" s="21" t="str">
-        <x:v>已发送换货单，或待确认、待推单、推单失败、已取消等状态会阻止换货单生成。</x:v>
+        <x:v>换货智能入库只收退回货品；生成的换货补发单在开启审核时进入待审核。</x:v>
       </x:c>
       <x:c r="AI265" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -32275,7 +32277,7 @@
     </x:row>
     <x:row r="266" ht="46" customHeight="1">
       <x:c r="A266" s="21" t="str">
-        <x:v>WDT-036-A</x:v>
+        <x:v>WDT-035-B</x:v>
       </x:c>
       <x:c r="B266" s="21" t="str">
         <x:v>旺店通-客服</x:v>
@@ -32284,7 +32286,7 @@
         <x:v>客服</x:v>
       </x:c>
       <x:c r="D266" s="21" t="str">
-        <x:v>补寄流程</x:v>
+        <x:v>换货流程</x:v>
       </x:c>
       <x:c r="E266" s="21" t="str">
         <x:v>通用</x:v>
@@ -32293,10 +32295,10 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G266" s="21" t="str">
-        <x:v>基础</x:v>
+        <x:v>进阶</x:v>
       </x:c>
       <x:c r="H266" s="21" t="str">
-        <x:v>中</x:v>
+        <x:v>高</x:v>
       </x:c>
       <x:c r="I266" s="21" t="str">
         <x:v>practice</x:v>
@@ -32305,74 +32307,74 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K266" s="21" t="str">
-        <x:v>WDT-K036</x:v>
+        <x:v>WDT-K035</x:v>
       </x:c>
       <x:c r="L266" s="21" t="str">
-        <x:v>补寄开关与生成限制</x:v>
+        <x:v>换货收货与换货单生成</x:v>
       </x:c>
       <x:c r="M266" s="21" t="str">
-        <x:v>补寄默认关闭，申请时生成需先拦截</x:v>
+        <x:v>退回货品先收货，符合状态再生成补发单</x:v>
       </x:c>
       <x:c r="N266" s="21" t="str">
-        <x:v>平台已有补寄申请但 ERP 没有补寄单，且该功能从未配置；首先应做什么？</x:v>
+        <x:v>以下哪种售后状态会阻止再次生成换货补发单？</x:v>
       </x:c>
       <x:c r="O266" s="21" t="str">
-        <x:v>在售后管理的售后设置开启自动退款，再检查退款记录</x:v>
+        <x:v>退回货品已全部收货，且当前状态允许生成补发单</x:v>
       </x:c>
       <x:c r="P266" s="21" t="str">
-        <x:v>在售后单直接新建补寄记录，不核对下载补寄单开关</x:v>
+        <x:v>已发送换货单，或处于待确认、推单失败等受限状态</x:v>
       </x:c>
       <x:c r="Q266" s="21" t="str">
-        <x:v>在售后管理的售后设置开启下载换货单，再检查换货记录</x:v>
+        <x:v>售后已完成智能退货入库，且订单审核功能当前已开启</x:v>
       </x:c>
       <x:c r="R266" s="21" t="str">
-        <x:v>在售后管理的售后设置开启下载补寄单，再检查售后记录</x:v>
+        <x:v>买家已填写退货物流，但换货补发单尚未生成</x:v>
       </x:c>
       <x:c r="S266" s="21" t="str">
-        <x:v>D</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="T266" s="21" t="str">
-        <x:v>在售后管理的售后设置开启下载补寄单，再检查售后记录</x:v>
+        <x:v>已发送换货单，或处于待确认、推单失败等受限状态</x:v>
       </x:c>
       <x:c r="U266" s="21" t="str">
-        <x:v>下载补寄单默认关闭，首次排查应先核对售后设置中的对应开关。</x:v>
+        <x:v>资料明确列出已发送换货单以及待确认、待推单、推单失败、已取消等状态不可生成。</x:v>
       </x:c>
       <x:c r="V266" s="21" t="str">
-        <x:v>{"A":"错开关：自动退款不控制补寄单下载。","B":"绕过根因：应先开启补寄下载并检查平台记录。","C":"错开关：下载换货单不控制补寄申请。"}</x:v>
+        <x:v>{"A":"允许场景：已收货且状态允许时可生成。","C":"错条件：审核开启只决定生成后进入待审核。","D":"非必然阻止：填写物流且未生成并不是资料列出的禁止状态。"}</x:v>
       </x:c>
       <x:c r="W266" s="21" t="str">
-        <x:v>让补寄申请按正确时点生成补发订单，并在商家同意前阻止仓库误发。</x:v>
+        <x:v>在确认退回货品后正确生成换货补发单，并阻止重复补发或异常状态下生成。</x:v>
       </x:c>
       <x:c r="X266" s="21" t="str">
-        <x:v>["售后","售后管理","售后设置","下载补寄单"]</x:v>
+        <x:v>["售后","智能退货入库","扫描退货信息","收货","生成换货单"]</x:v>
       </x:c>
       <x:c r="Y266" s="21" t="str">
-        <x:v>["下载补寄单已开启","售后尚未生成补寄单且当前状态允许","已选择申请时或同意后自动生成方式"]</x:v>
+        <x:v>["已定位到换货售后","已核对退回货品、换出货品及申请数量","售后状态允许生成且未生成过补发单"]</x:v>
       </x:c>
       <x:c r="Z266" s="21" t="str">
-        <x:v>["开启下载补寄单","按未生成状态筛选售后","选择手工生成或配置自动生成时点","若申请时生成则给补寄订单加异常标记","商家同意后移除标记再履约"]</x:v>
+        <x:v>["扫描退货物流、手机号或平台订单定位售后","只对实际退回货品确认收货数量","完成智能退货入库","手工生成或按设置自动生成换货补发单","在订单审核开启时到待审核继续处理，否则到待发货"]</x:v>
       </x:c>
       <x:c r="AA266" s="21" t="str">
-        <x:v>["补寄单仅生成一次","商家未同意前订单不会误发","补寄发货后物流回写到售后"]</x:v>
+        <x:v>["退回货品和换出货品信息核对一致","换货补发单只生成一次","生成后进入正确订单状态"]</x:v>
       </x:c>
       <x:c r="AB266" s="21" t="str">
-        <x:v>["待确认、待推单、推单失败、已取消、拒绝后等待买家修改或已发送补寄单等状态会阻止生成"]</x:v>
+        <x:v>["待确认、待推单、推单失败、已取消、拒绝后等待买家修改或已发送换货单等状态会阻止生成","换货补发单不能预发货、拆分或合并","打印或发货后取消会被异常订单拦截"]</x:v>
       </x:c>
       <x:c r="AC266" s="21" t="str">
-        <x:v>["把换货开关当补寄开关","用重新抓取订单代替开启售后下载"]</x:v>
+        <x:v>["忽略已生成标记导致重复补发","把审核开关误当生成限制"]</x:v>
       </x:c>
       <x:c r="AD266" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
       </x:c>
       <x:c r="AE266" s="21" t="str">
-        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/nqi6zfy7n0aq9vyy</x:v>
+        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/zr84k6f4fb69aatg</x:v>
       </x:c>
       <x:c r="AF266" s="21" t="str"/>
       <x:c r="AG266" s="21" t="str">
-        <x:v>补寄—开关、生成时点与限制</x:v>
+        <x:v>换货—智能收货、生成换货单与限制</x:v>
       </x:c>
       <x:c r="AH266" s="21" t="str">
-        <x:v>下载补寄单默认关闭，需在售后管理的售后设置中开启。</x:v>
+        <x:v>已发送换货单，或待确认、待推单、推单失败、已取消等状态会阻止换货单生成。</x:v>
       </x:c>
       <x:c r="AI266" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -32416,7 +32418,7 @@
       <x:c r="AV266" s="21" t="str"/>
       <x:c r="AW266" s="21" t="str"/>
       <x:c r="AX266" s="21" t="str">
-        <x:v>启用补寄单并防止未审核补发</x:v>
+        <x:v>收货后生成换货补发单并识别限制</x:v>
       </x:c>
       <x:c r="AY266" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -32424,7 +32426,7 @@
     </x:row>
     <x:row r="267" ht="46" customHeight="1">
       <x:c r="A267" s="21" t="str">
-        <x:v>WDT-036-B</x:v>
+        <x:v>WDT-036-A</x:v>
       </x:c>
       <x:c r="B267" s="21" t="str">
         <x:v>旺店通-客服</x:v>
@@ -32442,16 +32444,16 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G267" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="H267" s="21" t="str">
-        <x:v>高</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I267" s="21" t="str">
-        <x:v>redline</x:v>
+        <x:v>practice</x:v>
       </x:c>
       <x:c r="J267" s="22" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K267" s="21" t="str">
         <x:v>WDT-K036</x:v>
@@ -32463,31 +32465,31 @@
         <x:v>补寄默认关闭，申请时生成需先拦截</x:v>
       </x:c>
       <x:c r="N267" s="21" t="str">
-        <x:v>公司选择在买家提交补寄申请时自动生成补寄订单，按资料规定的标准控制措施，应怎样避免商家尚未同意就被仓库发出？</x:v>
+        <x:v>平台已有补寄申请但 ERP 没有补寄单，且该功能从未配置；首先应做什么？</x:v>
       </x:c>
       <x:c r="O267" s="21" t="str">
-        <x:v>生成时给补寄订单加异常标记，商家同意后再移除标记</x:v>
+        <x:v>在售后管理的售后设置开启自动退款，再检查退款记录</x:v>
       </x:c>
       <x:c r="P267" s="21" t="str">
-        <x:v>生成后先驳回审核，商家同意后再重新生成一张补寄单</x:v>
+        <x:v>在售后单直接新建补寄记录，不核对下载补寄单开关</x:v>
       </x:c>
       <x:c r="Q267" s="21" t="str">
-        <x:v>生成后只加客服备注，补寄订单仍允许进入仓库处理</x:v>
+        <x:v>在售后管理的售后设置开启下载换货单，再检查换货记录</x:v>
       </x:c>
       <x:c r="R267" s="21" t="str">
-        <x:v>生成后停在待审核，商家同意后普通审核但不加异常标记</x:v>
+        <x:v>在售后管理的售后设置开启下载补寄单，再检查售后记录</x:v>
       </x:c>
       <x:c r="S267" s="21" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="T267" s="21" t="str">
-        <x:v>生成时给补寄订单加异常标记，商家同意后再移除标记</x:v>
+        <x:v>在售后管理的售后设置开启下载补寄单，再检查售后记录</x:v>
       </x:c>
       <x:c r="U267" s="21" t="str">
-        <x:v>申请时生成比商家审批更早，资料要求先用异常标记拦截，批准后再放行。</x:v>
+        <x:v>下载补寄单默认关闭，首次排查应先核对售后设置中的对应开关。</x:v>
       </x:c>
       <x:c r="V267" s="21" t="str">
-        <x:v>{"B":"错流程：无需删除并重建，批准后移除异常标记即可。","C":"拦截不足：客服备注不能阻止补寄订单进入仓库。","D":"漏拦截：待审核状态本身不能替代资料要求的异常标记。"}</x:v>
+        <x:v>{"A":"错开关：自动退款不控制补寄单下载。","B":"绕过根因：应先开启补寄下载并检查平台记录。","C":"错开关：下载换货单不控制补寄申请。"}</x:v>
       </x:c>
       <x:c r="W267" s="21" t="str">
         <x:v>让补寄申请按正确时点生成补发订单，并在商家同意前阻止仓库误发。</x:v>
@@ -32508,7 +32510,7 @@
         <x:v>["待确认、待推单、推单失败、已取消、拒绝后等待买家修改或已发送补寄单等状态会阻止生成"]</x:v>
       </x:c>
       <x:c r="AC267" s="21" t="str">
-        <x:v>["未审批就放行仓库发货","商家同意后忘记移除异常标记"]</x:v>
+        <x:v>["把换货开关当补寄开关","用重新抓取订单代替开启售后下载"]</x:v>
       </x:c>
       <x:c r="AD267" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -32521,7 +32523,7 @@
         <x:v>补寄—开关、生成时点与限制</x:v>
       </x:c>
       <x:c r="AH267" s="21" t="str">
-        <x:v>补寄单在申请时自动生成时应添加异常标记，商家同意后移除。</x:v>
+        <x:v>下载补寄单默认关闭，需在售后管理的售后设置中开启。</x:v>
       </x:c>
       <x:c r="AI267" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -32573,7 +32575,7 @@
     </x:row>
     <x:row r="268" ht="46" customHeight="1">
       <x:c r="A268" s="21" t="str">
-        <x:v>WDT-037-A</x:v>
+        <x:v>WDT-036-B</x:v>
       </x:c>
       <x:c r="B268" s="21" t="str">
         <x:v>旺店通-客服</x:v>
@@ -32582,7 +32584,7 @@
         <x:v>客服</x:v>
       </x:c>
       <x:c r="D268" s="21" t="str">
-        <x:v>智能退货入库</x:v>
+        <x:v>补寄流程</x:v>
       </x:c>
       <x:c r="E268" s="21" t="str">
         <x:v>通用</x:v>
@@ -32594,83 +32596,83 @@
         <x:v>场景</x:v>
       </x:c>
       <x:c r="H268" s="21" t="str">
-        <x:v>中</x:v>
+        <x:v>高</x:v>
       </x:c>
       <x:c r="I268" s="21" t="str">
-        <x:v>practice</x:v>
+        <x:v>redline</x:v>
       </x:c>
       <x:c r="J268" s="22" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K268" s="21" t="str">
-        <x:v>WDT-K037</x:v>
+        <x:v>WDT-K036</x:v>
       </x:c>
       <x:c r="L268" s="21" t="str">
-        <x:v>智能退货入库边界</x:v>
+        <x:v>补寄开关与生成限制</x:v>
       </x:c>
       <x:c r="M268" s="21" t="str">
-        <x:v>扫描定位、按实收数量入库、拒收只改状态</x:v>
+        <x:v>补寄默认关闭，申请时生成需先拦截</x:v>
       </x:c>
       <x:c r="N268" s="21" t="str">
-        <x:v>退件已到仓，但平台售后没有填写退货物流，扫描物流号查不到；资料给出的替代查找方式是什么？</x:v>
+        <x:v>公司选择在买家提交补寄申请时自动生成补寄订单，按资料规定的标准控制措施，应怎样避免商家尚未同意就被仓库发出？</x:v>
       </x:c>
       <x:c r="O268" s="21" t="str">
-        <x:v>用手机号或买家昵称只查询近六个月待审核订单</x:v>
+        <x:v>生成时给补寄订单加异常标记，商家同意后再移除标记</x:v>
       </x:c>
       <x:c r="P268" s="21" t="str">
-        <x:v>先手工补填任意退货物流号，再继续只按物流号扫描</x:v>
+        <x:v>生成后先驳回审核，商家同意后再重新生成一张补寄单</x:v>
       </x:c>
       <x:c r="Q268" s="21" t="str">
-        <x:v>用手机号或买家昵称查询近六个月已完成或退款订单</x:v>
+        <x:v>生成后只加客服备注，补寄订单仍允许进入仓库处理</x:v>
       </x:c>
       <x:c r="R268" s="21" t="str">
-        <x:v>用平台订单号只查询近六个月尚未退款的售后单</x:v>
+        <x:v>生成后停在待审核，商家同意后普通审核但不加异常标记</x:v>
       </x:c>
       <x:c r="S268" s="21" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="T268" s="21" t="str">
-        <x:v>用手机号或买家昵称查询近六个月已完成或退款订单</x:v>
+        <x:v>生成时给补寄订单加异常标记，商家同意后再移除标记</x:v>
       </x:c>
       <x:c r="U268" s="21" t="str">
-        <x:v>没有退货物流时无法依赖单号，资料允许用手机号或买家昵称查近六个月相关订单。</x:v>
+        <x:v>申请时生成比商家审批更早，资料要求先用异常标记拦截，批准后再放行。</x:v>
       </x:c>
       <x:c r="V268" s="21" t="str">
-        <x:v>{"A":"错订单范围：资料指定近六个月已完成或退款订单。","B":"错误补录：不能为检索方便填写并不存在的物流号。","D":"范围过窄：未填写物流时资料给出的替代是手机号或昵称。"}</x:v>
+        <x:v>{"B":"错流程：无需删除并重建，批准后移除异常标记即可。","C":"拦截不足：客服备注不能阻止补寄订单进入仓库。","D":"漏拦截：待审核状态本身不能替代资料要求的异常标记。"}</x:v>
       </x:c>
       <x:c r="W268" s="21" t="str">
-        <x:v>准确定位退货售后，支持同单分批收货，并清楚拒收不会自动执行其他售后动作。</x:v>
+        <x:v>让补寄申请按正确时点生成补发订单，并在商家同意前阻止仓库误发。</x:v>
       </x:c>
       <x:c r="X268" s="21" t="str">
-        <x:v>["售后","智能退货入库"]</x:v>
+        <x:v>["售后","售后管理","售后设置","下载补寄单"]</x:v>
       </x:c>
       <x:c r="Y268" s="21" t="str">
-        <x:v>["退件已到仓或已取得可查询信息","已确认实际退回货品和数量"]</x:v>
+        <x:v>["下载补寄单已开启","售后尚未生成补寄单且当前状态允许","已选择申请时或同意后自动生成方式"]</x:v>
       </x:c>
       <x:c r="Z268" s="21" t="str">
-        <x:v>["扫描退货物流、手机号、平台订单或拣货标签定位售后","核对并可编辑本次收货数量","点击收货生成退货入库单","分批退回时后续继续读取剩余数量","拒绝入库时明确仅变更为拒绝入库状态"]</x:v>
+        <x:v>["开启下载补寄单","按未生成状态筛选售后","选择手工生成或配置自动生成时点","若申请时生成则给补寄订单加异常标记","商家同意后移除标记再履约"]</x:v>
       </x:c>
       <x:c r="AA268" s="21" t="str">
-        <x:v>["本次实收数量准确","售后显示部分或全部入库状态","分批收货后剩余待收数量正确","拒收后未误以为已退款或已取消"]</x:v>
+        <x:v>["补寄单仅生成一次","商家未同意前订单不会误发","补寄发货后物流回写到售后"]</x:v>
       </x:c>
       <x:c r="AB268" s="21" t="str">
-        <x:v>["未填写退货物流时直接扫物流可能失败，可用手机号或买家昵称查近六个月已完成或退款订单","同一物流号可匹配多张售后并一起收货","拒收只把状态改为拒绝入库，不会自动产生其他变化"]</x:v>
+        <x:v>["待确认、待推单、推单失败、已取消、拒绝后等待买家修改或已发送补寄单等状态会阻止生成"]</x:v>
       </x:c>
       <x:c r="AC268" s="21" t="str">
-        <x:v>["反复扫描未回传的物流号","通过改库存绕过售后收货"]</x:v>
+        <x:v>["未审批就放行仓库发货","商家同意后忘记移除异常标记"]</x:v>
       </x:c>
       <x:c r="AD268" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
       </x:c>
       <x:c r="AE268" s="21" t="str">
-        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/lz8g3ml0cdikdpeu</x:v>
+        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/nqi6zfy7n0aq9vyy</x:v>
       </x:c>
       <x:c r="AF268" s="21" t="str"/>
       <x:c r="AG268" s="21" t="str">
-        <x:v>智能退货入库—查询、分批收货与拒收</x:v>
+        <x:v>补寄—开关、生成时点与限制</x:v>
       </x:c>
       <x:c r="AH268" s="21" t="str">
-        <x:v>无退货物流时可用手机号或买家昵称查近六个月已完成或退款订单。</x:v>
+        <x:v>补寄单在申请时自动生成时应添加异常标记，商家同意后移除。</x:v>
       </x:c>
       <x:c r="AI268" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -32714,7 +32716,7 @@
       <x:c r="AV268" s="21" t="str"/>
       <x:c r="AW268" s="21" t="str"/>
       <x:c r="AX268" s="21" t="str">
-        <x:v>执行智能退货入库并处理分批与拒收</x:v>
+        <x:v>启用补寄单并防止未审核补发</x:v>
       </x:c>
       <x:c r="AY268" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -32722,7 +32724,7 @@
     </x:row>
     <x:row r="269" ht="46" customHeight="1">
       <x:c r="A269" s="21" t="str">
-        <x:v>WDT-037-B</x:v>
+        <x:v>WDT-037-A</x:v>
       </x:c>
       <x:c r="B269" s="21" t="str">
         <x:v>旺店通-客服</x:v>
@@ -32740,10 +32742,10 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G269" s="21" t="str">
-        <x:v>进阶</x:v>
+        <x:v>场景</x:v>
       </x:c>
       <x:c r="H269" s="21" t="str">
-        <x:v>高</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I269" s="21" t="str">
         <x:v>practice</x:v>
@@ -32761,31 +32763,31 @@
         <x:v>扫描定位、按实收数量入库、拒收只改状态</x:v>
       </x:c>
       <x:c r="N269" s="21" t="str">
-        <x:v>同一售后分两次退回，第一次只收到部分商品，应怎样记录本次收货？</x:v>
+        <x:v>退件已到仓，但平台售后没有填写退货物流，扫描物流号查不到；资料给出的替代查找方式是什么？</x:v>
       </x:c>
       <x:c r="O269" s="21" t="str">
-        <x:v>第一次按申请总数全部收货，第二次到货后用入库纠错补记</x:v>
+        <x:v>用手机号或买家昵称只查询近六个月待审核订单</x:v>
       </x:c>
       <x:c r="P269" s="21" t="str">
-        <x:v>按本次实收量部分收货，后续到货时再收剩余量</x:v>
+        <x:v>先手工补填任意退货物流号，再继续只按物流号扫描</x:v>
       </x:c>
       <x:c r="Q269" s="21" t="str">
-        <x:v>两批到齐后再一次性收货，第一次到货不留部分收货记录</x:v>
+        <x:v>用手机号或买家昵称查询近六个月已完成或退款订单</x:v>
       </x:c>
       <x:c r="R269" s="21" t="str">
-        <x:v>第一次按实收量收货，第二次另建系统售后再收余量</x:v>
+        <x:v>用平台订单号只查询近六个月尚未退款的售后单</x:v>
       </x:c>
       <x:c r="S269" s="21" t="str">
-        <x:v>B</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="T269" s="21" t="str">
-        <x:v>按本次实收量部分收货，后续到货时再收剩余量</x:v>
+        <x:v>用手机号或买家昵称查询近六个月已完成或退款订单</x:v>
       </x:c>
       <x:c r="U269" s="21" t="str">
-        <x:v>智能退货入库支持部分和多次收货，首次按实收量记录，后续继续读取剩余数量。</x:v>
+        <x:v>没有退货物流时无法依赖单号，资料允许用手机号或买家昵称查近六个月相关订单。</x:v>
       </x:c>
       <x:c r="V269" s="21" t="str">
-        <x:v>{"A":"错数量：应按本次实收数量收货，不可虚增。","C":"漏记录：首次实收应当及时部分收货，不能等齐后合并记录。","D":"错对象：同一售后支持多次收货，无需另建售后单。"}</x:v>
+        <x:v>{"A":"错订单范围：资料指定近六个月已完成或退款订单。","B":"错误补录：不能为检索方便填写并不存在的物流号。","D":"范围过窄：未填写物流时资料给出的替代是手机号或昵称。"}</x:v>
       </x:c>
       <x:c r="W269" s="21" t="str">
         <x:v>准确定位退货售后，支持同单分批收货，并清楚拒收不会自动执行其他售后动作。</x:v>
@@ -32806,7 +32808,7 @@
         <x:v>["未填写退货物流时直接扫物流可能失败，可用手机号或买家昵称查近六个月已完成或退款订单","同一物流号可匹配多张售后并一起收货","拒收只把状态改为拒绝入库，不会自动产生其他变化"]</x:v>
       </x:c>
       <x:c r="AC269" s="21" t="str">
-        <x:v>["部分到货按全部收货","等待全部到齐而不留首次收货记录"]</x:v>
+        <x:v>["反复扫描未回传的物流号","通过改库存绕过售后收货"]</x:v>
       </x:c>
       <x:c r="AD269" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -32819,7 +32821,7 @@
         <x:v>智能退货入库—查询、分批收货与拒收</x:v>
       </x:c>
       <x:c r="AH269" s="21" t="str">
-        <x:v>智能退货入库支持部分及多次收货，后续读取剩余数量。</x:v>
+        <x:v>无退货物流时可用手机号或买家昵称查近六个月已完成或退款订单。</x:v>
       </x:c>
       <x:c r="AI269" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -32871,16 +32873,16 @@
     </x:row>
     <x:row r="270" ht="46" customHeight="1">
       <x:c r="A270" s="21" t="str">
-        <x:v>WDT-038-A</x:v>
+        <x:v>WDT-037-B</x:v>
       </x:c>
       <x:c r="B270" s="21" t="str">
-        <x:v>旺店通-管理</x:v>
+        <x:v>旺店通-客服</x:v>
       </x:c>
       <x:c r="C270" s="21" t="str">
-        <x:v>管理</x:v>
+        <x:v>客服</x:v>
       </x:c>
       <x:c r="D270" s="21" t="str">
-        <x:v>账号管理</x:v>
+        <x:v>智能退货入库</x:v>
       </x:c>
       <x:c r="E270" s="21" t="str">
         <x:v>通用</x:v>
@@ -32889,10 +32891,10 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G270" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>进阶</x:v>
       </x:c>
       <x:c r="H270" s="21" t="str">
-        <x:v>中</x:v>
+        <x:v>高</x:v>
       </x:c>
       <x:c r="I270" s="21" t="str">
         <x:v>practice</x:v>
@@ -32901,74 +32903,74 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K270" s="21" t="str">
-        <x:v>WDT-K038</x:v>
+        <x:v>WDT-K037</x:v>
       </x:c>
       <x:c r="L270" s="21" t="str">
-        <x:v>账号注册与登录</x:v>
+        <x:v>智能退货入库边界</x:v>
       </x:c>
       <x:c r="M270" s="21" t="str">
-        <x:v>手机号注册次数决定登录凭证</x:v>
+        <x:v>扫描定位、按实收数量入库、拒收只改状态</x:v>
       </x:c>
       <x:c r="N270" s="21" t="str">
-        <x:v>同一手机号在旺店通注册过多个账号，登录目标卖家账号时应使用哪组凭证？</x:v>
+        <x:v>同一售后分两次退回，第一次只收到部分商品，应怎样记录本次收货？</x:v>
       </x:c>
       <x:c r="O270" s="21" t="str">
-        <x:v>多次注册时填写卖家主账号、员工登录名和短信验证码</x:v>
+        <x:v>第一次按申请总数全部收货，第二次到货后用入库纠错补记</x:v>
       </x:c>
       <x:c r="P270" s="21" t="str">
-        <x:v>多次注册时填写卖家主账号、注册手机号和登录密码三项</x:v>
+        <x:v>按本次实收量部分收货，后续到货时再收剩余量</x:v>
       </x:c>
       <x:c r="Q270" s="21" t="str">
-        <x:v>多次注册时填写卖家主账号、注册手机号和短信验证码</x:v>
+        <x:v>两批到齐后再一次性收货，第一次到货不留部分收货记录</x:v>
       </x:c>
       <x:c r="R270" s="21" t="str">
-        <x:v>多次注册时只填写注册手机号和登录密码，不选卖家主账号</x:v>
+        <x:v>第一次按实收量收货，第二次另建系统售后再收余量</x:v>
       </x:c>
       <x:c r="S270" s="21" t="str">
         <x:v>B</x:v>
       </x:c>
       <x:c r="T270" s="21" t="str">
-        <x:v>多次注册时填写卖家主账号、注册手机号和登录密码三项</x:v>
+        <x:v>按本次实收量部分收货，后续到货时再收剩余量</x:v>
       </x:c>
       <x:c r="U270" s="21" t="str">
-        <x:v>手机号多次注册时，需要用卖家主账号区分归属，再配合手机号和密码登录。</x:v>
+        <x:v>智能退货入库支持部分和多次收货，首次按实收量记录，后续继续读取剩余数量。</x:v>
       </x:c>
       <x:c r="V270" s="21" t="str">
-        <x:v>{"A":"错凭证：资料要求手机号和密码，不是员工登录名与验证码。","C":"错凭证：多注册场景资料要求使用密码，不是短信验证码。","D":"缺主账号：同手机号多账号时无法据此明确目标卖家账号。"}</x:v>
+        <x:v>{"A":"错数量：应按本次实收数量收货，不可虚增。","C":"漏记录：首次实收应当及时部分收货，不能等齐后合并记录。","D":"错对象：同一售后支持多次收货，无需另建售后单。"}</x:v>
       </x:c>
       <x:c r="W270" s="21" t="str">
-        <x:v>让员工和管理员按账号实际注册情况登录，减少因凭证组合错误导致的无法进入系统。</x:v>
+        <x:v>准确定位退货售后，支持同单分批收货，并清楚拒收不会自动执行其他售后动作。</x:v>
       </x:c>
       <x:c r="X270" s="21" t="str">
-        <x:v>["erp.huice.com","注册或登录"]</x:v>
+        <x:v>["售后","智能退货入库"]</x:v>
       </x:c>
       <x:c r="Y270" s="21" t="str">
-        <x:v>["已确认手机号是否只注册过一次","多注册场景已取得卖家主账号、手机号和密码"]</x:v>
+        <x:v>["退件已到仓或已取得可查询信息","已确认实际退回货品和数量"]</x:v>
       </x:c>
       <x:c r="Z270" s="21" t="str">
-        <x:v>["在 erp.huice.com 注册账号","确认手机号注册次数","单次注册使用手机号加密码或验证码登录","多次注册使用卖家主账号加手机号加密码登录","需要时绑定微信便于后续登录"]</x:v>
+        <x:v>["扫描退货物流、手机号、平台订单或拣货标签定位售后","核对并可编辑本次收货数量","点击收货生成退货入库单","分批退回时后续继续读取剩余数量","拒绝入库时明确仅变更为拒绝入库状态"]</x:v>
       </x:c>
       <x:c r="AA270" s="21" t="str">
-        <x:v>["使用的登录方式与手机号注册情况匹配","能进入正确卖家账号而非同手机号下的其他账号"]</x:v>
+        <x:v>["本次实收数量准确","售后显示部分或全部入库状态","分批收货后剩余待收数量正确","拒收后未误以为已退款或已取消"]</x:v>
       </x:c>
       <x:c r="AB270" s="21" t="str">
-        <x:v>["同一手机号注册过多次时，仅输入手机号与验证码不能明确目标卖家账号，应补充卖家主账号和密码"]</x:v>
+        <x:v>["未填写退货物流时直接扫物流可能失败，可用手机号或买家昵称查近六个月已完成或退款订单","同一物流号可匹配多张售后并一起收货","拒收只把状态改为拒绝入库，不会自动产生其他变化"]</x:v>
       </x:c>
       <x:c r="AC270" s="21" t="str">
-        <x:v>["只输入手机号验证码","把店铺名当卖家主账号"]</x:v>
+        <x:v>["部分到货按全部收货","等待全部到齐而不留首次收货记录"]</x:v>
       </x:c>
       <x:c r="AD270" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
       </x:c>
       <x:c r="AE270" s="21" t="str">
-        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/ggqlq7</x:v>
+        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/lz8g3ml0cdikdpeu</x:v>
       </x:c>
       <x:c r="AF270" s="21" t="str"/>
       <x:c r="AG270" s="21" t="str">
-        <x:v>账号注册与登录方式</x:v>
+        <x:v>智能退货入库—查询、分批收货与拒收</x:v>
       </x:c>
       <x:c r="AH270" s="21" t="str">
-        <x:v>手机号注册多次时，使用卖家主账号+手机号+密码登录。</x:v>
+        <x:v>智能退货入库支持部分及多次收货，后续读取剩余数量。</x:v>
       </x:c>
       <x:c r="AI270" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -33012,7 +33014,7 @@
       <x:c r="AV270" s="21" t="str"/>
       <x:c r="AW270" s="21" t="str"/>
       <x:c r="AX270" s="21" t="str">
-        <x:v>注册账号并选择正确登录方式</x:v>
+        <x:v>执行智能退货入库并处理分批与拒收</x:v>
       </x:c>
       <x:c r="AY270" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -33020,7 +33022,7 @@
     </x:row>
     <x:row r="271" ht="46" customHeight="1">
       <x:c r="A271" s="21" t="str">
-        <x:v>WDT-038-B</x:v>
+        <x:v>WDT-038-A</x:v>
       </x:c>
       <x:c r="B271" s="21" t="str">
         <x:v>旺店通-管理</x:v>
@@ -33038,10 +33040,10 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G271" s="21" t="str">
-        <x:v>基础</x:v>
+        <x:v>场景</x:v>
       </x:c>
       <x:c r="H271" s="21" t="str">
-        <x:v>低</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I271" s="21" t="str">
         <x:v>practice</x:v>
@@ -33059,31 +33061,31 @@
         <x:v>手机号注册次数决定登录凭证</x:v>
       </x:c>
       <x:c r="N271" s="21" t="str">
-        <x:v>某手机号确认只注册过一次旺店通账号，哪种登录方式符合资料？</x:v>
+        <x:v>同一手机号在旺店通注册过多个账号，登录目标卖家账号时应使用哪组凭证？</x:v>
       </x:c>
       <x:c r="O271" s="21" t="str">
-        <x:v>可使用手机号加密码，或手机号加验证码登录</x:v>
+        <x:v>多次注册时填写卖家主账号、员工登录名和短信验证码</x:v>
       </x:c>
       <x:c r="P271" s="21" t="str">
-        <x:v>必须使用卖家主账号、手机号和密码三项登录</x:v>
+        <x:v>多次注册时填写卖家主账号、注册手机号和登录密码三项</x:v>
       </x:c>
       <x:c r="Q271" s="21" t="str">
-        <x:v>必须使用员工登录名、手机号和密码三项登录</x:v>
+        <x:v>多次注册时填写卖家主账号、注册手机号和短信验证码</x:v>
       </x:c>
       <x:c r="R271" s="21" t="str">
-        <x:v>可使用手机号加店铺授权码，或手机号加主账号验证码登录</x:v>
+        <x:v>多次注册时只填写注册手机号和登录密码，不选卖家主账号</x:v>
       </x:c>
       <x:c r="S271" s="21" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="T271" s="21" t="str">
-        <x:v>可使用手机号加密码，或手机号加验证码登录</x:v>
+        <x:v>多次注册时填写卖家主账号、注册手机号和登录密码三项</x:v>
       </x:c>
       <x:c r="U271" s="21" t="str">
-        <x:v>手机号只注册一次时，系统可直接用手机号识别账号，支持密码或验证码。</x:v>
+        <x:v>手机号多次注册时，需要用卖家主账号区分归属，再配合手机号和密码登录。</x:v>
       </x:c>
       <x:c r="V271" s="21" t="str">
-        <x:v>{"B":"增加了不必要凭证：单次注册无需卖家主账号。","C":"错组合：资料未要求员工登录名作为单注册登录凭证。","D":"错凭证：店铺授权码和主账号验证码不是资料给出的方式。"}</x:v>
+        <x:v>{"A":"错凭证：资料要求手机号和密码，不是员工登录名与验证码。","C":"错凭证：多注册场景资料要求使用密码，不是短信验证码。","D":"缺主账号：同手机号多账号时无法据此明确目标卖家账号。"}</x:v>
       </x:c>
       <x:c r="W271" s="21" t="str">
         <x:v>让员工和管理员按账号实际注册情况登录，减少因凭证组合错误导致的无法进入系统。</x:v>
@@ -33104,7 +33106,7 @@
         <x:v>["同一手机号注册过多次时，仅输入手机号与验证码不能明确目标卖家账号，应补充卖家主账号和密码"]</x:v>
       </x:c>
       <x:c r="AC271" s="21" t="str">
-        <x:v>["单注册也强制填写卖家主账号","把员工编号当登录必填项"]</x:v>
+        <x:v>["只输入手机号验证码","把店铺名当卖家主账号"]</x:v>
       </x:c>
       <x:c r="AD271" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -33117,7 +33119,7 @@
         <x:v>账号注册与登录方式</x:v>
       </x:c>
       <x:c r="AH271" s="21" t="str">
-        <x:v>手机号只注册一次，可用手机号+密码或手机号+验证码登录。</x:v>
+        <x:v>手机号注册多次时，使用卖家主账号+手机号+密码登录。</x:v>
       </x:c>
       <x:c r="AI271" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -33169,7 +33171,7 @@
     </x:row>
     <x:row r="272" ht="46" customHeight="1">
       <x:c r="A272" s="21" t="str">
-        <x:v>WDT-039-A</x:v>
+        <x:v>WDT-038-B</x:v>
       </x:c>
       <x:c r="B272" s="21" t="str">
         <x:v>旺店通-管理</x:v>
@@ -33190,7 +33192,7 @@
         <x:v>基础</x:v>
       </x:c>
       <x:c r="H272" s="21" t="str">
-        <x:v>中</x:v>
+        <x:v>低</x:v>
       </x:c>
       <x:c r="I272" s="21" t="str">
         <x:v>practice</x:v>
@@ -33199,74 +33201,74 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K272" s="21" t="str">
-        <x:v>WDT-K039</x:v>
+        <x:v>WDT-K038</x:v>
       </x:c>
       <x:c r="L272" s="21" t="str">
-        <x:v>员工账号创建</x:v>
+        <x:v>账号注册与登录</x:v>
       </x:c>
       <x:c r="M272" s="21" t="str">
-        <x:v>从账号中心员工列表建号</x:v>
+        <x:v>手机号注册次数决定登录凭证</x:v>
       </x:c>
       <x:c r="N272" s="21" t="str">
-        <x:v>管理员要给新入职员工建立独立旺店通账号，正确入口是什么？</x:v>
+        <x:v>某手机号确认只注册过一次旺店通账号，哪种登录方式符合资料？</x:v>
       </x:c>
       <x:c r="O272" s="21" t="str">
-        <x:v>配置→权限设置→管理员工→账号中心员工列表→新建员工</x:v>
+        <x:v>可使用手机号加密码，或手机号加验证码登录</x:v>
       </x:c>
       <x:c r="P272" s="21" t="str">
-        <x:v>配置→权限设置→管理员工→账号中心员工列表→编辑已有员工</x:v>
+        <x:v>必须使用卖家主账号、手机号和密码三项登录</x:v>
       </x:c>
       <x:c r="Q272" s="21" t="str">
-        <x:v>配置→权限设置→管理员工→账号中心权限配置→新建员工</x:v>
+        <x:v>必须使用员工登录名、手机号和密码三项登录</x:v>
       </x:c>
       <x:c r="R272" s="21" t="str">
-        <x:v>配置→基本设置→权限开关→管理员工→新建员工</x:v>
+        <x:v>可使用手机号加店铺授权码，或手机号加主账号验证码登录</x:v>
       </x:c>
       <x:c r="S272" s="21" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="T272" s="21" t="str">
-        <x:v>配置→权限设置→管理员工→账号中心员工列表→新建员工</x:v>
+        <x:v>可使用手机号加密码，或手机号加验证码登录</x:v>
       </x:c>
       <x:c r="U272" s="21" t="str">
-        <x:v>员工账号统一在权限设置的管理员工入口进入账号中心后创建。</x:v>
+        <x:v>手机号只注册一次时，系统可直接用手机号识别账号，支持密码或验证码。</x:v>
       </x:c>
       <x:c r="V272" s="21" t="str">
-        <x:v>{"B":"错动作：编辑已有员工不会创建独立新账号。","C":"错层级：新建入口在员工列表，不在权限配置。","D":"错入口：权限开关控制权限维度，不负责建号。"}</x:v>
+        <x:v>{"B":"增加了不必要凭证：单次注册无需卖家主账号。","C":"错组合：资料未要求员工登录名作为单注册登录凭证。","D":"错凭证：店铺授权码和主账号验证码不是资料给出的方式。"}</x:v>
       </x:c>
       <x:c r="W272" s="21" t="str">
-        <x:v>为新员工建立可识别、可登录、可后续授权的独立账号，避免多人共用主账号。</x:v>
+        <x:v>让员工和管理员按账号实际注册情况登录，减少因凭证组合错误导致的无法进入系统。</x:v>
       </x:c>
       <x:c r="X272" s="21" t="str">
-        <x:v>["配置","权限设置","管理员工","账号中心","员工列表","新建员工"]</x:v>
+        <x:v>["erp.huice.com","注册或登录"]</x:v>
       </x:c>
       <x:c r="Y272" s="21" t="str">
-        <x:v>["操作者具备管理员工权限","已取得新员工手机号并可完成验证码校验"]</x:v>
+        <x:v>["已确认手机号是否只注册过一次","多注册场景已取得卖家主账号、手机号和密码"]</x:v>
       </x:c>
       <x:c r="Z272" s="21" t="str">
-        <x:v>["进入账号中心员工列表","新建员工","填写员工编号和昵称或登录名","填写手机号并完成验证码","设置密码和用户中心权限","保存后再配置岗位所需权限"]</x:v>
+        <x:v>["在 erp.huice.com 注册账号","确认手机号注册次数","单次注册使用手机号加密码或验证码登录","多次注册使用卖家主账号加手机号加密码登录","需要时绑定微信便于后续登录"]</x:v>
       </x:c>
       <x:c r="AA272" s="21" t="str">
-        <x:v>["员工可用自己的账号登录","员工信息可在列表中唯一识别","用户中心权限与职责匹配"]</x:v>
+        <x:v>["使用的登录方式与手机号注册情况匹配","能进入正确卖家账号而非同手机号下的其他账号"]</x:v>
       </x:c>
       <x:c r="AB272" s="21" t="str">
-        <x:v>["新建账号只是身份建立，业务功能、店铺和仓库等权限仍需另行配置"]</x:v>
+        <x:v>["同一手机号注册过多次时，仅输入手机号与验证码不能明确目标卖家账号，应补充卖家主账号和密码"]</x:v>
       </x:c>
       <x:c r="AC272" s="21" t="str">
-        <x:v>["在业务模块中创建岗位账号","直接让员工共用主账号"]</x:v>
+        <x:v>["单注册也强制填写卖家主账号","把员工编号当登录必填项"]</x:v>
       </x:c>
       <x:c r="AD272" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
       </x:c>
       <x:c r="AE272" s="21" t="str">
-        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/cgddc2</x:v>
+        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/ggqlq7</x:v>
       </x:c>
       <x:c r="AF272" s="21" t="str"/>
       <x:c r="AG272" s="21" t="str">
-        <x:v>账号管理—新建员工</x:v>
+        <x:v>账号注册与登录方式</x:v>
       </x:c>
       <x:c r="AH272" s="21" t="str">
-        <x:v>配置→权限设置→管理员工→账号中心→员工列表→新建员工。</x:v>
+        <x:v>手机号只注册一次，可用手机号+密码或手机号+验证码登录。</x:v>
       </x:c>
       <x:c r="AI272" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -33310,7 +33312,7 @@
       <x:c r="AV272" s="21" t="str"/>
       <x:c r="AW272" s="21" t="str"/>
       <x:c r="AX272" s="21" t="str">
-        <x:v>新建员工子账号</x:v>
+        <x:v>注册账号并选择正确登录方式</x:v>
       </x:c>
       <x:c r="AY272" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -33318,7 +33320,7 @@
     </x:row>
     <x:row r="273" ht="46" customHeight="1">
       <x:c r="A273" s="21" t="str">
-        <x:v>WDT-039-B</x:v>
+        <x:v>WDT-039-A</x:v>
       </x:c>
       <x:c r="B273" s="21" t="str">
         <x:v>旺店通-管理</x:v>
@@ -33357,31 +33359,31 @@
         <x:v>从账号中心员工列表建号</x:v>
       </x:c>
       <x:c r="N273" s="21" t="str">
-        <x:v>新建员工账号时，哪组信息最符合资料要求？</x:v>
+        <x:v>管理员要给新入职员工建立独立旺店通账号，正确入口是什么？</x:v>
       </x:c>
       <x:c r="O273" s="21" t="str">
-        <x:v>员工编号、昵称或登录名、未验证手机号、主账号密码、用户中心权限</x:v>
+        <x:v>配置→权限设置→管理员工→账号中心员工列表→新建员工</x:v>
       </x:c>
       <x:c r="P273" s="21" t="str">
-        <x:v>员工编号、昵称或登录名、手机号验证码、密码、功能权限</x:v>
+        <x:v>配置→权限设置→管理员工→账号中心员工列表→编辑已有员工</x:v>
       </x:c>
       <x:c r="Q273" s="21" t="str">
-        <x:v>员工编号、昵称或登录名、店铺授权码、密码、用户中心权限</x:v>
+        <x:v>配置→权限设置→管理员工→账号中心权限配置→新建员工</x:v>
       </x:c>
       <x:c r="R273" s="21" t="str">
-        <x:v>员工编号、昵称或登录名、手机号验证码、密码、用户中心权限</x:v>
+        <x:v>配置→基本设置→权限开关→管理员工→新建员工</x:v>
       </x:c>
       <x:c r="S273" s="21" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="T273" s="21" t="str">
-        <x:v>员工编号、昵称或登录名、手机号验证码、密码、用户中心权限</x:v>
+        <x:v>配置→权限设置→管理员工→账号中心员工列表→新建员工</x:v>
       </x:c>
       <x:c r="U273" s="21" t="str">
-        <x:v>这些字段用于建立员工身份、完成手机号校验并设定账号中心访问级别。</x:v>
+        <x:v>员工账号统一在权限设置的管理员工入口进入账号中心后创建。</x:v>
       </x:c>
       <x:c r="V273" s="21" t="str">
-        <x:v>{"A":"验证和密码错误：手机号需验证码，且不能使用主账号密码。","B":"字段替换错误：建号时资料要求用户中心权限，业务功能另行配置。","C":"验证方式错误：手机号验证码不能用店铺授权码代替。"}</x:v>
+        <x:v>{"B":"错动作：编辑已有员工不会创建独立新账号。","C":"错层级：新建入口在员工列表，不在权限配置。","D":"错入口：权限开关控制权限维度，不负责建号。"}</x:v>
       </x:c>
       <x:c r="W273" s="21" t="str">
         <x:v>为新员工建立可识别、可登录、可后续授权的独立账号，避免多人共用主账号。</x:v>
@@ -33402,7 +33404,7 @@
         <x:v>["新建账号只是身份建立，业务功能、店铺和仓库等权限仍需另行配置"]</x:v>
       </x:c>
       <x:c r="AC273" s="21" t="str">
-        <x:v>["把店铺或仓库编码当员工身份字段","漏设用户中心权限"]</x:v>
+        <x:v>["在业务模块中创建岗位账号","直接让员工共用主账号"]</x:v>
       </x:c>
       <x:c r="AD273" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -33415,7 +33417,7 @@
         <x:v>账号管理—新建员工</x:v>
       </x:c>
       <x:c r="AH273" s="21" t="str">
-        <x:v>新建员工填写员工编号、昵称或登录名、手机号验证码、密码和用户中心权限。</x:v>
+        <x:v>配置→权限设置→管理员工→账号中心→员工列表→新建员工。</x:v>
       </x:c>
       <x:c r="AI273" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -33467,7 +33469,7 @@
     </x:row>
     <x:row r="274" ht="46" customHeight="1">
       <x:c r="A274" s="21" t="str">
-        <x:v>WDT-040-A</x:v>
+        <x:v>WDT-039-B</x:v>
       </x:c>
       <x:c r="B274" s="21" t="str">
         <x:v>旺店通-管理</x:v>
@@ -33497,61 +33499,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K274" s="21" t="str">
-        <x:v>WDT-K040</x:v>
+        <x:v>WDT-K039</x:v>
       </x:c>
       <x:c r="L274" s="21" t="str">
-        <x:v>账号密码重置</x:v>
+        <x:v>员工账号创建</x:v>
       </x:c>
       <x:c r="M274" s="21" t="str">
-        <x:v>主账号从员工列表编辑登录账号</x:v>
+        <x:v>从账号中心员工列表建号</x:v>
       </x:c>
       <x:c r="N274" s="21" t="str">
-        <x:v>员工忘记旺店通密码且无法登录，主账号应从哪里重置？</x:v>
+        <x:v>新建员工账号时，哪组信息最符合资料要求？</x:v>
       </x:c>
       <x:c r="O274" s="21" t="str">
-        <x:v>在账号中心员工列表新建同名员工，用新账号密码替代原账号</x:v>
+        <x:v>员工编号、昵称或登录名、未验证手机号、主账号密码、用户中心权限</x:v>
       </x:c>
       <x:c r="P274" s="21" t="str">
-        <x:v>在账号中心员工列表找到该员工，点击配置权限并重置密码</x:v>
+        <x:v>员工编号、昵称或登录名、手机号验证码、密码、功能权限</x:v>
       </x:c>
       <x:c r="Q274" s="21" t="str">
-        <x:v>在账号中心员工列表找到该员工，点击编辑登录账号重置密码</x:v>
+        <x:v>员工编号、昵称或登录名、店铺授权码、密码、用户中心权限</x:v>
       </x:c>
       <x:c r="R274" s="21" t="str">
-        <x:v>在账号中心员工列表找到该员工，点击修改手机号并重置密码</x:v>
+        <x:v>员工编号、昵称或登录名、手机号验证码、密码、用户中心权限</x:v>
       </x:c>
       <x:c r="S274" s="21" t="str">
-        <x:v>C</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="T274" s="21" t="str">
-        <x:v>在账号中心员工列表找到该员工，点击编辑登录账号重置密码</x:v>
+        <x:v>员工编号、昵称或登录名、手机号验证码、密码、用户中心权限</x:v>
       </x:c>
       <x:c r="U274" s="21" t="str">
-        <x:v>主账号重置员工密码的资料路径是员工列表中的编辑登录账号。</x:v>
+        <x:v>这些字段用于建立员工身份、完成手机号校验并设定账号中心访问级别。</x:v>
       </x:c>
       <x:c r="V274" s="21" t="str">
-        <x:v>{"A":"错动作：不应为忘记密码创建重复员工账号。","B":"错动作：配置权限不负责修改登录密码。","D":"错动作：修改手机号不是资料给出的密码重置入口。"}</x:v>
+        <x:v>{"A":"验证和密码错误：手机号需验证码，且不能使用主账号密码。","B":"字段替换错误：建号时资料要求用户中心权限，业务功能另行配置。","C":"验证方式错误：手机号验证码不能用店铺授权码代替。"}</x:v>
       </x:c>
       <x:c r="W274" s="21" t="str">
-        <x:v>在员工无法登录时由主账号安全重置密码，快速恢复工作且不新建重复账号。</x:v>
+        <x:v>为新员工建立可识别、可登录、可后续授权的独立账号，避免多人共用主账号。</x:v>
       </x:c>
       <x:c r="X274" s="21" t="str">
-        <x:v>["配置","权限设置","管理员工","账号中心","员工列表","编辑登录账号"]</x:v>
+        <x:v>["配置","权限设置","管理员工","账号中心","员工列表","新建员工"]</x:v>
       </x:c>
       <x:c r="Y274" s="21" t="str">
-        <x:v>["操作者为主账号或具备相应员工管理权限","已确认需要重置的员工账号"]</x:v>
+        <x:v>["操作者具备管理员工权限","已取得新员工手机号并可完成验证码校验"]</x:v>
       </x:c>
       <x:c r="Z274" s="21" t="str">
-        <x:v>["进入账号中心员工列表","定位目标员工","点击编辑登录账号","重置密码","通知员工使用新密码登录并及时保管"]</x:v>
+        <x:v>["进入账号中心员工列表","新建员工","填写员工编号和昵称或登录名","填写手机号并完成验证码","设置密码和用户中心权限","保存后再配置岗位所需权限"]</x:v>
       </x:c>
       <x:c r="AA274" s="21" t="str">
-        <x:v>["密码已更新到目标员工而非其他账号","员工可使用新密码进入原有账号","原账号权限保持不变"]</x:v>
+        <x:v>["员工可用自己的账号登录","员工信息可在列表中唯一识别","用户中心权限与职责匹配"]</x:v>
       </x:c>
       <x:c r="AB274" s="21" t="str">
-        <x:v>["账号中心还支持修改手机号、重置密码和绑定微信；变更手机号前应核对账号归属"]</x:v>
+        <x:v>["新建账号只是身份建立，业务功能、店铺和仓库等权限仍需另行配置"]</x:v>
       </x:c>
       <x:c r="AC274" s="21" t="str">
-        <x:v>["重建账号代替重置密码","通过店铺重新授权处理员工登录"]</x:v>
+        <x:v>["把店铺或仓库编码当员工身份字段","漏设用户中心权限"]</x:v>
       </x:c>
       <x:c r="AD274" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -33561,10 +33563,10 @@
       </x:c>
       <x:c r="AF274" s="21" t="str"/>
       <x:c r="AG274" s="21" t="str">
-        <x:v>账号管理—密码重置与登录账号编辑</x:v>
+        <x:v>账号管理—新建员工</x:v>
       </x:c>
       <x:c r="AH274" s="21" t="str">
-        <x:v>主账号在员工列表通过编辑登录账号重置员工密码。</x:v>
+        <x:v>新建员工填写员工编号、昵称或登录名、手机号验证码、密码和用户中心权限。</x:v>
       </x:c>
       <x:c r="AI274" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -33608,7 +33610,7 @@
       <x:c r="AV274" s="21" t="str"/>
       <x:c r="AW274" s="21" t="str"/>
       <x:c r="AX274" s="21" t="str">
-        <x:v>重置员工登录密码</x:v>
+        <x:v>新建员工子账号</x:v>
       </x:c>
       <x:c r="AY274" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -33616,7 +33618,7 @@
     </x:row>
     <x:row r="275" ht="46" customHeight="1">
       <x:c r="A275" s="21" t="str">
-        <x:v>WDT-040-B</x:v>
+        <x:v>WDT-040-A</x:v>
       </x:c>
       <x:c r="B275" s="21" t="str">
         <x:v>旺店通-管理</x:v>
@@ -33634,10 +33636,10 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G275" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="H275" s="21" t="str">
-        <x:v>高</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I275" s="21" t="str">
         <x:v>practice</x:v>
@@ -33655,31 +33657,31 @@
         <x:v>主账号从员工列表编辑登录账号</x:v>
       </x:c>
       <x:c r="N275" s="21" t="str">
-        <x:v>主账号准备给一名同名员工重置密码，哪种做法最符合账号管理流程？</x:v>
+        <x:v>员工忘记旺店通密码且无法登录，主账号应从哪里重置？</x:v>
       </x:c>
       <x:c r="O275" s="21" t="str">
-        <x:v>先删除所有同名员工，再在员工列表新建一个共用账号并重新授权</x:v>
+        <x:v>在账号中心员工列表新建同名员工，用新账号密码替代原账号</x:v>
       </x:c>
       <x:c r="P275" s="21" t="str">
-        <x:v>先选择名字最接近的员工，再编辑登录账号而不核对唯一手机号或员工编号</x:v>
+        <x:v>在账号中心员工列表找到该员工，点击配置权限并重置密码</x:v>
       </x:c>
       <x:c r="Q275" s="21" t="str">
-        <x:v>先修改目标员工手机号并保留旧密码，再让员工继续尝试原登录方式</x:v>
+        <x:v>在账号中心员工列表找到该员工，点击编辑登录账号重置密码</x:v>
       </x:c>
       <x:c r="R275" s="21" t="str">
-        <x:v>先在员工列表核对目标账号，再编辑登录账号并确认员工可用新密码登录</x:v>
+        <x:v>在账号中心员工列表找到该员工，点击修改手机号并重置密码</x:v>
       </x:c>
       <x:c r="S275" s="21" t="str">
-        <x:v>D</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="T275" s="21" t="str">
-        <x:v>先在员工列表核对目标账号，再编辑登录账号并确认员工可用新密码登录</x:v>
+        <x:v>在账号中心员工列表找到该员工，点击编辑登录账号重置密码</x:v>
       </x:c>
       <x:c r="U275" s="21" t="str">
-        <x:v>重置前先定位正确员工，可避免误改他人账号；编辑原登录账号也能保留原权限。</x:v>
+        <x:v>主账号重置员工密码的资料路径是员工列表中的编辑登录账号。</x:v>
       </x:c>
       <x:c r="V275" s="21" t="str">
-        <x:v>{"A":"高风险：删除重建会制造共用账号并破坏权限关系。","B":"高风险：同名员工必须核对唯一账号，不能凭姓名近似操作。","C":"未解决问题：修改手机号但保留遗忘的旧密码不能恢复登录。"}</x:v>
+        <x:v>{"A":"错动作：不应为忘记密码创建重复员工账号。","B":"错动作：配置权限不负责修改登录密码。","D":"错动作：修改手机号不是资料给出的密码重置入口。"}</x:v>
       </x:c>
       <x:c r="W275" s="21" t="str">
         <x:v>在员工无法登录时由主账号安全重置密码，快速恢复工作且不新建重复账号。</x:v>
@@ -33700,7 +33702,7 @@
         <x:v>["账号中心还支持修改手机号、重置密码和绑定微信；变更手机号前应核对账号归属"]</x:v>
       </x:c>
       <x:c r="AC275" s="21" t="str">
-        <x:v>["未核对账号就重置","删除重建导致原权限丢失或重复"]</x:v>
+        <x:v>["重建账号代替重置密码","通过店铺重新授权处理员工登录"]</x:v>
       </x:c>
       <x:c r="AD275" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -33713,7 +33715,7 @@
         <x:v>账号管理—密码重置与登录账号编辑</x:v>
       </x:c>
       <x:c r="AH275" s="21" t="str">
-        <x:v>在员工列表定位员工后编辑登录账号并重置密码。</x:v>
+        <x:v>主账号在员工列表通过编辑登录账号重置员工密码。</x:v>
       </x:c>
       <x:c r="AI275" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -33765,7 +33767,7 @@
     </x:row>
     <x:row r="276" ht="46" customHeight="1">
       <x:c r="A276" s="21" t="str">
-        <x:v>WDT-041-A</x:v>
+        <x:v>WDT-040-B</x:v>
       </x:c>
       <x:c r="B276" s="21" t="str">
         <x:v>旺店通-管理</x:v>
@@ -33774,7 +33776,7 @@
         <x:v>管理</x:v>
       </x:c>
       <x:c r="D276" s="21" t="str">
-        <x:v>权限管理</x:v>
+        <x:v>账号管理</x:v>
       </x:c>
       <x:c r="E276" s="21" t="str">
         <x:v>通用</x:v>
@@ -33795,61 +33797,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K276" s="21" t="str">
-        <x:v>WDT-K041</x:v>
+        <x:v>WDT-K040</x:v>
       </x:c>
       <x:c r="L276" s="21" t="str">
-        <x:v>员工权限维度与权限开关</x:v>
+        <x:v>账号密码重置</x:v>
       </x:c>
       <x:c r="M276" s="21" t="str">
-        <x:v>先开权限维度，再给员工配置范围</x:v>
+        <x:v>主账号从员工列表编辑登录账号</x:v>
       </x:c>
       <x:c r="N276" s="21" t="str">
-        <x:v>管理员配置员工时只看到功能权限，看不到店铺、仓库和字段权限，应先做什么？</x:v>
+        <x:v>主账号准备给一名同名员工重置密码，哪种做法最符合账号管理流程？</x:v>
       </x:c>
       <x:c r="O276" s="21" t="str">
-        <x:v>在员工配置权限页面反复勾选功能权限，等待店仓字段自动显示</x:v>
+        <x:v>先删除所有同名员工，再在员工列表新建一个共用账号并重新授权</x:v>
       </x:c>
       <x:c r="P276" s="21" t="str">
-        <x:v>把用户中心权限改为可操作，等待店仓字段显示后再刷新权限页</x:v>
+        <x:v>先选择名字最接近的员工，再编辑登录账号而不核对唯一手机号或员工编号</x:v>
       </x:c>
       <x:c r="Q276" s="21" t="str">
-        <x:v>在员工列表重新新建同一员工，再分别给两个账号配置店仓权限</x:v>
+        <x:v>先修改目标员工手机号并保留旧密码，再让员工继续尝试原登录方式</x:v>
       </x:c>
       <x:c r="R276" s="21" t="str">
-        <x:v>到配置→基本设置→权限开关启用对应维度，再返回员工权限页</x:v>
+        <x:v>先在员工列表核对目标账号，再编辑登录账号并确认员工可用新密码登录</x:v>
       </x:c>
       <x:c r="S276" s="21" t="str">
         <x:v>D</x:v>
       </x:c>
       <x:c r="T276" s="21" t="str">
-        <x:v>到配置→基本设置→权限开关启用对应维度，再返回员工权限页</x:v>
+        <x:v>先在员工列表核对目标账号，再编辑登录账号并确认员工可用新密码登录</x:v>
       </x:c>
       <x:c r="U276" s="21" t="str">
-        <x:v>系统默认只显示功能权限，店铺、仓库和字段权限需先启用对应权限开关。</x:v>
+        <x:v>重置前先定位正确员工，可避免误改他人账号；编辑原登录账号也能保留原权限。</x:v>
       </x:c>
       <x:c r="V276" s="21" t="str">
-        <x:v>{"A":"错层级：功能权限页面不能代替基本设置中的权限开关。","B":"概念错误：用户中心权限不控制店铺、仓库和字段维度显示。","C":"错动作：重建员工不能开启权限维度，还会产生重复账号。"}</x:v>
+        <x:v>{"A":"高风险：删除重建会制造共用账号并破坏权限关系。","B":"高风险：同名员工必须核对唯一账号，不能凭姓名近似操作。","C":"未解决问题：修改手机号但保留遗忘的旧密码不能恢复登录。"}</x:v>
       </x:c>
       <x:c r="W276" s="21" t="str">
-        <x:v>按岗位限定员工能使用的功能和能看到的数据范围，避免越权操作或看错店仓数据。</x:v>
+        <x:v>在员工无法登录时由主账号安全重置密码，快速恢复工作且不新建重复账号。</x:v>
       </x:c>
       <x:c r="X276" s="21" t="str">
-        <x:v>["配置","基本设置","权限开关","配置","权限设置","管理员工","配置权限"]</x:v>
+        <x:v>["配置","权限设置","管理员工","账号中心","员工列表","编辑登录账号"]</x:v>
       </x:c>
       <x:c r="Y276" s="21" t="str">
-        <x:v>["已建立员工账号","已明确岗位需要的功能、店铺、仓库和字段范围"]</x:v>
+        <x:v>["操作者为主账号或具备相应员工管理权限","已确认需要重置的员工账号"]</x:v>
       </x:c>
       <x:c r="Z276" s="21" t="str">
-        <x:v>["在基本设置的权限开关中启用需要控制的店铺、仓库或字段维度","进入管理员工并选择目标员工","点击配置权限","分别配置功能模块、店铺、仓库、安全、字段和应用权限","用员工账号验证可见范围"]</x:v>
+        <x:v>["进入账号中心员工列表","定位目标员工","点击编辑登录账号","重置密码","通知员工使用新密码登录并及时保管"]</x:v>
       </x:c>
       <x:c r="AA276" s="21" t="str">
-        <x:v>["目标员工只看到授权功能和数据范围","未授权店铺、仓库或字段不可见或不可操作","权限开关与员工配置均已生效"]</x:v>
+        <x:v>["密码已更新到目标员工而非其他账号","员工可使用新密码进入原有账号","原账号权限保持不变"]</x:v>
       </x:c>
       <x:c r="AB276" s="21" t="str">
-        <x:v>["系统默认只显示功能权限；店铺、仓库和字段等权限需先在基本设置的权限开关中启用后才能精细配置"]</x:v>
+        <x:v>["账号中心还支持修改手机号、重置密码和绑定微信；变更手机号前应核对账号归属"]</x:v>
       </x:c>
       <x:c r="AC276" s="21" t="str">
-        <x:v>["误以为账号创建失败","通过重新绑定店铺解决权限维度未开启"]</x:v>
+        <x:v>["未核对账号就重置","删除重建导致原权限丢失或重复"]</x:v>
       </x:c>
       <x:c r="AD276" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -33859,10 +33861,10 @@
       </x:c>
       <x:c r="AF276" s="21" t="str"/>
       <x:c r="AG276" s="21" t="str">
-        <x:v>员工权限—权限维度与权限开关</x:v>
+        <x:v>账号管理—密码重置与登录账号编辑</x:v>
       </x:c>
       <x:c r="AH276" s="21" t="str">
-        <x:v>店铺、仓库和字段权限需先在配置→基本设置→权限开关开启。</x:v>
+        <x:v>在员工列表定位员工后编辑登录账号并重置密码。</x:v>
       </x:c>
       <x:c r="AI276" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -33906,7 +33908,7 @@
       <x:c r="AV276" s="21" t="str"/>
       <x:c r="AW276" s="21" t="str"/>
       <x:c r="AX276" s="21" t="str">
-        <x:v>配置功能、店铺、仓库和字段权限</x:v>
+        <x:v>重置员工登录密码</x:v>
       </x:c>
       <x:c r="AY276" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -33914,7 +33916,7 @@
     </x:row>
     <x:row r="277" ht="46" customHeight="1">
       <x:c r="A277" s="21" t="str">
-        <x:v>WDT-041-B</x:v>
+        <x:v>WDT-041-A</x:v>
       </x:c>
       <x:c r="B277" s="21" t="str">
         <x:v>旺店通-管理</x:v>
@@ -33932,10 +33934,10 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G277" s="21" t="str">
-        <x:v>基础</x:v>
+        <x:v>场景</x:v>
       </x:c>
       <x:c r="H277" s="21" t="str">
-        <x:v>中</x:v>
+        <x:v>高</x:v>
       </x:c>
       <x:c r="I277" s="21" t="str">
         <x:v>practice</x:v>
@@ -33953,31 +33955,31 @@
         <x:v>先开权限维度，再给员工配置范围</x:v>
       </x:c>
       <x:c r="N277" s="21" t="str">
-        <x:v>进入某员工的“配置权限”后，资料列出的可配置范围是哪一组？</x:v>
+        <x:v>管理员配置员工时只看到功能权限，看不到店铺、仓库和字段权限，应先做什么？</x:v>
       </x:c>
       <x:c r="O277" s="21" t="str">
-        <x:v>功能模块、店铺、仓库、安全、字段和应用权限配置</x:v>
+        <x:v>在员工配置权限页面反复勾选功能权限，等待店仓字段自动显示</x:v>
       </x:c>
       <x:c r="P277" s="21" t="str">
-        <x:v>功能模块、店铺、仓库、安全、字段和用户中心等级</x:v>
+        <x:v>把用户中心权限改为可操作，等待店仓字段显示后再刷新权限页</x:v>
       </x:c>
       <x:c r="Q277" s="21" t="str">
-        <x:v>功能模块、店铺、仓库、登录密码、字段和应用权限</x:v>
+        <x:v>在员工列表重新新建同一员工，再分别给两个账号配置店仓权限</x:v>
       </x:c>
       <x:c r="R277" s="21" t="str">
-        <x:v>功能模块、店铺、仓库、安全、手机号和应用权限</x:v>
+        <x:v>到配置→基本设置→权限开关启用对应维度，再返回员工权限页</x:v>
       </x:c>
       <x:c r="S277" s="21" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="T277" s="21" t="str">
-        <x:v>功能模块、店铺、仓库、安全、字段和应用权限配置</x:v>
+        <x:v>到配置→基本设置→权限开关启用对应维度，再返回员工权限页</x:v>
       </x:c>
       <x:c r="U277" s="21" t="str">
-        <x:v>这些是员工权限配置页面提供的主要权限维度。</x:v>
+        <x:v>系统默认只显示功能权限，店铺、仓库和字段权限需先启用对应权限开关。</x:v>
       </x:c>
       <x:c r="V277" s="21" t="str">
-        <x:v>{"B":"范围混淆：用户中心等级单独设置，不替代应用权限维度。","C":"字段替换错误：登录密码属于账号信息，不是该权限维度。","D":"字段替换错误：手机号属于账号信息，不是字段权限。"}</x:v>
+        <x:v>{"A":"错层级：功能权限页面不能代替基本设置中的权限开关。","B":"概念错误：用户中心权限不控制店铺、仓库和字段维度显示。","C":"错动作：重建员工不能开启权限维度，还会产生重复账号。"}</x:v>
       </x:c>
       <x:c r="W277" s="21" t="str">
         <x:v>按岗位限定员工能使用的功能和能看到的数据范围，避免越权操作或看错店仓数据。</x:v>
@@ -33998,7 +34000,7 @@
         <x:v>["系统默认只显示功能权限；店铺、仓库和字段等权限需先在基本设置的权限开关中启用后才能精细配置"]</x:v>
       </x:c>
       <x:c r="AC277" s="21" t="str">
-        <x:v>["把账号资料字段当权限维度","只配置业务功能不限制店仓范围"]</x:v>
+        <x:v>["误以为账号创建失败","通过重新绑定店铺解决权限维度未开启"]</x:v>
       </x:c>
       <x:c r="AD277" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -34011,7 +34013,7 @@
         <x:v>员工权限—权限维度与权限开关</x:v>
       </x:c>
       <x:c r="AH277" s="21" t="str">
-        <x:v>员工配置权限包含功能模块、店铺、仓库、安全、字段和应用。</x:v>
+        <x:v>店铺、仓库和字段权限需先在配置→基本设置→权限开关开启。</x:v>
       </x:c>
       <x:c r="AI277" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -34063,7 +34065,7 @@
     </x:row>
     <x:row r="278" ht="46" customHeight="1">
       <x:c r="A278" s="21" t="str">
-        <x:v>WDT-042-A</x:v>
+        <x:v>WDT-041-B</x:v>
       </x:c>
       <x:c r="B278" s="21" t="str">
         <x:v>旺店通-管理</x:v>
@@ -34081,10 +34083,10 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G278" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="H278" s="21" t="str">
-        <x:v>高</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I278" s="21" t="str">
         <x:v>practice</x:v>
@@ -34093,61 +34095,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K278" s="21" t="str">
-        <x:v>WDT-K042</x:v>
+        <x:v>WDT-K041</x:v>
       </x:c>
       <x:c r="L278" s="21" t="str">
-        <x:v>最小权限与用户中心权限</x:v>
+        <x:v>员工权限维度与权限开关</x:v>
       </x:c>
       <x:c r="M278" s="21" t="str">
-        <x:v>无、可访问、可操作三档要按职责分配</x:v>
+        <x:v>先开权限维度，再给员工配置范围</x:v>
       </x:c>
       <x:c r="N278" s="21" t="str">
-        <x:v>客服员工只需处理售后，不承担员工账号管理；用户中心权限应如何设置？</x:v>
+        <x:v>进入某员工的“配置权限”后，资料列出的可配置范围是哪一组？</x:v>
       </x:c>
       <x:c r="O278" s="21" t="str">
-        <x:v>用户中心权限设为无，再单独配置其所需售后业务权限范围</x:v>
+        <x:v>功能模块、店铺、仓库、安全、字段和应用权限配置</x:v>
       </x:c>
       <x:c r="P278" s="21" t="str">
-        <x:v>用户中心设为可访问，再配置其所需售后业务权限范围</x:v>
+        <x:v>功能模块、店铺、仓库、安全、字段和用户中心等级</x:v>
       </x:c>
       <x:c r="Q278" s="21" t="str">
-        <x:v>用户中心设为无，不再单独配置售后业务权限</x:v>
+        <x:v>功能模块、店铺、仓库、登录密码、字段和应用权限</x:v>
       </x:c>
       <x:c r="R278" s="21" t="str">
-        <x:v>用户中心设为可操作，但只授权一个售后店铺范围</x:v>
+        <x:v>功能模块、店铺、仓库、安全、手机号和应用权限</x:v>
       </x:c>
       <x:c r="S278" s="21" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="T278" s="21" t="str">
-        <x:v>用户中心权限设为无，再单独配置其所需售后业务权限范围</x:v>
+        <x:v>功能模块、店铺、仓库、安全、字段和应用权限配置</x:v>
       </x:c>
       <x:c r="U278" s="21" t="str">
-        <x:v>无表示不能访问员工列表；客服业务功能可另行授权，不需要为登录或售后工作开放员工管理。</x:v>
+        <x:v>这些是员工权限配置页面提供的主要权限维度。</x:v>
       </x:c>
       <x:c r="V278" s="21" t="str">
-        <x:v>{"B":"权限过宽：客服不承担员工管理，无需查看用户中心。","C":"权限不足：关闭用户中心后仍需单独授予其售后业务权限。","D":"风险过高：店铺范围不能消除用户中心可编辑、删除员工的能力。"}</x:v>
+        <x:v>{"B":"范围混淆：用户中心等级单独设置，不替代应用权限维度。","C":"字段替换错误：登录密码属于账号信息，不是该权限维度。","D":"字段替换错误：手机号属于账号信息，不是字段权限。"}</x:v>
       </x:c>
       <x:c r="W278" s="21" t="str">
-        <x:v>把员工管理能力限定给真正负责账号管理的人，防止普通员工查看、修改或删除其他员工。</x:v>
+        <x:v>按岗位限定员工能使用的功能和能看到的数据范围，避免越权操作或看错店仓数据。</x:v>
       </x:c>
       <x:c r="X278" s="21" t="str">
-        <x:v>["配置","权限设置","管理员工","员工列表","用户中心权限"]</x:v>
+        <x:v>["配置","基本设置","权限开关","配置","权限设置","管理员工","配置权限"]</x:v>
       </x:c>
       <x:c r="Y278" s="21" t="str">
-        <x:v>["已明确员工是否承担账号管理职责","已区分只看员工列表与可编辑删除员工的风险"]</x:v>
+        <x:v>["已建立员工账号","已明确岗位需要的功能、店铺、仓库和字段范围"]</x:v>
       </x:c>
       <x:c r="Z278" s="21" t="str">
-        <x:v>["确认岗位职责","普通业务员工不需要账号中心时选择无","只需查看时选择可访问","需要管理全部员工时才选择可操作","再单独配置该岗位必需的业务权限并验证"]</x:v>
+        <x:v>["在基本设置的权限开关中启用需要控制的店铺、仓库或字段维度","进入管理员工并选择目标员工","点击配置权限","分别配置功能模块、店铺、仓库、安全、字段和应用权限","用员工账号验证可见范围"]</x:v>
       </x:c>
       <x:c r="AA278" s="21" t="str">
-        <x:v>["普通员工不能进入员工列表","查看人员不能编辑或删除员工","只有授权管理员能编辑或删除员工"]</x:v>
+        <x:v>["目标员工只看到授权功能和数据范围","未授权店铺、仓库或字段不可见或不可操作","权限开关与员工配置均已生效"]</x:v>
       </x:c>
       <x:c r="AB278" s="21" t="str">
-        <x:v>["可操作权限可以查看、编辑和删除任意员工，属于高风险权限；资料没有规定固定岗位模板，最终范围应按实际职责确认"]</x:v>
+        <x:v>["系统默认只显示功能权限；店铺、仓库和字段等权限需先在基本设置的权限开关中启用后才能精细配置"]</x:v>
       </x:c>
       <x:c r="AC278" s="21" t="str">
-        <x:v>["把用户中心权限当业务功能总开关","为方便给普通员工可操作"]</x:v>
+        <x:v>["把账号资料字段当权限维度","只配置业务功能不限制店仓范围"]</x:v>
       </x:c>
       <x:c r="AD278" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -34157,10 +34159,10 @@
       </x:c>
       <x:c r="AF278" s="21" t="str"/>
       <x:c r="AG278" s="21" t="str">
-        <x:v>员工权限—用户中心权限等级</x:v>
+        <x:v>员工权限—权限维度与权限开关</x:v>
       </x:c>
       <x:c r="AH278" s="21" t="str">
-        <x:v>用户中心权限为无时不能访问员工列表，业务功能权限可单独配置。</x:v>
+        <x:v>员工配置权限包含功能模块、店铺、仓库、安全、字段和应用。</x:v>
       </x:c>
       <x:c r="AI278" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -34204,7 +34206,7 @@
       <x:c r="AV278" s="21" t="str"/>
       <x:c r="AW278" s="21" t="str"/>
       <x:c r="AX278" s="21" t="str">
-        <x:v>按职责控制用户中心高风险权限</x:v>
+        <x:v>配置功能、店铺、仓库和字段权限</x:v>
       </x:c>
       <x:c r="AY278" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -34212,7 +34214,7 @@
     </x:row>
     <x:row r="279" ht="46" customHeight="1">
       <x:c r="A279" s="21" t="str">
-        <x:v>WDT-042-B</x:v>
+        <x:v>WDT-042-A</x:v>
       </x:c>
       <x:c r="B279" s="21" t="str">
         <x:v>旺店通-管理</x:v>
@@ -34230,16 +34232,16 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G279" s="21" t="str">
-        <x:v>基础</x:v>
+        <x:v>场景</x:v>
       </x:c>
       <x:c r="H279" s="21" t="str">
         <x:v>高</x:v>
       </x:c>
       <x:c r="I279" s="21" t="str">
-        <x:v>redline</x:v>
+        <x:v>practice</x:v>
       </x:c>
       <x:c r="J279" s="22" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K279" s="21" t="str">
         <x:v>WDT-K042</x:v>
@@ -34251,31 +34253,31 @@
         <x:v>无、可访问、可操作三档要按职责分配</x:v>
       </x:c>
       <x:c r="N279" s="21" t="str">
-        <x:v>哪一档用户中心权限能够查看、编辑并删除任意员工，因此应作为高风险权限控制？</x:v>
+        <x:v>客服员工只需处理售后，不承担员工账号管理；用户中心权限应如何设置？</x:v>
       </x:c>
       <x:c r="O279" s="21" t="str">
-        <x:v>功能权限，因为该档可访问账号中心并删除任意员工</x:v>
+        <x:v>用户中心权限设为无，再单独配置其所需售后业务权限范围</x:v>
       </x:c>
       <x:c r="P279" s="21" t="str">
-        <x:v>可访问，因为该档可查看列表并编辑任意员工</x:v>
+        <x:v>用户中心设为可访问，再配置其所需售后业务权限范围</x:v>
       </x:c>
       <x:c r="Q279" s="21" t="str">
-        <x:v>无，因为该档可隐藏员工列表并删除任意员工</x:v>
+        <x:v>用户中心设为无，不再单独配置售后业务权限</x:v>
       </x:c>
       <x:c r="R279" s="21" t="str">
-        <x:v>可操作，因为该档可查看、编辑和删除任意员工</x:v>
+        <x:v>用户中心设为可操作，但只授权一个售后店铺范围</x:v>
       </x:c>
       <x:c r="S279" s="21" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="T279" s="21" t="str">
-        <x:v>可操作，因为该档可查看、编辑和删除任意员工</x:v>
+        <x:v>用户中心权限设为无，再单独配置其所需售后业务权限范围</x:v>
       </x:c>
       <x:c r="U279" s="21" t="str">
-        <x:v>资料对可操作的定义包含查看、编辑和删除任意员工，权限影响范围最大。</x:v>
+        <x:v>无表示不能访问员工列表；客服业务功能可另行授权，不需要为登录或售后工作开放员工管理。</x:v>
       </x:c>
       <x:c r="V279" s="21" t="str">
-        <x:v>{"A":"概念错误：功能权限不是用户中心三档之一。","B":"定义错误：可访问仅允许查看。","C":"定义错误：无表示不能访问员工列表。"}</x:v>
+        <x:v>{"B":"权限过宽：客服不承担员工管理，无需查看用户中心。","C":"权限不足：关闭用户中心后仍需单独授予其售后业务权限。","D":"风险过高：店铺范围不能消除用户中心可编辑、删除员工的能力。"}</x:v>
       </x:c>
       <x:c r="W279" s="21" t="str">
         <x:v>把员工管理能力限定给真正负责账号管理的人，防止普通员工查看、修改或删除其他员工。</x:v>
@@ -34296,7 +34298,7 @@
         <x:v>["可操作权限可以查看、编辑和删除任意员工，属于高风险权限；资料没有规定固定岗位模板，最终范围应按实际职责确认"]</x:v>
       </x:c>
       <x:c r="AC279" s="21" t="str">
-        <x:v>["以为可访问也能编辑员工","把功能权限与用户中心权限混为一谈"]</x:v>
+        <x:v>["把用户中心权限当业务功能总开关","为方便给普通员工可操作"]</x:v>
       </x:c>
       <x:c r="AD279" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -34309,7 +34311,7 @@
         <x:v>员工权限—用户中心权限等级</x:v>
       </x:c>
       <x:c r="AH279" s="21" t="str">
-        <x:v>用户中心权限可操作=可查看、编辑、删除任意员工。</x:v>
+        <x:v>用户中心权限为无时不能访问员工列表，业务功能权限可单独配置。</x:v>
       </x:c>
       <x:c r="AI279" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -34361,16 +34363,16 @@
     </x:row>
     <x:row r="280" ht="46" customHeight="1">
       <x:c r="A280" s="21" t="str">
-        <x:v>WDT-043-A</x:v>
+        <x:v>WDT-042-B</x:v>
       </x:c>
       <x:c r="B280" s="21" t="str">
-        <x:v>旺店通-审单</x:v>
+        <x:v>旺店通-管理</x:v>
       </x:c>
       <x:c r="C280" s="21" t="str">
-        <x:v>审单</x:v>
+        <x:v>管理</x:v>
       </x:c>
       <x:c r="D280" s="21" t="str">
-        <x:v>无效货品</x:v>
+        <x:v>权限管理</x:v>
       </x:c>
       <x:c r="E280" s="21" t="str">
         <x:v>通用</x:v>
@@ -34379,86 +34381,86 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G280" s="21" t="str">
-        <x:v>进阶</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="H280" s="21" t="str">
         <x:v>高</x:v>
       </x:c>
       <x:c r="I280" s="21" t="str">
-        <x:v>practice</x:v>
+        <x:v>redline</x:v>
       </x:c>
       <x:c r="J280" s="22" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K280" s="21" t="str">
-        <x:v>WDT-K043</x:v>
+        <x:v>WDT-K042</x:v>
       </x:c>
       <x:c r="L280" s="21" t="str">
-        <x:v>无效货品成因与入口</x:v>
+        <x:v>最小权限与用户中心权限</x:v>
       </x:c>
       <x:c r="M280" s="21" t="str">
-        <x:v>先判断未匹配，再进入待发货未匹配</x:v>
+        <x:v>无、可访问、可操作三档要按职责分配</x:v>
       </x:c>
       <x:c r="N280" s="21" t="str">
-        <x:v>平台订单已抓取但未进入 ERP，检查发现相关平台货品没有匹配系统货品；在什么设置组合下会形成无效货品？</x:v>
+        <x:v>哪一档用户中心权限能够查看、编辑并删除任意员工，因此应作为高风险权限控制？</x:v>
       </x:c>
       <x:c r="O280" s="21" t="str">
-        <x:v>开启自动创建系统货品，且平台货品已经匹配</x:v>
+        <x:v>功能权限，因为该档可访问账号中心并删除任意员工</x:v>
       </x:c>
       <x:c r="P280" s="21" t="str">
-        <x:v>关闭自动创建系统货品，但平台货品已经匹配</x:v>
+        <x:v>可访问，因为该档可查看列表并编辑任意员工</x:v>
       </x:c>
       <x:c r="Q280" s="21" t="str">
-        <x:v>关闭自动创建系统货品，且平台货品尚未匹配</x:v>
+        <x:v>无，因为该档可隐藏员工列表并删除任意员工</x:v>
       </x:c>
       <x:c r="R280" s="21" t="str">
-        <x:v>开启自动创建系统货品，但系统货品库存不足</x:v>
+        <x:v>可操作，因为该档可查看、编辑和删除任意员工</x:v>
       </x:c>
       <x:c r="S280" s="21" t="str">
-        <x:v>C</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="T280" s="21" t="str">
-        <x:v>关闭自动创建系统货品，且平台货品尚未匹配</x:v>
+        <x:v>可操作，因为该档可查看、编辑和删除任意员工</x:v>
       </x:c>
       <x:c r="U280" s="21" t="str">
-        <x:v>资料明确指出，自动创建系统货品关闭且平台货品未匹配时，订单会因无效货品无法进入 ERP。</x:v>
+        <x:v>资料对可操作的定义包含查看、编辑和删除任意员工，权限影响范围最大。</x:v>
       </x:c>
       <x:c r="V280" s="21" t="str">
-        <x:v>{"A":"错条件：货品已经匹配时不会形成该类无效货品。","B":"错条件：即使关闭自动创建，已完成匹配也不属于该异常。","D":"错原因：库存不足属于库存问题，不等于货品未匹配。"}</x:v>
+        <x:v>{"A":"概念错误：功能权限不是用户中心三档之一。","B":"定义错误：可访问仅允许查看。","C":"定义错误：无表示不能访问员工列表。"}</x:v>
       </x:c>
       <x:c r="W280" s="21" t="str">
-        <x:v>快速定位因平台货品未匹配而无法进入 ERP 的订单，避免漏单和超时发货。</x:v>
+        <x:v>把员工管理能力限定给真正负责账号管理的人，防止普通员工查看、修改或删除其他员工。</x:v>
       </x:c>
       <x:c r="X280" s="21" t="str">
-        <x:v>["订单页面右上角","无效货品","货品匹配","待发货未匹配"]</x:v>
+        <x:v>["配置","权限设置","管理员工","员工列表","用户中心权限"]</x:v>
       </x:c>
       <x:c r="Y280" s="21" t="str">
-        <x:v>["平台订单已抓取","订单中的平台货品尚未完成系统货品匹配"]</x:v>
+        <x:v>["已明确员工是否承担账号管理职责","已区分只看员工列表与可编辑删除员工的风险"]</x:v>
       </x:c>
       <x:c r="Z280" s="21" t="str">
-        <x:v>["查看订单页右上角无效货品红色数量","点击无效货品进入货品匹配","打开待发货未匹配","按货品主数据情况选择后续匹配方式"]</x:v>
+        <x:v>["确认岗位职责","普通业务员工不需要账号中心时选择无","只需查看时选择可访问","需要管理全部员工时才选择可操作","再单独配置该岗位必需的业务权限并验证"]</x:v>
       </x:c>
       <x:c r="AA280" s="21" t="str">
-        <x:v>["可在待发货未匹配中看到待处理平台货品","已明确是自动匹配、新建货品还是组合匹配场景"]</x:v>
+        <x:v>["普通员工不能进入员工列表","查看人员不能编辑或删除员工","只有授权管理员能编辑或删除员工"]</x:v>
       </x:c>
       <x:c r="AB280" s="21" t="str">
-        <x:v>["只有关闭自动创建系统货品且平台货品未匹配时，相关订单才会因无效货品无法进入 ERP"]</x:v>
+        <x:v>["可操作权限可以查看、编辑和删除任意员工，属于高风险权限；资料没有规定固定岗位模板，最终范围应按实际职责确认"]</x:v>
       </x:c>
       <x:c r="AC280" s="21" t="str">
-        <x:v>["把库存不足当作无效货品成因","忽略自动创建系统货品开关"]</x:v>
+        <x:v>["以为可访问也能编辑员工","把功能权限与用户中心权限混为一谈"]</x:v>
       </x:c>
       <x:c r="AD280" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
       </x:c>
       <x:c r="AE280" s="21" t="str">
-        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/cldrxggkpa0czr46</x:v>
+        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/cgddc2</x:v>
       </x:c>
       <x:c r="AF280" s="21" t="str"/>
       <x:c r="AG280" s="21" t="str">
-        <x:v>无效货品—产生原因与处理入口</x:v>
+        <x:v>员工权限—用户中心权限等级</x:v>
       </x:c>
       <x:c r="AH280" s="21" t="str">
-        <x:v>关闭自动创建系统货品且平台货品未匹配，会产生无效货品并阻止订单进入 ERP。</x:v>
+        <x:v>用户中心权限可操作=可查看、编辑、删除任意员工。</x:v>
       </x:c>
       <x:c r="AI280" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -34502,7 +34504,7 @@
       <x:c r="AV280" s="21" t="str"/>
       <x:c r="AW280" s="21" t="str"/>
       <x:c r="AX280" s="21" t="str">
-        <x:v>识别无效货品并找到处理入口</x:v>
+        <x:v>按职责控制用户中心高风险权限</x:v>
       </x:c>
       <x:c r="AY280" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -34510,7 +34512,7 @@
     </x:row>
     <x:row r="281" ht="46" customHeight="1">
       <x:c r="A281" s="21" t="str">
-        <x:v>WDT-043-B</x:v>
+        <x:v>WDT-043-A</x:v>
       </x:c>
       <x:c r="B281" s="21" t="str">
         <x:v>旺店通-审单</x:v>
@@ -34528,7 +34530,7 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G281" s="21" t="str">
-        <x:v>基础</x:v>
+        <x:v>进阶</x:v>
       </x:c>
       <x:c r="H281" s="21" t="str">
         <x:v>高</x:v>
@@ -34549,31 +34551,31 @@
         <x:v>先判断未匹配，再进入待发货未匹配</x:v>
       </x:c>
       <x:c r="N281" s="21" t="str">
-        <x:v>发现订单页右上角出现无效货品红色数量后，正确的处理入口顺序是什么？</x:v>
+        <x:v>平台订单已抓取但未进入 ERP，检查发现相关平台货品没有匹配系统货品；在什么设置组合下会形成无效货品？</x:v>
       </x:c>
       <x:c r="O281" s="21" t="str">
-        <x:v>点击无效货品，进入货品匹配，再打开已发货未匹配</x:v>
+        <x:v>开启自动创建系统货品，且平台货品已经匹配</x:v>
       </x:c>
       <x:c r="P281" s="21" t="str">
-        <x:v>点击待审核，进入货品匹配，再打开待发货未匹配</x:v>
+        <x:v>关闭自动创建系统货品，但平台货品已经匹配</x:v>
       </x:c>
       <x:c r="Q281" s="21" t="str">
-        <x:v>点击无效货品，进入货品匹配，再打开待发货未匹配</x:v>
+        <x:v>关闭自动创建系统货品，且平台货品尚未匹配</x:v>
       </x:c>
       <x:c r="R281" s="21" t="str">
-        <x:v>点击无效货品，进入货品匹配，再打开待审核未匹配</x:v>
+        <x:v>开启自动创建系统货品，但系统货品库存不足</x:v>
       </x:c>
       <x:c r="S281" s="21" t="str">
         <x:v>C</x:v>
       </x:c>
       <x:c r="T281" s="21" t="str">
-        <x:v>点击无效货品，进入货品匹配，再打开待发货未匹配</x:v>
+        <x:v>关闭自动创建系统货品，且平台货品尚未匹配</x:v>
       </x:c>
       <x:c r="U281" s="21" t="str">
-        <x:v>无效货品红色数量是入口提示，待处理记录位于货品匹配的待发货未匹配。</x:v>
+        <x:v>资料明确指出，自动创建系统货品关闭且平台货品未匹配时，订单会因无效货品无法进入 ERP。</x:v>
       </x:c>
       <x:c r="V281" s="21" t="str">
-        <x:v>{"A":"错状态：待处理的是待发货未匹配，不是已发货未匹配。","B":"错首入口：应从订单页右上角无效货品进入。","D":"错状态：资料指定进入待发货未匹配。"}</x:v>
+        <x:v>{"A":"错条件：货品已经匹配时不会形成该类无效货品。","B":"错条件：即使关闭自动创建，已完成匹配也不属于该异常。","D":"错原因：库存不足属于库存问题，不等于货品未匹配。"}</x:v>
       </x:c>
       <x:c r="W281" s="21" t="str">
         <x:v>快速定位因平台货品未匹配而无法进入 ERP 的订单，避免漏单和超时发货。</x:v>
@@ -34594,7 +34596,7 @@
         <x:v>["只有关闭自动创建系统货品且平台货品未匹配时，相关订单才会因无效货品无法进入 ERP"]</x:v>
       </x:c>
       <x:c r="AC281" s="21" t="str">
-        <x:v>["进入缺货列表处理","从待发货拆单入口寻找匹配功能"]</x:v>
+        <x:v>["把库存不足当作无效货品成因","忽略自动创建系统货品开关"]</x:v>
       </x:c>
       <x:c r="AD281" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -34607,7 +34609,7 @@
         <x:v>无效货品—产生原因与处理入口</x:v>
       </x:c>
       <x:c r="AH281" s="21" t="str">
-        <x:v>订单页右上角无效货品→货品匹配→待发货未匹配。</x:v>
+        <x:v>关闭自动创建系统货品且平台货品未匹配，会产生无效货品并阻止订单进入 ERP。</x:v>
       </x:c>
       <x:c r="AI281" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -34659,7 +34661,7 @@
     </x:row>
     <x:row r="282" ht="46" customHeight="1">
       <x:c r="A282" s="21" t="str">
-        <x:v>WDT-044-A</x:v>
+        <x:v>WDT-043-B</x:v>
       </x:c>
       <x:c r="B282" s="21" t="str">
         <x:v>旺店通-审单</x:v>
@@ -34680,7 +34682,7 @@
         <x:v>基础</x:v>
       </x:c>
       <x:c r="H282" s="21" t="str">
-        <x:v>中</x:v>
+        <x:v>高</x:v>
       </x:c>
       <x:c r="I282" s="21" t="str">
         <x:v>practice</x:v>
@@ -34689,61 +34691,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K282" s="21" t="str">
-        <x:v>WDT-K044</x:v>
+        <x:v>WDT-K043</x:v>
       </x:c>
       <x:c r="L282" s="21" t="str">
-        <x:v>无效货品自动匹配</x:v>
+        <x:v>无效货品成因与入口</x:v>
       </x:c>
       <x:c r="M282" s="21" t="str">
-        <x:v>有商家编码时先尝试批量自动匹配</x:v>
+        <x:v>先判断未匹配，再进入待发货未匹配</x:v>
       </x:c>
       <x:c r="N282" s="21" t="str">
-        <x:v>准备对待发货未匹配货品执行批量自动匹配，资料给出的关键前提是什么？</x:v>
+        <x:v>发现订单页右上角出现无效货品红色数量后，正确的处理入口顺序是什么？</x:v>
       </x:c>
       <x:c r="O282" s="21" t="str">
-        <x:v>平台货品有商家编码，但尚未开启自动匹配</x:v>
+        <x:v>点击无效货品，进入货品匹配，再打开已发货未匹配</x:v>
       </x:c>
       <x:c r="P282" s="21" t="str">
-        <x:v>平台货品没有商家编码，但已经开启自动匹配</x:v>
+        <x:v>点击待审核，进入货品匹配，再打开待发货未匹配</x:v>
       </x:c>
       <x:c r="Q282" s="21" t="str">
-        <x:v>平台货品没有商家编码，并且未开启自动匹配</x:v>
+        <x:v>点击无效货品，进入货品匹配，再打开待发货未匹配</x:v>
       </x:c>
       <x:c r="R282" s="21" t="str">
-        <x:v>平台货品有商家编码，并且已开启自动匹配</x:v>
+        <x:v>点击无效货品，进入货品匹配，再打开待审核未匹配</x:v>
       </x:c>
       <x:c r="S282" s="21" t="str">
-        <x:v>D</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="T282" s="21" t="str">
-        <x:v>平台货品有商家编码，并且已开启自动匹配</x:v>
+        <x:v>点击无效货品，进入货品匹配，再打开待发货未匹配</x:v>
       </x:c>
       <x:c r="U282" s="21" t="str">
-        <x:v>批量自动匹配依赖可识别的商家编码及已开启的自动匹配能力。</x:v>
+        <x:v>无效货品红色数量是入口提示，待处理记录位于货品匹配的待发货未匹配。</x:v>
       </x:c>
       <x:c r="V282" s="21" t="str">
-        <x:v>{"A":"缺少开关：只有商家编码而未开启自动匹配仍不满足条件。","B":"缺少编码：开启自动匹配也需要平台货品有商家编码。","C":"两个前置都缺失：既没有商家编码也没有开启自动匹配。"}</x:v>
+        <x:v>{"A":"错状态：待处理的是待发货未匹配，不是已发货未匹配。","B":"错首入口：应从订单页右上角无效货品进入。","D":"错状态：资料指定进入待发货未匹配。"}</x:v>
       </x:c>
       <x:c r="W282" s="21" t="str">
-        <x:v>利用平台商家编码批量建立正确货品关系，提高异常订单回流效率。</x:v>
+        <x:v>快速定位因平台货品未匹配而无法进入 ERP 的订单，避免漏单和超时发货。</x:v>
       </x:c>
       <x:c r="X282" s="21" t="str">
         <x:v>["订单页面右上角","无效货品","货品匹配","待发货未匹配"]</x:v>
       </x:c>
       <x:c r="Y282" s="21" t="str">
-        <x:v>["平台货品已填写可用商家编码","系统已开启自动匹配"]</x:v>
+        <x:v>["平台订单已抓取","订单中的平台货品尚未完成系统货品匹配"]</x:v>
       </x:c>
       <x:c r="Z282" s="21" t="str">
-        <x:v>["勾选需要处理的未匹配货品","点击批量自动匹配","确认本次匹配策略","检查匹配结果"]</x:v>
+        <x:v>["查看订单页右上角无效货品红色数量","点击无效货品进入货品匹配","打开待发货未匹配","按货品主数据情况选择后续匹配方式"]</x:v>
       </x:c>
       <x:c r="AA282" s="21" t="str">
-        <x:v>["平台货品已建立到正确系统货品的映射","对应订单可继续自动提交"]</x:v>
+        <x:v>["可在待发货未匹配中看到待处理平台货品","已明确是自动匹配、新建货品还是组合匹配场景"]</x:v>
       </x:c>
       <x:c r="AB282" s="21" t="str">
-        <x:v>["没有商家编码或无法按编码命中时，应转用新建系统货品或组合匹配"]</x:v>
+        <x:v>["只有关闭自动创建系统货品且平台货品未匹配时，相关订单才会因无效货品无法进入 ERP"]</x:v>
       </x:c>
       <x:c r="AC282" s="21" t="str">
-        <x:v>["无编码也直接自动匹配","把库存存在等同于匹配关系存在"]</x:v>
+        <x:v>["进入缺货列表处理","从待发货拆单入口寻找匹配功能"]</x:v>
       </x:c>
       <x:c r="AD282" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -34753,10 +34755,10 @@
       </x:c>
       <x:c r="AF282" s="21" t="str"/>
       <x:c r="AG282" s="21" t="str">
-        <x:v>无效货品—批量自动匹配</x:v>
+        <x:v>无效货品—产生原因与处理入口</x:v>
       </x:c>
       <x:c r="AH282" s="21" t="str">
-        <x:v>有商家编码且开启自动匹配后，才适用批量自动匹配。</x:v>
+        <x:v>订单页右上角无效货品→货品匹配→待发货未匹配。</x:v>
       </x:c>
       <x:c r="AI282" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -34800,7 +34802,7 @@
       <x:c r="AV282" s="21" t="str"/>
       <x:c r="AW282" s="21" t="str"/>
       <x:c r="AX282" s="21" t="str">
-        <x:v>用商家编码批量自动匹配无效货品</x:v>
+        <x:v>识别无效货品并找到处理入口</x:v>
       </x:c>
       <x:c r="AY282" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -34808,7 +34810,7 @@
     </x:row>
     <x:row r="283" ht="46" customHeight="1">
       <x:c r="A283" s="21" t="str">
-        <x:v>WDT-044-B</x:v>
+        <x:v>WDT-044-A</x:v>
       </x:c>
       <x:c r="B283" s="21" t="str">
         <x:v>旺店通-审单</x:v>
@@ -34826,7 +34828,7 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G283" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="H283" s="21" t="str">
         <x:v>中</x:v>
@@ -34847,31 +34849,31 @@
         <x:v>有商家编码时先尝试批量自动匹配</x:v>
       </x:c>
       <x:c r="N283" s="21" t="str">
-        <x:v>未匹配列表中有一批带商家编码的货品，正确的批量操作顺序是什么？</x:v>
+        <x:v>准备对待发货未匹配货品执行批量自动匹配，资料给出的关键前提是什么？</x:v>
       </x:c>
       <x:c r="O283" s="21" t="str">
-        <x:v>先批量生成货品，再开启自动匹配，最后删除原记录</x:v>
+        <x:v>平台货品有商家编码，但尚未开启自动匹配</x:v>
       </x:c>
       <x:c r="P283" s="21" t="str">
-        <x:v>先确认策略，再勾选货品，最后点击组合匹配</x:v>
+        <x:v>平台货品没有商家编码，但已经开启自动匹配</x:v>
       </x:c>
       <x:c r="Q283" s="21" t="str">
-        <x:v>先勾选未匹配货品，再点批量自动匹配并确认策略</x:v>
+        <x:v>平台货品没有商家编码，并且未开启自动匹配</x:v>
       </x:c>
       <x:c r="R283" s="21" t="str">
-        <x:v>先打开订单详情，再逐单新建货品，最后批量审核</x:v>
+        <x:v>平台货品有商家编码，并且已开启自动匹配</x:v>
       </x:c>
       <x:c r="S283" s="21" t="str">
-        <x:v>C</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="T283" s="21" t="str">
-        <x:v>先勾选未匹配货品，再点批量自动匹配并确认策略</x:v>
+        <x:v>平台货品有商家编码，并且已开启自动匹配</x:v>
       </x:c>
       <x:c r="U283" s="21" t="str">
-        <x:v>资料给出的顺序是先选中异常货品，再执行批量自动匹配并确认匹配策略。</x:v>
+        <x:v>批量自动匹配依赖可识别的商家编码及已开启的自动匹配能力。</x:v>
       </x:c>
       <x:c r="V283" s="21" t="str">
-        <x:v>{"A":"错动作：已有编码时不应先批量生成重复系统货品。","B":"错顺序和方式：应先选货品，且本场景用自动匹配。","D":"错范围：批量场景无需先逐单新建系统货品。"}</x:v>
+        <x:v>{"A":"缺少开关：只有商家编码而未开启自动匹配仍不满足条件。","B":"缺少编码：开启自动匹配也需要平台货品有商家编码。","C":"两个前置都缺失：既没有商家编码也没有开启自动匹配。"}</x:v>
       </x:c>
       <x:c r="W283" s="21" t="str">
         <x:v>利用平台商家编码批量建立正确货品关系，提高异常订单回流效率。</x:v>
@@ -34892,7 +34894,7 @@
         <x:v>["没有商家编码或无法按编码命中时，应转用新建系统货品或组合匹配"]</x:v>
       </x:c>
       <x:c r="AC283" s="21" t="str">
-        <x:v>["未勾选目标就执行","把自动匹配和组合匹配混用"]</x:v>
+        <x:v>["无编码也直接自动匹配","把库存存在等同于匹配关系存在"]</x:v>
       </x:c>
       <x:c r="AD283" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -34905,7 +34907,7 @@
         <x:v>无效货品—批量自动匹配</x:v>
       </x:c>
       <x:c r="AH283" s="21" t="str">
-        <x:v>选择未匹配货品→批量自动匹配→确认策略。</x:v>
+        <x:v>有商家编码且开启自动匹配后，才适用批量自动匹配。</x:v>
       </x:c>
       <x:c r="AI283" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -34957,7 +34959,7 @@
     </x:row>
     <x:row r="284" ht="46" customHeight="1">
       <x:c r="A284" s="21" t="str">
-        <x:v>WDT-045-A</x:v>
+        <x:v>WDT-044-B</x:v>
       </x:c>
       <x:c r="B284" s="21" t="str">
         <x:v>旺店通-审单</x:v>
@@ -34987,61 +34989,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K284" s="21" t="str">
-        <x:v>WDT-K045</x:v>
+        <x:v>WDT-K044</x:v>
       </x:c>
       <x:c r="L284" s="21" t="str">
-        <x:v>无效货品新建系统货品</x:v>
+        <x:v>无效货品自动匹配</x:v>
       </x:c>
       <x:c r="M284" s="21" t="str">
-        <x:v>少量一对一新建，大量批量生成</x:v>
+        <x:v>有商家编码时先尝试批量自动匹配</x:v>
       </x:c>
       <x:c r="N284" s="21" t="str">
-        <x:v>确认只有两条平台货品在 ERP 中没有对应系统货品，最合适的处理是什么？</x:v>
+        <x:v>未匹配列表中有一批带商家编码的货品，正确的批量操作顺序是什么？</x:v>
       </x:c>
       <x:c r="O284" s="21" t="str">
-        <x:v>先批量生成全部平台货品，再删除重复的系统货品</x:v>
+        <x:v>先批量生成货品，再开启自动匹配，最后删除原记录</x:v>
       </x:c>
       <x:c r="P284" s="21" t="str">
-        <x:v>直接批量自动匹配到名称相近的已有货品</x:v>
+        <x:v>先确认策略，再勾选货品，最后点击组合匹配</x:v>
       </x:c>
       <x:c r="Q284" s="21" t="str">
-        <x:v>分别点击新建，按平台货品一对一创建系统货品</x:v>
+        <x:v>先勾选未匹配货品，再点批量自动匹配并确认策略</x:v>
       </x:c>
       <x:c r="R284" s="21" t="str">
-        <x:v>先做组合匹配，再把已有系统货品规格全部覆盖</x:v>
+        <x:v>先打开订单详情，再逐单新建货品，最后批量审核</x:v>
       </x:c>
       <x:c r="S284" s="21" t="str">
         <x:v>C</x:v>
       </x:c>
       <x:c r="T284" s="21" t="str">
-        <x:v>分别点击新建，按平台货品一对一创建系统货品</x:v>
+        <x:v>先勾选未匹配货品，再点批量自动匹配并确认策略</x:v>
       </x:c>
       <x:c r="U284" s="21" t="str">
-        <x:v>系统货品不存在且数量较少时，资料建议通过新建进行一对一创建，便于逐条核对。</x:v>
+        <x:v>资料给出的顺序是先选中异常货品，再执行批量自动匹配并确认匹配策略。</x:v>
       </x:c>
       <x:c r="V284" s="21" t="str">
-        <x:v>{"A":"错范围：少量记录无需扩大为全量批量生成。","B":"错依据：名称相近不能证明是同一系统货品。","D":"错适用：组合匹配要求已有可复用系统货品。"}</x:v>
+        <x:v>{"A":"错动作：已有编码时不应先批量生成重复系统货品。","B":"错顺序和方式：应先选货品，且本场景用自动匹配。","D":"错范围：批量场景无需先逐单新建系统货品。"}</x:v>
       </x:c>
       <x:c r="W284" s="21" t="str">
-        <x:v>在系统货品确实不存在时，按待处理规模选择高效且可核验的新建方式。</x:v>
+        <x:v>利用平台商家编码批量建立正确货品关系，提高异常订单回流效率。</x:v>
       </x:c>
       <x:c r="X284" s="21" t="str">
-        <x:v>["货品匹配","待发货未匹配","新建或批量生成系统货品"]</x:v>
+        <x:v>["订单页面右上角","无效货品","货品匹配","待发货未匹配"]</x:v>
       </x:c>
       <x:c r="Y284" s="21" t="str">
-        <x:v>["已确认 ERP 中不存在可复用的系统货品","平台货品信息可用于建立系统货品"]</x:v>
+        <x:v>["平台货品已填写可用商家编码","系统已开启自动匹配"]</x:v>
       </x:c>
       <x:c r="Z284" s="21" t="str">
-        <x:v>["少量货品点击新建进行一对一创建","大量货品选择批量生成系统货品","核对新建结果和匹配关系","检查订单是否恢复提交"]</x:v>
+        <x:v>["勾选需要处理的未匹配货品","点击批量自动匹配","确认本次匹配策略","检查匹配结果"]</x:v>
       </x:c>
       <x:c r="AA284" s="21" t="str">
-        <x:v>["每个平台货品已关联到应有系统货品","没有因批量操作生成明显重复货品"]</x:v>
+        <x:v>["平台货品已建立到正确系统货品的映射","对应订单可继续自动提交"]</x:v>
       </x:c>
       <x:c r="AB284" s="21" t="str">
-        <x:v>["如果 ERP 已有对应系统货品，应使用组合匹配而不是重复新建"]</x:v>
+        <x:v>["没有商家编码或无法按编码命中时，应转用新建系统货品或组合匹配"]</x:v>
       </x:c>
       <x:c r="AC284" s="21" t="str">
-        <x:v>["按相似名称盲目自动匹配","为少量记录大范围批量生成"]</x:v>
+        <x:v>["未勾选目标就执行","把自动匹配和组合匹配混用"]</x:v>
       </x:c>
       <x:c r="AD284" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -35051,10 +35053,10 @@
       </x:c>
       <x:c r="AF284" s="21" t="str"/>
       <x:c r="AG284" s="21" t="str">
-        <x:v>无效货品—新建系统货品</x:v>
+        <x:v>无效货品—批量自动匹配</x:v>
       </x:c>
       <x:c r="AH284" s="21" t="str">
-        <x:v>少量且不存在系统货品时，点击新建进行一对一创建。</x:v>
+        <x:v>选择未匹配货品→批量自动匹配→确认策略。</x:v>
       </x:c>
       <x:c r="AI284" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -35098,7 +35100,7 @@
       <x:c r="AV284" s="21" t="str"/>
       <x:c r="AW284" s="21" t="str"/>
       <x:c r="AX284" s="21" t="str">
-        <x:v>按数量新建缺失的系统货品</x:v>
+        <x:v>用商家编码批量自动匹配无效货品</x:v>
       </x:c>
       <x:c r="AY284" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -35106,7 +35108,7 @@
     </x:row>
     <x:row r="285" ht="46" customHeight="1">
       <x:c r="A285" s="21" t="str">
-        <x:v>WDT-045-B</x:v>
+        <x:v>WDT-045-A</x:v>
       </x:c>
       <x:c r="B285" s="21" t="str">
         <x:v>旺店通-审单</x:v>
@@ -35124,7 +35126,7 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G285" s="21" t="str">
-        <x:v>基础</x:v>
+        <x:v>场景</x:v>
       </x:c>
       <x:c r="H285" s="21" t="str">
         <x:v>中</x:v>
@@ -35145,31 +35147,31 @@
         <x:v>少量一对一新建，大量批量生成</x:v>
       </x:c>
       <x:c r="N285" s="21" t="str">
-        <x:v>待发货未匹配中有大量平台货品，且确认系统内都没有对应货品，应选哪种方式？</x:v>
+        <x:v>确认只有两条平台货品在 ERP 中没有对应系统货品，最合适的处理是什么？</x:v>
       </x:c>
       <x:c r="O285" s="21" t="str">
-        <x:v>逐条点击新建并一对一生成所有系统货品</x:v>
+        <x:v>先批量生成全部平台货品，再删除重复的系统货品</x:v>
       </x:c>
       <x:c r="P285" s="21" t="str">
-        <x:v>选择批量生成系统货品并核对生成结果</x:v>
+        <x:v>直接批量自动匹配到名称相近的已有货品</x:v>
       </x:c>
       <x:c r="Q285" s="21" t="str">
-        <x:v>逐条自动匹配到相同价格的系统货品</x:v>
+        <x:v>分别点击新建，按平台货品一对一创建系统货品</x:v>
       </x:c>
       <x:c r="R285" s="21" t="str">
-        <x:v>逐条组合匹配到最近使用的系统货品</x:v>
+        <x:v>先做组合匹配，再把已有系统货品规格全部覆盖</x:v>
       </x:c>
       <x:c r="S285" s="21" t="str">
-        <x:v>B</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="T285" s="21" t="str">
-        <x:v>选择批量生成系统货品并核对生成结果</x:v>
+        <x:v>分别点击新建，按平台货品一对一创建系统货品</x:v>
       </x:c>
       <x:c r="U285" s="21" t="str">
-        <x:v>当缺失的系统货品数量多时，批量生成是资料给出的高效方式，生成后仍需核验。</x:v>
+        <x:v>系统货品不存在且数量较少时，资料建议通过新建进行一对一创建，便于逐条核对。</x:v>
       </x:c>
       <x:c r="V285" s="21" t="str">
-        <x:v>{"A":"错效率：逐条新建适合少量货品，大量应批量生成。","C":"错依据：价格相同不是货品匹配依据。","D":"错适用：不存在对应系统货品时不能随意组合匹配。"}</x:v>
+        <x:v>{"A":"错范围：少量记录无需扩大为全量批量生成。","B":"错依据：名称相近不能证明是同一系统货品。","D":"错适用：组合匹配要求已有可复用系统货品。"}</x:v>
       </x:c>
       <x:c r="W285" s="21" t="str">
         <x:v>在系统货品确实不存在时，按待处理规模选择高效且可核验的新建方式。</x:v>
@@ -35190,7 +35192,7 @@
         <x:v>["如果 ERP 已有对应系统货品，应使用组合匹配而不是重复新建"]</x:v>
       </x:c>
       <x:c r="AC285" s="21" t="str">
-        <x:v>["大量记录仍逐条创建","把订单拆分当作货品建档"]</x:v>
+        <x:v>["按相似名称盲目自动匹配","为少量记录大范围批量生成"]</x:v>
       </x:c>
       <x:c r="AD285" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -35203,7 +35205,7 @@
         <x:v>无效货品—新建系统货品</x:v>
       </x:c>
       <x:c r="AH285" s="21" t="str">
-        <x:v>大量且不存在系统货品时，可批量生成系统货品。</x:v>
+        <x:v>少量且不存在系统货品时，点击新建进行一对一创建。</x:v>
       </x:c>
       <x:c r="AI285" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -35255,7 +35257,7 @@
     </x:row>
     <x:row r="286" ht="46" customHeight="1">
       <x:c r="A286" s="21" t="str">
-        <x:v>WDT-046-A</x:v>
+        <x:v>WDT-045-B</x:v>
       </x:c>
       <x:c r="B286" s="21" t="str">
         <x:v>旺店通-审单</x:v>
@@ -35273,10 +35275,10 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G286" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="H286" s="21" t="str">
-        <x:v>高</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I286" s="21" t="str">
         <x:v>practice</x:v>
@@ -35285,61 +35287,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K286" s="21" t="str">
-        <x:v>WDT-K046</x:v>
+        <x:v>WDT-K045</x:v>
       </x:c>
       <x:c r="L286" s="21" t="str">
-        <x:v>无效货品组合匹配</x:v>
+        <x:v>无效货品新建系统货品</x:v>
       </x:c>
       <x:c r="M286" s="21" t="str">
-        <x:v>已有系统货品时不要重复新建</x:v>
+        <x:v>少量一对一新建，大量批量生成</x:v>
       </x:c>
       <x:c r="N286" s="21" t="str">
-        <x:v>平台货品对应的系统商品已经存在，正确的匹配动作是什么？</x:v>
+        <x:v>待发货未匹配中有大量平台货品，且确认系统内都没有对应货品，应选哪种方式？</x:v>
       </x:c>
       <x:c r="O286" s="21" t="str">
-        <x:v>使用组合匹配，选择最近或其他系统货品或对应新规格</x:v>
+        <x:v>逐条点击新建并一对一生成所有系统货品</x:v>
       </x:c>
       <x:c r="P286" s="21" t="str">
-        <x:v>使用批量自动匹配，仅按名称选择现有系统货品</x:v>
+        <x:v>选择批量生成系统货品并核对生成结果</x:v>
       </x:c>
       <x:c r="Q286" s="21" t="str">
-        <x:v>再新建一条同名系统货品，随后删除原系统货品</x:v>
+        <x:v>逐条自动匹配到相同价格的系统货品</x:v>
       </x:c>
       <x:c r="R286" s="21" t="str">
-        <x:v>先批量生成系统货品，再用商家编码覆盖原规格</x:v>
+        <x:v>逐条组合匹配到最近使用的系统货品</x:v>
       </x:c>
       <x:c r="S286" s="21" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="T286" s="21" t="str">
-        <x:v>使用组合匹配，选择最近或其他系统货品或对应新规格</x:v>
+        <x:v>选择批量生成系统货品并核对生成结果</x:v>
       </x:c>
       <x:c r="U286" s="21" t="str">
-        <x:v>已有系统货品时应复用既有主数据，通过组合匹配建立平台货品关系。</x:v>
+        <x:v>当缺失的系统货品数量多时，批量生成是资料给出的高效方式，生成后仍需核验。</x:v>
       </x:c>
       <x:c r="V286" s="21" t="str">
-        <x:v>{"B":"错依据：仅凭名称自动匹配不能保证规格关系准确。","C":"错动作：会制造重复主数据并破坏原关系。","D":"错适用：批量生成用于系统货品不存在的场景。"}</x:v>
+        <x:v>{"A":"错效率：逐条新建适合少量货品，大量应批量生成。","C":"错依据：价格相同不是货品匹配依据。","D":"错适用：不存在对应系统货品时不能随意组合匹配。"}</x:v>
       </x:c>
       <x:c r="W286" s="21" t="str">
-        <x:v>将一个或多个平台货品准确映射到既有系统货品，恢复订单自动提交。</x:v>
+        <x:v>在系统货品确实不存在时，按待处理规模选择高效且可核验的新建方式。</x:v>
       </x:c>
       <x:c r="X286" s="21" t="str">
-        <x:v>["货品匹配","待发货未匹配","组合匹配"]</x:v>
+        <x:v>["货品匹配","待发货未匹配","新建或批量生成系统货品"]</x:v>
       </x:c>
       <x:c r="Y286" s="21" t="str">
-        <x:v>["ERP 中已有可复用的系统货品或系统规格","已核对平台规格与目标系统货品一致"]</x:v>
+        <x:v>["已确认 ERP 中不存在可复用的系统货品","平台货品信息可用于建立系统货品"]</x:v>
       </x:c>
       <x:c r="Z286" s="21" t="str">
-        <x:v>["选择待匹配的平台货品","进入组合匹配","选择最近使用或其他系统货品，必要时选择新系统规格","确认匹配并查看订单提交结果"]</x:v>
+        <x:v>["少量货品点击新建进行一对一创建","大量货品选择批量生成系统货品","核对新建结果和匹配关系","检查订单是否恢复提交"]</x:v>
       </x:c>
       <x:c r="AA286" s="21" t="str">
-        <x:v>["待发货未匹配列表不再保留已处理货品","相关订单自动提交进入后续流程"]</x:v>
+        <x:v>["每个平台货品已关联到应有系统货品","没有因批量操作生成明显重复货品"]</x:v>
       </x:c>
       <x:c r="AB286" s="21" t="str">
-        <x:v>["一个或多个平台货品均可映射到同一个系统货品，但必须先确认业务上确为同一履约货品"]</x:v>
+        <x:v>["如果 ERP 已有对应系统货品，应使用组合匹配而不是重复新建"]</x:v>
       </x:c>
       <x:c r="AC286" s="21" t="str">
-        <x:v>["重复建立同一系统货品","取消订单代替修复货品关系"]</x:v>
+        <x:v>["大量记录仍逐条创建","把订单拆分当作货品建档"]</x:v>
       </x:c>
       <x:c r="AD286" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -35349,10 +35351,10 @@
       </x:c>
       <x:c r="AF286" s="21" t="str"/>
       <x:c r="AG286" s="21" t="str">
-        <x:v>无效货品—组合匹配与结果核验</x:v>
+        <x:v>无效货品—新建系统货品</x:v>
       </x:c>
       <x:c r="AH286" s="21" t="str">
-        <x:v>已有系统货品时，组合匹配可选择最近、其他系统货品或新系统规格。</x:v>
+        <x:v>大量且不存在系统货品时，可批量生成系统货品。</x:v>
       </x:c>
       <x:c r="AI286" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -35396,7 +35398,7 @@
       <x:c r="AV286" s="21" t="str"/>
       <x:c r="AW286" s="21" t="str"/>
       <x:c r="AX286" s="21" t="str">
-        <x:v>把平台货品组合匹配到已有系统货品</x:v>
+        <x:v>按数量新建缺失的系统货品</x:v>
       </x:c>
       <x:c r="AY286" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -35404,7 +35406,7 @@
     </x:row>
     <x:row r="287" ht="46" customHeight="1">
       <x:c r="A287" s="21" t="str">
-        <x:v>WDT-046-B</x:v>
+        <x:v>WDT-046-A</x:v>
       </x:c>
       <x:c r="B287" s="21" t="str">
         <x:v>旺店通-审单</x:v>
@@ -35422,7 +35424,7 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G287" s="21" t="str">
-        <x:v>进阶</x:v>
+        <x:v>场景</x:v>
       </x:c>
       <x:c r="H287" s="21" t="str">
         <x:v>高</x:v>
@@ -35443,31 +35445,31 @@
         <x:v>已有系统货品时不要重复新建</x:v>
       </x:c>
       <x:c r="N287" s="21" t="str">
-        <x:v>完成无效货品匹配后，哪组结果才能证明本次处理已生效？</x:v>
+        <x:v>平台货品对应的系统商品已经存在，正确的匹配动作是什么？</x:v>
       </x:c>
       <x:c r="O287" s="21" t="str">
-        <x:v>未匹配列表已清空，但没有继续核对相关订单是否提交</x:v>
+        <x:v>使用组合匹配，选择最近或其他系统货品或对应新规格</x:v>
       </x:c>
       <x:c r="P287" s="21" t="str">
-        <x:v>页面提示匹配成功，只看提示、不复查列表与订单状态</x:v>
+        <x:v>使用批量自动匹配，仅按名称选择现有系统货品</x:v>
       </x:c>
       <x:c r="Q287" s="21" t="str">
-        <x:v>待发货未匹配不再有该货品，相关订单自动提交</x:v>
+        <x:v>再新建一条同名系统货品，随后删除原系统货品</x:v>
       </x:c>
       <x:c r="R287" s="21" t="str">
-        <x:v>相关订单已提交，但该货品仍留在待发货未匹配</x:v>
+        <x:v>先批量生成系统货品，再用商家编码覆盖原规格</x:v>
       </x:c>
       <x:c r="S287" s="21" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="T287" s="21" t="str">
-        <x:v>待发货未匹配不再有该货品，相关订单自动提交</x:v>
+        <x:v>使用组合匹配，选择最近或其他系统货品或对应新规格</x:v>
       </x:c>
       <x:c r="U287" s="21" t="str">
-        <x:v>资料把未匹配列表清空和订单自动提交作为匹配成功后的直接结果。</x:v>
+        <x:v>已有系统货品时应复用既有主数据，通过组合匹配建立平台货品关系。</x:v>
       </x:c>
       <x:c r="V287" s="21" t="str">
-        <x:v>{"A":"核验不完整：还必须确认相关订单已经自动提交。","B":"证据不足：成功提示不能替代列表和订单状态复查。","D":"核验不完整：该货品不应继续留在未匹配列表。"}</x:v>
+        <x:v>{"B":"错依据：仅凭名称自动匹配不能保证规格关系准确。","C":"错动作：会制造重复主数据并破坏原关系。","D":"错适用：批量生成用于系统货品不存在的场景。"}</x:v>
       </x:c>
       <x:c r="W287" s="21" t="str">
         <x:v>将一个或多个平台货品准确映射到既有系统货品，恢复订单自动提交。</x:v>
@@ -35488,7 +35490,7 @@
         <x:v>["一个或多个平台货品均可映射到同一个系统货品，但必须先确认业务上确为同一履约货品"]</x:v>
       </x:c>
       <x:c r="AC287" s="21" t="str">
-        <x:v>["只看匹配弹窗成功不查列表","列表清空后不核对订单流转"]</x:v>
+        <x:v>["重复建立同一系统货品","取消订单代替修复货品关系"]</x:v>
       </x:c>
       <x:c r="AD287" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -35501,7 +35503,7 @@
         <x:v>无效货品—组合匹配与结果核验</x:v>
       </x:c>
       <x:c r="AH287" s="21" t="str">
-        <x:v>匹配成功后待发货未匹配为空，订单会自动提交。</x:v>
+        <x:v>已有系统货品时，组合匹配可选择最近、其他系统货品或新系统规格。</x:v>
       </x:c>
       <x:c r="AI287" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -35553,16 +35555,16 @@
     </x:row>
     <x:row r="288" ht="46" customHeight="1">
       <x:c r="A288" s="21" t="str">
-        <x:v>WDT-047-A</x:v>
+        <x:v>WDT-046-B</x:v>
       </x:c>
       <x:c r="B288" s="21" t="str">
-        <x:v>旺店通-运营</x:v>
+        <x:v>旺店通-审单</x:v>
       </x:c>
       <x:c r="C288" s="21" t="str">
-        <x:v>运营</x:v>
+        <x:v>审单</x:v>
       </x:c>
       <x:c r="D288" s="21" t="str">
-        <x:v>店铺对接</x:v>
+        <x:v>无效货品</x:v>
       </x:c>
       <x:c r="E288" s="21" t="str">
         <x:v>通用</x:v>
@@ -35571,7 +35573,7 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G288" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>进阶</x:v>
       </x:c>
       <x:c r="H288" s="21" t="str">
         <x:v>高</x:v>
@@ -35583,74 +35585,74 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K288" s="21" t="str">
-        <x:v>WDT-K047</x:v>
+        <x:v>WDT-K046</x:v>
       </x:c>
       <x:c r="L288" s="21" t="str">
-        <x:v>店铺通用绑定流程</x:v>
+        <x:v>无效货品组合匹配</x:v>
       </x:c>
       <x:c r="M288" s="21" t="str">
-        <x:v>从绑定新店铺开始，以绑定成功结束</x:v>
+        <x:v>已有系统货品时不要重复新建</x:v>
       </x:c>
       <x:c r="N288" s="21" t="str">
-        <x:v>新店铺已经在平台服务市场完成订购，接下来要把它接入旺店通，正确操作是什么？</x:v>
+        <x:v>完成无效货品匹配后，哪组结果才能证明本次处理已生效？</x:v>
       </x:c>
       <x:c r="O288" s="21" t="str">
-        <x:v>返回配置—绑定店铺，在对应平台只点击去绑定不再登录</x:v>
+        <x:v>未匹配列表已清空，但没有继续核对相关订单是否提交</x:v>
       </x:c>
       <x:c r="P288" s="21" t="str">
-        <x:v>返回 ERP 新建同名店铺，但跳过平台账号授权</x:v>
+        <x:v>页面提示匹配成功，只看提示、不复查列表与订单状态</x:v>
       </x:c>
       <x:c r="Q288" s="21" t="str">
-        <x:v>返回配置—绑定店铺，在对应平台点击去绑定并登录授权</x:v>
+        <x:v>待发货未匹配不再有该货品，相关订单自动提交</x:v>
       </x:c>
       <x:c r="R288" s="21" t="str">
-        <x:v>在平台后台等待自动同步，出现订单后再回 ERP</x:v>
+        <x:v>相关订单已提交，但该货品仍留在待发货未匹配</x:v>
       </x:c>
       <x:c r="S288" s="21" t="str">
         <x:v>C</x:v>
       </x:c>
       <x:c r="T288" s="21" t="str">
-        <x:v>返回配置—绑定店铺，在对应平台点击去绑定并登录授权</x:v>
+        <x:v>待发货未匹配不再有该货品，相关订单自动提交</x:v>
       </x:c>
       <x:c r="U288" s="21" t="str">
-        <x:v>平台订购只是前段步骤，仍需返回 ERP 通过去绑定完成平台账号授权。</x:v>
+        <x:v>资料把未匹配列表清空和订单自动提交作为匹配成功后的直接结果。</x:v>
       </x:c>
       <x:c r="V288" s="21" t="str">
-        <x:v>{"A":"动作不完整：点击去绑定后仍需登录平台完成授权。","B":"错前置：建立名称不能替代平台授权。","D":"错顺序：未完成 ERP 绑定前不能依赖自动同步。"}</x:v>
+        <x:v>{"A":"核验不完整：还必须确认相关订单已经自动提交。","B":"证据不足：成功提示不能替代列表和订单状态复查。","D":"核验不完整：该货品不应继续留在未匹配列表。"}</x:v>
       </x:c>
       <x:c r="W288" s="21" t="str">
-        <x:v>让目标平台店铺完整接入 ERP，并在操作后留下可核验的绑定状态。</x:v>
+        <x:v>将一个或多个平台货品准确映射到既有系统货品，恢复订单自动提交。</x:v>
       </x:c>
       <x:c r="X288" s="21" t="str">
-        <x:v>["配置","绑定店铺","绑定新店铺"]</x:v>
+        <x:v>["货品匹配","待发货未匹配","组合匹配"]</x:v>
       </x:c>
       <x:c r="Y288" s="21" t="str">
-        <x:v>["已确认目标店铺对应的平台类型","已准备目标平台可授权的登录账号"]</x:v>
+        <x:v>["ERP 中已有可复用的系统货品或系统规格","已核对平台规格与目标系统货品一致"]</x:v>
       </x:c>
       <x:c r="Z288" s="21" t="str">
-        <x:v>["选择目标平台并进入订购授权流程","按平台要求完成订购、审核或付款","返回 ERP 在对应平台点击去绑定","登录平台完成授权","回到店铺列表核验绑定结果"]</x:v>
+        <x:v>["选择待匹配的平台货品","进入组合匹配","选择最近使用或其他系统货品，必要时选择新系统规格","确认匹配并查看订单提交结果"]</x:v>
       </x:c>
       <x:c r="AA288" s="21" t="str">
-        <x:v>["店铺列表显示正确的平台和店铺名称","可看到绑定时间且状态为绑定成功"]</x:v>
+        <x:v>["待发货未匹配列表不再保留已处理货品","相关订单自动提交进入后续流程"]</x:v>
       </x:c>
       <x:c r="AB288" s="21" t="str">
-        <x:v>["淘系和京东存在提交订单、审核等特殊步骤；其他平台按当前平台页面直接订购付款"]</x:v>
+        <x:v>["一个或多个平台货品均可映射到同一个系统货品，但必须先确认业务上确为同一履约货品"]</x:v>
       </x:c>
       <x:c r="AC288" s="21" t="str">
-        <x:v>["把订购成功等同于 ERP 已绑定","跳过平台登录授权"]</x:v>
+        <x:v>["只看匹配弹窗成功不查列表","列表清空后不核对订单流转"]</x:v>
       </x:c>
       <x:c r="AD288" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
       </x:c>
       <x:c r="AE288" s="21" t="str">
-        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/opgdsg</x:v>
+        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/cldrxggkpa0czr46</x:v>
       </x:c>
       <x:c r="AF288" s="21" t="str"/>
       <x:c r="AG288" s="21" t="str">
-        <x:v>店铺管理—通用订购授权绑定流程</x:v>
+        <x:v>无效货品—组合匹配与结果核验</x:v>
       </x:c>
       <x:c r="AH288" s="21" t="str">
-        <x:v>订购完成后返回 ERP 对应平台点击去绑定并登录授权。</x:v>
+        <x:v>匹配成功后待发货未匹配为空，订单会自动提交。</x:v>
       </x:c>
       <x:c r="AI288" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -35694,7 +35696,7 @@
       <x:c r="AV288" s="21" t="str"/>
       <x:c r="AW288" s="21" t="str"/>
       <x:c r="AX288" s="21" t="str">
-        <x:v>完成店铺订购、授权、绑定与结果核验</x:v>
+        <x:v>把平台货品组合匹配到已有系统货品</x:v>
       </x:c>
       <x:c r="AY288" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -35702,7 +35704,7 @@
     </x:row>
     <x:row r="289" ht="46" customHeight="1">
       <x:c r="A289" s="21" t="str">
-        <x:v>WDT-047-B</x:v>
+        <x:v>WDT-047-A</x:v>
       </x:c>
       <x:c r="B289" s="21" t="str">
         <x:v>旺店通-运营</x:v>
@@ -35720,7 +35722,7 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G289" s="21" t="str">
-        <x:v>基础</x:v>
+        <x:v>场景</x:v>
       </x:c>
       <x:c r="H289" s="21" t="str">
         <x:v>高</x:v>
@@ -35741,31 +35743,31 @@
         <x:v>从绑定新店铺开始，以绑定成功结束</x:v>
       </x:c>
       <x:c r="N289" s="21" t="str">
-        <x:v>店铺授权页面提示完成后，运营应在 ERP 店铺列表核验哪组信息？</x:v>
+        <x:v>新店铺已经在平台服务市场完成订购，接下来要把它接入旺店通，正确操作是什么？</x:v>
       </x:c>
       <x:c r="O289" s="21" t="str">
-        <x:v>平台名称、店铺名称、订购时间、服务付款状态</x:v>
+        <x:v>返回配置—绑定店铺，在对应平台只点击去绑定不再登录</x:v>
       </x:c>
       <x:c r="P289" s="21" t="str">
-        <x:v>平台名称、店铺名称、授权账号、平台登录状态</x:v>
+        <x:v>返回 ERP 新建同名店铺，但跳过平台账号授权</x:v>
       </x:c>
       <x:c r="Q289" s="21" t="str">
-        <x:v>平台名称、店铺名称、绑定时间、绑定成功状态</x:v>
+        <x:v>返回配置—绑定店铺，在对应平台点击去绑定并登录授权</x:v>
       </x:c>
       <x:c r="R289" s="21" t="str">
-        <x:v>平台名称、店铺名称、服务到期日、订购成功状态</x:v>
+        <x:v>在平台后台等待自动同步，出现订单后再回 ERP</x:v>
       </x:c>
       <x:c r="S289" s="21" t="str">
         <x:v>C</x:v>
       </x:c>
       <x:c r="T289" s="21" t="str">
-        <x:v>平台名称、店铺名称、绑定时间、绑定成功状态</x:v>
+        <x:v>返回配置—绑定店铺，在对应平台点击去绑定并登录授权</x:v>
       </x:c>
       <x:c r="U289" s="21" t="str">
-        <x:v>资料要求在店铺列表用这四项确认接入对象和绑定结果，不能只依赖平台页面提示。</x:v>
+        <x:v>平台订购只是前段步骤，仍需返回 ERP 通过去绑定完成平台账号授权。</x:v>
       </x:c>
       <x:c r="V289" s="21" t="str">
-        <x:v>{"A":"错结果：订购付款状态不能证明 ERP 绑定已经成功。","B":"错结果：平台登录成功不等于 ERP 列表绑定成功。","D":"错结果：订购状态与服务期限不能替代绑定状态核验。"}</x:v>
+        <x:v>{"A":"动作不完整：点击去绑定后仍需登录平台完成授权。","B":"错前置：建立名称不能替代平台授权。","D":"错顺序：未完成 ERP 绑定前不能依赖自动同步。"}</x:v>
       </x:c>
       <x:c r="W289" s="21" t="str">
         <x:v>让目标平台店铺完整接入 ERP，并在操作后留下可核验的绑定状态。</x:v>
@@ -35786,7 +35788,7 @@
         <x:v>["淘系和京东存在提交订单、审核等特殊步骤；其他平台按当前平台页面直接订购付款"]</x:v>
       </x:c>
       <x:c r="AC289" s="21" t="str">
-        <x:v>["只核对店铺名不核平台","只看授权弹窗不查最终状态"]</x:v>
+        <x:v>["把订购成功等同于 ERP 已绑定","跳过平台登录授权"]</x:v>
       </x:c>
       <x:c r="AD289" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -35799,7 +35801,7 @@
         <x:v>店铺管理—通用订购授权绑定流程</x:v>
       </x:c>
       <x:c r="AH289" s="21" t="str">
-        <x:v>绑定后核验列表中的平台、店铺名称、绑定时间及绑定成功。</x:v>
+        <x:v>订购完成后返回 ERP 对应平台点击去绑定并登录授权。</x:v>
       </x:c>
       <x:c r="AI289" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -35851,7 +35853,7 @@
     </x:row>
     <x:row r="290" ht="46" customHeight="1">
       <x:c r="A290" s="21" t="str">
-        <x:v>WDT-048-A</x:v>
+        <x:v>WDT-047-B</x:v>
       </x:c>
       <x:c r="B290" s="21" t="str">
         <x:v>旺店通-运营</x:v>
@@ -35869,7 +35871,7 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G290" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="H290" s="21" t="str">
         <x:v>高</x:v>
@@ -35881,61 +35883,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K290" s="21" t="str">
-        <x:v>WDT-K048</x:v>
+        <x:v>WDT-K047</x:v>
       </x:c>
       <x:c r="L290" s="21" t="str">
-        <x:v>店铺绑定风险控制</x:v>
+        <x:v>店铺通用绑定流程</x:v>
       </x:c>
       <x:c r="M290" s="21" t="str">
-        <x:v>从 ERP 发起登录，平台类型一次选对</x:v>
+        <x:v>从绑定新店铺开始，以绑定成功结束</x:v>
       </x:c>
       <x:c r="N290" s="21" t="str">
-        <x:v>从旺店通点击去绑定并进入平台登录页后，怎样操作最能避免本次授权会话失败？</x:v>
+        <x:v>店铺授权页面提示完成后，运营应在 ERP 店铺列表核验哪组信息？</x:v>
       </x:c>
       <x:c r="O290" s="21" t="str">
-        <x:v>另开一个新浏览器页面先登录平台，再返回原页授权</x:v>
+        <x:v>平台名称、店铺名称、订购时间、服务付款状态</x:v>
       </x:c>
       <x:c r="P290" s="21" t="str">
-        <x:v>同时打开两个登录页面，哪个先成功就保留哪个</x:v>
+        <x:v>平台名称、店铺名称、授权账号、平台登录状态</x:v>
       </x:c>
       <x:c r="Q290" s="21" t="str">
-        <x:v>关闭当前授权页面后从平台首页进入旺店通配置</x:v>
+        <x:v>平台名称、店铺名称、绑定时间、绑定成功状态</x:v>
       </x:c>
       <x:c r="R290" s="21" t="str">
-        <x:v>继续在当前授权流程登录，不另开页面重复登录平台</x:v>
+        <x:v>平台名称、店铺名称、服务到期日、订购成功状态</x:v>
       </x:c>
       <x:c r="S290" s="21" t="str">
-        <x:v>D</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="T290" s="21" t="str">
-        <x:v>继续在当前授权流程登录，不另开页面重复登录平台</x:v>
+        <x:v>平台名称、店铺名称、绑定时间、绑定成功状态</x:v>
       </x:c>
       <x:c r="U290" s="21" t="str">
-        <x:v>资料明确提示，从 ERP 发起平台登录后再开其他页面登录会导致绑定失败。</x:v>
+        <x:v>资料要求在店铺列表用这四项确认接入对象和绑定结果，不能只依赖平台页面提示。</x:v>
       </x:c>
       <x:c r="V290" s="21" t="str">
-        <x:v>{"A":"错会话：另开登录页可能使原授权链路失效。","B":"错做法：并发登录会增加会话错乱和绑定失败风险。","C":"错入口：关闭当前页会中断 ERP 发起的绑定流程。"}</x:v>
+        <x:v>{"A":"错结果：订购付款状态不能证明 ERP 绑定已经成功。","B":"错结果：平台登录成功不等于 ERP 列表绑定成功。","D":"错结果：订购状态与服务期限不能替代绑定状态核验。"}</x:v>
       </x:c>
       <x:c r="W290" s="21" t="str">
-        <x:v>在授权前控制会话和平台类型，避免绑定失败或产生难以修正的错误数据。</x:v>
+        <x:v>让目标平台店铺完整接入 ERP，并在操作后留下可核验的绑定状态。</x:v>
       </x:c>
       <x:c r="X290" s="21" t="str">
-        <x:v>["配置","绑定店铺","绑定新店铺","选择平台","去绑定"]</x:v>
+        <x:v>["配置","绑定店铺","绑定新店铺"]</x:v>
       </x:c>
       <x:c r="Y290" s="21" t="str">
-        <x:v>["已确认店铺真实平台类型","已准备在当前授权页面完成平台登录"]</x:v>
+        <x:v>["已确认目标店铺对应的平台类型","已准备目标平台可授权的登录账号"]</x:v>
       </x:c>
       <x:c r="Z290" s="21" t="str">
-        <x:v>["在 ERP 准确选择平台类型","从 ERP 点击去绑定进入平台登录","在该授权流程内完成登录","绑定后核对平台类型与店铺信息"]</x:v>
+        <x:v>["选择目标平台并进入订购授权流程","按平台要求完成订购、审核或付款","返回 ERP 在对应平台点击去绑定","登录平台完成授权","回到店铺列表核验绑定结果"]</x:v>
       </x:c>
       <x:c r="AA290" s="21" t="str">
-        <x:v>["授权过程没有切换到另一个新开的平台登录页","ERP 显示的平台类型与实际店铺一致"]</x:v>
+        <x:v>["店铺列表显示正确的平台和店铺名称","可看到绑定时间且状态为绑定成功"]</x:v>
       </x:c>
       <x:c r="AB290" s="21" t="str">
-        <x:v>["淘宝、天猫、淘工厂、淘特、阿里巴巴类型不能选错；选错后通常需要技术支持处理数据再重绑"]</x:v>
+        <x:v>["淘系和京东存在提交订单、审核等特殊步骤；其他平台按当前平台页面直接订购付款"]</x:v>
       </x:c>
       <x:c r="AC290" s="21" t="str">
-        <x:v>["另开页面抢占登录会话","关闭 ERP 发起的授权链路"]</x:v>
+        <x:v>["只核对店铺名不核平台","只看授权弹窗不查最终状态"]</x:v>
       </x:c>
       <x:c r="AD290" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -35945,10 +35947,10 @@
       </x:c>
       <x:c r="AF290" s="21" t="str"/>
       <x:c r="AG290" s="21" t="str">
-        <x:v>店铺管理—登录页与平台类型注意事项</x:v>
+        <x:v>店铺管理—通用订购授权绑定流程</x:v>
       </x:c>
       <x:c r="AH290" s="21" t="str">
-        <x:v>ERP 发起平台登录后，不要再开其他浏览器页面登录平台。</x:v>
+        <x:v>绑定后核验列表中的平台、店铺名称、绑定时间及绑定成功。</x:v>
       </x:c>
       <x:c r="AI290" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -35992,7 +35994,7 @@
       <x:c r="AV290" s="21" t="str"/>
       <x:c r="AW290" s="21" t="str"/>
       <x:c r="AX290" s="21" t="str">
-        <x:v>规避授权会话与平台类型选错风险</x:v>
+        <x:v>完成店铺订购、授权、绑定与结果核验</x:v>
       </x:c>
       <x:c r="AY290" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -36000,7 +36002,7 @@
     </x:row>
     <x:row r="291" ht="46" customHeight="1">
       <x:c r="A291" s="21" t="str">
-        <x:v>WDT-048-B</x:v>
+        <x:v>WDT-048-A</x:v>
       </x:c>
       <x:c r="B291" s="21" t="str">
         <x:v>旺店通-运营</x:v>
@@ -36012,22 +36014,22 @@
         <x:v>店铺对接</x:v>
       </x:c>
       <x:c r="E291" s="21" t="str">
-        <x:v>阿里巴巴</x:v>
+        <x:v>通用</x:v>
       </x:c>
       <x:c r="F291" s="21" t="str">
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G291" s="21" t="str">
-        <x:v>进阶</x:v>
+        <x:v>场景</x:v>
       </x:c>
       <x:c r="H291" s="21" t="str">
         <x:v>高</x:v>
       </x:c>
       <x:c r="I291" s="21" t="str">
-        <x:v>redline</x:v>
+        <x:v>practice</x:v>
       </x:c>
       <x:c r="J291" s="22" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K291" s="21" t="str">
         <x:v>WDT-K048</x:v>
@@ -36039,31 +36041,31 @@
         <x:v>从 ERP 发起登录，平台类型一次选对</x:v>
       </x:c>
       <x:c r="N291" s="21" t="str">
-        <x:v>绑定淘系或阿里巴巴店铺前，运营对平台类型应采取什么做法？</x:v>
+        <x:v>从旺店通点击去绑定并进入平台登录页后，怎样操作最能避免本次授权会话失败？</x:v>
       </x:c>
       <x:c r="O291" s="21" t="str">
-        <x:v>先核实真实平台并准确选择，避免后续技术删数据重绑</x:v>
+        <x:v>另开一个新浏览器页面先登录平台，再返回原页授权</x:v>
       </x:c>
       <x:c r="P291" s="21" t="str">
-        <x:v>先选择淘宝类型，后续用店铺名称自动识别真实平台</x:v>
+        <x:v>同时打开两个登录页面，哪个先成功就保留哪个</x:v>
       </x:c>
       <x:c r="Q291" s="21" t="str">
-        <x:v>先选择阿里巴巴类型，绑定后再用授权账号覆盖类型</x:v>
+        <x:v>关闭当前授权页面后从平台首页进入旺店通配置</x:v>
       </x:c>
       <x:c r="R291" s="21" t="str">
-        <x:v>先选择任一淘系类型，抓到订单后再按订单来源修改</x:v>
+        <x:v>继续在当前授权流程登录，不另开页面重复登录平台</x:v>
       </x:c>
       <x:c r="S291" s="21" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="T291" s="21" t="str">
-        <x:v>先核实真实平台并准确选择，避免后续技术删数据重绑</x:v>
+        <x:v>继续在当前授权流程登录，不另开页面重复登录平台</x:v>
       </x:c>
       <x:c r="U291" s="21" t="str">
-        <x:v>淘宝、天猫、淘工厂、淘特和阿里巴巴的平台类型一旦选错，后续处理成本高，应在绑定前准确确认。</x:v>
+        <x:v>资料明确提示，从 ERP 发起平台登录后再开其他页面登录会导致绑定失败。</x:v>
       </x:c>
       <x:c r="V291" s="21" t="str">
-        <x:v>{"B":"错假设：资料没有自动识别并纠正类型的规则。","C":"错方法：授权账号不能覆盖已选的平台类型。","D":"错时机：有订单数据后再修改风险更高。"}</x:v>
+        <x:v>{"A":"错会话：另开登录页可能使原授权链路失效。","B":"错做法：并发登录会增加会话错乱和绑定失败风险。","C":"错入口：关闭当前页会中断 ERP 发起的绑定流程。"}</x:v>
       </x:c>
       <x:c r="W291" s="21" t="str">
         <x:v>在授权前控制会话和平台类型，避免绑定失败或产生难以修正的错误数据。</x:v>
@@ -36084,7 +36086,7 @@
         <x:v>["淘宝、天猫、淘工厂、淘特、阿里巴巴类型不能选错；选错后通常需要技术支持处理数据再重绑"]</x:v>
       </x:c>
       <x:c r="AC291" s="21" t="str">
-        <x:v>["先随意选类型再看结果","认为店铺名称会自动纠正平台类型"]</x:v>
+        <x:v>["另开页面抢占登录会话","关闭 ERP 发起的授权链路"]</x:v>
       </x:c>
       <x:c r="AD291" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -36097,7 +36099,7 @@
         <x:v>店铺管理—登录页与平台类型注意事项</x:v>
       </x:c>
       <x:c r="AH291" s="21" t="str">
-        <x:v>淘系及阿里巴巴的平台类型不能选错，选错通常需技术处理数据并重绑。</x:v>
+        <x:v>ERP 发起平台登录后，不要再开其他浏览器页面登录平台。</x:v>
       </x:c>
       <x:c r="AI291" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -36149,7 +36151,7 @@
     </x:row>
     <x:row r="292" ht="46" customHeight="1">
       <x:c r="A292" s="21" t="str">
-        <x:v>WDT-049-A</x:v>
+        <x:v>WDT-048-B</x:v>
       </x:c>
       <x:c r="B292" s="21" t="str">
         <x:v>旺店通-运营</x:v>
@@ -36161,7 +36163,7 @@
         <x:v>店铺对接</x:v>
       </x:c>
       <x:c r="E292" s="21" t="str">
-        <x:v>天猫/淘宝</x:v>
+        <x:v>阿里巴巴</x:v>
       </x:c>
       <x:c r="F292" s="21" t="str">
         <x:v>单选题</x:v>
@@ -36170,70 +36172,70 @@
         <x:v>进阶</x:v>
       </x:c>
       <x:c r="H292" s="21" t="str">
-        <x:v>中</x:v>
+        <x:v>高</x:v>
       </x:c>
       <x:c r="I292" s="21" t="str">
-        <x:v>practice</x:v>
+        <x:v>redline</x:v>
       </x:c>
       <x:c r="J292" s="22" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K292" s="21" t="str">
-        <x:v>WDT-K049</x:v>
+        <x:v>WDT-K048</x:v>
       </x:c>
       <x:c r="L292" s="21" t="str">
-        <x:v>淘宝天猫店铺绑定</x:v>
+        <x:v>店铺绑定风险控制</x:v>
       </x:c>
       <x:c r="M292" s="21" t="str">
-        <x:v>淘系先审核订购，类型误选按数据状态处理</x:v>
+        <x:v>从 ERP 发起登录，平台类型一次选对</x:v>
       </x:c>
       <x:c r="N292" s="21" t="str">
-        <x:v>与多数可直接订购付款的平台相比，淘宝天猫接入前的订购流程有什么差异？</x:v>
+        <x:v>绑定淘系或阿里巴巴店铺前，运营对平台类型应采取什么做法？</x:v>
       </x:c>
       <x:c r="O292" s="21" t="str">
-        <x:v>先完成店铺绑定，再提交服务订单补做平台审核</x:v>
+        <x:v>先核实真实平台并准确选择，避免后续技术删数据重绑</x:v>
       </x:c>
       <x:c r="P292" s="21" t="str">
-        <x:v>需要提交订单并等待审核，通过后再完成付款和确认</x:v>
+        <x:v>先选择淘宝类型，后续用店铺名称自动识别真实平台</x:v>
       </x:c>
       <x:c r="Q292" s="21" t="str">
-        <x:v>先在 ERP 抓取订单，再由平台审核是否允许订购</x:v>
+        <x:v>先选择阿里巴巴类型，绑定后再用授权账号覆盖类型</x:v>
       </x:c>
       <x:c r="R292" s="21" t="str">
-        <x:v>选择平台后直接付款，平台无需接收订购申请</x:v>
+        <x:v>先选择任一淘系类型，抓到订单后再按订单来源修改</x:v>
       </x:c>
       <x:c r="S292" s="21" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="T292" s="21" t="str">
-        <x:v>需要提交订单并等待审核，通过后再完成付款和确认</x:v>
+        <x:v>先核实真实平台并准确选择，避免后续技术删数据重绑</x:v>
       </x:c>
       <x:c r="U292" s="21" t="str">
-        <x:v>资料把淘系和京东列为订购时存在提交订单、审核步骤的平台。</x:v>
+        <x:v>淘宝、天猫、淘工厂、淘特和阿里巴巴的平台类型一旦选错，后续处理成本高，应在绑定前准确确认。</x:v>
       </x:c>
       <x:c r="V292" s="21" t="str">
-        <x:v>{"A":"错顺序：应先完成订购，再返回 ERP 绑定。","C":"错顺序：服务订购审核发生在 ERP 抓单前。","D":"错流程：淘系不是资料中的直接订购免审核场景。"}</x:v>
+        <x:v>{"B":"错假设：资料没有自动识别并纠正类型的规则。","C":"错方法：授权账号不能覆盖已选的平台类型。","D":"错时机：有订单数据后再修改风险更高。"}</x:v>
       </x:c>
       <x:c r="W292" s="21" t="str">
-        <x:v>按淘系特殊订购流程完成绑定，并在尚无订单数据时安全修正平台类型误选。</x:v>
+        <x:v>在授权前控制会话和平台类型，避免绑定失败或产生难以修正的错误数据。</x:v>
       </x:c>
       <x:c r="X292" s="21" t="str">
-        <x:v>["配置","绑定店铺","绑定新店铺","淘宝或天猫"]</x:v>
+        <x:v>["配置","绑定店铺","绑定新店铺","选择平台","去绑定"]</x:v>
       </x:c>
       <x:c r="Y292" s="21" t="str">
-        <x:v>["已确认是淘宝还是天猫店铺","已准备平台主账号完成服务订购与授权"]</x:v>
+        <x:v>["已确认店铺真实平台类型","已准备在当前授权页面完成平台登录"]</x:v>
       </x:c>
       <x:c r="Z292" s="21" t="str">
-        <x:v>["选择准确的淘宝或天猫平台类型","按平台流程提交订单并等待审核","审核通过后完成付款和服务确认","返回 ERP 点击去绑定并授权","核验绑定成功"]</x:v>
+        <x:v>["在 ERP 准确选择平台类型","从 ERP 点击去绑定进入平台登录","在该授权流程内完成登录","绑定后核对平台类型与店铺信息"]</x:v>
       </x:c>
       <x:c r="AA292" s="21" t="str">
-        <x:v>["列表平台类型与实际店铺一致","店铺状态为绑定成功"]</x:v>
+        <x:v>["授权过程没有切换到另一个新开的平台登录页","ERP 显示的平台类型与实际店铺一致"]</x:v>
       </x:c>
       <x:c r="AB292" s="21" t="str">
-        <x:v>["天猫误选为淘宝且尚无订单数据时，可先解绑，联系售后或销售修改配置后再正确选择重绑；已有订单数据时资料不建议解绑"]</x:v>
+        <x:v>["淘宝、天猫、淘工厂、淘特、阿里巴巴类型不能选错；选错后通常需要技术支持处理数据再重绑"]</x:v>
       </x:c>
       <x:c r="AC292" s="21" t="str">
-        <x:v>["按其他平台直接付款","先绑定后补订购审核"]</x:v>
+        <x:v>["先随意选类型再看结果","认为店铺名称会自动纠正平台类型"]</x:v>
       </x:c>
       <x:c r="AD292" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -36243,10 +36245,10 @@
       </x:c>
       <x:c r="AF292" s="21" t="str"/>
       <x:c r="AG292" s="21" t="str">
-        <x:v>店铺管理—淘宝天猫绑定与类型误选</x:v>
+        <x:v>店铺管理—登录页与平台类型注意事项</x:v>
       </x:c>
       <x:c r="AH292" s="21" t="str">
-        <x:v>淘系订购需提交订单和审核，审核后再付款确认。</x:v>
+        <x:v>淘系及阿里巴巴的平台类型不能选错，选错通常需技术处理数据并重绑。</x:v>
       </x:c>
       <x:c r="AI292" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -36290,7 +36292,7 @@
       <x:c r="AV292" s="21" t="str"/>
       <x:c r="AW292" s="21" t="str"/>
       <x:c r="AX292" s="21" t="str">
-        <x:v>绑定淘宝天猫并处理无订单的类型误选</x:v>
+        <x:v>规避授权会话与平台类型选错风险</x:v>
       </x:c>
       <x:c r="AY292" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -36298,7 +36300,7 @@
     </x:row>
     <x:row r="293" ht="46" customHeight="1">
       <x:c r="A293" s="21" t="str">
-        <x:v>WDT-049-B</x:v>
+        <x:v>WDT-049-A</x:v>
       </x:c>
       <x:c r="B293" s="21" t="str">
         <x:v>旺店通-运营</x:v>
@@ -36316,10 +36318,10 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G293" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>进阶</x:v>
       </x:c>
       <x:c r="H293" s="21" t="str">
-        <x:v>高</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I293" s="21" t="str">
         <x:v>practice</x:v>
@@ -36337,31 +36339,31 @@
         <x:v>淘系先审核订购，类型误选按数据状态处理</x:v>
       </x:c>
       <x:c r="N293" s="21" t="str">
-        <x:v>天猫店铺误按淘宝类型绑定，确认 ERP 还没有该店铺订单数据，资料建议怎样修正？</x:v>
+        <x:v>与多数可直接订购付款的平台相比，淘宝天猫接入前的订购流程有什么差异？</x:v>
       </x:c>
       <x:c r="O293" s="21" t="str">
-        <x:v>先抓取一笔订单产生数据，再按无订单流程解绑重绑</x:v>
+        <x:v>先完成店铺绑定，再提交服务订单补做平台审核</x:v>
       </x:c>
       <x:c r="P293" s="21" t="str">
-        <x:v>直接解绑后选择天猫重绑，不联系修改原平台配置</x:v>
+        <x:v>需要提交订单并等待审核，通过后再完成付款和确认</x:v>
       </x:c>
       <x:c r="Q293" s="21" t="str">
-        <x:v>先解绑，联系售后或销售修改配置，再选天猫重新绑定</x:v>
+        <x:v>先在 ERP 抓取订单，再由平台审核是否允许订购</x:v>
       </x:c>
       <x:c r="R293" s="21" t="str">
-        <x:v>保留错误绑定，只在店铺名称后补写天猫标识</x:v>
+        <x:v>选择平台后直接付款，平台无需接收订购申请</x:v>
       </x:c>
       <x:c r="S293" s="21" t="str">
-        <x:v>C</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="T293" s="21" t="str">
-        <x:v>先解绑，联系售后或销售修改配置，再选天猫重新绑定</x:v>
+        <x:v>需要提交订单并等待审核，通过后再完成付款和确认</x:v>
       </x:c>
       <x:c r="U293" s="21" t="str">
-        <x:v>无订单数据时可以按资料路径解绑并让售后或销售修正配置，再用正确类型重绑。</x:v>
+        <x:v>资料把淘系和京东列为订购时存在提交订单、审核步骤的平台。</x:v>
       </x:c>
       <x:c r="V293" s="21" t="str">
-        <x:v>{"A":"错时机：产生订单数据后资料不建议自行解绑。","B":"步骤缺失：资料要求联系售后或销售修改配置。","D":"错对象：店铺名称不能改变底层平台类型。"}</x:v>
+        <x:v>{"A":"错顺序：应先完成订购，再返回 ERP 绑定。","C":"错顺序：服务订购审核发生在 ERP 抓单前。","D":"错流程：淘系不是资料中的直接订购免审核场景。"}</x:v>
       </x:c>
       <x:c r="W293" s="21" t="str">
         <x:v>按淘系特殊订购流程完成绑定，并在尚无订单数据时安全修正平台类型误选。</x:v>
@@ -36382,7 +36384,7 @@
         <x:v>["天猫误选为淘宝且尚无订单数据时，可先解绑，联系售后或销售修改配置后再正确选择重绑；已有订单数据时资料不建议解绑"]</x:v>
       </x:c>
       <x:c r="AC293" s="21" t="str">
-        <x:v>["用改店铺名称替代平台类型修正","先产生订单数据再处理误选"]</x:v>
+        <x:v>["按其他平台直接付款","先绑定后补订购审核"]</x:v>
       </x:c>
       <x:c r="AD293" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -36395,7 +36397,7 @@
         <x:v>店铺管理—淘宝天猫绑定与类型误选</x:v>
       </x:c>
       <x:c r="AH293" s="21" t="str">
-        <x:v>天猫误选淘宝且无订单数据时，解绑后联系售后或销售改配置，再选择正确平台重绑。</x:v>
+        <x:v>淘系订购需提交订单和审核，审核后再付款确认。</x:v>
       </x:c>
       <x:c r="AI293" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -36447,7 +36449,7 @@
     </x:row>
     <x:row r="294" ht="46" customHeight="1">
       <x:c r="A294" s="21" t="str">
-        <x:v>WDT-050-A</x:v>
+        <x:v>WDT-049-B</x:v>
       </x:c>
       <x:c r="B294" s="21" t="str">
         <x:v>旺店通-运营</x:v>
@@ -36459,7 +36461,7 @@
         <x:v>店铺对接</x:v>
       </x:c>
       <x:c r="E294" s="21" t="str">
-        <x:v>拼多多</x:v>
+        <x:v>天猫/淘宝</x:v>
       </x:c>
       <x:c r="F294" s="21" t="str">
         <x:v>单选题</x:v>
@@ -36477,61 +36479,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K294" s="21" t="str">
-        <x:v>WDT-K050</x:v>
+        <x:v>WDT-K049</x:v>
       </x:c>
       <x:c r="L294" s="21" t="str">
-        <x:v>拼多多店铺绑定</x:v>
+        <x:v>淘宝天猫店铺绑定</x:v>
       </x:c>
       <x:c r="M294" s="21" t="str">
-        <x:v>拼多多选择企业版一年后返回 ERP 绑定</x:v>
+        <x:v>淘系先审核订购，类型误选按数据状态处理</x:v>
       </x:c>
       <x:c r="N294" s="21" t="str">
-        <x:v>拼多多平台服务已完成订购付款，哪一步才能完成 ERP 侧店铺绑定？</x:v>
+        <x:v>天猫店铺误按淘宝类型绑定，确认 ERP 还没有该店铺订单数据，资料建议怎样修正？</x:v>
       </x:c>
       <x:c r="O294" s="21" t="str">
-        <x:v>返回 ERP 拼多多入口后另开平台首页完成登录</x:v>
+        <x:v>先抓取一笔订单产生数据，再按无订单流程解绑重绑</x:v>
       </x:c>
       <x:c r="P294" s="21" t="str">
-        <x:v>返回 ERP 拼多多入口只核对服务订单是否付款</x:v>
+        <x:v>直接解绑后选择天猫重绑，不联系修改原平台配置</x:v>
       </x:c>
       <x:c r="Q294" s="21" t="str">
-        <x:v>留在平台服务市场等待 ERP 自动同步绑定状态</x:v>
+        <x:v>先解绑，联系售后或销售修改配置，再选天猫重新绑定</x:v>
       </x:c>
       <x:c r="R294" s="21" t="str">
-        <x:v>返回 ERP 拼多多入口点击去绑定并完成登录授权</x:v>
+        <x:v>保留错误绑定，只在店铺名称后补写天猫标识</x:v>
       </x:c>
       <x:c r="S294" s="21" t="str">
-        <x:v>D</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="T294" s="21" t="str">
-        <x:v>返回 ERP 拼多多入口点击去绑定并完成登录授权</x:v>
+        <x:v>先解绑，联系售后或销售修改配置，再选天猫重新绑定</x:v>
       </x:c>
       <x:c r="U294" s="21" t="str">
-        <x:v>平台订购付款不等于 ERP 已绑定；还要回到对应平台入口发起去绑定并完成登录授权。</x:v>
+        <x:v>无订单数据时可以按资料路径解绑并让售后或销售修正配置，再用正确类型重绑。</x:v>
       </x:c>
       <x:c r="V294" s="21" t="str">
-        <x:v>{"A":"错会话：应在 ERP 发起的授权流程内登录。","B":"动作不完整：核对付款不能建立授权关系。","C":"错顺序：服务市场不会替代 ERP 侧授权。"}</x:v>
+        <x:v>{"A":"错时机：产生订单数据后资料不建议自行解绑。","B":"步骤缺失：资料要求联系售后或销售修改配置。","D":"错对象：店铺名称不能改变底层平台类型。"}</x:v>
       </x:c>
       <x:c r="W294" s="21" t="str">
-        <x:v>按资料指定的服务版本和周期完成拼多多店铺订购与授权。</x:v>
+        <x:v>按淘系特殊订购流程完成绑定，并在尚无订单数据时安全修正平台类型误选。</x:v>
       </x:c>
       <x:c r="X294" s="21" t="str">
-        <x:v>["配置","绑定店铺","绑定新店铺","拼多多"]</x:v>
+        <x:v>["配置","绑定店铺","绑定新店铺","淘宝或天猫"]</x:v>
       </x:c>
       <x:c r="Y294" s="21" t="str">
-        <x:v>["已确认目标拼多多店铺账号","已准备完成服务市场订购"]</x:v>
+        <x:v>["已确认是淘宝还是天猫店铺","已准备平台主账号完成服务订购与授权"]</x:v>
       </x:c>
       <x:c r="Z294" s="21" t="str">
-        <x:v>["选择拼多多平台","在服务市场选择企业版和一年周期","完成订购付款","返回 ERP 点击去绑定并登录授权","核验绑定成功"]</x:v>
+        <x:v>["选择准确的淘宝或天猫平台类型","按平台流程提交订单并等待审核","审核通过后完成付款和服务确认","返回 ERP 点击去绑定并授权","核验绑定成功"]</x:v>
       </x:c>
       <x:c r="AA294" s="21" t="str">
-        <x:v>["订购版本为企业版且周期为一年","ERP 店铺列表显示正确店铺并绑定成功"]</x:v>
+        <x:v>["列表平台类型与实际店铺一致","店铺状态为绑定成功"]</x:v>
       </x:c>
       <x:c r="AB294" s="21" t="str">
-        <x:v>["平台产品名称和订购页面可能调整，上线操作时仍需按当前后台复核"]</x:v>
+        <x:v>["天猫误选为淘宝且尚无订单数据时，可先解绑，联系售后或销售修改配置后再正确选择重绑；已有订单数据时资料不建议解绑"]</x:v>
       </x:c>
       <x:c r="AC294" s="21" t="str">
-        <x:v>["把订购付款当作绑定完成","另开平台页面导致授权会话中断"]</x:v>
+        <x:v>["用改店铺名称替代平台类型修正","先产生订单数据再处理误选"]</x:v>
       </x:c>
       <x:c r="AD294" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -36541,10 +36543,10 @@
       </x:c>
       <x:c r="AF294" s="21" t="str"/>
       <x:c r="AG294" s="21" t="str">
-        <x:v>店铺管理—拼多多店铺绑定</x:v>
+        <x:v>店铺管理—淘宝天猫绑定与类型误选</x:v>
       </x:c>
       <x:c r="AH294" s="21" t="str">
-        <x:v>拼多多订购付款完成后，返回 ERP 对应平台去绑定并授权。</x:v>
+        <x:v>天猫误选淘宝且无订单数据时，解绑后联系售后或销售改配置，再选择正确平台重绑。</x:v>
       </x:c>
       <x:c r="AI294" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -36588,7 +36590,7 @@
       <x:c r="AV294" s="21" t="str"/>
       <x:c r="AW294" s="21" t="str"/>
       <x:c r="AX294" s="21" t="str">
-        <x:v>按指定服务规格接入拼多多店铺</x:v>
+        <x:v>绑定淘宝天猫并处理无订单的类型误选</x:v>
       </x:c>
       <x:c r="AY294" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -36596,7 +36598,7 @@
     </x:row>
     <x:row r="295" ht="46" customHeight="1">
       <x:c r="A295" s="21" t="str">
-        <x:v>WDT-050-B</x:v>
+        <x:v>WDT-050-A</x:v>
       </x:c>
       <x:c r="B295" s="21" t="str">
         <x:v>旺店通-运营</x:v>
@@ -36635,31 +36637,31 @@
         <x:v>拼多多选择企业版一年后返回 ERP 绑定</x:v>
       </x:c>
       <x:c r="N295" s="21" t="str">
-        <x:v>拼多多授权页面提示完成后，哪组 ERP 列表结果才能证明绑定成功？</x:v>
+        <x:v>拼多多平台服务已完成订购付款，哪一步才能完成 ERP 侧店铺绑定？</x:v>
       </x:c>
       <x:c r="O295" s="21" t="str">
-        <x:v>店铺名和绑定时间正确，但平台类型不是拼多多</x:v>
+        <x:v>返回 ERP 拼多多入口后另开平台首页完成登录</x:v>
       </x:c>
       <x:c r="P295" s="21" t="str">
-        <x:v>平台和店铺名称正确、状态绑定成功，但未显示绑定时间</x:v>
+        <x:v>返回 ERP 拼多多入口只核对服务订单是否付款</x:v>
       </x:c>
       <x:c r="Q295" s="21" t="str">
-        <x:v>平台、店铺和绑定时间正确，但状态仍为授权中</x:v>
+        <x:v>留在平台服务市场等待 ERP 自动同步绑定状态</x:v>
       </x:c>
       <x:c r="R295" s="21" t="str">
-        <x:v>平台和店铺名称正确，显示绑定时间且状态为绑定成功</x:v>
+        <x:v>返回 ERP 拼多多入口点击去绑定并完成登录授权</x:v>
       </x:c>
       <x:c r="S295" s="21" t="str">
         <x:v>D</x:v>
       </x:c>
       <x:c r="T295" s="21" t="str">
-        <x:v>平台和店铺名称正确，显示绑定时间且状态为绑定成功</x:v>
+        <x:v>返回 ERP 拼多多入口点击去绑定并完成登录授权</x:v>
       </x:c>
       <x:c r="U295" s="21" t="str">
-        <x:v>最终应回到 ERP 店铺列表核验平台、店铺名称、绑定时间和绑定成功状态。</x:v>
+        <x:v>平台订购付款不等于 ERP 已绑定；还要回到对应平台入口发起去绑定并完成登录授权。</x:v>
       </x:c>
       <x:c r="V295" s="21" t="str">
-        <x:v>{"A":"对象错误：平台类型必须与拼多多店铺一致。","B":"核验缺项：完整结果还应显示绑定时间。","C":"状态未完成：授权中不能证明已经绑定成功。"}</x:v>
+        <x:v>{"A":"错会话：应在 ERP 发起的授权流程内登录。","B":"动作不完整：核对付款不能建立授权关系。","C":"错顺序：服务市场不会替代 ERP 侧授权。"}</x:v>
       </x:c>
       <x:c r="W295" s="21" t="str">
         <x:v>按资料指定的服务版本和周期完成拼多多店铺订购与授权。</x:v>
@@ -36680,7 +36682,7 @@
         <x:v>["平台产品名称和订购页面可能调整，上线操作时仍需按当前后台复核"]</x:v>
       </x:c>
       <x:c r="AC295" s="21" t="str">
-        <x:v>["只看平台付款状态","ERP 仍显示未绑定就开始抓单"]</x:v>
+        <x:v>["把订购付款当作绑定完成","另开平台页面导致授权会话中断"]</x:v>
       </x:c>
       <x:c r="AD295" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -36693,7 +36695,7 @@
         <x:v>店铺管理—拼多多店铺绑定</x:v>
       </x:c>
       <x:c r="AH295" s="21" t="str">
-        <x:v>拼多多绑定后应在 ERP 列表核验平台、店铺、绑定时间和绑定成功状态。</x:v>
+        <x:v>拼多多订购付款完成后，返回 ERP 对应平台去绑定并授权。</x:v>
       </x:c>
       <x:c r="AI295" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -36745,7 +36747,7 @@
     </x:row>
     <x:row r="296" ht="46" customHeight="1">
       <x:c r="A296" s="21" t="str">
-        <x:v>WDT-051-A</x:v>
+        <x:v>WDT-050-B</x:v>
       </x:c>
       <x:c r="B296" s="21" t="str">
         <x:v>旺店通-运营</x:v>
@@ -36757,7 +36759,7 @@
         <x:v>店铺对接</x:v>
       </x:c>
       <x:c r="E296" s="21" t="str">
-        <x:v>京东</x:v>
+        <x:v>拼多多</x:v>
       </x:c>
       <x:c r="F296" s="21" t="str">
         <x:v>单选题</x:v>
@@ -36766,7 +36768,7 @@
         <x:v>场景</x:v>
       </x:c>
       <x:c r="H296" s="21" t="str">
-        <x:v>中</x:v>
+        <x:v>高</x:v>
       </x:c>
       <x:c r="I296" s="21" t="str">
         <x:v>practice</x:v>
@@ -36775,61 +36777,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K296" s="21" t="str">
-        <x:v>WDT-K051</x:v>
+        <x:v>WDT-K050</x:v>
       </x:c>
       <x:c r="L296" s="21" t="str">
-        <x:v>京东店铺绑定</x:v>
+        <x:v>拼多多店铺绑定</x:v>
       </x:c>
       <x:c r="M296" s="21" t="str">
-        <x:v>京东订购先提交审核，再回 ERP 去绑定</x:v>
+        <x:v>拼多多选择企业版一年后返回 ERP 绑定</x:v>
       </x:c>
       <x:c r="N296" s="21" t="str">
-        <x:v>京东服务订单已提交但仍在审核中，此时运营应如何判断后续动作？</x:v>
+        <x:v>拼多多授权页面提示完成后，哪组 ERP 列表结果才能证明绑定成功？</x:v>
       </x:c>
       <x:c r="O296" s="21" t="str">
-        <x:v>取消当前申请，改用其他平台类型绕过审核流程</x:v>
+        <x:v>店铺名和绑定时间正确，但平台类型不是拼多多</x:v>
       </x:c>
       <x:c r="P296" s="21" t="str">
-        <x:v>等待审核通过，再付款确认并返回 ERP 完成授权绑定</x:v>
+        <x:v>平台和店铺名称正确、状态绑定成功，但未显示绑定时间</x:v>
       </x:c>
       <x:c r="Q296" s="21" t="str">
-        <x:v>先建立同名虚拟店铺，审核通过后覆盖原平台类型</x:v>
+        <x:v>平台、店铺和绑定时间正确，但状态仍为授权中</x:v>
       </x:c>
       <x:c r="R296" s="21" t="str">
-        <x:v>直接回 ERP 去绑定，平台审核会在抓单后自动完成</x:v>
+        <x:v>平台和店铺名称正确，显示绑定时间且状态为绑定成功</x:v>
       </x:c>
       <x:c r="S296" s="21" t="str">
-        <x:v>B</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="T296" s="21" t="str">
-        <x:v>等待审核通过，再付款确认并返回 ERP 完成授权绑定</x:v>
+        <x:v>平台和店铺名称正确，显示绑定时间且状态为绑定成功</x:v>
       </x:c>
       <x:c r="U296" s="21" t="str">
-        <x:v>京东订购包含平台审核，审核通过并完成付款确认后才进入 ERP 授权步骤。</x:v>
+        <x:v>最终应回到 ERP 店铺列表核验平台、店铺名称、绑定时间和绑定成功状态。</x:v>
       </x:c>
       <x:c r="V296" s="21" t="str">
-        <x:v>{"A":"错做法：平台类型必须真实且不能用于绕过审核。","C":"错动作：虚拟店铺不能替代真实服务授权。","D":"错顺序：抓单不能替代平台服务审核。"}</x:v>
+        <x:v>{"A":"对象错误：平台类型必须与拼多多店铺一致。","B":"核验缺项：完整结果还应显示绑定时间。","C":"状态未完成：授权中不能证明已经绑定成功。"}</x:v>
       </x:c>
       <x:c r="W296" s="21" t="str">
-        <x:v>按京东特殊审核链路完成服务订购与 ERP 授权，避免把订购中状态误当作已接入。</x:v>
+        <x:v>按资料指定的服务版本和周期完成拼多多店铺订购与授权。</x:v>
       </x:c>
       <x:c r="X296" s="21" t="str">
-        <x:v>["配置","绑定店铺","绑定新店铺","京东"]</x:v>
+        <x:v>["配置","绑定店铺","绑定新店铺","拼多多"]</x:v>
       </x:c>
       <x:c r="Y296" s="21" t="str">
-        <x:v>["已准备京东店铺可授权账号","已确认平台服务订购信息"]</x:v>
+        <x:v>["已确认目标拼多多店铺账号","已准备完成服务市场订购"]</x:v>
       </x:c>
       <x:c r="Z296" s="21" t="str">
-        <x:v>["选择京东平台进入服务订购","提交订单并等待平台审核","审核通过后完成付款和服务确认","返回 ERP 点击去绑定并授权","核验绑定成功"]</x:v>
+        <x:v>["选择拼多多平台","在服务市场选择企业版和一年周期","完成订购付款","返回 ERP 点击去绑定并登录授权","核验绑定成功"]</x:v>
       </x:c>
       <x:c r="AA296" s="21" t="str">
-        <x:v>["服务订单已通过审核并完成付款确认","ERP 列表中京东店铺状态为绑定成功"]</x:v>
+        <x:v>["订购版本为企业版且周期为一年","ERP 店铺列表显示正确店铺并绑定成功"]</x:v>
       </x:c>
       <x:c r="AB296" s="21" t="str">
-        <x:v>["京东与淘系一样存在提交订单和审核步骤，不能直接跳到付款后假定绑定完成"]</x:v>
+        <x:v>["平台产品名称和订购页面可能调整，上线操作时仍需按当前后台复核"]</x:v>
       </x:c>
       <x:c r="AC296" s="21" t="str">
-        <x:v>["审核中就开始绑定","改平台类型绕过审核"]</x:v>
+        <x:v>["只看平台付款状态","ERP 仍显示未绑定就开始抓单"]</x:v>
       </x:c>
       <x:c r="AD296" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -36839,10 +36841,10 @@
       </x:c>
       <x:c r="AF296" s="21" t="str"/>
       <x:c r="AG296" s="21" t="str">
-        <x:v>店铺管理—京东店铺绑定</x:v>
+        <x:v>店铺管理—拼多多店铺绑定</x:v>
       </x:c>
       <x:c r="AH296" s="21" t="str">
-        <x:v>京东服务订单先审核，通过后付款确认，再回 ERP 绑定。</x:v>
+        <x:v>拼多多绑定后应在 ERP 列表核验平台、店铺、绑定时间和绑定成功状态。</x:v>
       </x:c>
       <x:c r="AI296" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -36886,7 +36888,7 @@
       <x:c r="AV296" s="21" t="str"/>
       <x:c r="AW296" s="21" t="str"/>
       <x:c r="AX296" s="21" t="str">
-        <x:v>完成京东服务审核后再授权绑定</x:v>
+        <x:v>按指定服务规格接入拼多多店铺</x:v>
       </x:c>
       <x:c r="AY296" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -36894,7 +36896,7 @@
     </x:row>
     <x:row r="297" ht="46" customHeight="1">
       <x:c r="A297" s="21" t="str">
-        <x:v>WDT-051-B</x:v>
+        <x:v>WDT-051-A</x:v>
       </x:c>
       <x:c r="B297" s="21" t="str">
         <x:v>旺店通-运营</x:v>
@@ -36912,10 +36914,10 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G297" s="21" t="str">
-        <x:v>基础</x:v>
+        <x:v>场景</x:v>
       </x:c>
       <x:c r="H297" s="21" t="str">
-        <x:v>高</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I297" s="21" t="str">
         <x:v>practice</x:v>
@@ -36933,31 +36935,31 @@
         <x:v>京东订购先提交审核，再回 ERP 去绑定</x:v>
       </x:c>
       <x:c r="N297" s="21" t="str">
-        <x:v>京东服务已审核通过并完成付款确认，哪一步才会完成 ERP 侧授权？</x:v>
+        <x:v>京东服务订单已提交但仍在审核中，此时运营应如何判断后续动作？</x:v>
       </x:c>
       <x:c r="O297" s="21" t="str">
-        <x:v>返回 ERP 京东平台入口，点击去绑定并登录授权</x:v>
+        <x:v>取消当前申请，改用其他平台类型绕过审核流程</x:v>
       </x:c>
       <x:c r="P297" s="21" t="str">
-        <x:v>留在平台服务订单页，等待 ERP 自动完成授权</x:v>
+        <x:v>等待审核通过，再付款确认并返回 ERP 完成授权绑定</x:v>
       </x:c>
       <x:c r="Q297" s="21" t="str">
-        <x:v>返回 ERP 京东平台入口，只刷新店铺列表等待授权</x:v>
+        <x:v>先建立同名虚拟店铺，审核通过后覆盖原平台类型</x:v>
       </x:c>
       <x:c r="R297" s="21" t="str">
-        <x:v>返回 ERP 京东平台入口，另开平台首页完成登录</x:v>
+        <x:v>直接回 ERP 去绑定，平台审核会在抓单后自动完成</x:v>
       </x:c>
       <x:c r="S297" s="21" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="T297" s="21" t="str">
-        <x:v>返回 ERP 京东平台入口，点击去绑定并登录授权</x:v>
+        <x:v>等待审核通过，再付款确认并返回 ERP 完成授权绑定</x:v>
       </x:c>
       <x:c r="U297" s="21" t="str">
-        <x:v>订购和授权是两个阶段；完成服务订单后仍需在 ERP 发起京东授权。</x:v>
+        <x:v>京东订购包含平台审核，审核通过并完成付款确认后才进入 ERP 授权步骤。</x:v>
       </x:c>
       <x:c r="V297" s="21" t="str">
-        <x:v>{"B":"错范围：服务订单完成不等于 ERP 已获得授权。","C":"动作不完整：刷新列表不能替代去绑定和登录。","D":"错会话：应在 ERP 发起的授权流程内完成登录。"}</x:v>
+        <x:v>{"A":"错做法：平台类型必须真实且不能用于绕过审核。","C":"错动作：虚拟店铺不能替代真实服务授权。","D":"错顺序：抓单不能替代平台服务审核。"}</x:v>
       </x:c>
       <x:c r="W297" s="21" t="str">
         <x:v>按京东特殊审核链路完成服务订购与 ERP 授权，避免把订购中状态误当作已接入。</x:v>
@@ -36978,7 +36980,7 @@
         <x:v>["京东与淘系一样存在提交订单和审核步骤，不能直接跳到付款后假定绑定完成"]</x:v>
       </x:c>
       <x:c r="AC297" s="21" t="str">
-        <x:v>["把服务确认当 ERP 授权","用抓单动作试探是否已绑定"]</x:v>
+        <x:v>["审核中就开始绑定","改平台类型绕过审核"]</x:v>
       </x:c>
       <x:c r="AD297" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -36991,7 +36993,7 @@
         <x:v>店铺管理—京东店铺绑定</x:v>
       </x:c>
       <x:c r="AH297" s="21" t="str">
-        <x:v>京东订购完成后返回 ERP，点击去绑定并登录授权。</x:v>
+        <x:v>京东服务订单先审核，通过后付款确认，再回 ERP 绑定。</x:v>
       </x:c>
       <x:c r="AI297" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -37043,7 +37045,7 @@
     </x:row>
     <x:row r="298" ht="46" customHeight="1">
       <x:c r="A298" s="21" t="str">
-        <x:v>WDT-052-A</x:v>
+        <x:v>WDT-051-B</x:v>
       </x:c>
       <x:c r="B298" s="21" t="str">
         <x:v>旺店通-运营</x:v>
@@ -37055,7 +37057,7 @@
         <x:v>店铺对接</x:v>
       </x:c>
       <x:c r="E298" s="21" t="str">
-        <x:v>视频号</x:v>
+        <x:v>京东</x:v>
       </x:c>
       <x:c r="F298" s="21" t="str">
         <x:v>单选题</x:v>
@@ -37073,61 +37075,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K298" s="21" t="str">
-        <x:v>WDT-K052</x:v>
+        <x:v>WDT-K051</x:v>
       </x:c>
       <x:c r="L298" s="21" t="str">
-        <x:v>视频号授权费返款</x:v>
+        <x:v>京东店铺绑定</x:v>
       </x:c>
       <x:c r="M298" s="21" t="str">
-        <x:v>返款申请第 3 步选择视频号专属产品</x:v>
+        <x:v>京东订购先提交审核，再回 ERP 去绑定</x:v>
       </x:c>
       <x:c r="N298" s="21" t="str">
-        <x:v>申请微信视频号店铺授权费返款，在“选择所授权的服务产品”时应选哪一项？</x:v>
+        <x:v>京东服务已审核通过并完成付款确认，哪一步才会完成 ERP 侧授权？</x:v>
       </x:c>
       <x:c r="O298" s="21" t="str">
-        <x:v>旺店通ERP-微信视频号</x:v>
+        <x:v>返回 ERP 京东平台入口，点击去绑定并登录授权</x:v>
       </x:c>
       <x:c r="P298" s="21" t="str">
-        <x:v>沿用上次其他平台返款申请中的产品</x:v>
+        <x:v>留在平台服务订单页，等待 ERP 自动完成授权</x:v>
       </x:c>
       <x:c r="Q298" s="21" t="str">
-        <x:v>旺店通ERP（其他平台通用产品）</x:v>
+        <x:v>返回 ERP 京东平台入口，只刷新店铺列表等待授权</x:v>
       </x:c>
       <x:c r="R298" s="21" t="str">
-        <x:v>旺店通ERP，并在备注补充微信视频号</x:v>
+        <x:v>返回 ERP 京东平台入口，另开平台首页完成登录</x:v>
       </x:c>
       <x:c r="S298" s="21" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="T298" s="21" t="str">
-        <x:v>旺店通ERP-微信视频号</x:v>
+        <x:v>返回 ERP 京东平台入口，点击去绑定并登录授权</x:v>
       </x:c>
       <x:c r="U298" s="21" t="str">
-        <x:v>资料在授权费返款操作指引第 3 步明确区分：微信视频号选择专属产品。</x:v>
+        <x:v>订购和授权是两个阶段；完成服务订单后仍需在 ERP 发起京东授权。</x:v>
       </x:c>
       <x:c r="V298" s="21" t="str">
-        <x:v>{"B":"错对象：不能沿用其他平台申请中的产品字段。","C":"错产品：通用旺店通ERP用于其他平台返款申请。","D":"错字段：备注不能替代视频号专属产品选项。"}</x:v>
+        <x:v>{"B":"错范围：服务订单完成不等于 ERP 已获得授权。","C":"动作不完整：刷新列表不能替代去绑定和登录。","D":"错会话：应在 ERP 发起的授权流程内完成登录。"}</x:v>
       </x:c>
       <x:c r="W298" s="21" t="str">
-        <x:v>在申请授权费返款时选对产品字段，避免视频号申请因产品选错被退回。</x:v>
+        <x:v>按京东特殊审核链路完成服务订购与 ERP 授权，避免把订购中状态误当作已接入。</x:v>
       </x:c>
       <x:c r="X298" s="21" t="str">
-        <x:v>["配置","绑定店铺","申请返款","返款申请","右上角申请"]</x:v>
+        <x:v>["配置","绑定店铺","绑定新店铺","京东"]</x:v>
       </x:c>
       <x:c r="Y298" s="21" t="str">
-        <x:v>["已确认申请对象为微信视频号店铺","正在按授权费返款操作指引提交申请"]</x:v>
+        <x:v>["已准备京东店铺可授权账号","已确认平台服务订购信息"]</x:v>
       </x:c>
       <x:c r="Z298" s="21" t="str">
-        <x:v>["进入授权费返款申请流程","在操作指引第 3 步定位产品字段","视频号选择旺店通ERP-微信视频号","其他平台选择旺店通ERP","提交前再次核对平台与产品对应关系"]</x:v>
+        <x:v>["选择京东平台进入服务订购","提交订单并等待平台审核","审核通过后完成付款和服务确认","返回 ERP 点击去绑定并授权","核验绑定成功"]</x:v>
       </x:c>
       <x:c r="AA298" s="21" t="str">
-        <x:v>["视频号返款申请的产品字段为旺店通ERP-微信视频号","其他平台返款申请的产品字段为旺店通ERP"]</x:v>
+        <x:v>["服务订单已通过审核并完成付款确认","ERP 列表中京东店铺状态为绑定成功"]</x:v>
       </x:c>
       <x:c r="AB298" s="21" t="str">
-        <x:v>["本条规则仅适用于申请授权费返款时的产品字段选择，不代表店铺订购或绑定入口"]</x:v>
+        <x:v>["京东与淘系一样存在提交订单和审核步骤，不能直接跳到付款后假定绑定完成"]</x:v>
       </x:c>
       <x:c r="AC298" s="21" t="str">
-        <x:v>["把通用产品用于视频号返款申请","以备注代替正确产品字段"]</x:v>
+        <x:v>["把服务确认当 ERP 授权","用抓单动作试探是否已绑定"]</x:v>
       </x:c>
       <x:c r="AD298" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -37137,10 +37139,10 @@
       </x:c>
       <x:c r="AF298" s="21" t="str"/>
       <x:c r="AG298" s="21" t="str">
-        <x:v>店铺管理—申请授权费返款操作指引步骤 3</x:v>
+        <x:v>店铺管理—京东店铺绑定</x:v>
       </x:c>
       <x:c r="AH298" s="21" t="str">
-        <x:v>申请授权费返款步骤 3：微信视频号选择旺店通ERP-微信视频号。</x:v>
+        <x:v>京东订购完成后返回 ERP，点击去绑定并登录授权。</x:v>
       </x:c>
       <x:c r="AI298" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -37184,7 +37186,7 @@
       <x:c r="AV298" s="21" t="str"/>
       <x:c r="AW298" s="21" t="str"/>
       <x:c r="AX298" s="21" t="str">
-        <x:v>申请店铺授权费返款时选择正确服务产品</x:v>
+        <x:v>完成京东服务审核后再授权绑定</x:v>
       </x:c>
       <x:c r="AY298" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -37192,7 +37194,7 @@
     </x:row>
     <x:row r="299" ht="46" customHeight="1">
       <x:c r="A299" s="21" t="str">
-        <x:v>WDT-052-B</x:v>
+        <x:v>WDT-052-A</x:v>
       </x:c>
       <x:c r="B299" s="21" t="str">
         <x:v>旺店通-运营</x:v>
@@ -37210,7 +37212,7 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G299" s="21" t="str">
-        <x:v>进阶</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="H299" s="21" t="str">
         <x:v>高</x:v>
@@ -37231,31 +37233,31 @@
         <x:v>返款申请第 3 步选择视频号专属产品</x:v>
       </x:c>
       <x:c r="N299" s="21" t="str">
-        <x:v>提交不同平台的店铺授权费返款申请时，服务产品选择规则是什么？</x:v>
+        <x:v>申请微信视频号店铺授权费返款，在“选择所授权的服务产品”时应选哪一项？</x:v>
       </x:c>
       <x:c r="O299" s="21" t="str">
-        <x:v>视频号先选旺店通ERP，其他平台审核后再改成视频号专属产品</x:v>
+        <x:v>旺店通ERP-微信视频号</x:v>
       </x:c>
       <x:c r="P299" s="21" t="str">
-        <x:v>所有平台统一选旺店通ERP，视频号在备注补充专属产品名</x:v>
+        <x:v>沿用上次其他平台返款申请中的产品</x:v>
       </x:c>
       <x:c r="Q299" s="21" t="str">
-        <x:v>只有视频号选旺店通ERP-微信视频号，其他平台选旺店通ERP</x:v>
+        <x:v>旺店通ERP（其他平台通用产品）</x:v>
       </x:c>
       <x:c r="R299" s="21" t="str">
-        <x:v>视频号与淘系都选旺店通ERP-微信视频号，其他平台选旺店通ERP</x:v>
+        <x:v>旺店通ERP，并在备注补充微信视频号</x:v>
       </x:c>
       <x:c r="S299" s="21" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="T299" s="21" t="str">
-        <x:v>只有视频号选旺店通ERP-微信视频号，其他平台选旺店通ERP</x:v>
+        <x:v>旺店通ERP-微信视频号</x:v>
       </x:c>
       <x:c r="U299" s="21" t="str">
-        <x:v>这是授权费返款申请第 3 步的产品选择边界，不能扩展成订购或绑定规则。</x:v>
+        <x:v>资料在授权费返款操作指引第 3 步明确区分：微信视频号选择专属产品。</x:v>
       </x:c>
       <x:c r="V299" s="21" t="str">
-        <x:v>{"A":"错顺序与范围：不应先提交错误产品，也不能让其他平台改选视频号专属产品。","B":"错字段：视频号必须选择专属产品，不能只写备注。","D":"错范围：淘系不应选择视频号专属产品。"}</x:v>
+        <x:v>{"B":"错对象：不能沿用其他平台申请中的产品字段。","C":"错产品：通用旺店通ERP用于其他平台返款申请。","D":"错字段：备注不能替代视频号专属产品选项。"}</x:v>
       </x:c>
       <x:c r="W299" s="21" t="str">
         <x:v>在申请授权费返款时选对产品字段，避免视频号申请因产品选错被退回。</x:v>
@@ -37276,7 +37278,7 @@
         <x:v>["本条规则仅适用于申请授权费返款时的产品字段选择，不代表店铺订购或绑定入口"]</x:v>
       </x:c>
       <x:c r="AC299" s="21" t="str">
-        <x:v>["用备注代替专属产品字段","把视频号专属产品扩展到淘系"]</x:v>
+        <x:v>["把通用产品用于视频号返款申请","以备注代替正确产品字段"]</x:v>
       </x:c>
       <x:c r="AD299" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -37289,7 +37291,7 @@
         <x:v>店铺管理—申请授权费返款操作指引步骤 3</x:v>
       </x:c>
       <x:c r="AH299" s="21" t="str">
-        <x:v>申请授权费返款时，视频号选旺店通ERP-微信视频号，其他平台选旺店通ERP。</x:v>
+        <x:v>申请授权费返款步骤 3：微信视频号选择旺店通ERP-微信视频号。</x:v>
       </x:c>
       <x:c r="AI299" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -37341,7 +37343,7 @@
     </x:row>
     <x:row r="300" ht="46" customHeight="1">
       <x:c r="A300" s="21" t="str">
-        <x:v>WDT-053-A</x:v>
+        <x:v>WDT-052-B</x:v>
       </x:c>
       <x:c r="B300" s="21" t="str">
         <x:v>旺店通-运营</x:v>
@@ -37353,13 +37355,13 @@
         <x:v>店铺对接</x:v>
       </x:c>
       <x:c r="E300" s="21" t="str">
-        <x:v>抖音电商</x:v>
+        <x:v>视频号</x:v>
       </x:c>
       <x:c r="F300" s="21" t="str">
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G300" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>进阶</x:v>
       </x:c>
       <x:c r="H300" s="21" t="str">
         <x:v>高</x:v>
@@ -37371,61 +37373,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K300" s="21" t="str">
-        <x:v>WDT-K053</x:v>
+        <x:v>WDT-K052</x:v>
       </x:c>
       <x:c r="L300" s="21" t="str">
-        <x:v>抖音店铺绑定</x:v>
+        <x:v>视频号授权费返款</x:v>
       </x:c>
       <x:c r="M300" s="21" t="str">
-        <x:v>抖音选择企业版一年后返回 ERP 授权</x:v>
+        <x:v>返款申请第 3 步选择视频号专属产品</x:v>
       </x:c>
       <x:c r="N300" s="21" t="str">
-        <x:v>抖音平台服务完成订购付款后，正确的后续步骤是什么？</x:v>
+        <x:v>提交不同平台的店铺授权费返款申请时，服务产品选择规则是什么？</x:v>
       </x:c>
       <x:c r="O300" s="21" t="str">
-        <x:v>返回 ERP 抖音入口点击去绑定，完成登录授权并核验</x:v>
+        <x:v>视频号先选旺店通ERP，其他平台审核后再改成视频号专属产品</x:v>
       </x:c>
       <x:c r="P300" s="21" t="str">
-        <x:v>返回 ERP 选择视频号入口，用同一账号完成平台授权</x:v>
+        <x:v>所有平台统一选旺店通ERP，视频号在备注补充专属产品名</x:v>
       </x:c>
       <x:c r="Q300" s="21" t="str">
-        <x:v>留在服务市场等待绑定成功，再返回 ERP 抓单</x:v>
+        <x:v>只有视频号选旺店通ERP-微信视频号，其他平台选旺店通ERP</x:v>
       </x:c>
       <x:c r="R300" s="21" t="str">
-        <x:v>返回 ERP 抖音入口只刷新列表，不再发起平台授权</x:v>
+        <x:v>视频号与淘系都选旺店通ERP-微信视频号，其他平台选旺店通ERP</x:v>
       </x:c>
       <x:c r="S300" s="21" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="T300" s="21" t="str">
-        <x:v>返回 ERP 抖音入口点击去绑定，完成登录授权并核验</x:v>
+        <x:v>只有视频号选旺店通ERP-微信视频号，其他平台选旺店通ERP</x:v>
       </x:c>
       <x:c r="U300" s="21" t="str">
-        <x:v>订购付款后必须回到 ERP 对应平台入口完成去绑定和平台登录授权，最后核验列表状态。</x:v>
+        <x:v>这是授权费返款申请第 3 步的产品选择边界，不能扩展成订购或绑定规则。</x:v>
       </x:c>
       <x:c r="V300" s="21" t="str">
-        <x:v>{"B":"错平台：抖音店铺必须从抖音入口授权。","C":"错顺序：服务市场付款不会自动完成 ERP 授权。","D":"动作不完整：刷新列表不能替代去绑定。"}</x:v>
+        <x:v>{"A":"错顺序与范围：不应先提交错误产品，也不能让其他平台改选视频号专属产品。","B":"错字段：视频号必须选择专属产品，不能只写备注。","D":"错范围：淘系不应选择视频号专属产品。"}</x:v>
       </x:c>
       <x:c r="W300" s="21" t="str">
-        <x:v>按资料指定的服务版本与周期完成抖音店铺订购和授权。</x:v>
+        <x:v>在申请授权费返款时选对产品字段，避免视频号申请因产品选错被退回。</x:v>
       </x:c>
       <x:c r="X300" s="21" t="str">
-        <x:v>["配置","绑定店铺","绑定新店铺","抖音"]</x:v>
+        <x:v>["配置","绑定店铺","申请返款","返款申请","右上角申请"]</x:v>
       </x:c>
       <x:c r="Y300" s="21" t="str">
-        <x:v>["已确认目标抖店账号","已准备完成服务市场订购"]</x:v>
+        <x:v>["已确认申请对象为微信视频号店铺","正在按授权费返款操作指引提交申请"]</x:v>
       </x:c>
       <x:c r="Z300" s="21" t="str">
-        <x:v>["选择抖音平台","在服务市场选择企业版和一年周期","完成订购付款","返回 ERP 点击去绑定并登录授权","核验绑定成功"]</x:v>
+        <x:v>["进入授权费返款申请流程","在操作指引第 3 步定位产品字段","视频号选择旺店通ERP-微信视频号","其他平台选择旺店通ERP","提交前再次核对平台与产品对应关系"]</x:v>
       </x:c>
       <x:c r="AA300" s="21" t="str">
-        <x:v>["订购版本为企业版且周期为一年","店铺列表显示抖音店铺并绑定成功"]</x:v>
+        <x:v>["视频号返款申请的产品字段为旺店通ERP-微信视频号","其他平台返款申请的产品字段为旺店通ERP"]</x:v>
       </x:c>
       <x:c r="AB300" s="21" t="str">
-        <x:v>["平台产品名称和订购页面可能调整，上线操作时仍需按当前后台复核"]</x:v>
+        <x:v>["本条规则仅适用于申请授权费返款时的产品字段选择，不代表店铺订购或绑定入口"]</x:v>
       </x:c>
       <x:c r="AC300" s="21" t="str">
-        <x:v>["把订购付款当作绑定完成","进入错误平台授权入口"]</x:v>
+        <x:v>["用备注代替专属产品字段","把视频号专属产品扩展到淘系"]</x:v>
       </x:c>
       <x:c r="AD300" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -37435,10 +37437,10 @@
       </x:c>
       <x:c r="AF300" s="21" t="str"/>
       <x:c r="AG300" s="21" t="str">
-        <x:v>店铺管理—抖音店铺绑定</x:v>
+        <x:v>店铺管理—申请授权费返款操作指引步骤 3</x:v>
       </x:c>
       <x:c r="AH300" s="21" t="str">
-        <x:v>抖音订购付款后返回 ERP 去绑定，登录授权并核验。</x:v>
+        <x:v>申请授权费返款时，视频号选旺店通ERP-微信视频号，其他平台选旺店通ERP。</x:v>
       </x:c>
       <x:c r="AI300" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -37482,7 +37484,7 @@
       <x:c r="AV300" s="21" t="str"/>
       <x:c r="AW300" s="21" t="str"/>
       <x:c r="AX300" s="21" t="str">
-        <x:v>按指定服务规格接入抖音店铺</x:v>
+        <x:v>申请店铺授权费返款时选择正确服务产品</x:v>
       </x:c>
       <x:c r="AY300" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -37490,7 +37492,7 @@
     </x:row>
     <x:row r="301" ht="46" customHeight="1">
       <x:c r="A301" s="21" t="str">
-        <x:v>WDT-053-B</x:v>
+        <x:v>WDT-053-A</x:v>
       </x:c>
       <x:c r="B301" s="21" t="str">
         <x:v>旺店通-运营</x:v>
@@ -37529,31 +37531,31 @@
         <x:v>抖音选择企业版一年后返回 ERP 授权</x:v>
       </x:c>
       <x:c r="N301" s="21" t="str">
-        <x:v>抖音授权操作结束后，哪组信息是 ERP 侧绑定成功的完整核验依据？</x:v>
+        <x:v>抖音平台服务完成订购付款后，正确的后续步骤是什么？</x:v>
       </x:c>
       <x:c r="O301" s="21" t="str">
-        <x:v>平台和店铺名称正确，并显示绑定时间与绑定成功</x:v>
+        <x:v>返回 ERP 抖音入口点击去绑定，完成登录授权并核验</x:v>
       </x:c>
       <x:c r="P301" s="21" t="str">
-        <x:v>平台、店铺和绑定时间正确，但状态仍为授权中</x:v>
+        <x:v>返回 ERP 选择视频号入口，用同一账号完成平台授权</x:v>
       </x:c>
       <x:c r="Q301" s="21" t="str">
-        <x:v>店铺名和绑定时间正确，但平台类型显示视频号</x:v>
+        <x:v>留在服务市场等待绑定成功，再返回 ERP 抓单</x:v>
       </x:c>
       <x:c r="R301" s="21" t="str">
-        <x:v>平台和店铺名称正确、状态绑定成功，但未显示绑定时间</x:v>
+        <x:v>返回 ERP 抖音入口只刷新列表，不再发起平台授权</x:v>
       </x:c>
       <x:c r="S301" s="21" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="T301" s="21" t="str">
-        <x:v>平台和店铺名称正确，并显示绑定时间与绑定成功</x:v>
+        <x:v>返回 ERP 抖音入口点击去绑定，完成登录授权并核验</x:v>
       </x:c>
       <x:c r="U301" s="21" t="str">
-        <x:v>授权结束后要回到 ERP 店铺列表，以平台、店铺名称、绑定时间和绑定成功状态共同核验。</x:v>
+        <x:v>订购付款后必须回到 ERP 对应平台入口完成去绑定和平台登录授权，最后核验列表状态。</x:v>
       </x:c>
       <x:c r="V301" s="21" t="str">
-        <x:v>{"B":"状态未完成：授权中不能证明已经绑定成功。","C":"对象错误：ERP 平台类型必须为抖音。","D":"核验缺项：完整结果还应显示绑定时间。"}</x:v>
+        <x:v>{"B":"错平台：抖音店铺必须从抖音入口授权。","C":"错顺序：服务市场付款不会自动完成 ERP 授权。","D":"动作不完整：刷新列表不能替代去绑定。"}</x:v>
       </x:c>
       <x:c r="W301" s="21" t="str">
         <x:v>按资料指定的服务版本与周期完成抖音店铺订购和授权。</x:v>
@@ -37574,7 +37576,7 @@
         <x:v>["平台产品名称和订购页面可能调整，上线操作时仍需按当前后台复核"]</x:v>
       </x:c>
       <x:c r="AC301" s="21" t="str">
-        <x:v>["只看平台登录成功","只看服务付款不查 ERP 状态"]</x:v>
+        <x:v>["把订购付款当作绑定完成","进入错误平台授权入口"]</x:v>
       </x:c>
       <x:c r="AD301" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -37587,7 +37589,7 @@
         <x:v>店铺管理—抖音店铺绑定</x:v>
       </x:c>
       <x:c r="AH301" s="21" t="str">
-        <x:v>抖音绑定后核验平台、店铺名称、绑定时间和绑定成功状态。</x:v>
+        <x:v>抖音订购付款后返回 ERP 去绑定，登录授权并核验。</x:v>
       </x:c>
       <x:c r="AI301" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -37639,7 +37641,7 @@
     </x:row>
     <x:row r="302" ht="46" customHeight="1">
       <x:c r="A302" s="21" t="str">
-        <x:v>WDT-054-A</x:v>
+        <x:v>WDT-053-B</x:v>
       </x:c>
       <x:c r="B302" s="21" t="str">
         <x:v>旺店通-运营</x:v>
@@ -37651,7 +37653,7 @@
         <x:v>店铺对接</x:v>
       </x:c>
       <x:c r="E302" s="21" t="str">
-        <x:v>唯品会</x:v>
+        <x:v>抖音电商</x:v>
       </x:c>
       <x:c r="F302" s="21" t="str">
         <x:v>单选题</x:v>
@@ -37669,74 +37671,74 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K302" s="21" t="str">
-        <x:v>WDT-K054</x:v>
+        <x:v>WDT-K053</x:v>
       </x:c>
       <x:c r="L302" s="21" t="str">
-        <x:v>唯品会 MP、JITX 与 JIT</x:v>
+        <x:v>抖音店铺绑定</x:v>
       </x:c>
       <x:c r="M302" s="21" t="str">
-        <x:v>先分清谁发货、货到哪里</x:v>
+        <x:v>抖音选择企业版一年后返回 ERP 授权</x:v>
       </x:c>
       <x:c r="N302" s="21" t="str">
-        <x:v>商品属于唯品会自营，但由供应商直接发给消费者、不进入唯品会仓库，应选择哪种业务？</x:v>
+        <x:v>抖音授权操作结束后，哪组信息是 ERP 侧绑定成功的完整核验依据？</x:v>
       </x:c>
       <x:c r="O302" s="21" t="str">
-        <x:v>MP 业务</x:v>
+        <x:v>平台和店铺名称正确，并显示绑定时间与绑定成功</x:v>
       </x:c>
       <x:c r="P302" s="21" t="str">
-        <x:v>JIT 业务</x:v>
+        <x:v>平台、店铺和绑定时间正确，但状态仍为授权中</x:v>
       </x:c>
       <x:c r="Q302" s="21" t="str">
-        <x:v>普通采购业务</x:v>
+        <x:v>店铺名和绑定时间正确，但平台类型显示视频号</x:v>
       </x:c>
       <x:c r="R302" s="21" t="str">
-        <x:v>JITX 业务</x:v>
+        <x:v>平台和店铺名称正确、状态绑定成功，但未显示绑定时间</x:v>
       </x:c>
       <x:c r="S302" s="21" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="T302" s="21" t="str">
-        <x:v>JITX 业务</x:v>
+        <x:v>平台和店铺名称正确，并显示绑定时间与绑定成功</x:v>
       </x:c>
       <x:c r="U302" s="21" t="str">
-        <x:v>JITX 的核心特征是唯品会自营、供应商直发消费者，不进入唯品会仓库。</x:v>
+        <x:v>授权结束后要回到 ERP 店铺列表，以平台、店铺名称、绑定时间和绑定成功状态共同核验。</x:v>
       </x:c>
       <x:c r="V302" s="21" t="str">
-        <x:v>{"A":"错模式：MP 是商家自营发消费者。","B":"错目的地：JIT 货品需要进入唯品会仓库。","C":"错业务：普通采购不是本题唯品会履约模式。"}</x:v>
+        <x:v>{"B":"状态未完成：授权中不能证明已经绑定成功。","C":"对象错误：ERP 平台类型必须为抖音。","D":"核验缺项：完整结果还应显示绑定时间。"}</x:v>
       </x:c>
       <x:c r="W302" s="21" t="str">
-        <x:v>根据实际履约路径选择并授权正确的唯品会业务，避免订单进入错误履约链路。</x:v>
+        <x:v>按资料指定的服务版本与周期完成抖音店铺订购和授权。</x:v>
       </x:c>
       <x:c r="X302" s="21" t="str">
-        <x:v>["配置","绑定店铺","唯品会","业务授权"]</x:v>
+        <x:v>["配置","绑定店铺","绑定新店铺","抖音"]</x:v>
       </x:c>
       <x:c r="Y302" s="21" t="str">
-        <x:v>["已确认合同对应的唯品会业务模式","已确认商品由谁发货以及是否进入唯品会仓库"]</x:v>
+        <x:v>["已确认目标抖店账号","已准备完成服务市场订购"]</x:v>
       </x:c>
       <x:c r="Z302" s="21" t="str">
-        <x:v>["商家自营直发消费者时选择 MP","唯品会自营且供应商直发消费者时选择 JITX","商品先进入唯品会仓库时选择 JIT","按实际模式完成对应业务授权"]</x:v>
+        <x:v>["选择抖音平台","在服务市场选择企业版和一年周期","完成订购付款","返回 ERP 点击去绑定并登录授权","核验绑定成功"]</x:v>
       </x:c>
       <x:c r="AA302" s="21" t="str">
-        <x:v>["业务类型与实际发货主体和目的地一致","系统已授权对应的唯品会业务"]</x:v>
+        <x:v>["订购版本为企业版且周期为一年","店铺列表显示抖音店铺并绑定成功"]</x:v>
       </x:c>
       <x:c r="AB302" s="21" t="str">
-        <x:v>["MP、JITX 和 JIT 的履约责任不同，不能只按店铺名称选择"]</x:v>
+        <x:v>["平台产品名称和订购页面可能调整，上线操作时仍需按当前后台复核"]</x:v>
       </x:c>
       <x:c r="AC302" s="21" t="str">
-        <x:v>["看到唯品会自营就选 JIT","忽略是否进入唯品会仓库"]</x:v>
+        <x:v>["只看平台登录成功","只看服务付款不查 ERP 状态"]</x:v>
       </x:c>
       <x:c r="AD302" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
       </x:c>
       <x:c r="AE302" s="21" t="str">
-        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/sv0h8l9k3tqz0nbh</x:v>
+        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/opgdsg</x:v>
       </x:c>
       <x:c r="AF302" s="21" t="str"/>
       <x:c r="AG302" s="21" t="str">
-        <x:v>唯品会—MP、JITX、JIT 业务模式</x:v>
+        <x:v>店铺管理—抖音店铺绑定</x:v>
       </x:c>
       <x:c r="AH302" s="21" t="str">
-        <x:v>JITX 为唯品会自营，供应商直发消费者。</x:v>
+        <x:v>抖音绑定后核验平台、店铺名称、绑定时间和绑定成功状态。</x:v>
       </x:c>
       <x:c r="AI302" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -37780,7 +37782,7 @@
       <x:c r="AV302" s="21" t="str"/>
       <x:c r="AW302" s="21" t="str"/>
       <x:c r="AX302" s="21" t="str">
-        <x:v>按履约模式选择唯品会业务类型</x:v>
+        <x:v>按指定服务规格接入抖音店铺</x:v>
       </x:c>
       <x:c r="AY302" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -37788,7 +37790,7 @@
     </x:row>
     <x:row r="303" ht="46" customHeight="1">
       <x:c r="A303" s="21" t="str">
-        <x:v>WDT-054-B</x:v>
+        <x:v>WDT-054-A</x:v>
       </x:c>
       <x:c r="B303" s="21" t="str">
         <x:v>旺店通-运营</x:v>
@@ -37806,7 +37808,7 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G303" s="21" t="str">
-        <x:v>基础</x:v>
+        <x:v>场景</x:v>
       </x:c>
       <x:c r="H303" s="21" t="str">
         <x:v>高</x:v>
@@ -37827,31 +37829,31 @@
         <x:v>先分清谁发货、货到哪里</x:v>
       </x:c>
       <x:c r="N303" s="21" t="str">
-        <x:v>某批商品需要先送入唯品会仓库，再由唯品会完成后续履约，应选择哪种业务？</x:v>
+        <x:v>商品属于唯品会自营，但由供应商直接发给消费者、不进入唯品会仓库，应选择哪种业务？</x:v>
       </x:c>
       <x:c r="O303" s="21" t="str">
+        <x:v>MP 业务</x:v>
+      </x:c>
+      <x:c r="P303" s="21" t="str">
         <x:v>JIT 业务</x:v>
       </x:c>
-      <x:c r="P303" s="21" t="str">
-        <x:v>MP 业务</x:v>
-      </x:c>
       <x:c r="Q303" s="21" t="str">
+        <x:v>普通采购业务</x:v>
+      </x:c>
+      <x:c r="R303" s="21" t="str">
         <x:v>JITX 业务</x:v>
       </x:c>
-      <x:c r="R303" s="21" t="str">
-        <x:v>商家直发业务</x:v>
-      </x:c>
       <x:c r="S303" s="21" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="T303" s="21" t="str">
-        <x:v>JIT 业务</x:v>
+        <x:v>JITX 业务</x:v>
       </x:c>
       <x:c r="U303" s="21" t="str">
-        <x:v>JIT 的识别点是货品先进入唯品会仓库。</x:v>
+        <x:v>JITX 的核心特征是唯品会自营、供应商直发消费者，不进入唯品会仓库。</x:v>
       </x:c>
       <x:c r="V303" s="21" t="str">
-        <x:v>{"B":"错履约方：MP 是商家自营直发消费者。","C":"错目的地：JITX 是供应商直发消费者。","D":"错范围：商家直发不是该进仓场景。"}</x:v>
+        <x:v>{"A":"错模式：MP 是商家自营发消费者。","B":"错目的地：JIT 货品需要进入唯品会仓库。","C":"错业务：普通采购不是本题唯品会履约模式。"}</x:v>
       </x:c>
       <x:c r="W303" s="21" t="str">
         <x:v>根据实际履约路径选择并授权正确的唯品会业务，避免订单进入错误履约链路。</x:v>
@@ -37872,7 +37874,7 @@
         <x:v>["MP、JITX 和 JIT 的履约责任不同，不能只按店铺名称选择"]</x:v>
       </x:c>
       <x:c r="AC303" s="21" t="str">
-        <x:v>["把进唯品会仓误选为 JITX","只按自营二字判断模式"]</x:v>
+        <x:v>["看到唯品会自营就选 JIT","忽略是否进入唯品会仓库"]</x:v>
       </x:c>
       <x:c r="AD303" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -37885,7 +37887,7 @@
         <x:v>唯品会—MP、JITX、JIT 业务模式</x:v>
       </x:c>
       <x:c r="AH303" s="21" t="str">
-        <x:v>JIT 业务的货品需送入唯品会仓库。</x:v>
+        <x:v>JITX 为唯品会自营，供应商直发消费者。</x:v>
       </x:c>
       <x:c r="AI303" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -37937,7 +37939,7 @@
     </x:row>
     <x:row r="304" ht="46" customHeight="1">
       <x:c r="A304" s="21" t="str">
-        <x:v>WDT-055-A</x:v>
+        <x:v>WDT-054-B</x:v>
       </x:c>
       <x:c r="B304" s="21" t="str">
         <x:v>旺店通-运营</x:v>
@@ -37955,73 +37957,73 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G304" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="H304" s="21" t="str">
         <x:v>高</x:v>
       </x:c>
       <x:c r="I304" s="21" t="str">
-        <x:v>redline</x:v>
+        <x:v>practice</x:v>
       </x:c>
       <x:c r="J304" s="22" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K304" s="21" t="str">
-        <x:v>WDT-K055</x:v>
+        <x:v>WDT-K054</x:v>
       </x:c>
       <x:c r="L304" s="21" t="str">
-        <x:v>唯品会抓单前配置</x:v>
+        <x:v>唯品会 MP、JITX 与 JIT</x:v>
       </x:c>
       <x:c r="M304" s="21" t="str">
-        <x:v>先限定常态，再映射平台仓</x:v>
+        <x:v>先分清谁发货、货到哪里</x:v>
       </x:c>
       <x:c r="N304" s="21" t="str">
-        <x:v>同一唯品会店铺有多个平台商家仓，准备开始抓单前必须先完成什么？</x:v>
+        <x:v>某批商品需要先送入唯品会仓库，再由唯品会完成后续履约，应选择哪种业务？</x:v>
       </x:c>
       <x:c r="O304" s="21" t="str">
-        <x:v>先抓单到默认仓，再按发货结果补做仓库调整</x:v>
+        <x:v>JIT 业务</x:v>
       </x:c>
       <x:c r="P304" s="21" t="str">
-        <x:v>把所有平台仓改成同一个平台仓编码再抓单</x:v>
+        <x:v>MP 业务</x:v>
       </x:c>
       <x:c r="Q304" s="21" t="str">
-        <x:v>把平台商家仓逐一映射到对应的系统仓库</x:v>
+        <x:v>JITX 业务</x:v>
       </x:c>
       <x:c r="R304" s="21" t="str">
-        <x:v>关闭所有仓库权限，只保留店铺权限后再抓单</x:v>
+        <x:v>商家直发业务</x:v>
       </x:c>
       <x:c r="S304" s="21" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="T304" s="21" t="str">
-        <x:v>把平台商家仓逐一映射到对应的系统仓库</x:v>
+        <x:v>JIT 业务</x:v>
       </x:c>
       <x:c r="U304" s="21" t="str">
-        <x:v>多平台商家仓场景必须先做仓库映射，系统才能据此进行订单选仓和库存同步。</x:v>
+        <x:v>JIT 的识别点是货品先进入唯品会仓库。</x:v>
       </x:c>
       <x:c r="V304" s="21" t="str">
-        <x:v>{"A":"错顺序：先抓单可能导致订单落错仓。","B":"错处理：会丢失真实仓库对应关系。","D":"错设置：权限不能替代平台仓到系统仓映射。"}</x:v>
+        <x:v>{"B":"错履约方：MP 是商家自营直发消费者。","C":"错目的地：JITX 是供应商直发消费者。","D":"错范围：商家直发不是该进仓场景。"}</x:v>
       </x:c>
       <x:c r="W304" s="21" t="str">
-        <x:v>让系统只下载责任范围内的唯品会业务，并把多仓订单准确分配到系统仓。</x:v>
+        <x:v>根据实际履约路径选择并授权正确的唯品会业务，避免订单进入错误履约链路。</x:v>
       </x:c>
       <x:c r="X304" s="21" t="str">
-        <x:v>["配置","绑定店铺","唯品会店铺","编辑"]</x:v>
+        <x:v>["配置","绑定店铺","唯品会","业务授权"]</x:v>
       </x:c>
       <x:c r="Y304" s="21" t="str">
-        <x:v>["已完成对应唯品会业务授权","多品牌或多团队时已明确各自负责的常态","存在多个平台商家仓时已取得仓库对应关系"]</x:v>
+        <x:v>["已确认合同对应的唯品会业务模式","已确认商品由谁发货以及是否进入唯品会仓库"]</x:v>
       </x:c>
       <x:c r="Z304" s="21" t="str">
-        <x:v>["编辑店铺并选择本系统负责的正常常态","若本系统负责全部常态则按资料保持不维护","存在多个平台商家仓时建立平台仓到系统仓映射","再开启抓单并核验订单仓库"]</x:v>
+        <x:v>["商家自营直发消费者时选择 MP","唯品会自营且供应商直发消费者时选择 JITX","商品先进入唯品会仓库时选择 JIT","按实际模式完成对应业务授权"]</x:v>
       </x:c>
       <x:c r="AA304" s="21" t="str">
-        <x:v>["系统只下载应负责常态的订单和商品","多仓订单落到正确系统仓库"]</x:v>
+        <x:v>["业务类型与实际发货主体和目的地一致","系统已授权对应的唯品会业务"]</x:v>
       </x:c>
       <x:c r="AB304" s="21" t="str">
-        <x:v>["未维护任何常态时默认处理全部正常常态","无法获取常态时需联系唯品会平台","报错平台商品无有效的常态编码时需手工下载商品更新"]</x:v>
+        <x:v>["MP、JITX 和 JIT 的履约责任不同，不能只按店铺名称选择"]</x:v>
       </x:c>
       <x:c r="AC304" s="21" t="str">
-        <x:v>["先抓单后补映射","把多个真实仓强行并成一个编码"]</x:v>
+        <x:v>["把进唯品会仓误选为 JITX","只按自营二字判断模式"]</x:v>
       </x:c>
       <x:c r="AD304" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -38031,10 +38033,10 @@
       </x:c>
       <x:c r="AF304" s="21" t="str"/>
       <x:c r="AG304" s="21" t="str">
-        <x:v>唯品会—常态维护与平台仓映射</x:v>
+        <x:v>唯品会—MP、JITX、JIT 业务模式</x:v>
       </x:c>
       <x:c r="AH304" s="21" t="str">
-        <x:v>多平台商家仓在抓单前需映射到系统仓库。</x:v>
+        <x:v>JIT 业务的货品需送入唯品会仓库。</x:v>
       </x:c>
       <x:c r="AI304" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -38078,7 +38080,7 @@
       <x:c r="AV304" s="21" t="str"/>
       <x:c r="AW304" s="21" t="str"/>
       <x:c r="AX304" s="21" t="str">
-        <x:v>配置唯品会常态与平台仓映射</x:v>
+        <x:v>按履约模式选择唯品会业务类型</x:v>
       </x:c>
       <x:c r="AY304" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -38086,7 +38088,7 @@
     </x:row>
     <x:row r="305" ht="46" customHeight="1">
       <x:c r="A305" s="21" t="str">
-        <x:v>WDT-055-B</x:v>
+        <x:v>WDT-055-A</x:v>
       </x:c>
       <x:c r="B305" s="21" t="str">
         <x:v>旺店通-运营</x:v>
@@ -38104,16 +38106,16 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G305" s="21" t="str">
-        <x:v>进阶</x:v>
+        <x:v>场景</x:v>
       </x:c>
       <x:c r="H305" s="21" t="str">
-        <x:v>中</x:v>
+        <x:v>高</x:v>
       </x:c>
       <x:c r="I305" s="21" t="str">
-        <x:v>practice</x:v>
+        <x:v>redline</x:v>
       </x:c>
       <x:c r="J305" s="22" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K305" s="21" t="str">
         <x:v>WDT-K055</x:v>
@@ -38125,31 +38127,31 @@
         <x:v>先限定常态，再映射平台仓</x:v>
       </x:c>
       <x:c r="N305" s="21" t="str">
-        <x:v>唯品会店铺没有维护任何正常常态时，资料说明系统默认怎样处理？</x:v>
+        <x:v>同一唯品会店铺有多个平台商家仓，准备开始抓单前必须先完成什么？</x:v>
       </x:c>
       <x:c r="O305" s="21" t="str">
-        <x:v>默认不下载任何常态的订单和商品</x:v>
+        <x:v>先抓单到默认仓，再按发货结果补做仓库调整</x:v>
       </x:c>
       <x:c r="P305" s="21" t="str">
-        <x:v>默认随机选择一个正常常态下载订单商品</x:v>
+        <x:v>把所有平台仓改成同一个平台仓编码再抓单</x:v>
       </x:c>
       <x:c r="Q305" s="21" t="str">
-        <x:v>默认只下载最近新增常态的订单和商品</x:v>
+        <x:v>把平台商家仓逐一映射到对应的系统仓库</x:v>
       </x:c>
       <x:c r="R305" s="21" t="str">
-        <x:v>默认处理全部正常常态的订单和商品</x:v>
+        <x:v>关闭所有仓库权限，只保留店铺权限后再抓单</x:v>
       </x:c>
       <x:c r="S305" s="21" t="str">
-        <x:v>D</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="T305" s="21" t="str">
-        <x:v>默认处理全部正常常态的订单和商品</x:v>
+        <x:v>把平台商家仓逐一映射到对应的系统仓库</x:v>
       </x:c>
       <x:c r="U305" s="21" t="str">
-        <x:v>未维护常态并不代表不处理；资料明确说明默认按全部正常常态处理。</x:v>
+        <x:v>多平台商家仓场景必须先做仓库映射，系统才能据此进行订单选仓和库存同步。</x:v>
       </x:c>
       <x:c r="V305" s="21" t="str">
-        <x:v>{"A":"规则相反：空配置默认不是零下载。","B":"错规则：系统不会随机选择常态。","C":"错范围：资料没有仅取最新常态的规则。"}</x:v>
+        <x:v>{"A":"错顺序：先抓单可能导致订单落错仓。","B":"错处理：会丢失真实仓库对应关系。","D":"错设置：权限不能替代平台仓到系统仓映射。"}</x:v>
       </x:c>
       <x:c r="W305" s="21" t="str">
         <x:v>让系统只下载责任范围内的唯品会业务，并把多仓订单准确分配到系统仓。</x:v>
@@ -38170,7 +38172,7 @@
         <x:v>["未维护任何常态时默认处理全部正常常态","无法获取常态时需联系唯品会平台","报错平台商品无有效的常态编码时需手工下载商品更新"]</x:v>
       </x:c>
       <x:c r="AC305" s="21" t="str">
-        <x:v>["把空配置理解为零范围","多团队仍依赖默认全量范围"]</x:v>
+        <x:v>["先抓单后补映射","把多个真实仓强行并成一个编码"]</x:v>
       </x:c>
       <x:c r="AD305" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -38183,7 +38185,7 @@
         <x:v>唯品会—常态维护与平台仓映射</x:v>
       </x:c>
       <x:c r="AH305" s="21" t="str">
-        <x:v>没有维护常态时，默认处理全部正常常态。</x:v>
+        <x:v>多平台商家仓在抓单前需映射到系统仓库。</x:v>
       </x:c>
       <x:c r="AI305" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -38235,19 +38237,19 @@
     </x:row>
     <x:row r="306" ht="46" customHeight="1">
       <x:c r="A306" s="21" t="str">
-        <x:v>WDT-056-A</x:v>
+        <x:v>WDT-055-B</x:v>
       </x:c>
       <x:c r="B306" s="21" t="str">
-        <x:v>旺店通-采购</x:v>
+        <x:v>旺店通-运营</x:v>
       </x:c>
       <x:c r="C306" s="21" t="str">
-        <x:v>采购</x:v>
+        <x:v>运营</x:v>
       </x:c>
       <x:c r="D306" s="21" t="str">
-        <x:v>采购入库</x:v>
+        <x:v>店铺对接</x:v>
       </x:c>
       <x:c r="E306" s="21" t="str">
-        <x:v>阿里巴巴</x:v>
+        <x:v>唯品会</x:v>
       </x:c>
       <x:c r="F306" s="21" t="str">
         <x:v>单选题</x:v>
@@ -38256,7 +38258,7 @@
         <x:v>进阶</x:v>
       </x:c>
       <x:c r="H306" s="21" t="str">
-        <x:v>高</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I306" s="21" t="str">
         <x:v>practice</x:v>
@@ -38265,74 +38267,74 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K306" s="21" t="str">
-        <x:v>WDT-K056</x:v>
+        <x:v>WDT-K055</x:v>
       </x:c>
       <x:c r="L306" s="21" t="str">
-        <x:v>1688 采购全链路</x:v>
+        <x:v>唯品会抓单前配置</x:v>
       </x:c>
       <x:c r="M306" s="21" t="str">
-        <x:v>主账号授权，先匹配再下单付款</x:v>
+        <x:v>先限定常态，再映射平台仓</x:v>
       </x:c>
       <x:c r="N306" s="21" t="str">
-        <x:v>首次配置 1688 采购账号并准备绑定供应商、匹配商品，哪组前置条件正确？</x:v>
+        <x:v>唯品会店铺没有维护任何正常常态时，资料说明系统默认怎样处理？</x:v>
       </x:c>
       <x:c r="O306" s="21" t="str">
-        <x:v>使用 1688 子账号授权，且与待绑定供应商没有历史交易</x:v>
+        <x:v>默认不下载任何常态的订单和商品</x:v>
       </x:c>
       <x:c r="P306" s="21" t="str">
-        <x:v>使用 ERP 员工账号授权，且按商品名称自动建立交易记录</x:v>
+        <x:v>默认随机选择一个正常常态下载订单商品</x:v>
       </x:c>
       <x:c r="Q306" s="21" t="str">
-        <x:v>使用任意平台账号授权，且先付款后再补供应商商品关系</x:v>
+        <x:v>默认只下载最近新增常态的订单和商品</x:v>
       </x:c>
       <x:c r="R306" s="21" t="str">
-        <x:v>使用 1688 主账号授权，且与待绑定供应商或商品已有交易</x:v>
+        <x:v>默认处理全部正常常态的订单和商品</x:v>
       </x:c>
       <x:c r="S306" s="21" t="str">
         <x:v>D</x:v>
       </x:c>
       <x:c r="T306" s="21" t="str">
-        <x:v>使用 1688 主账号授权，且与待绑定供应商或商品已有交易</x:v>
+        <x:v>默认处理全部正常常态的订单和商品</x:v>
       </x:c>
       <x:c r="U306" s="21" t="str">
-        <x:v>子账号无法获取 API 授权；供应商绑定和商品匹配都以已有交易关系为前提。</x:v>
+        <x:v>未维护常态并不代表不处理；资料明确说明默认按全部正常常态处理。</x:v>
       </x:c>
       <x:c r="V306" s="21" t="str">
-        <x:v>{"A":"两个前置都错：子账号不能授权且缺少交易关系。","B":"错账号：ERP 员工账号不能替代 1688 主账号授权。","C":"错顺序：不能先付款再补建采购关系。"}</x:v>
+        <x:v>{"A":"规则相反：空配置默认不是零下载。","B":"错规则：系统不会随机选择常态。","C":"错范围：资料没有仅取最新常态的规则。"}</x:v>
       </x:c>
       <x:c r="W306" s="21" t="str">
-        <x:v>建立可追踪的 1688 采购链路，从账号授权和货品关系一直衔接到正常采购入库。</x:v>
+        <x:v>让系统只下载责任范围内的唯品会业务，并把多仓订单准确分配到系统仓。</x:v>
       </x:c>
       <x:c r="X306" s="21" t="str">
-        <x:v>["配置","基本配置","1688配置","采购","供应商","1688采购账号管理"]</x:v>
+        <x:v>["配置","绑定店铺","唯品会店铺","编辑"]</x:v>
       </x:c>
       <x:c r="Y306" s="21" t="str">
-        <x:v>["已开启 1688 配置","使用 1688 主账号完成 API 授权","需要绑定的供应商或商品与账号已有历史交易"]</x:v>
+        <x:v>["已完成对应唯品会业务授权","多品牌或多团队时已明确各自负责的常态","存在多个平台商家仓时已取得仓库对应关系"]</x:v>
       </x:c>
       <x:c r="Z306" s="21" t="str">
-        <x:v>["在 1688 采购账号管理绑定主账号","按需把 ERP 供应商与 1688 供应商一对一绑定","用商品链接将 ERP 货品与 1688 商品匹配","审核 ERP 采购单后进入 1688 一键下单","在 1688 采购支付同步单据并用支付宝付款","卖家发货后按正常采购入库"]</x:v>
+        <x:v>["编辑店铺并选择本系统负责的正常常态","若本系统负责全部常态则按资料保持不维护","存在多个平台商家仓时建立平台仓到系统仓映射","再开启抓单并核验订单仓库"]</x:v>
       </x:c>
       <x:c r="AA306" s="21" t="str">
-        <x:v>["账号授权、供应商和商品关系均正确","下单后进入待买家付款，支付后进入待卖家发货","收货可衔接正常采购入库"]</x:v>
+        <x:v>["系统只下载应负责常态的订单和商品","多仓订单落到正确系统仓库"]</x:v>
       </x:c>
       <x:c r="AB306" s="21" t="str">
-        <x:v>["1688 子账号无法取得 API 授权","绑定供应商和匹配商品要求账号与对应对象有过交易","一键下单前 ERP 采购单必须审核"]</x:v>
+        <x:v>["未维护任何常态时默认处理全部正常常态","无法获取常态时需联系唯品会平台","报错平台商品无有效的常态编码时需手工下载商品更新"]</x:v>
       </x:c>
       <x:c r="AC306" s="21" t="str">
-        <x:v>["使用子账号授权","没有历史交易仍反复绑定匹配"]</x:v>
+        <x:v>["把空配置理解为零范围","多团队仍依赖默认全量范围"]</x:v>
       </x:c>
       <x:c r="AD306" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
       </x:c>
       <x:c r="AE306" s="21" t="str">
-        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/hc37akriw5yevbei</x:v>
+        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/sv0h8l9k3tqz0nbh</x:v>
       </x:c>
       <x:c r="AF306" s="21" t="str"/>
       <x:c r="AG306" s="21" t="str">
-        <x:v>1688—账号授权、供应商商品匹配与采购支付</x:v>
+        <x:v>唯品会—常态维护与平台仓映射</x:v>
       </x:c>
       <x:c r="AH306" s="21" t="str">
-        <x:v>1688 使用主账号授权；供应商及商品匹配要求此前有交易。</x:v>
+        <x:v>没有维护常态时，默认处理全部正常常态。</x:v>
       </x:c>
       <x:c r="AI306" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -38376,7 +38378,7 @@
       <x:c r="AV306" s="21" t="str"/>
       <x:c r="AW306" s="21" t="str"/>
       <x:c r="AX306" s="21" t="str">
-        <x:v>完成 1688 授权匹配与采购支付链路</x:v>
+        <x:v>配置唯品会常态与平台仓映射</x:v>
       </x:c>
       <x:c r="AY306" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -38384,7 +38386,7 @@
     </x:row>
     <x:row r="307" ht="46" customHeight="1">
       <x:c r="A307" s="21" t="str">
-        <x:v>WDT-056-B</x:v>
+        <x:v>WDT-056-A</x:v>
       </x:c>
       <x:c r="B307" s="21" t="str">
         <x:v>旺店通-采购</x:v>
@@ -38402,7 +38404,7 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G307" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>进阶</x:v>
       </x:c>
       <x:c r="H307" s="21" t="str">
         <x:v>高</x:v>
@@ -38423,31 +38425,31 @@
         <x:v>主账号授权，先匹配再下单付款</x:v>
       </x:c>
       <x:c r="N307" s="21" t="str">
-        <x:v>ERP 采购单已审核且 1688 商品匹配完成，正确的下单支付状态链路是什么？</x:v>
+        <x:v>首次配置 1688 采购账号并准备绑定供应商、匹配商品，哪组前置条件正确？</x:v>
       </x:c>
       <x:c r="O307" s="21" t="str">
-        <x:v>先正常采购入库，再一键下单，最后同步单据退款</x:v>
+        <x:v>使用 1688 子账号授权，且与待绑定供应商没有历史交易</x:v>
       </x:c>
       <x:c r="P307" s="21" t="str">
-        <x:v>先在支付页付款，再补建采购单，最后等待买家发货</x:v>
+        <x:v>使用 ERP 员工账号授权，且按商品名称自动建立交易记录</x:v>
       </x:c>
       <x:c r="Q307" s="21" t="str">
-        <x:v>先取消采购审核，再推送商品，最后由卖家代为付款</x:v>
+        <x:v>使用任意平台账号授权，且先付款后再补供应商商品关系</x:v>
       </x:c>
       <x:c r="R307" s="21" t="str">
-        <x:v>先一键下单进入待买家付款，再同步支付，付款后待卖家发货</x:v>
+        <x:v>使用 1688 主账号授权，且与待绑定供应商或商品已有交易</x:v>
       </x:c>
       <x:c r="S307" s="21" t="str">
         <x:v>D</x:v>
       </x:c>
       <x:c r="T307" s="21" t="str">
-        <x:v>先一键下单进入待买家付款，再同步支付，付款后待卖家发货</x:v>
+        <x:v>使用 1688 主账号授权，且与待绑定供应商或商品已有交易</x:v>
       </x:c>
       <x:c r="U307" s="21" t="str">
-        <x:v>审核后的采购单一键下单成功会进入待买家付款；支付页同步 1688 单据并完成支付宝付款后进入待卖家发货。</x:v>
+        <x:v>子账号无法获取 API 授权；供应商绑定和商品匹配都以已有交易关系为前提。</x:v>
       </x:c>
       <x:c r="V307" s="21" t="str">
-        <x:v>{"A":"错顺序：采购入库在卖家发货和收货之后。","B":"错前置：支付必须有已推送的审核采购单。","C":"错状态和责任：采购单需保持审核，买家完成付款。"}</x:v>
+        <x:v>{"A":"两个前置都错：子账号不能授权且缺少交易关系。","B":"错账号：ERP 员工账号不能替代 1688 主账号授权。","C":"错顺序：不能先付款再补建采购关系。"}</x:v>
       </x:c>
       <x:c r="W307" s="21" t="str">
         <x:v>建立可追踪的 1688 采购链路，从账号授权和货品关系一直衔接到正常采购入库。</x:v>
@@ -38468,7 +38470,7 @@
         <x:v>["1688 子账号无法取得 API 授权","绑定供应商和匹配商品要求账号与对应对象有过交易","一键下单前 ERP 采购单必须审核"]</x:v>
       </x:c>
       <x:c r="AC307" s="21" t="str">
-        <x:v>["先入库再下单","未审核或取消审核后推送"]</x:v>
+        <x:v>["使用子账号授权","没有历史交易仍反复绑定匹配"]</x:v>
       </x:c>
       <x:c r="AD307" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -38481,7 +38483,7 @@
         <x:v>1688—账号授权、供应商商品匹配与采购支付</x:v>
       </x:c>
       <x:c r="AH307" s="21" t="str">
-        <x:v>审核采购单→1688一键下单→待买家付款→同步支付→待卖家发货→正常采购入库。</x:v>
+        <x:v>1688 使用主账号授权；供应商及商品匹配要求此前有交易。</x:v>
       </x:c>
       <x:c r="AI307" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -38533,28 +38535,28 @@
     </x:row>
     <x:row r="308" ht="46" customHeight="1">
       <x:c r="A308" s="21" t="str">
-        <x:v>WDT-057-A</x:v>
+        <x:v>WDT-056-B</x:v>
       </x:c>
       <x:c r="B308" s="21" t="str">
-        <x:v>旺店通-运营</x:v>
+        <x:v>旺店通-采购</x:v>
       </x:c>
       <x:c r="C308" s="21" t="str">
-        <x:v>运营</x:v>
+        <x:v>采购</x:v>
       </x:c>
       <x:c r="D308" s="21" t="str">
-        <x:v>经营报表</x:v>
+        <x:v>采购入库</x:v>
       </x:c>
       <x:c r="E308" s="21" t="str">
-        <x:v>通用</x:v>
+        <x:v>阿里巴巴</x:v>
       </x:c>
       <x:c r="F308" s="21" t="str">
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G308" s="21" t="str">
-        <x:v>基础</x:v>
+        <x:v>场景</x:v>
       </x:c>
       <x:c r="H308" s="21" t="str">
-        <x:v>中</x:v>
+        <x:v>高</x:v>
       </x:c>
       <x:c r="I308" s="21" t="str">
         <x:v>practice</x:v>
@@ -38563,74 +38565,74 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K308" s="21" t="str">
-        <x:v>WDT-K057</x:v>
+        <x:v>WDT-K056</x:v>
       </x:c>
       <x:c r="L308" s="21" t="str">
-        <x:v>销售利润报表</x:v>
+        <x:v>1688 采购全链路</x:v>
       </x:c>
       <x:c r="M308" s="21" t="str">
-        <x:v>按店铺或货品看收入、退款和成本</x:v>
+        <x:v>主账号授权，先匹配再下单付款</x:v>
       </x:c>
       <x:c r="N308" s="21" t="str">
-        <x:v>运营要按店铺和系统规格比较销售额、退款、成本与毛利，应进入哪个报表？</x:v>
+        <x:v>ERP 采购单已审核且 1688 商品匹配完成，正确的下单支付状态链路是什么？</x:v>
       </x:c>
       <x:c r="O308" s="21" t="str">
-        <x:v>进入发货明细报表，按快递单号统计销售毛利</x:v>
+        <x:v>先正常采购入库，再一键下单，最后同步单据退款</x:v>
       </x:c>
       <x:c r="P308" s="21" t="str">
-        <x:v>进入销售利润报表，按店铺或货品维度查看</x:v>
+        <x:v>先在支付页付款，再补建采购单，最后等待买家发货</x:v>
       </x:c>
       <x:c r="Q308" s="21" t="str">
-        <x:v>进入采购汇总报表，按供应商维度统计销售毛利</x:v>
+        <x:v>先取消采购审核，再推送商品，最后由卖家代为付款</x:v>
       </x:c>
       <x:c r="R308" s="21" t="str">
-        <x:v>进入库存查询报表，按默认库位统计销售毛利</x:v>
+        <x:v>先一键下单进入待买家付款，再同步支付，付款后待卖家发货</x:v>
       </x:c>
       <x:c r="S308" s="21" t="str">
-        <x:v>B</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="T308" s="21" t="str">
-        <x:v>进入销售利润报表，按店铺或货品维度查看</x:v>
+        <x:v>先一键下单进入待买家付款，再同步支付，付款后待卖家发货</x:v>
       </x:c>
       <x:c r="U308" s="21" t="str">
-        <x:v>销售利润报表就是按店铺和货品多维分析销售、退款、成本和毛利的入口。</x:v>
+        <x:v>审核后的采购单一键下单成功会进入待买家付款；支付页同步 1688 单据并完成支付宝付款后进入待卖家发货。</x:v>
       </x:c>
       <x:c r="V308" s="21" t="str">
-        <x:v>{"A":"错报表：发货明细关注已发货订单，不提供完整毛利口径。","C":"错报表：采购汇总用于采购到货和供应商对账。","D":"错报表：库存查询不能替代销售利润核算。"}</x:v>
+        <x:v>{"A":"错顺序：采购入库在卖家发货和收货之后。","B":"错前置：支付必须有已推送的审核采购单。","C":"错状态和责任：采购单需保持审核，买家完成付款。"}</x:v>
       </x:c>
       <x:c r="W308" s="21" t="str">
-        <x:v>用统一口径识别店铺和货品的收入、退款、成本及毛利表现，为投放与商品优化提供依据。</x:v>
+        <x:v>建立可追踪的 1688 采购链路，从账号授权和货品关系一直衔接到正常采购入库。</x:v>
       </x:c>
       <x:c r="X308" s="21" t="str">
-        <x:v>["报表","销售利润报表"]</x:v>
+        <x:v>["配置","基本配置","1688配置","采购","供应商","1688采购账号管理"]</x:v>
       </x:c>
       <x:c r="Y308" s="21" t="str">
-        <x:v>["已确定按付款时间还是发货时间分析","已明确需要的店铺、仓库和货品范围"]</x:v>
+        <x:v>["已开启 1688 配置","使用 1688 主账号完成 API 授权","需要绑定的供应商或商品与账号已有历史交易"]</x:v>
       </x:c>
       <x:c r="Z308" s="21" t="str">
-        <x:v>["进入销售利润报表","设置时间口径、店铺和仓库筛选","按店铺、平台链接、系统规格或组合装查看","核对销售额、退款、成本、毛利与毛利率","按筛选结果导出"]</x:v>
+        <x:v>["在 1688 采购账号管理绑定主账号","按需把 ERP 供应商与 1688 供应商一对一绑定","用商品链接将 ERP 货品与 1688 商品匹配","审核 ERP 采购单后进入 1688 一键下单","在 1688 采购支付同步单据并用支付宝付款","卖家发货后按正常采购入库"]</x:v>
       </x:c>
       <x:c r="AA308" s="21" t="str">
-        <x:v>["销售收入按销售额减退款理解","毛利计算包含发出成本、退回成本与快递成本","导出范围与页面筛选一致"]</x:v>
+        <x:v>["账号授权、供应商和商品关系均正确","下单后进入待买家付款，支付后进入待卖家发货","收货可衔接正常采购入库"]</x:v>
       </x:c>
       <x:c r="AB308" s="21" t="str">
-        <x:v>["付款时间口径可能包含尚未在 ERP 发货的订单","报表数据按日更新到前一日"]</x:v>
+        <x:v>["1688 子账号无法取得 API 授权","绑定供应商和匹配商品要求账号与对应对象有过交易","一键下单前 ERP 采购单必须审核"]</x:v>
       </x:c>
       <x:c r="AC308" s="21" t="str">
-        <x:v>["用发货明细替代利润分析","用采购汇总解释销售毛利"]</x:v>
+        <x:v>["先入库再下单","未审核或取消审核后推送"]</x:v>
       </x:c>
       <x:c r="AD308" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
       </x:c>
       <x:c r="AE308" s="21" t="str">
-        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/orpevw</x:v>
+        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/hc37akriw5yevbei</x:v>
       </x:c>
       <x:c r="AF308" s="21" t="str"/>
       <x:c r="AG308" s="21" t="str">
-        <x:v>报表—销售利润报表</x:v>
+        <x:v>1688—账号授权、供应商商品匹配与采购支付</x:v>
       </x:c>
       <x:c r="AH308" s="21" t="str">
-        <x:v>报表→销售利润报表，支持店铺和货品多维分析。</x:v>
+        <x:v>审核采购单→1688一键下单→待买家付款→同步支付→待卖家发货→正常采购入库。</x:v>
       </x:c>
       <x:c r="AI308" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -38674,7 +38676,7 @@
       <x:c r="AV308" s="21" t="str"/>
       <x:c r="AW308" s="21" t="str"/>
       <x:c r="AX308" s="21" t="str">
-        <x:v>用销售利润报表分析销售与毛利</x:v>
+        <x:v>完成 1688 授权匹配与采购支付链路</x:v>
       </x:c>
       <x:c r="AY308" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -38682,7 +38684,7 @@
     </x:row>
     <x:row r="309" ht="46" customHeight="1">
       <x:c r="A309" s="21" t="str">
-        <x:v>WDT-057-B</x:v>
+        <x:v>WDT-057-A</x:v>
       </x:c>
       <x:c r="B309" s="21" t="str">
         <x:v>旺店通-运营</x:v>
@@ -38700,10 +38702,10 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G309" s="21" t="str">
-        <x:v>进阶</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="H309" s="21" t="str">
-        <x:v>高</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I309" s="21" t="str">
         <x:v>practice</x:v>
@@ -38721,31 +38723,31 @@
         <x:v>按店铺或货品看收入、退款和成本</x:v>
       </x:c>
       <x:c r="N309" s="21" t="str">
-        <x:v>下列哪一个毛利计算口径符合销售利润报表资料？</x:v>
+        <x:v>运营要按店铺和系统规格比较销售额、退款、成本与毛利，应进入哪个报表？</x:v>
       </x:c>
       <x:c r="O309" s="21" t="str">
-        <x:v>销售额减退款，再加发出成本并减退回成本</x:v>
+        <x:v>进入发货明细报表，按快递单号统计销售毛利</x:v>
       </x:c>
       <x:c r="P309" s="21" t="str">
-        <x:v>销售额减退款减发出成本，加退回成本，再减快递成本</x:v>
+        <x:v>进入销售利润报表，按店铺或货品维度查看</x:v>
       </x:c>
       <x:c r="Q309" s="21" t="str">
-        <x:v>销售额加退款减发出成本，减退回成本，再加快递成本</x:v>
+        <x:v>进入采购汇总报表，按供应商维度统计销售毛利</x:v>
       </x:c>
       <x:c r="R309" s="21" t="str">
-        <x:v>销售额减发出货品成本，再加快递成本和退款</x:v>
+        <x:v>进入库存查询报表，按默认库位统计销售毛利</x:v>
       </x:c>
       <x:c r="S309" s="21" t="str">
         <x:v>B</x:v>
       </x:c>
       <x:c r="T309" s="21" t="str">
-        <x:v>销售额减退款减发出成本，加退回成本，再减快递成本</x:v>
+        <x:v>进入销售利润报表，按店铺或货品维度查看</x:v>
       </x:c>
       <x:c r="U309" s="21" t="str">
-        <x:v>退回货品重新回到库存，因此按资料口径加回退回成本；退款、发出成本和快递成本均从销售额扣减。</x:v>
+        <x:v>销售利润报表就是按店铺和货品多维分析销售、退款、成本和毛利的入口。</x:v>
       </x:c>
       <x:c r="V309" s="21" t="str">
-        <x:v>{"A":"符号错误：发出成本应减，退回成本应加。","C":"多项符号相反：退款和快递成本都应扣减。","D":"符号错误：退款和快递成本不应加回。"}</x:v>
+        <x:v>{"A":"错报表：发货明细关注已发货订单，不提供完整毛利口径。","C":"错报表：采购汇总用于采购到货和供应商对账。","D":"错报表：库存查询不能替代销售利润核算。"}</x:v>
       </x:c>
       <x:c r="W309" s="21" t="str">
         <x:v>用统一口径识别店铺和货品的收入、退款、成本及毛利表现，为投放与商品优化提供依据。</x:v>
@@ -38766,7 +38768,7 @@
         <x:v>["付款时间口径可能包含尚未在 ERP 发货的订单","报表数据按日更新到前一日"]</x:v>
       </x:c>
       <x:c r="AC309" s="21" t="str">
-        <x:v>["把退款加回销售额","把快递成本当收益相加"]</x:v>
+        <x:v>["用发货明细替代利润分析","用采购汇总解释销售毛利"]</x:v>
       </x:c>
       <x:c r="AD309" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -38779,7 +38781,7 @@
         <x:v>报表—销售利润报表</x:v>
       </x:c>
       <x:c r="AH309" s="21" t="str">
-        <x:v>毛利=销售额-退款-发出货品成本+退回货品成本-快递成本。</x:v>
+        <x:v>报表→销售利润报表，支持店铺和货品多维分析。</x:v>
       </x:c>
       <x:c r="AI309" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -38831,7 +38833,7 @@
     </x:row>
     <x:row r="310" ht="46" customHeight="1">
       <x:c r="A310" s="21" t="str">
-        <x:v>WDT-058-A</x:v>
+        <x:v>WDT-057-B</x:v>
       </x:c>
       <x:c r="B310" s="21" t="str">
         <x:v>旺店通-运营</x:v>
@@ -38849,10 +38851,10 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G310" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>进阶</x:v>
       </x:c>
       <x:c r="H310" s="21" t="str">
-        <x:v>中</x:v>
+        <x:v>高</x:v>
       </x:c>
       <x:c r="I310" s="21" t="str">
         <x:v>practice</x:v>
@@ -38861,74 +38863,74 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K310" s="21" t="str">
-        <x:v>WDT-K058</x:v>
+        <x:v>WDT-K057</x:v>
       </x:c>
       <x:c r="L310" s="21" t="str">
-        <x:v>发货明细报表</x:v>
+        <x:v>销售利润报表</x:v>
       </x:c>
       <x:c r="M310" s="21" t="str">
-        <x:v>实时查看已发货订单明细</x:v>
+        <x:v>按店铺或货品看收入、退款和成本</x:v>
       </x:c>
       <x:c r="N310" s="21" t="str">
-        <x:v>运营要立即核对今天已发货的代发订单和供应商履约，应优先使用哪个报表？</x:v>
+        <x:v>下列哪一个毛利计算口径符合销售利润报表资料？</x:v>
       </x:c>
       <x:c r="O310" s="21" t="str">
-        <x:v>销售利润报表，按付款时间查看到前一日</x:v>
+        <x:v>销售额减退款，再加发出成本并减退回成本</x:v>
       </x:c>
       <x:c r="P310" s="21" t="str">
-        <x:v>采购汇总报表，按采购单时间查看到货</x:v>
+        <x:v>销售额减退款减发出成本，加退回成本，再减快递成本</x:v>
       </x:c>
       <x:c r="Q310" s="21" t="str">
-        <x:v>发货明细报表，按发货时间和供应商查看</x:v>
+        <x:v>销售额加退款减发出成本，减退回成本，再加快递成本</x:v>
       </x:c>
       <x:c r="R310" s="21" t="str">
-        <x:v>库存查询报表，按默认库位查看现存量</x:v>
+        <x:v>销售额减发出货品成本，再加快递成本和退款</x:v>
       </x:c>
       <x:c r="S310" s="21" t="str">
-        <x:v>C</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="T310" s="21" t="str">
-        <x:v>发货明细报表，按发货时间和供应商查看</x:v>
+        <x:v>销售额减退款减发出成本，加退回成本，再减快递成本</x:v>
       </x:c>
       <x:c r="U310" s="21" t="str">
-        <x:v>发货明细是实时已发货口径，并且支持供应商筛选，适合当天履约和代发核对。</x:v>
+        <x:v>退回货品重新回到库存，因此按资料口径加回退回成本；退款、发出成本和快递成本均从销售额扣减。</x:v>
       </x:c>
       <x:c r="V310" s="21" t="str">
-        <x:v>{"A":"错时效和对象：利润报表按日更新且不是发货履约明细。","B":"错业务：采购到货不等于销售订单已发货。","D":"错对象：现存量不能证明哪些订单已发货。"}</x:v>
+        <x:v>{"A":"符号错误：发出成本应减，退回成本应加。","C":"多项符号相反：退款和快递成本都应扣减。","D":"符号错误：退款和快递成本不应加回。"}</x:v>
       </x:c>
       <x:c r="W310" s="21" t="str">
-        <x:v>按发货结果及时核对代发、分销、供应商履约和仓库作业表现。</x:v>
+        <x:v>用统一口径识别店铺和货品的收入、退款、成本及毛利表现，为投放与商品优化提供依据。</x:v>
       </x:c>
       <x:c r="X310" s="21" t="str">
-        <x:v>["报表","发货明细报表"]</x:v>
+        <x:v>["报表","销售利润报表"]</x:v>
       </x:c>
       <x:c r="Y310" s="21" t="str">
-        <x:v>["订单已在系统形成发货记录","已确定发货时间和核对对象"]</x:v>
+        <x:v>["已确定按付款时间还是发货时间分析","已明确需要的店铺、仓库和货品范围"]</x:v>
       </x:c>
       <x:c r="Z310" s="21" t="str">
-        <x:v>["进入发货明细报表","按发货时间、仓库、店铺或供应商筛选","按系统规格、店铺或订单明细查看","需要时叠加订单标签","导出筛选结果进行对账"]</x:v>
+        <x:v>["进入销售利润报表","设置时间口径、店铺和仓库筛选","按店铺、平台链接、系统规格或组合装查看","核对销售额、退款、成本、毛利与毛利率","按筛选结果导出"]</x:v>
       </x:c>
       <x:c r="AA310" s="21" t="str">
-        <x:v>["页面反映实时已发货订单","筛选范围与代发、分销或供应商对账对象一致"]</x:v>
+        <x:v>["销售收入按销售额减退款理解","毛利计算包含发出成本、退回成本与快递成本","导出范围与页面筛选一致"]</x:v>
       </x:c>
       <x:c r="AB310" s="21" t="str">
-        <x:v>["该报表基于已发货订单，未发货订单不属于其主要核对范围"]</x:v>
+        <x:v>["付款时间口径可能包含尚未在 ERP 发货的订单","报表数据按日更新到前一日"]</x:v>
       </x:c>
       <x:c r="AC310" s="21" t="str">
-        <x:v>["用 T+1 利润报表追实时发货","用采购到货数据代替销售履约"]</x:v>
+        <x:v>["把退款加回销售额","把快递成本当收益相加"]</x:v>
       </x:c>
       <x:c r="AD310" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
       </x:c>
       <x:c r="AE310" s="21" t="str">
-        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/udks3t</x:v>
+        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/orpevw</x:v>
       </x:c>
       <x:c r="AF310" s="21" t="str"/>
       <x:c r="AG310" s="21" t="str">
-        <x:v>报表—发货明细报表</x:v>
+        <x:v>报表—销售利润报表</x:v>
       </x:c>
       <x:c r="AH310" s="21" t="str">
-        <x:v>发货明细报表实时反映已发货订单，并支持发货时间和供应商筛选。</x:v>
+        <x:v>毛利=销售额-退款-发出货品成本+退回货品成本-快递成本。</x:v>
       </x:c>
       <x:c r="AI310" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -38972,7 +38974,7 @@
       <x:c r="AV310" s="21" t="str"/>
       <x:c r="AW310" s="21" t="str"/>
       <x:c r="AX310" s="21" t="str">
-        <x:v>用发货明细报表做履约与供应商核对</x:v>
+        <x:v>用销售利润报表分析销售与毛利</x:v>
       </x:c>
       <x:c r="AY310" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -38980,7 +38982,7 @@
     </x:row>
     <x:row r="311" ht="46" customHeight="1">
       <x:c r="A311" s="21" t="str">
-        <x:v>WDT-058-B</x:v>
+        <x:v>WDT-058-A</x:v>
       </x:c>
       <x:c r="B311" s="21" t="str">
         <x:v>旺店通-运营</x:v>
@@ -38998,7 +39000,7 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G311" s="21" t="str">
-        <x:v>进阶</x:v>
+        <x:v>场景</x:v>
       </x:c>
       <x:c r="H311" s="21" t="str">
         <x:v>中</x:v>
@@ -39019,31 +39021,31 @@
         <x:v>实时查看已发货订单明细</x:v>
       </x:c>
       <x:c r="N311" s="21" t="str">
-        <x:v>用发货明细做某供应商代发对账时，哪组筛选最贴近资料提供的字段？</x:v>
+        <x:v>运营要立即核对今天已发货的代发订单和供应商履约，应优先使用哪个报表？</x:v>
       </x:c>
       <x:c r="O311" s="21" t="str">
-        <x:v>付款时间、退款原因、售后状态、退货物流，必要时加客服备注</x:v>
+        <x:v>销售利润报表，按付款时间查看到前一日</x:v>
       </x:c>
       <x:c r="P311" s="21" t="str">
-        <x:v>采购时间、采购状态、到货月份、供应商，必要时加采购价格</x:v>
+        <x:v>采购汇总报表，按采购单时间查看到货</x:v>
       </x:c>
       <x:c r="Q311" s="21" t="str">
-        <x:v>发货时间、仓库、店铺、供应商，必要时加订单标签</x:v>
+        <x:v>发货明细报表，按发货时间和供应商查看</x:v>
       </x:c>
       <x:c r="R311" s="21" t="str">
-        <x:v>绑定时间、平台类型、授权状态、店铺名称，必要时加服务订单号</x:v>
+        <x:v>库存查询报表，按默认库位查看现存量</x:v>
       </x:c>
       <x:c r="S311" s="21" t="str">
         <x:v>C</x:v>
       </x:c>
       <x:c r="T311" s="21" t="str">
-        <x:v>发货时间、仓库、店铺、供应商，必要时加订单标签</x:v>
+        <x:v>发货明细报表，按发货时间和供应商查看</x:v>
       </x:c>
       <x:c r="U311" s="21" t="str">
-        <x:v>这些都是发货明细资料列出的筛选维度，可将代发对账范围锁定到正确时间、仓店和供应商。</x:v>
+        <x:v>发货明细是实时已发货口径，并且支持供应商筛选，适合当天履约和代发核对。</x:v>
       </x:c>
       <x:c r="V311" s="21" t="str">
-        <x:v>{"A":"错报表字段：更接近售后核对。","B":"错口径：更接近采购汇总筛选。","D":"错口径：更接近店铺绑定核验。"}</x:v>
+        <x:v>{"A":"错时效和对象：利润报表按日更新且不是发货履约明细。","B":"错业务：采购到货不等于销售订单已发货。","D":"错对象：现存量不能证明哪些订单已发货。"}</x:v>
       </x:c>
       <x:c r="W311" s="21" t="str">
         <x:v>按发货结果及时核对代发、分销、供应商履约和仓库作业表现。</x:v>
@@ -39064,7 +39066,7 @@
         <x:v>["该报表基于已发货订单，未发货订单不属于其主要核对范围"]</x:v>
       </x:c>
       <x:c r="AC311" s="21" t="str">
-        <x:v>["只筛供应商不限定时间","把售后或采购字段当发货筛选项"]</x:v>
+        <x:v>["用 T+1 利润报表追实时发货","用采购到货数据代替销售履约"]</x:v>
       </x:c>
       <x:c r="AD311" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -39077,7 +39079,7 @@
         <x:v>报表—发货明细报表</x:v>
       </x:c>
       <x:c r="AH311" s="21" t="str">
-        <x:v>发货明细支持发货时间、仓库、店铺、供应商和标签筛选。</x:v>
+        <x:v>发货明细报表实时反映已发货订单，并支持发货时间和供应商筛选。</x:v>
       </x:c>
       <x:c r="AI311" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -39129,7 +39131,7 @@
     </x:row>
     <x:row r="312" ht="46" customHeight="1">
       <x:c r="A312" s="21" t="str">
-        <x:v>WDT-059-A</x:v>
+        <x:v>WDT-058-B</x:v>
       </x:c>
       <x:c r="B312" s="21" t="str">
         <x:v>旺店通-运营</x:v>
@@ -39147,7 +39149,7 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G312" s="21" t="str">
-        <x:v>基础</x:v>
+        <x:v>进阶</x:v>
       </x:c>
       <x:c r="H312" s="21" t="str">
         <x:v>中</x:v>
@@ -39159,74 +39161,74 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K312" s="21" t="str">
-        <x:v>WDT-K059</x:v>
+        <x:v>WDT-K058</x:v>
       </x:c>
       <x:c r="L312" s="21" t="str">
-        <x:v>采购汇总报表</x:v>
+        <x:v>发货明细报表</x:v>
       </x:c>
       <x:c r="M312" s="21" t="str">
-        <x:v>按货品或供应商加货品看月度到货</x:v>
+        <x:v>实时查看已发货订单明细</x:v>
       </x:c>
       <x:c r="N312" s="21" t="str">
-        <x:v>要按供应商和货品查看本月采购到货并用于对账，应使用哪个报表和维度？</x:v>
+        <x:v>用发货明细做某供应商代发对账时，哪组筛选最贴近资料提供的字段？</x:v>
       </x:c>
       <x:c r="O312" s="21" t="str">
-        <x:v>库存查询报表，按仓库加默认库位查看</x:v>
+        <x:v>付款时间、退款原因、售后状态、退货物流，必要时加客服备注</x:v>
       </x:c>
       <x:c r="P312" s="21" t="str">
-        <x:v>发货明细报表，按仓库加订单明细查看</x:v>
+        <x:v>采购时间、采购状态、到货月份、供应商，必要时加采购价格</x:v>
       </x:c>
       <x:c r="Q312" s="21" t="str">
-        <x:v>销售利润报表，按店铺加系统规格查看</x:v>
+        <x:v>发货时间、仓库、店铺、供应商，必要时加订单标签</x:v>
       </x:c>
       <x:c r="R312" s="21" t="str">
-        <x:v>采购汇总报表，按供应商加货品查看</x:v>
+        <x:v>绑定时间、平台类型、授权状态、店铺名称，必要时加服务订单号</x:v>
       </x:c>
       <x:c r="S312" s="21" t="str">
-        <x:v>D</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="T312" s="21" t="str">
-        <x:v>采购汇总报表，按供应商加货品查看</x:v>
+        <x:v>发货时间、仓库、店铺、供应商，必要时加订单标签</x:v>
       </x:c>
       <x:c r="U312" s="21" t="str">
-        <x:v>采购汇总报表支持供应商加货品维度，适合按月核对具体供应商的到货。</x:v>
+        <x:v>这些都是发货明细资料列出的筛选维度，可将代发对账范围锁定到正确时间、仓店和供应商。</x:v>
       </x:c>
       <x:c r="V312" s="21" t="str">
-        <x:v>{"A":"错口径：库存余额不能替代采购到货记录。","B":"错口径：发货明细是销售履约。","C":"错报表：销售利润不汇总采购到货。"}</x:v>
+        <x:v>{"A":"错报表字段：更接近售后核对。","B":"错口径：更接近采购汇总筛选。","D":"错口径：更接近店铺绑定核验。"}</x:v>
       </x:c>
       <x:c r="W312" s="21" t="str">
-        <x:v>以采购单和到货口径汇总供应商履约，为采购复盘与供应商对账提供依据。</x:v>
+        <x:v>按发货结果及时核对代发、分销、供应商履约和仓库作业表现。</x:v>
       </x:c>
       <x:c r="X312" s="21" t="str">
-        <x:v>["报表","采购汇总报表"]</x:v>
+        <x:v>["报表","发货明细报表"]</x:v>
       </x:c>
       <x:c r="Y312" s="21" t="str">
-        <x:v>["已确定需要核对的采购时间范围","已明确货品、供应商或采购单状态范围"]</x:v>
+        <x:v>["订单已在系统形成发货记录","已确定发货时间和核对对象"]</x:v>
       </x:c>
       <x:c r="Z312" s="21" t="str">
-        <x:v>["进入采购汇总报表","按采购单时间设置统计范围","选择货品或供应商加货品的查看维度","按供应商和采购单状态进一步筛选","导出结果完成月度到货对账"]</x:v>
+        <x:v>["进入发货明细报表","按发货时间、仓库、店铺或供应商筛选","按系统规格、店铺或订单明细查看","需要时叠加订单标签","导出筛选结果进行对账"]</x:v>
       </x:c>
       <x:c r="AA312" s="21" t="str">
-        <x:v>["汇总维度与对账对象一致","采购时间、供应商和采购状态筛选准确"]</x:v>
+        <x:v>["页面反映实时已发货订单","筛选范围与代发、分销或供应商对账对象一致"]</x:v>
       </x:c>
       <x:c r="AB312" s="21" t="str">
-        <x:v>["采购汇总用于采购到货与供应商对账，不替代销售发货明细或销售利润分析"]</x:v>
+        <x:v>["该报表基于已发货订单，未发货订单不属于其主要核对范围"]</x:v>
       </x:c>
       <x:c r="AC312" s="21" t="str">
-        <x:v>["用销售报表对采购到货","只看库存余额推断本月到货"]</x:v>
+        <x:v>["只筛供应商不限定时间","把售后或采购字段当发货筛选项"]</x:v>
       </x:c>
       <x:c r="AD312" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
       </x:c>
       <x:c r="AE312" s="21" t="str">
-        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/glfdi78gghft0wfr</x:v>
+        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/udks3t</x:v>
       </x:c>
       <x:c r="AF312" s="21" t="str"/>
       <x:c r="AG312" s="21" t="str">
-        <x:v>报表—采购汇总报表</x:v>
+        <x:v>报表—发货明细报表</x:v>
       </x:c>
       <x:c r="AH312" s="21" t="str">
-        <x:v>采购汇总可按供应商加货品查看月度到货。</x:v>
+        <x:v>发货明细支持发货时间、仓库、店铺、供应商和标签筛选。</x:v>
       </x:c>
       <x:c r="AI312" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -39270,7 +39272,7 @@
       <x:c r="AV312" s="21" t="str"/>
       <x:c r="AW312" s="21" t="str"/>
       <x:c r="AX312" s="21" t="str">
-        <x:v>用采购汇总报表核对供应商到货</x:v>
+        <x:v>用发货明细报表做履约与供应商核对</x:v>
       </x:c>
       <x:c r="AY312" s="21" t="str">
         <x:v>2026-08-11</x:v>
@@ -39278,7 +39280,7 @@
     </x:row>
     <x:row r="313" ht="46" customHeight="1">
       <x:c r="A313" s="21" t="str">
-        <x:v>WDT-059-B</x:v>
+        <x:v>WDT-059-A</x:v>
       </x:c>
       <x:c r="B313" s="21" t="str">
         <x:v>旺店通-运营</x:v>
@@ -39296,7 +39298,7 @@
         <x:v>单选题</x:v>
       </x:c>
       <x:c r="G313" s="21" t="str">
-        <x:v>场景</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="H313" s="21" t="str">
         <x:v>中</x:v>
@@ -39317,31 +39319,31 @@
         <x:v>按货品或供应商加货品看月度到货</x:v>
       </x:c>
       <x:c r="N313" s="21" t="str">
-        <x:v>准备导出某供应商已完成采购单的到货汇总，哪组筛选最符合资料？</x:v>
+        <x:v>要按供应商和货品查看本月采购到货并用于对账，应使用哪个报表和维度？</x:v>
       </x:c>
       <x:c r="O313" s="21" t="str">
-        <x:v>采购单时间、货品、供应商、采购单状态</x:v>
+        <x:v>库存查询报表，按仓库加默认库位查看</x:v>
       </x:c>
       <x:c r="P313" s="21" t="str">
-        <x:v>付款时间、平台链接、退款金额、毛利率</x:v>
+        <x:v>发货明细报表，按仓库加订单明细查看</x:v>
       </x:c>
       <x:c r="Q313" s="21" t="str">
-        <x:v>发货时间、店铺、仓库、订单标签</x:v>
+        <x:v>销售利润报表，按店铺加系统规格查看</x:v>
       </x:c>
       <x:c r="R313" s="21" t="str">
-        <x:v>绑定时间、平台类型、店铺名称、授权状态</x:v>
+        <x:v>采购汇总报表，按供应商加货品查看</x:v>
       </x:c>
       <x:c r="S313" s="21" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="T313" s="21" t="str">
-        <x:v>采购单时间、货品、供应商、采购单状态</x:v>
+        <x:v>采购汇总报表，按供应商加货品查看</x:v>
       </x:c>
       <x:c r="U313" s="21" t="str">
-        <x:v>这四项是采购汇总资料列出的核心筛选字段，可准确锁定目标供应商和采购状态。</x:v>
+        <x:v>采购汇总报表支持供应商加货品维度，适合按月核对具体供应商的到货。</x:v>
       </x:c>
       <x:c r="V313" s="21" t="str">
-        <x:v>{"B":"错报表字段：属于销售利润范围。","C":"错报表字段：属于发货明细范围。","D":"错报表字段：属于店铺绑定范围。"}</x:v>
+        <x:v>{"A":"错口径：库存余额不能替代采购到货记录。","B":"错口径：发货明细是销售履约。","C":"错报表：销售利润不汇总采购到货。"}</x:v>
       </x:c>
       <x:c r="W313" s="21" t="str">
         <x:v>以采购单和到货口径汇总供应商履约，为采购复盘与供应商对账提供依据。</x:v>
@@ -39362,7 +39364,7 @@
         <x:v>["采购汇总用于采购到货与供应商对账，不替代销售发货明细或销售利润分析"]</x:v>
       </x:c>
       <x:c r="AC313" s="21" t="str">
-        <x:v>["用发货时间替代采购单时间","漏筛采购单状态"]</x:v>
+        <x:v>["用销售报表对采购到货","只看库存余额推断本月到货"]</x:v>
       </x:c>
       <x:c r="AD313" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
@@ -39375,7 +39377,7 @@
         <x:v>报表—采购汇总报表</x:v>
       </x:c>
       <x:c r="AH313" s="21" t="str">
-        <x:v>采购汇总支持采购单时间、货品、供应商、采购单状态筛选。</x:v>
+        <x:v>采购汇总可按供应商加货品查看月度到货。</x:v>
       </x:c>
       <x:c r="AI313" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -39427,7 +39429,7 @@
     </x:row>
     <x:row r="314" ht="46" customHeight="1">
       <x:c r="A314" s="21" t="str">
-        <x:v>WDT-060-A</x:v>
+        <x:v>WDT-059-B</x:v>
       </x:c>
       <x:c r="B314" s="21" t="str">
         <x:v>旺店通-运营</x:v>
@@ -39448,7 +39450,7 @@
         <x:v>场景</x:v>
       </x:c>
       <x:c r="H314" s="21" t="str">
-        <x:v>高</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I314" s="21" t="str">
         <x:v>practice</x:v>
@@ -39457,76 +39459,74 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K314" s="21" t="str">
-        <x:v>WDT-K060</x:v>
+        <x:v>WDT-K059</x:v>
       </x:c>
       <x:c r="L314" s="21" t="str">
-        <x:v>报表更新时间与订单范围</x:v>
+        <x:v>采购汇总报表</x:v>
       </x:c>
       <x:c r="M314" s="21" t="str">
-        <x:v>利润看前一日，发货明细看实时</x:v>
+        <x:v>按货品或供应商加货品看月度到货</x:v>
       </x:c>
       <x:c r="N314" s="21" t="str">
-        <x:v>上午要核对今天刚发出的订单，同时复盘截至昨天的毛利，正确的报表组合是什么？</x:v>
+        <x:v>准备导出某供应商已完成采购单的到货汇总，哪组筛选最符合资料？</x:v>
       </x:c>
       <x:c r="O314" s="21" t="str">
-        <x:v>今天发货看实时发货明细，毛利复盘看更新至前一日的销售利润</x:v>
+        <x:v>采购单时间、货品、供应商、采购单状态</x:v>
       </x:c>
       <x:c r="P314" s="21" t="str">
-        <x:v>今天发货和毛利都看销售利润，只分别切换付款时间与发货时间</x:v>
+        <x:v>付款时间、平台链接、退款金额、毛利率</x:v>
       </x:c>
       <x:c r="Q314" s="21" t="str">
-        <x:v>今天发货看利润报表的付款时间口径，毛利看实时发货明细</x:v>
+        <x:v>发货时间、店铺、仓库、订单标签</x:v>
       </x:c>
       <x:c r="R314" s="21" t="str">
-        <x:v>今天发货按销售利润当日付款数估算，毛利看前一日发货明细</x:v>
+        <x:v>绑定时间、平台类型、店铺名称、授权状态</x:v>
       </x:c>
       <x:c r="S314" s="21" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="T314" s="21" t="str">
-        <x:v>今天发货看实时发货明细，毛利复盘看更新至前一日的销售利润</x:v>
+        <x:v>采购单时间、货品、供应商、采购单状态</x:v>
       </x:c>
       <x:c r="U314" s="21" t="str">
-        <x:v>两张报表的数据时效不同：发货明细反映实时已发货，销售利润按日更新至前一日。</x:v>
+        <x:v>这四项是采购汇总资料列出的核心筛选字段，可准确锁定目标供应商和采购状态。</x:v>
       </x:c>
       <x:c r="V314" s="21" t="str">
-        <x:v>{"B":"错时效：销售利润更新至前一日，切换时间字段仍不能核对今天刚发货。","C":"口径颠倒：付款时间不能证明今天已发货，发货明细也不是毛利报表。","D":"错时效：付款数不等于实时已发货，前一日发货明细也不能替代利润。"}</x:v>
+        <x:v>{"B":"错报表字段：属于销售利润范围。","C":"错报表字段：属于发货明细范围。","D":"错报表字段：属于店铺绑定范围。"}</x:v>
       </x:c>
       <x:c r="W314" s="21" t="str">
-        <x:v>按决策时效选择正确报表，并避免把付款订单范围误当作 ERP 已发货范围。</x:v>
+        <x:v>以采购单和到货口径汇总供应商履约，为采购复盘与供应商对账提供依据。</x:v>
       </x:c>
       <x:c r="X314" s="21" t="str">
-        <x:v>["报表","销售利润报表或发货明细报表"]</x:v>
+        <x:v>["报表","采购汇总报表"]</x:v>
       </x:c>
       <x:c r="Y314" s="21" t="str">
-        <x:v>["已明确问题是利润复盘还是实时发货跟进","已明确是否只统计本系统发货订单"]</x:v>
+        <x:v>["已确定需要核对的采购时间范围","已明确货品、供应商或采购单状态范围"]</x:v>
       </x:c>
       <x:c r="Z314" s="21" t="str">
-        <x:v>["利润复盘使用销售利润报表并按前一日数据理解","当天已发货跟进使用实时发货明细报表","使用付款时间口径时注意可能包含未在 ERP 发货订单","只看 ERP 发货时在已完结中筛是否本系统发货为是"]</x:v>
+        <x:v>["进入采购汇总报表","按采购单时间设置统计范围","选择货品或供应商加货品的查看维度","按供应商和采购单状态进一步筛选","导出结果完成月度到货对账"]</x:v>
       </x:c>
       <x:c r="AA314" s="21" t="str">
-        <x:v>["报告结论与数据更新时间一致","未把付款订单数量直接当作 ERP 已发货数量"]</x:v>
+        <x:v>["汇总维度与对账对象一致","采购时间、供应商和采购状态筛选准确"]</x:v>
       </x:c>
       <x:c r="AB314" s="21" t="str">
-        <x:v>["销售利润报表按日更新至前一日；发货明细为实时已发货口径"]</x:v>
+        <x:v>["采购汇总用于采购到货与供应商对账，不替代销售发货明细或销售利润分析"]</x:v>
       </x:c>
       <x:c r="AC314" s="21" t="str">
-        <x:v>["用 T+1 利润数据追今天发货","把实时发货明细当完整毛利报表"]</x:v>
+        <x:v>["用发货时间替代采购单时间","漏筛采购单状态"]</x:v>
       </x:c>
       <x:c r="AD314" s="21" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
       </x:c>
       <x:c r="AE314" s="21" t="str">
-        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/orpevw</x:v>
-      </x:c>
-      <x:c r="AF314" s="21" t="str">
-        <x:v>[{"section":"销售利润—更新至前一日","url":"https://zsxj.yuque.com/da3ftb/vgswhb/orpevw"},{"section":"发货明细—实时已发货","url":"https://zsxj.yuque.com/da3ftb/vgswhb/udks3t"}]</x:v>
-      </x:c>
+        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/glfdi78gghft0wfr</x:v>
+      </x:c>
+      <x:c r="AF314" s="21" t="str"/>
       <x:c r="AG314" s="21" t="str">
-        <x:v>发货明细—实时口径；销售利润—更新至前一日</x:v>
+        <x:v>报表—采购汇总报表</x:v>
       </x:c>
       <x:c r="AH314" s="21" t="str">
-        <x:v>发货明细实时；销售利润报表每日更新至前一日。</x:v>
+        <x:v>采购汇总支持采购单时间、货品、供应商、采购单状态筛选。</x:v>
       </x:c>
       <x:c r="AI314" s="21" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
@@ -39570,167 +39570,318 @@
       <x:c r="AV314" s="21" t="str"/>
       <x:c r="AW314" s="21" t="str"/>
       <x:c r="AX314" s="21" t="str">
-        <x:v>区分经营报表的实时与 T+1 口径</x:v>
+        <x:v>用采购汇总报表核对供应商到货</x:v>
       </x:c>
       <x:c r="AY314" s="21" t="str">
         <x:v>2026-08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="315" ht="46" customHeight="1">
-      <x:c r="A315" s="23" t="str">
+      <x:c r="A315" s="21" t="str">
+        <x:v>WDT-060-A</x:v>
+      </x:c>
+      <x:c r="B315" s="21" t="str">
+        <x:v>旺店通-运营</x:v>
+      </x:c>
+      <x:c r="C315" s="21" t="str">
+        <x:v>运营</x:v>
+      </x:c>
+      <x:c r="D315" s="21" t="str">
+        <x:v>经营报表</x:v>
+      </x:c>
+      <x:c r="E315" s="21" t="str">
+        <x:v>通用</x:v>
+      </x:c>
+      <x:c r="F315" s="21" t="str">
+        <x:v>单选题</x:v>
+      </x:c>
+      <x:c r="G315" s="21" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="H315" s="21" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I315" s="21" t="str">
+        <x:v>practice</x:v>
+      </x:c>
+      <x:c r="J315" s="22" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K315" s="21" t="str">
+        <x:v>WDT-K060</x:v>
+      </x:c>
+      <x:c r="L315" s="21" t="str">
+        <x:v>报表更新时间与订单范围</x:v>
+      </x:c>
+      <x:c r="M315" s="21" t="str">
+        <x:v>利润看前一日，发货明细看实时</x:v>
+      </x:c>
+      <x:c r="N315" s="21" t="str">
+        <x:v>上午要核对今天刚发出的订单，同时复盘截至昨天的毛利，正确的报表组合是什么？</x:v>
+      </x:c>
+      <x:c r="O315" s="21" t="str">
+        <x:v>今天发货看实时发货明细，毛利复盘看更新至前一日的销售利润</x:v>
+      </x:c>
+      <x:c r="P315" s="21" t="str">
+        <x:v>今天发货和毛利都看销售利润，只分别切换付款时间与发货时间</x:v>
+      </x:c>
+      <x:c r="Q315" s="21" t="str">
+        <x:v>今天发货看利润报表的付款时间口径，毛利看实时发货明细</x:v>
+      </x:c>
+      <x:c r="R315" s="21" t="str">
+        <x:v>今天发货按销售利润当日付款数估算，毛利看前一日发货明细</x:v>
+      </x:c>
+      <x:c r="S315" s="21" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T315" s="21" t="str">
+        <x:v>今天发货看实时发货明细，毛利复盘看更新至前一日的销售利润</x:v>
+      </x:c>
+      <x:c r="U315" s="21" t="str">
+        <x:v>两张报表的数据时效不同：发货明细反映实时已发货，销售利润按日更新至前一日。</x:v>
+      </x:c>
+      <x:c r="V315" s="21" t="str">
+        <x:v>{"B":"错时效：销售利润更新至前一日，切换时间字段仍不能核对今天刚发货。","C":"口径颠倒：付款时间不能证明今天已发货，发货明细也不是毛利报表。","D":"错时效：付款数不等于实时已发货，前一日发货明细也不能替代利润。"}</x:v>
+      </x:c>
+      <x:c r="W315" s="21" t="str">
+        <x:v>按决策时效选择正确报表，并避免把付款订单范围误当作 ERP 已发货范围。</x:v>
+      </x:c>
+      <x:c r="X315" s="21" t="str">
+        <x:v>["报表","销售利润报表或发货明细报表"]</x:v>
+      </x:c>
+      <x:c r="Y315" s="21" t="str">
+        <x:v>["已明确问题是利润复盘还是实时发货跟进","已明确是否只统计本系统发货订单"]</x:v>
+      </x:c>
+      <x:c r="Z315" s="21" t="str">
+        <x:v>["利润复盘使用销售利润报表并按前一日数据理解","当天已发货跟进使用实时发货明细报表","使用付款时间口径时注意可能包含未在 ERP 发货订单","只看 ERP 发货时在已完结中筛是否本系统发货为是"]</x:v>
+      </x:c>
+      <x:c r="AA315" s="21" t="str">
+        <x:v>["报告结论与数据更新时间一致","未把付款订单数量直接当作 ERP 已发货数量"]</x:v>
+      </x:c>
+      <x:c r="AB315" s="21" t="str">
+        <x:v>["销售利润报表按日更新至前一日；发货明细为实时已发货口径"]</x:v>
+      </x:c>
+      <x:c r="AC315" s="21" t="str">
+        <x:v>["用 T+1 利润数据追今天发货","把实时发货明细当完整毛利报表"]</x:v>
+      </x:c>
+      <x:c r="AD315" s="21" t="str">
+        <x:v>旺店通操作手册与金尊内部操作口径</x:v>
+      </x:c>
+      <x:c r="AE315" s="21" t="str">
+        <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/orpevw</x:v>
+      </x:c>
+      <x:c r="AF315" s="21" t="str">
+        <x:v>[{"section":"销售利润—更新至前一日","url":"https://zsxj.yuque.com/da3ftb/vgswhb/orpevw"},{"section":"发货明细—实时已发货","url":"https://zsxj.yuque.com/da3ftb/vgswhb/udks3t"}]</x:v>
+      </x:c>
+      <x:c r="AG315" s="21" t="str">
+        <x:v>发货明细—实时口径；销售利润—更新至前一日</x:v>
+      </x:c>
+      <x:c r="AH315" s="21" t="str">
+        <x:v>发货明细实时；销售利润报表每日更新至前一日。</x:v>
+      </x:c>
+      <x:c r="AI315" s="21" t="str">
+        <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
+      </x:c>
+      <x:c r="AJ315" s="21" t="str">
+        <x:v>旺店通操作手册与金尊内部操作口径</x:v>
+      </x:c>
+      <x:c r="AK315" s="21" t="str">
+        <x:v>internal_sop</x:v>
+      </x:c>
+      <x:c r="AL315" s="21" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="AM315" s="21" t="str">
+        <x:v>internal_sop</x:v>
+      </x:c>
+      <x:c r="AN315" s="21" t="str">
+        <x:v>verified</x:v>
+      </x:c>
+      <x:c r="AO315" s="22" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP315" s="21" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="AQ315" s="22" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AR315" s="22" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AS315" s="21" t="str">
+        <x:v>2026-08-11</x:v>
+      </x:c>
+      <x:c r="AT315" s="21" t="str">
+        <x:v>已按旺店通语雀操作手册和金尊内部操作口径核对题干、步骤、答案与干扰项。</x:v>
+      </x:c>
+      <x:c r="AU315" s="21" t="str">
+        <x:v>20260811-wangdiantong-quiz1</x:v>
+      </x:c>
+      <x:c r="AV315" s="21" t="str"/>
+      <x:c r="AW315" s="21" t="str"/>
+      <x:c r="AX315" s="21" t="str">
+        <x:v>区分经营报表的实时与 T+1 口径</x:v>
+      </x:c>
+      <x:c r="AY315" s="21" t="str">
+        <x:v>2026-08-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="316" ht="46" customHeight="1">
+      <x:c r="A316" s="23" t="str">
         <x:v>WDT-060-B</x:v>
       </x:c>
-      <x:c r="B315" s="23" t="str">
+      <x:c r="B316" s="23" t="str">
         <x:v>旺店通-运营</x:v>
       </x:c>
-      <x:c r="C315" s="23" t="str">
+      <x:c r="C316" s="23" t="str">
         <x:v>运营</x:v>
       </x:c>
-      <x:c r="D315" s="23" t="str">
+      <x:c r="D316" s="23" t="str">
         <x:v>经营报表</x:v>
       </x:c>
-      <x:c r="E315" s="23" t="str">
+      <x:c r="E316" s="23" t="str">
         <x:v>通用</x:v>
       </x:c>
-      <x:c r="F315" s="23" t="str">
+      <x:c r="F316" s="23" t="str">
         <x:v>单选题</x:v>
       </x:c>
-      <x:c r="G315" s="23" t="str">
+      <x:c r="G316" s="23" t="str">
         <x:v>进阶</x:v>
       </x:c>
-      <x:c r="H315" s="23" t="str">
+      <x:c r="H316" s="23" t="str">
         <x:v>高</x:v>
       </x:c>
-      <x:c r="I315" s="23" t="str">
+      <x:c r="I316" s="23" t="str">
         <x:v>practice</x:v>
       </x:c>
-      <x:c r="J315" s="24" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K315" s="23" t="str">
+      <x:c r="J316" s="24" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K316" s="23" t="str">
         <x:v>WDT-K060</x:v>
       </x:c>
-      <x:c r="L315" s="23" t="str">
+      <x:c r="L316" s="23" t="str">
         <x:v>报表更新时间与订单范围</x:v>
       </x:c>
-      <x:c r="M315" s="23" t="str">
+      <x:c r="M316" s="23" t="str">
         <x:v>利润看前一日，发货明细看实时</x:v>
       </x:c>
-      <x:c r="N315" s="23" t="str">
+      <x:c r="N316" s="23" t="str">
         <x:v>按付款时间查看销售利润时，只想保留由本 ERP 发货的订单，应怎样控制范围？</x:v>
       </x:c>
-      <x:c r="O315" s="23" t="str">
+      <x:c r="O316" s="23" t="str">
         <x:v>在已完结订单只按仓库和发货时间筛选，不使用是否本系统发货条件</x:v>
       </x:c>
-      <x:c r="P315" s="23" t="str">
+      <x:c r="P316" s="23" t="str">
         <x:v>在已完结订单中把是否本系统发货筛选为是</x:v>
       </x:c>
-      <x:c r="Q315" s="23" t="str">
+      <x:c r="Q316" s="23" t="str">
         <x:v>在待发货列表筛是否本系统发货为是，再返回利润报表</x:v>
       </x:c>
-      <x:c r="R315" s="23" t="str">
+      <x:c r="R316" s="23" t="str">
         <x:v>在销售利润报表直接筛是否本系统发货为是，不切到已完结订单</x:v>
       </x:c>
-      <x:c r="S315" s="23" t="str">
+      <x:c r="S316" s="23" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="T315" s="23" t="str">
+      <x:c r="T316" s="23" t="str">
         <x:v>在已完结订单中把是否本系统发货筛选为是</x:v>
       </x:c>
-      <x:c r="U315" s="23" t="str">
+      <x:c r="U316" s="23" t="str">
         <x:v>付款时间口径可能包含未在 ERP 发货的订单，资料给出的限定方式是筛选是否本系统发货为是。</x:v>
       </x:c>
-      <x:c r="V315" s="23" t="str">
+      <x:c r="V316" s="23" t="str">
         <x:v>{"A":"漏条件：仓库和发货时间不能替代是否本系统发货筛选。","C":"错状态：待发货订单不能代表已经由本系统发货。","D":"错入口：资料要求在已完结订单中使用该筛选条件。"}</x:v>
       </x:c>
-      <x:c r="W315" s="23" t="str">
+      <x:c r="W316" s="23" t="str">
         <x:v>按决策时效选择正确报表，并避免把付款订单范围误当作 ERP 已发货范围。</x:v>
       </x:c>
-      <x:c r="X315" s="23" t="str">
+      <x:c r="X316" s="23" t="str">
         <x:v>["报表","销售利润报表或发货明细报表"]</x:v>
       </x:c>
-      <x:c r="Y315" s="23" t="str">
+      <x:c r="Y316" s="23" t="str">
         <x:v>["已明确问题是利润复盘还是实时发货跟进","已明确是否只统计本系统发货订单"]</x:v>
       </x:c>
-      <x:c r="Z315" s="23" t="str">
+      <x:c r="Z316" s="23" t="str">
         <x:v>["利润复盘使用销售利润报表并按前一日数据理解","当天已发货跟进使用实时发货明细报表","使用付款时间口径时注意可能包含未在 ERP 发货订单","只看 ERP 发货时在已完结中筛是否本系统发货为是"]</x:v>
       </x:c>
-      <x:c r="AA315" s="23" t="str">
+      <x:c r="AA316" s="23" t="str">
         <x:v>["报告结论与数据更新时间一致","未把付款订单数量直接当作 ERP 已发货数量"]</x:v>
       </x:c>
-      <x:c r="AB315" s="23" t="str">
+      <x:c r="AB316" s="23" t="str">
         <x:v>["销售利润报表按日更新至前一日；发货明细为实时已发货口径"]</x:v>
       </x:c>
-      <x:c r="AC315" s="23" t="str">
+      <x:c r="AC316" s="23" t="str">
         <x:v>["默认全部付款订单均由本系统发货","改用无关时间字段规避范围问题"]</x:v>
       </x:c>
-      <x:c r="AD315" s="23" t="str">
+      <x:c r="AD316" s="23" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
       </x:c>
-      <x:c r="AE315" s="23" t="str">
+      <x:c r="AE316" s="23" t="str">
         <x:v>https://zsxj.yuque.com/da3ftb/vgswhb/orpevw</x:v>
       </x:c>
-      <x:c r="AF315" s="23" t="str">
+      <x:c r="AF316" s="23" t="str">
         <x:v>[{"section":"销售利润—更新至前一日","url":"https://zsxj.yuque.com/da3ftb/vgswhb/orpevw"},{"section":"发货明细—实时已发货","url":"https://zsxj.yuque.com/da3ftb/vgswhb/udks3t"}]</x:v>
       </x:c>
-      <x:c r="AG315" s="23" t="str">
+      <x:c r="AG316" s="23" t="str">
         <x:v>报表—更新时间与付款、发货口径</x:v>
       </x:c>
-      <x:c r="AH315" s="23" t="str">
+      <x:c r="AH316" s="23" t="str">
         <x:v>付款时间包含未在 ERP 发货订单；只看 ERP 发货时在已完结筛是否本系统发货=是。</x:v>
       </x:c>
-      <x:c r="AI315" s="23" t="str">
+      <x:c r="AI316" s="23" t="str">
         <x:v>INTERNAL-WDT-YUQUE-SOP-2026</x:v>
       </x:c>
-      <x:c r="AJ315" s="23" t="str">
+      <x:c r="AJ316" s="23" t="str">
         <x:v>旺店通操作手册与金尊内部操作口径</x:v>
       </x:c>
-      <x:c r="AK315" s="23" t="str">
-        <x:v>internal_sop</x:v>
-      </x:c>
-      <x:c r="AL315" s="23" t="str">
+      <x:c r="AK316" s="23" t="str">
+        <x:v>internal_sop</x:v>
+      </x:c>
+      <x:c r="AL316" s="23" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="AM315" s="23" t="str">
-        <x:v>internal_sop</x:v>
-      </x:c>
-      <x:c r="AN315" s="23" t="str">
+      <x:c r="AM316" s="23" t="str">
+        <x:v>internal_sop</x:v>
+      </x:c>
+      <x:c r="AN316" s="23" t="str">
         <x:v>verified</x:v>
       </x:c>
-      <x:c r="AO315" s="24" t="b">
+      <x:c r="AO316" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AP315" s="23" t="str">
+      <x:c r="AP316" s="23" t="str">
         <x:v>approved</x:v>
       </x:c>
-      <x:c r="AQ315" s="24" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AR315" s="24" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS315" s="23" t="str">
+      <x:c r="AQ316" s="24" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AR316" s="24" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AS316" s="23" t="str">
         <x:v>2026-08-11</x:v>
       </x:c>
-      <x:c r="AT315" s="23" t="str">
+      <x:c r="AT316" s="23" t="str">
         <x:v>已按旺店通语雀操作手册和金尊内部操作口径核对题干、步骤、答案与干扰项。</x:v>
       </x:c>
-      <x:c r="AU315" s="23" t="str">
+      <x:c r="AU316" s="23" t="str">
         <x:v>20260811-wangdiantong-quiz1</x:v>
       </x:c>
-      <x:c r="AV315" s="23" t="str"/>
-      <x:c r="AW315" s="23" t="str"/>
-      <x:c r="AX315" s="23" t="str">
+      <x:c r="AV316" s="23" t="str"/>
+      <x:c r="AW316" s="23" t="str"/>
+      <x:c r="AX316" s="23" t="str">
         <x:v>区分经营报表的实时与 T+1 口径</x:v>
       </x:c>
-      <x:c r="AY315" s="23" t="str">
+      <x:c r="AY316" s="23" t="str">
         <x:v>2026-08-11</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dfeb9d77d85496e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cf94ec64a8f435c"/>
   </x:tableParts>
 </x:worksheet>
 </file>